--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Control_Plantillas" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Control_Plantillas!$A$3:$AE$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Control_Plantillas!$A$3:$AE$44</definedName>
     <definedName name="Cat_Areas">Catalogos!$H$3:$H$10</definedName>
     <definedName name="Cat_Estatus">Catalogos!$A$3:$A$7</definedName>
     <definedName name="Cat_Etapas">Catalogos!$J$3:$J$8</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="285">
   <si>
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
@@ -812,18 +812,6 @@
   </si>
   <si>
     <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>MFG-02</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>Artículos Otros Cargos para la Compra</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
   </si>
   <si>
     <t>MFG-03</t>
@@ -1270,7 +1258,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -1282,20 +1270,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFE4E7EC"/>
           <bgColor rgb="FFE4E7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1364,226 +1338,6 @@
       </font>
       <fill>
         <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF667085"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E7EC"/>
-          <bgColor rgb="FFE4E7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C6500"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF667085"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E7EC"/>
-          <bgColor rgb="FFE4E7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C6500"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF667085"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E7EC"/>
-          <bgColor rgb="FFE4E7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C6500"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF667085"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E7EC"/>
-          <bgColor rgb="FFE4E7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C6500"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF006100"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -1903,8 +1657,8 @@
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="12">
-        <f>COUNTA(Control_Plantillas!$A$4:$A$60)</f>
-        <v>43</v>
+        <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
+        <v>42</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>56</v>
@@ -1937,18 +1691,18 @@
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="14">
-        <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$60),0)</f>
-        <v>0.27674418604651135</v>
+        <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
+        <v>0.2785714285714283</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="17">
-        <f>COUNTIF(Control_Plantillas!$B$4:$B$60,$E7)</f>
+        <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
       <c r="G7" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E7,Control_Plantillas!$Z$4:$Z$60),0)</f>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.65833333333333333</v>
       </c>
       <c r="H7" s="17">
@@ -1958,15 +1712,15 @@
         <v>6</v>
       </c>
       <c r="J7" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E7,Control_Plantillas!$O$4:$O$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>5</v>
       </c>
       <c r="K7" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E7,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L7" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E7,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -1976,38 +1730,38 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="12">
-        <f>COUNTIF(Control_Plantillas!$I$4:$I$60,"Completado")</f>
+        <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>8</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <f>COUNTIF(Control_Plantillas!$B$4:$B$60,$E8)</f>
+        <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
       <c r="G8" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$Z$4:$Z$60),0)</f>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.625</v>
       </c>
       <c r="H8" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$I$4:$I$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
       <c r="I8" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$L$4:$L$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
       <c r="J8" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$O$4:$O$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
       <c r="K8" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L8" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E8,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2017,38 +1771,38 @@
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="12">
-        <f>COUNTIF(Control_Plantillas!$I$4:$I$60,"En proceso")</f>
-        <v>32</v>
+        <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
+        <v>31</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17">
-        <f>COUNTIF(Control_Plantillas!$B$4:$B$60,$E9)</f>
+        <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
       <c r="G9" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$Z$4:$Z$60),0)</f>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
       <c r="H9" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$I$4:$I$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
       <c r="I9" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$L$4:$L$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="J9" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$O$4:$O$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="K9" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L9" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E9,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2058,38 +1812,38 @@
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="12">
-        <f>COUNTIF(Control_Plantillas!$I$4:$I$60,"No iniciado")</f>
+        <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>3</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F10" s="17">
-        <f>COUNTIF(Control_Plantillas!$B$4:$B$60,$E10)</f>
+        <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
       <c r="G10" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$Z$4:$Z$60),0)</f>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.20000000000000007</v>
       </c>
       <c r="H10" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$I$4:$I$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="I10" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$L$4:$L$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="J10" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$O$4:$O$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="K10" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L10" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E10,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2099,7 +1853,7 @@
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12">
-        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$60,"Bloqueado")</f>
+        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
       <c r="E11" s="15" t="s">
@@ -2109,8 +1863,8 @@
         <v>5</v>
       </c>
       <c r="G11" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E11,Control_Plantillas!$Z$4:$Z$60),0)</f>
-        <v>0.19999999999999998</v>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
+        <v>0.2</v>
       </c>
       <c r="H11" s="17">
         <v>1</v>
@@ -2122,11 +1876,11 @@
         <v>1</v>
       </c>
       <c r="K11" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E11,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L11" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E11,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2136,38 +1890,38 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="12">
-        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$60,"Vencido")</f>
-        <v>33</v>
+        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
+        <v>32</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="17">
-        <f>COUNTIF(Control_Plantillas!$B$4:$B$60,$E12)</f>
+        <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>3</v>
       </c>
       <c r="G12" s="18">
-        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$Z$4:$Z$60),0)</f>
+        <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$I$4:$I$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="I12" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$L$4:$L$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="J12" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$O$4:$O$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="K12" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$R$4:$R$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
       <c r="L12" s="17">
-        <f>COUNTIFS(Control_Plantillas!$B$4:$B$60,$E12,Control_Plantillas!$U$4:$U$60,"Completado")</f>
+        <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2177,7 +1931,7 @@
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="12">
-        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$60,"En riesgo")</f>
+        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
       <c r="E13" s="26" t="s">
@@ -2188,8 +1942,8 @@
         <v>42</v>
       </c>
       <c r="G13" s="28">
-        <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$60),0)</f>
-        <v>0.27674418604651135</v>
+        <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
+        <v>0.2785714285714283</v>
       </c>
       <c r="H13" s="27">
         <f t="shared" ref="H13:L13" si="0">SUM(H7:H12)</f>
@@ -2218,7 +1972,7 @@
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="12">
-        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$60,"Sin fecha")</f>
+        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
         <v>10</v>
       </c>
     </row>
@@ -2228,7 +1982,7 @@
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="12">
-        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$60,"Cerrado")</f>
+        <f ca="1">COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
@@ -2255,12 +2009,12 @@
         <v>15</v>
       </c>
       <c r="F20" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E20)</f>
-        <v>35</v>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
+        <v>34</v>
       </c>
       <c r="G20" s="18">
         <f t="shared" ref="G20:G25" si="1">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.81395348837209303</v>
+        <v>0.80952380952380953</v>
       </c>
     </row>
     <row r="21" spans="5:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2268,12 +2022,12 @@
         <v>20</v>
       </c>
       <c r="F21" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E21)</f>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
         <v>2</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="1"/>
-        <v>4.6511627906976744E-2</v>
+        <v>4.7619047619047616E-2</v>
       </c>
     </row>
     <row r="22" spans="5:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2281,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E22)</f>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
       <c r="G22" s="18">
@@ -2294,12 +2048,12 @@
         <v>33</v>
       </c>
       <c r="F23" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E23)</f>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
         <v>6</v>
       </c>
       <c r="G23" s="18">
         <f t="shared" si="1"/>
-        <v>0.13953488372093023</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="24" spans="5:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2307,7 +2061,7 @@
         <v>37</v>
       </c>
       <c r="F24" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E24)</f>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
       <c r="G24" s="18">
@@ -2320,7 +2074,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="17">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$60,$E25)</f>
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
       <c r="G25" s="18">
@@ -6091,7 +5845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE1000"/>
+  <dimension ref="A1:AE999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6350,7 +6104,7 @@
       <c r="V4" s="24"/>
       <c r="W4" s="24"/>
       <c r="X4" s="19">
-        <f t="shared" ref="X4:X46" si="0">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
+        <f t="shared" ref="X4:X45" si="0">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
       <c r="Y4" s="25" t="str">
@@ -6362,15 +6116,15 @@
         <v>0.75</v>
       </c>
       <c r="AA4" s="31" t="str">
-        <f t="shared" ref="AA4:AA46" si="1">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
+        <f t="shared" ref="AA4:AA45" si="1">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
       <c r="AB4" s="19" t="str">
-        <f t="shared" ref="AB4:AB46" ca="1" si="2">IF($AA4="","",$AA4-TODAY())</f>
+        <f t="shared" ref="AB4:AB45" ca="1" si="2">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
       <c r="AC4" s="19" t="str">
-        <f t="shared" ref="AC4:AC46" si="3">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
+        <f t="shared" ref="AC4:AC45" si="3">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
       <c r="AD4" s="19" t="s">
@@ -9436,22 +9190,22 @@
         <v>Vencido</v>
       </c>
       <c r="AD40" s="19" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AE40" s="21"/>
     </row>
     <row r="41" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C41" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>271</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>272</v>
       </c>
       <c r="E41" s="22" t="s">
         <v>36</v>
@@ -9521,55 +9275,45 @@
         <v>Vencido</v>
       </c>
       <c r="AD41" s="19" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AE41" s="21"/>
     </row>
     <row r="42" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="19" t="s">
+      <c r="D42" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>275</v>
-      </c>
       <c r="E42" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>167</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
       <c r="H42" s="19" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="24">
-        <v>46274</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J42" s="24"/>
       <c r="K42" s="24"/>
       <c r="L42" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M42" s="24">
-        <v>46275</v>
-      </c>
+      <c r="M42" s="24"/>
       <c r="N42" s="24"/>
       <c r="O42" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="24">
-        <v>46276</v>
-      </c>
+      <c r="P42" s="24"/>
       <c r="Q42" s="24"/>
       <c r="R42" s="19" t="s">
         <v>10</v>
@@ -9591,24 +9335,24 @@
       </c>
       <c r="Z42" s="29">
         <f t="array" ref="Z42">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I42,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L42,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O42,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R42,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U42,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA42" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>46274</v>
-      </c>
-      <c r="AB42" s="19">
+        <v/>
+      </c>
+      <c r="AB42" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>-3</v>
+        <v/>
       </c>
       <c r="AC42" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD42" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE42" s="21"/>
+        <f t="shared" si="3"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD42" s="19"/>
+      <c r="AE42" s="21" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="43" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="19" t="s">
@@ -9682,21 +9426,21 @@
       </c>
       <c r="AD43" s="19"/>
       <c r="AE43" s="21" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C44" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>281</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>282</v>
       </c>
       <c r="E44" s="22" t="s">
         <v>39</v>
@@ -9757,32 +9501,36 @@
       </c>
       <c r="AD44" s="19"/>
       <c r="AE44" s="21" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B45" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>285</v>
-      </c>
       <c r="E45" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
+        <v>13</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>143</v>
+      </c>
       <c r="H45" s="19" t="s">
         <v>18</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J45" s="24"/>
       <c r="K45" s="24"/>
@@ -9816,7 +9564,7 @@
       </c>
       <c r="Z45" s="29">
         <f t="array" ref="Z45">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I45,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L45,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O45,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R45,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U45,Cat_Estatus,0)),0),4)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA45" s="31" t="str">
         <f t="shared" si="1"/>
@@ -9830,91 +9578,22 @@
         <f t="shared" si="3"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD45" s="19"/>
+      <c r="AD45" s="34">
+        <v>46270</v>
+      </c>
       <c r="AE45" s="21" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="M46" s="24"/>
-      <c r="N46" s="24"/>
-      <c r="O46" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="24"/>
-      <c r="R46" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S46" s="24"/>
-      <c r="T46" s="24"/>
-      <c r="U46" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="V46" s="24"/>
-      <c r="W46" s="24"/>
-      <c r="X46" s="19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y46" s="25" t="str">
-        <f t="array" ref="Y46">INDEX(Cat_Etapas,$X46)</f>
-        <v>1. Llenado de plantilla</v>
-      </c>
-      <c r="Z46" s="29">
-        <f t="array" ref="Z46">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I46,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L46,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O46,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R46,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U46,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA46" s="31" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB46" s="19" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="AC46" s="19" t="str">
-        <f t="shared" si="3"/>
-        <v>Sin fecha</v>
-      </c>
-      <c r="AD46" s="34">
-        <v>46270</v>
-      </c>
-      <c r="AE46" s="21" t="s">
-        <v>288</v>
-      </c>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="U46" s="35"/>
     </row>
     <row r="47" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="35"/>
@@ -10046,16 +9725,7 @@
       <c r="R59" s="35"/>
       <c r="U59" s="35"/>
     </row>
-    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="U60" s="35"/>
-    </row>
+    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="63" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -10995,9 +10665,8 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A3:AE45"/>
+  <autoFilter ref="A3:AE44"/>
   <mergeCells count="8">
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="A2:H2"/>
@@ -11008,152 +10677,67 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:I1000">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+  <conditionalFormatting sqref="I4:I999 L4:L999 O4:O999 R4:R999 U4:U999">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Completado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I1000">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+  <conditionalFormatting sqref="I4:I999 L4:L999 O4:O999 R4:R999 U4:U999">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"En proceso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I1000">
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+  <conditionalFormatting sqref="I4:I999 L4:L999 O4:O999 R4:R999 U4:U999 AC4:AC999">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I1000">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+  <conditionalFormatting sqref="I4:I999 L4:L999 O4:O999 R4:R999 U4:U999">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"No aplica"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L1000">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
-      <formula>"Completado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L1000">
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
-      <formula>"En proceso"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L1000">
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
-      <formula>"Bloqueado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L1000">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
-      <formula>"No aplica"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O1000">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
-      <formula>"Completado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O1000">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
-      <formula>"En proceso"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O1000">
-    <cfRule type="cellIs" dxfId="16" priority="11" operator="equal">
-      <formula>"Bloqueado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O1000">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
-      <formula>"No aplica"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R1000">
-    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
-      <formula>"Completado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R1000">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>"En proceso"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R1000">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
-      <formula>"Bloqueado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R1000">
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
-      <formula>"No aplica"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U1000">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
-      <formula>"Completado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U1000">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
-      <formula>"En proceso"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U1000">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="equal">
-      <formula>"Bloqueado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U1000">
-    <cfRule type="cellIs" dxfId="7" priority="20" operator="equal">
-      <formula>"No aplica"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB4:AB1000">
-    <cfRule type="cellIs" dxfId="6" priority="21" operator="lessThan">
+  <conditionalFormatting sqref="AB4:AB999">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
-    <cfRule type="cellIs" dxfId="5" priority="22" operator="equal">
+  <conditionalFormatting sqref="AC4:AC999">
+    <cfRule type="cellIs" dxfId="4" priority="22" operator="equal">
       <formula>"Cerrado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
-    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
+  <conditionalFormatting sqref="AC4:AC999">
+    <cfRule type="cellIs" dxfId="3" priority="23" operator="equal">
       <formula>"En tiempo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
+  <conditionalFormatting sqref="AC4:AC999">
+    <cfRule type="cellIs" dxfId="2" priority="24" operator="equal">
       <formula>"En riesgo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
-    <cfRule type="cellIs" dxfId="2" priority="25" operator="equal">
+  <conditionalFormatting sqref="AC4:AC999">
+    <cfRule type="cellIs" dxfId="1" priority="25" operator="equal">
       <formula>"Vencido"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
-    <cfRule type="cellIs" dxfId="1" priority="26" operator="equal">
-      <formula>"Bloqueado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC1000">
+  <conditionalFormatting sqref="AC4:AC999">
     <cfRule type="cellIs" dxfId="0" priority="27" operator="equal">
       <formula>"Sin fecha"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="H4:H60">
+    <dataValidation type="list" allowBlank="1" sqref="H4:H59">
       <formula1>Cat_Prioridad</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I4:I60 L4:L60 O4:O60 R4:R60 U4:U60">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U59 R4:R59 O4:O59 L4:L59 I4:I59">
       <formula1>Cat_Estatus</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E4:E60">
+    <dataValidation type="list" allowBlank="1" sqref="E4:E59">
       <formula1>Cat_Areas</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B60">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B59">
       <formula1>Cat_Modulos</formula1>
     </dataValidation>
   </dataValidations>

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -27,267 +27,384 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="274">
+  <si>
+    <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
+  </si>
+  <si>
+    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
+  </si>
   <si>
     <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
   </si>
   <si>
+    <t>Factor avance</t>
+  </si>
+  <si>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
+  </si>
+  <si>
+    <t>Módulos</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
     <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
   </si>
   <si>
-    <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
-  </si>
-  <si>
-    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
-  </si>
-  <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
+    <t>Áreas / Frentes</t>
+  </si>
+  <si>
+    <t>Etapas</t>
+  </si>
+  <si>
+    <t>Peso etapa</t>
+  </si>
+  <si>
+    <t>No iniciado</t>
+  </si>
+  <si>
+    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
+  </si>
+  <si>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
+    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
   </si>
   <si>
     <t>INDICADORES CLAVE</t>
   </si>
   <si>
-    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
-  </si>
-  <si>
-    <t>Estatus</t>
-  </si>
-  <si>
-    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
-  </si>
-  <si>
-    <t>Factor avance</t>
-  </si>
-  <si>
-    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
-  </si>
-  <si>
-    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
-  </si>
-  <si>
-    <t>Módulos</t>
-  </si>
-  <si>
-    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
-  </si>
-  <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>E1 · LLENADO</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
+    <t>E2 · REVISIÓN</t>
   </si>
   <si>
     <t>AVANCE POR MÓDULO</t>
   </si>
   <si>
-    <t>Áreas / Frentes</t>
-  </si>
-  <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
-  </si>
-  <si>
-    <t>Etapas</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
+  </si>
+  <si>
+    <t>E3 · REPOSITORIO ORACLE</t>
+  </si>
+  <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
+  </si>
+  <si>
+    <t>E4 · SANDBOX</t>
   </si>
   <si>
     <t>Plantillas totales</t>
   </si>
   <si>
-    <t>Peso etapa</t>
-  </si>
-  <si>
-    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
-  </si>
-  <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
-  </si>
-  <si>
-    <t>No iniciado</t>
-  </si>
-  <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
-  </si>
-  <si>
     <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
   </si>
   <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
+  </si>
+  <si>
+    <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
     <t>3. Valores de estatus permitidos</t>
   </si>
   <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
-    <t>1. Llenado de plantilla</t>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>SEGUIMIENTO AUTOMÁTICO</t>
+  </si>
+  <si>
+    <t>Activos Fijos / Patrimonio</t>
+  </si>
+  <si>
+    <t>6. Cerrado</t>
   </si>
   <si>
     <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
     <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
   </si>
   <si>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
     <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
   </si>
   <si>
-    <t>En proceso</t>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Plantilla</t>
+  </si>
+  <si>
+    <t>Área Responsable</t>
   </si>
   <si>
     <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
-    <t>Compras (P2P)</t>
+    <t>Key User</t>
   </si>
   <si>
     <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
   </si>
   <si>
-    <t>Alta</t>
+    <t>Consultor Oracle</t>
   </si>
   <si>
     <t>4. Lectura del semáforo</t>
   </si>
   <si>
-    <t>Compras / Abastecimiento</t>
-  </si>
-  <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>2. Revisión y validación</t>
-  </si>
-  <si>
-    <t>Completado</t>
+    <t>E1 Llenado</t>
+  </si>
+  <si>
+    <t>E1 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E1 F. Real</t>
+  </si>
+  <si>
+    <t>E2 Revisión</t>
   </si>
   <si>
     <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
   </si>
   <si>
+    <t>E2 F. Compromiso</t>
+  </si>
+  <si>
+    <t>PMO / Consultoría</t>
+  </si>
+  <si>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
+  </si>
+  <si>
+    <t>E2 F. Real</t>
+  </si>
+  <si>
+    <t>E3 Repositorio</t>
+  </si>
+  <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+  </si>
+  <si>
+    <t>E3 F. Compromiso</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+  </si>
+  <si>
+    <t>E3 F. Real</t>
+  </si>
+  <si>
+    <t>E4 Sandbox</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
+  </si>
+  <si>
+    <t>E4 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E4 F. Real</t>
+  </si>
+  <si>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
+  </si>
+  <si>
+    <t>E5 Productivo</t>
+  </si>
+  <si>
     <t>Plantillas</t>
   </si>
   <si>
-    <t>Ventas (O2C)</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
+    <t>5. Conexión con el tablero HTML</t>
+  </si>
+  <si>
+    <t>E5 F. Compromiso</t>
   </si>
   <si>
     <t>% Avance</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+    <t>E5 F. Real</t>
+  </si>
+  <si>
+    <t>Etapa #</t>
   </si>
   <si>
     <t>E1 Llenado OK</t>
   </si>
   <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
+    <t>Etapa Actual</t>
   </si>
   <si>
     <t>E2 Revisión OK</t>
   </si>
   <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
-    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
     <t>E3 Repositorio OK</t>
   </si>
   <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
+    <t>Próx. Compromiso</t>
+  </si>
+  <si>
+    <t>Días Restantes</t>
   </si>
   <si>
     <t>E4 Sandbox OK</t>
   </si>
   <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>5. Conexión con el tablero HTML</t>
-  </si>
-  <si>
-    <t>Baja</t>
+    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
+  </si>
+  <si>
+    <t>Semáforo</t>
   </si>
   <si>
     <t>E5 Productivo OK</t>
   </si>
   <si>
-    <t>Almacén / Inventarios</t>
+    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
+  </si>
+  <si>
+    <t>Observaciones / Bloqueos</t>
+  </si>
+  <si>
+    <t>FIN-01</t>
   </si>
   <si>
     <t>Avance global ponderado</t>
   </si>
   <si>
-    <t>4. Ambiente Sandbox</t>
-  </si>
-  <si>
-    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
-  </si>
-  <si>
-    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
-  </si>
-  <si>
     <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
   </si>
   <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
-  </si>
-  <si>
     <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
   </si>
   <si>
-    <t>E1 · LLENADO</t>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Clases</t>
   </si>
   <si>
     <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
-    <t>Activos Fijos (FA)</t>
-  </si>
-  <si>
-    <t>Activos Fijos / Patrimonio</t>
+    <t>Angelica Ramirez</t>
   </si>
   <si>
     <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
   </si>
   <si>
-    <t>6. Cerrado</t>
-  </si>
-  <si>
-    <t>E2 · REVISIÓN</t>
+    <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
     <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
@@ -299,190 +416,91 @@
     <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
   </si>
   <si>
-    <t>E3 · REPOSITORIO ORACLE</t>
-  </si>
-  <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
     <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
-    <t>Suma de pesos (debe ser 100%)</t>
-  </si>
-  <si>
     <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
-    <t>E4 · SANDBOX</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>E5 · PRODUCTIVO</t>
-  </si>
-  <si>
     <t>VTA-01</t>
   </si>
   <si>
-    <t>SEGUIMIENTO AUTOMÁTICO</t>
-  </si>
-  <si>
-    <t>PMO / Consultoría</t>
-  </si>
-  <si>
-    <t>Plantilla</t>
-  </si>
-  <si>
     <t>300 MX Clientes (Final)</t>
   </si>
   <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Key User</t>
-  </si>
-  <si>
     <t>Itzel Bárcena</t>
   </si>
   <si>
-    <t>Área Responsable</t>
-  </si>
-  <si>
     <t>Revisor / Consultor</t>
   </si>
   <si>
     <t>Brandon Hernández</t>
   </si>
   <si>
-    <t>Consultor Oracle</t>
-  </si>
-  <si>
-    <t>E1 Llenado</t>
-  </si>
-  <si>
-    <t>E1 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E1 F. Real</t>
-  </si>
-  <si>
-    <t>E2 Revisión</t>
+    <t>Llenado completado</t>
   </si>
   <si>
     <t>15/05/2026</t>
   </si>
   <si>
-    <t>E2 F. Compromiso</t>
-  </si>
-  <si>
     <t>26/05/2026</t>
   </si>
   <si>
-    <t>E2 F. Real</t>
-  </si>
-  <si>
-    <t>E3 Repositorio</t>
-  </si>
-  <si>
-    <t>E3 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E3 F. Real</t>
-  </si>
-  <si>
-    <t>E4 Sandbox</t>
-  </si>
-  <si>
-    <t>Llenado completado</t>
-  </si>
-  <si>
     <t>28/08/2026</t>
   </si>
   <si>
-    <t>E4 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E4 F. Real</t>
-  </si>
-  <si>
-    <t>E5 Productivo</t>
-  </si>
-  <si>
     <t>Observaciones</t>
   </si>
   <si>
-    <t>E5 F. Compromiso</t>
-  </si>
-  <si>
     <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
   </si>
   <si>
-    <t>E5 F. Real</t>
-  </si>
-  <si>
-    <t>Etapa #</t>
-  </si>
-  <si>
-    <t>Etapa Actual</t>
-  </si>
-  <si>
-    <t>Próx. Compromiso</t>
-  </si>
-  <si>
-    <t>Días Restantes</t>
-  </si>
-  <si>
-    <t>Semáforo</t>
-  </si>
-  <si>
-    <t>Observaciones / Bloqueos</t>
-  </si>
-  <si>
-    <t>FIN-01</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Clases</t>
-  </si>
-  <si>
-    <t>Angelica Ramirez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fredy Sanchez </t>
-  </si>
-  <si>
     <t>Llenado en proceso</t>
   </si>
   <si>
+    <t>FIN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+  </si>
+  <si>
     <t>Sin iniciar</t>
   </si>
   <si>
+    <t>FIN-03</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Departamentos</t>
+  </si>
+  <si>
     <t>Bloqueadas</t>
   </si>
   <si>
-    <t>FIN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+    <t>FIN-04</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
     <t>Vencidas</t>
   </si>
   <si>
+    <t>FIN-05</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Ubicaciones</t>
+  </si>
+  <si>
     <t>En riesgo (≤7 días)</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>FIN-03</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Departamentos</t>
+    <t>FIN-06</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Impuestos y Retenciones MX</t>
   </si>
   <si>
     <t>Sin fecha compromiso</t>
@@ -498,24 +516,6 @@
   </si>
   <si>
     <t>% del total</t>
-  </si>
-  <si>
-    <t>FIN-04</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Plantilla Subsidiarias</t>
-  </si>
-  <si>
-    <t>FIN-05</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Ubicaciones</t>
-  </si>
-  <si>
-    <t>FIN-06</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Impuestos y Retenciones MX</t>
   </si>
   <si>
     <t>CMP-01</t>
@@ -586,10 +586,10 @@
     <t>MX Unidades de Medida</t>
   </si>
   <si>
-    <t>Manuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mateo </t>
+    <t>Edgar Manuel Avila</t>
+  </si>
+  <si>
+    <t>Mateo Escallón</t>
   </si>
   <si>
     <t>INV-02</t>
@@ -851,9 +851,6 @@
   </si>
   <si>
     <t>Tipos de Activo Fijo</t>
-  </si>
-  <si>
-    <t>Fredy</t>
   </si>
 </sst>
 </file>
@@ -873,23 +870,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
-      <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
@@ -901,8 +881,38 @@
     </font>
     <font>
       <b/>
+      <sz val="14.0"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font/>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -911,16 +921,9 @@
       <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
+      <sz val="9.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
@@ -932,11 +935,10 @@
     <font>
       <b/>
       <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
       <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -950,11 +952,6 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F4E79"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -984,14 +981,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16406B"/>
-        <bgColor rgb="FF16406B"/>
+        <fgColor rgb="FF0B2A4A"/>
+        <bgColor rgb="FF0B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B2A4A"/>
-        <bgColor rgb="FF0B2A4A"/>
+        <fgColor rgb="FF16406B"/>
+        <bgColor rgb="FF16406B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1017,6 +1014,12 @@
     <border/>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <top/>
       <bottom/>
     </border>
@@ -1025,12 +1028,6 @@
       <bottom/>
     </border>
     <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -1079,82 +1076,82 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1166,16 +1163,16 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1516,29 +1513,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
+      <c r="A3" s="13" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
         <v> Actualizado al: 12/09/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="s">
-        <v>5</v>
+      <c r="A5" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="E5" s="12" t="s">
-        <v>16</v>
+      <c r="C5" s="10"/>
+      <c r="E5" s="15" t="s">
+        <v>41</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -1546,299 +1543,299 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="9"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17">
+      <c r="A6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="22">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="18" t="s">
+      <c r="E6" s="23" t="s">
         <v>67</v>
       </c>
+      <c r="F6" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="21">
+      <c r="A7" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="26">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3329268293</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="24">
+      <c r="E7" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.725</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17">
+      <c r="A8" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="22">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>12</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="24">
+      <c r="E8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.625</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17">
+      <c r="B9" s="18"/>
+      <c r="C9" s="22">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
         <v>29</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="24">
+      <c r="E9" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="17">
+      <c r="A10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="22">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="24">
+      <c r="E10" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.2</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17">
+      <c r="A11" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="22">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="24">
+      <c r="E11" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3416666667</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="17">
+      <c r="A12" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="22">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
         <v>1</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="24">
+      <c r="E12" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="32">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="32">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17">
+      <c r="A13" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="22">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>33</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F13" s="41">
         <f>SUM(F7:F12)</f>
@@ -1870,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="17">
+      <c r="A14" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="22">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
         <v>7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17">
+      <c r="A15" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="22">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="12" t="s">
-        <v>154</v>
+      <c r="E18" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19">
-      <c r="E19" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="43" t="s">
-        <v>156</v>
+      <c r="E19" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="24">
+      <c r="E20" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
         <v>29</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="33">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
         <v>0.7073170732</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="24">
+      <c r="E21" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
         <v>4</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="33">
         <f t="shared" si="2"/>
         <v>0.09756097561</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="24">
+      <c r="E22" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="33">
         <f t="shared" si="2"/>
         <v>0.0243902439</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="24">
+      <c r="E23" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
         <v>7</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="33">
         <f t="shared" si="2"/>
         <v>0.1707317073</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="24">
+      <c r="E24" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="24">
+      <c r="E25" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="32">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2987,369 +2984,369 @@
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
+      <c r="A3" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>6</v>
+      <c r="A4" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>8</v>
+      <c r="A5" s="12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>10</v>
+      <c r="A6" s="12" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>11</v>
+      <c r="A7" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
-        <v>14</v>
+      <c r="A9" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>18</v>
+      <c r="A10" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>20</v>
+      <c r="A11" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>23</v>
+      <c r="A12" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>24</v>
+      <c r="A13" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>26</v>
+      <c r="A14" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="s">
-        <v>27</v>
+      <c r="A15" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>30</v>
+      <c r="A17" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>33</v>
+      <c r="A18" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
-        <v>34</v>
+      <c r="A19" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="s">
-        <v>35</v>
+      <c r="A20" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="10" t="s">
-        <v>37</v>
+      <c r="A21" s="12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="10" t="s">
-        <v>39</v>
+      <c r="A22" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>41</v>
+      <c r="A24" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="10" t="s">
-        <v>46</v>
+      <c r="A25" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="s">
-        <v>49</v>
+      <c r="A26" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="s">
-        <v>52</v>
+      <c r="A27" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="s">
-        <v>55</v>
+      <c r="A28" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>58</v>
+      <c r="A29" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="s">
-        <v>62</v>
+      <c r="A30" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>65</v>
+      <c r="A32" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="s">
-        <v>71</v>
+      <c r="A33" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="10" t="s">
-        <v>73</v>
+      <c r="A34" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="10" t="s">
-        <v>75</v>
+      <c r="A35" s="12" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="10" t="s">
-        <v>76</v>
+      <c r="A36" s="12" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="10" t="s">
-        <v>79</v>
+      <c r="A37" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6" t="s">
-        <v>81</v>
+      <c r="A39" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
+      <c r="F39" s="10"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="10" t="s">
-        <v>84</v>
+      <c r="A40" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="10" t="s">
-        <v>87</v>
+      <c r="A41" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="10" t="s">
-        <v>88</v>
+      <c r="A42" s="12" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="10" t="s">
-        <v>89</v>
+      <c r="A43" s="12" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="10" t="s">
-        <v>92</v>
+      <c r="A44" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>94</v>
+      <c r="A46" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="F46" s="10"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="A47" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
+      <c r="A48" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
+      <c r="A49" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
+      <c r="A50" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
+      <c r="A51" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
+      <c r="A52" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
+      <c r="A53" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
+      <c r="A54" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
+      <c r="A55" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
+      <c r="A56" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
+      <c r="A57" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
+      <c r="A58" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4373,245 +4370,245 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="s">
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="11" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="11" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="15">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2">
         <v>0.0</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="15">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="5">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2">
         <v>1.0</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="5">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
         <v>0.0</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="I9" s="2"/>
+      <c r="J9" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="15">
+      <c r="K9" s="2"/>
+      <c r="L9" s="11">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5636,8 +5633,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>13</v>
+      <c r="A1" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5667,11 +5664,11 @@
       <c r="AA1" s="8"/>
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
-      <c r="AD1" s="9"/>
+      <c r="AD1" s="10"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>59</v>
+      <c r="A2" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5679,197 +5676,197 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="20" t="s">
-        <v>80</v>
+      <c r="H2" s="10"/>
+      <c r="I2" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="20" t="s">
-        <v>86</v>
+      <c r="K2" s="10"/>
+      <c r="L2" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="M2" s="8"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="20" t="s">
-        <v>90</v>
+      <c r="N2" s="10"/>
+      <c r="O2" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="20" t="s">
-        <v>95</v>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="S2" s="8"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="20" t="s">
-        <v>97</v>
+      <c r="T2" s="10"/>
+      <c r="U2" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="V2" s="8"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="19" t="s">
-        <v>99</v>
+      <c r="W2" s="10"/>
+      <c r="X2" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
       <c r="AA2" s="8"/>
       <c r="AB2" s="8"/>
       <c r="AC2" s="8"/>
-      <c r="AD2" s="9"/>
+      <c r="AD2" s="10"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="N3" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="U3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="V3" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="W3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="29" t="s">
+      <c r="X3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="Z3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="AC3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD3" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="P3" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="29" t="s">
+      <c r="C4" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="S3" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="T3" s="29" t="s">
+      <c r="E4" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="U3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="W3" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="X3" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA3" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB3" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC3" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="AD3" s="29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="36">
+      <c r="H4" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="36">
+      <c r="L4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="36">
+      <c r="O4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="31">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="31">
+      <c r="R4" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="24">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5885,79 +5882,79 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="31" t="str">
+      <c r="AB4" s="24" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="31" t="str">
+      <c r="AC4" s="24" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="32"/>
+      <c r="AD4" s="25"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="36">
+      <c r="A5" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="31">
         <v>46268.0</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="31">
         <v>46268.0</v>
       </c>
-      <c r="L5" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="36">
+      <c r="L5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="31">
         <v>46269.0</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="31">
         <v>46269.0</v>
       </c>
-      <c r="O5" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="36">
+      <c r="O5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="31">
         <v>46269.0</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="31">
         <v>46269.0</v>
       </c>
-      <c r="R5" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="31">
+      <c r="R5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5973,79 +5970,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="31" t="str">
+      <c r="AB5" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC5" s="31" t="str">
+      <c r="AC5" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD5" s="32"/>
+      <c r="AD5" s="25"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="36">
+      <c r="A6" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="36">
+      <c r="L6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="36">
+      <c r="O6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="31">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="31">
+      <c r="R6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6061,79 +6058,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="31" t="str">
+      <c r="AB6" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="31" t="str">
+      <c r="AC6" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="32"/>
+      <c r="AD6" s="25"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="36">
+      <c r="A7" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7" s="36">
+      <c r="L7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="36">
+      <c r="O7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="Q7" s="36">
+      <c r="Q7" s="31">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="31">
+      <c r="R7" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6149,79 +6146,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="31" t="str">
+      <c r="AB7" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="31" t="str">
+      <c r="AC7" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="32"/>
+      <c r="AD7" s="25"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="36">
+      <c r="A8" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="31">
         <v>46272.0</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="31">
         <v>46272.0</v>
       </c>
-      <c r="L8" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="36">
+      <c r="L8" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="31">
         <v>46273.0</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="31">
         <v>46272.0</v>
       </c>
-      <c r="O8" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="36">
+      <c r="O8" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="31">
         <v>46273.0</v>
       </c>
-      <c r="Q8" s="36">
+      <c r="Q8" s="31">
         <v>46272.0</v>
       </c>
-      <c r="R8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="31">
+      <c r="R8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6237,77 +6234,77 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="31" t="str">
+      <c r="AB8" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="31" t="str">
+      <c r="AC8" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="32"/>
+      <c r="AD8" s="25"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="36">
+      <c r="A9" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="31">
         <v>46274.0</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="31">
         <v>46274.0</v>
       </c>
-      <c r="L9" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="36">
+      <c r="L9" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="31">
         <v>46277.0</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="31">
         <v>46277.0</v>
       </c>
-      <c r="O9" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="36">
+      <c r="O9" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="31">
         <v>46277.0</v>
       </c>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="31">
+      <c r="Q9" s="31"/>
+      <c r="R9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="24">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -6323,52 +6320,52 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB9" s="31">
+      <c r="AB9" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC9" s="31" t="str">
+      <c r="AC9" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD9" s="32"/>
+      <c r="AD9" s="25"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>42</v>
+      <c r="E10" s="27" t="s">
+        <v>26</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="36">
+      <c r="H10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="31">
         <v>46272.0</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="31">
         <v>46272.0</v>
       </c>
-      <c r="L10" s="44" t="s">
-        <v>36</v>
+      <c r="L10" s="43" t="s">
+        <v>21</v>
       </c>
       <c r="M10" s="46">
         <v>46277.0</v>
@@ -6376,24 +6373,24 @@
       <c r="N10" s="46">
         <v>46277.0</v>
       </c>
-      <c r="O10" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10" s="36">
+      <c r="O10" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="31">
         <v>46277.0</v>
       </c>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="31">
+      <c r="Q10" s="31"/>
+      <c r="R10" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="24">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6409,79 +6406,79 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB10" s="31">
+      <c r="AB10" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC10" s="31" t="str">
+      <c r="AC10" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD10" s="32"/>
+      <c r="AD10" s="25"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="34" t="s">
+      <c r="E11" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="36">
+      <c r="H11" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="31">
         <v>46268.0</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="31">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11" s="36">
+      <c r="L11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="31">
         <v>46269.0</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="31">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="36">
+      <c r="O11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="31">
         <v>46269.0</v>
       </c>
-      <c r="Q11" s="36">
+      <c r="Q11" s="31">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="31">
+      <c r="R11" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6497,75 +6494,75 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="31" t="str">
+      <c r="AB11" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="31" t="str">
+      <c r="AC11" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="32"/>
+      <c r="AD11" s="25"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="A12" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="33" t="s">
-        <v>54</v>
+      <c r="E12" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="F12" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="36">
+      <c r="H12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="31">
         <v>46274.0</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="31">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="46">
+      <c r="L12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="31">
         <v>46277.0</v>
       </c>
-      <c r="N12" s="36"/>
-      <c r="O12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12" s="36">
+      <c r="N12" s="31"/>
+      <c r="O12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="31">
+      <c r="Q12" s="31"/>
+      <c r="R12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="24">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6581,73 +6578,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="31">
+      <c r="AB12" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC12" s="31" t="str">
+      <c r="AC12" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD12" s="32"/>
+      <c r="AD12" s="25"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>54</v>
+      <c r="E13" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="F13" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="36">
+      <c r="H13" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="31">
         <v>46277.0</v>
       </c>
-      <c r="K13" s="36"/>
-      <c r="L13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N13" s="36"/>
-      <c r="O13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P13" s="36">
+      <c r="K13" s="31"/>
+      <c r="L13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="31">
+        <v>46277.0</v>
+      </c>
+      <c r="N13" s="31"/>
+      <c r="O13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="31">
+      <c r="Q13" s="31"/>
+      <c r="R13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6663,73 +6660,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="31">
+      <c r="AB13" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC13" s="31" t="str">
+      <c r="AC13" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD13" s="32"/>
+      <c r="AD13" s="25"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="33" t="s">
-        <v>54</v>
+      <c r="E14" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="F14" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="36">
+      <c r="H14" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="31">
         <v>46277.0</v>
       </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N14" s="36"/>
-      <c r="O14" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P14" s="36">
+      <c r="K14" s="31"/>
+      <c r="L14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N14" s="31"/>
+      <c r="O14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="31">
+      <c r="Q14" s="31"/>
+      <c r="R14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6745,73 +6742,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB14" s="31">
+      <c r="AB14" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="31" t="str">
+      <c r="AC14" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD14" s="32"/>
+      <c r="AD14" s="25"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="34" t="s">
+      <c r="E15" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="36">
+      <c r="H15" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K15" s="36"/>
-      <c r="L15" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N15" s="36"/>
-      <c r="O15" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P15" s="36">
+      <c r="K15" s="31"/>
+      <c r="L15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N15" s="31"/>
+      <c r="O15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S15" s="36"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="31">
+      <c r="Q15" s="31"/>
+      <c r="R15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6827,73 +6824,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="31">
+      <c r="AB15" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC15" s="31" t="str">
+      <c r="AC15" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD15" s="32"/>
+      <c r="AD15" s="25"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="34" t="s">
+      <c r="E16" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="36">
+      <c r="H16" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K16" s="36"/>
-      <c r="L16" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N16" s="36"/>
-      <c r="O16" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="36">
+      <c r="K16" s="31"/>
+      <c r="L16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N16" s="31"/>
+      <c r="O16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="31">
+      <c r="Q16" s="31"/>
+      <c r="R16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6909,73 +6906,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="31">
+      <c r="AB16" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC16" s="31" t="str">
+      <c r="AC16" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD16" s="32"/>
+      <c r="AD16" s="25"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="34" t="s">
+      <c r="E17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="36">
+      <c r="H17" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K17" s="36"/>
-      <c r="L17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N17" s="36"/>
-      <c r="O17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="36">
+      <c r="K17" s="31"/>
+      <c r="L17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N17" s="31"/>
+      <c r="O17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="31">
+      <c r="Q17" s="31"/>
+      <c r="R17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6991,73 +6988,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="31">
+      <c r="AB17" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC17" s="31" t="str">
+      <c r="AC17" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD17" s="32"/>
+      <c r="AD17" s="25"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="34" t="s">
+      <c r="E18" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="36">
+      <c r="H18" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K18" s="36"/>
-      <c r="L18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N18" s="36"/>
-      <c r="O18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P18" s="36">
+      <c r="K18" s="31"/>
+      <c r="L18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N18" s="31"/>
+      <c r="O18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="31">
+      <c r="Q18" s="31"/>
+      <c r="R18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7073,73 +7070,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="31">
+      <c r="AB18" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC18" s="31" t="str">
+      <c r="AC18" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD18" s="32"/>
+      <c r="AD18" s="25"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="34" t="s">
+      <c r="E19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="36">
+      <c r="H19" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K19" s="36"/>
-      <c r="L19" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N19" s="36"/>
-      <c r="O19" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="36">
+      <c r="K19" s="31"/>
+      <c r="L19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="31">
+      <c r="Q19" s="31"/>
+      <c r="R19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7155,73 +7152,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="31">
+      <c r="AB19" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC19" s="31" t="str">
+      <c r="AC19" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD19" s="32"/>
+      <c r="AD19" s="25"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="34" t="s">
+      <c r="E20" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="36">
+      <c r="H20" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N20" s="36"/>
-      <c r="O20" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20" s="36">
+      <c r="K20" s="31"/>
+      <c r="L20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="31">
+      <c r="Q20" s="31"/>
+      <c r="R20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7237,73 +7234,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC20" s="31" t="str">
+      <c r="AC20" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD20" s="32"/>
+      <c r="AD20" s="25"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="34" t="s">
+      <c r="E21" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="36">
+      <c r="H21" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K21" s="36"/>
-      <c r="L21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N21" s="36"/>
-      <c r="O21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P21" s="36">
+      <c r="K21" s="31"/>
+      <c r="L21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N21" s="31"/>
+      <c r="O21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="31">
+      <c r="Q21" s="31"/>
+      <c r="R21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7319,73 +7316,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC21" s="31" t="str">
+      <c r="AC21" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD21" s="32"/>
+      <c r="AD21" s="25"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="34" t="s">
+      <c r="E22" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="36">
+      <c r="H22" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N22" s="36"/>
-      <c r="O22" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="36">
+      <c r="K22" s="31"/>
+      <c r="L22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N22" s="31"/>
+      <c r="O22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="31">
+      <c r="Q22" s="31"/>
+      <c r="R22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7401,73 +7398,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="31">
+      <c r="AB22" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC22" s="31" t="str">
+      <c r="AC22" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD22" s="32"/>
+      <c r="AD22" s="25"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="31" t="s">
+      <c r="B23" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="34" t="s">
+      <c r="E23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="36">
+      <c r="H23" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K23" s="36"/>
-      <c r="L23" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N23" s="36"/>
-      <c r="O23" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23" s="36">
+      <c r="K23" s="31"/>
+      <c r="L23" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N23" s="31"/>
+      <c r="O23" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P23" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S23" s="36"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="31">
+      <c r="Q23" s="31"/>
+      <c r="R23" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7483,73 +7480,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="31">
+      <c r="AB23" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC23" s="31" t="str">
+      <c r="AC23" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD23" s="32"/>
+      <c r="AD23" s="25"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="31" t="s">
+      <c r="B24" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="34" t="s">
+      <c r="E24" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="34" t="s">
+      <c r="G24" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="H24" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K24" s="36"/>
-      <c r="L24" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N24" s="36"/>
-      <c r="O24" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24" s="36">
+      <c r="K24" s="31"/>
+      <c r="L24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N24" s="31"/>
+      <c r="O24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S24" s="36"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="31">
+      <c r="Q24" s="31"/>
+      <c r="R24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7565,73 +7562,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC24" s="31" t="str">
+      <c r="AC24" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD24" s="32"/>
+      <c r="AD24" s="25"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="31" t="s">
+      <c r="B25" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="34" t="s">
+      <c r="E25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="36">
+      <c r="H25" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N25" s="36"/>
-      <c r="O25" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P25" s="36">
+      <c r="K25" s="31"/>
+      <c r="L25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N25" s="31"/>
+      <c r="O25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="31">
+      <c r="Q25" s="31"/>
+      <c r="R25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7647,73 +7644,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="31">
+      <c r="AB25" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC25" s="31" t="str">
+      <c r="AC25" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD25" s="32"/>
+      <c r="AD25" s="25"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="31" t="s">
+      <c r="B26" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="34" t="s">
+      <c r="E26" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="34" t="s">
+      <c r="G26" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="36">
+      <c r="H26" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N26" s="36"/>
-      <c r="O26" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="36">
+      <c r="K26" s="31"/>
+      <c r="L26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="31">
+      <c r="Q26" s="31"/>
+      <c r="R26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7729,73 +7726,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="31">
+      <c r="AB26" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC26" s="31" t="str">
+      <c r="AC26" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD26" s="32"/>
+      <c r="AD26" s="25"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="34" t="s">
+      <c r="E27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="34" t="s">
+      <c r="G27" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I27" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="36">
+      <c r="H27" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K27" s="36"/>
-      <c r="L27" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N27" s="36"/>
-      <c r="O27" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P27" s="36">
+      <c r="K27" s="31"/>
+      <c r="L27" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N27" s="31"/>
+      <c r="O27" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P27" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="31">
+      <c r="Q27" s="31"/>
+      <c r="R27" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7811,73 +7808,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC27" s="31" t="str">
+      <c r="AC27" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD27" s="32"/>
+      <c r="AD27" s="25"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="31" t="s">
+      <c r="B28" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="34" t="s">
+      <c r="E28" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G28" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" s="36">
+      <c r="H28" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N28" s="36"/>
-      <c r="O28" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28" s="36">
+      <c r="K28" s="31"/>
+      <c r="L28" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N28" s="31"/>
+      <c r="O28" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S28" s="36"/>
-      <c r="T28" s="36"/>
-      <c r="U28" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="31">
+      <c r="Q28" s="31"/>
+      <c r="R28" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7893,73 +7890,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="31">
+      <c r="AB28" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC28" s="31" t="str">
+      <c r="AC28" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD28" s="32"/>
+      <c r="AD28" s="25"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="B29" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="34" t="s">
+      <c r="E29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="34" t="s">
+      <c r="G29" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J29" s="36">
+      <c r="H29" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K29" s="36"/>
-      <c r="L29" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N29" s="36"/>
-      <c r="O29" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P29" s="36">
+      <c r="K29" s="31"/>
+      <c r="L29" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N29" s="31"/>
+      <c r="O29" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q29" s="36"/>
-      <c r="R29" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S29" s="36"/>
-      <c r="T29" s="36"/>
-      <c r="U29" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
-      <c r="X29" s="31">
+      <c r="Q29" s="31"/>
+      <c r="R29" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7975,73 +7972,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="31">
+      <c r="AB29" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC29" s="31" t="str">
+      <c r="AC29" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD29" s="32"/>
+      <c r="AD29" s="25"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="34" t="s">
+      <c r="E30" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" s="36">
+      <c r="H30" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K30" s="36"/>
-      <c r="L30" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N30" s="36"/>
-      <c r="O30" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P30" s="36">
+      <c r="K30" s="31"/>
+      <c r="L30" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N30" s="31"/>
+      <c r="O30" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="31">
+      <c r="Q30" s="31"/>
+      <c r="R30" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8057,73 +8054,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="31">
+      <c r="AB30" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC30" s="31" t="str">
+      <c r="AC30" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD30" s="32"/>
+      <c r="AD30" s="25"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="31" t="s">
+      <c r="B31" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="34" t="s">
+      <c r="E31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="34" t="s">
+      <c r="G31" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I31" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J31" s="36">
+      <c r="H31" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K31" s="36"/>
-      <c r="L31" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N31" s="36"/>
-      <c r="O31" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P31" s="36">
+      <c r="K31" s="31"/>
+      <c r="L31" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N31" s="31"/>
+      <c r="O31" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P31" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q31" s="36"/>
-      <c r="R31" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S31" s="36"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="31">
+      <c r="Q31" s="31"/>
+      <c r="R31" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8139,73 +8136,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="31">
+      <c r="AB31" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC31" s="31" t="str">
+      <c r="AC31" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD31" s="32"/>
+      <c r="AD31" s="25"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="31" t="s">
+      <c r="B32" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="E32" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="G32" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J32" s="36">
+      <c r="H32" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N32" s="36"/>
-      <c r="O32" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32" s="36">
+      <c r="K32" s="31"/>
+      <c r="L32" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N32" s="31"/>
+      <c r="O32" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P32" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="31">
+      <c r="Q32" s="31"/>
+      <c r="R32" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8221,73 +8218,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="31">
+      <c r="AB32" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC32" s="31" t="str">
+      <c r="AC32" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD32" s="32"/>
+      <c r="AD32" s="25"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="31" t="s">
+      <c r="B33" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="34" t="s">
+      <c r="E33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="34" t="s">
+      <c r="G33" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J33" s="36">
+      <c r="H33" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P33" s="36">
+      <c r="K33" s="31"/>
+      <c r="L33" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N33" s="31"/>
+      <c r="O33" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P33" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="31">
+      <c r="Q33" s="31"/>
+      <c r="R33" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8303,73 +8300,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="31">
+      <c r="AB33" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC33" s="31" t="str">
+      <c r="AC33" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD33" s="32"/>
+      <c r="AD33" s="25"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="31" t="s">
+      <c r="B34" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="34" t="s">
+      <c r="E34" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G34" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J34" s="36">
+      <c r="H34" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N34" s="36"/>
-      <c r="O34" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P34" s="36">
+      <c r="K34" s="31"/>
+      <c r="L34" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N34" s="31"/>
+      <c r="O34" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="31">
+      <c r="Q34" s="31"/>
+      <c r="R34" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8385,73 +8382,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="31">
+      <c r="AB34" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC34" s="31" t="str">
+      <c r="AC34" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD34" s="32"/>
+      <c r="AD34" s="25"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="B35" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="34" t="s">
+      <c r="E35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="34" t="s">
+      <c r="G35" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I35" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="36">
+      <c r="H35" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K35" s="36"/>
-      <c r="L35" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N35" s="36"/>
-      <c r="O35" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P35" s="36">
+      <c r="K35" s="31"/>
+      <c r="L35" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N35" s="31"/>
+      <c r="O35" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="31">
+      <c r="Q35" s="31"/>
+      <c r="R35" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8467,73 +8464,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="31">
+      <c r="AB35" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC35" s="31" t="str">
+      <c r="AC35" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD35" s="32"/>
+      <c r="AD35" s="25"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="B36" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F36" s="34" t="s">
+      <c r="E36" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="34" t="s">
+      <c r="G36" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" s="36">
+      <c r="H36" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K36" s="36"/>
-      <c r="L36" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N36" s="36"/>
-      <c r="O36" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P36" s="36">
+      <c r="K36" s="31"/>
+      <c r="L36" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N36" s="31"/>
+      <c r="O36" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="31">
+      <c r="Q36" s="31"/>
+      <c r="R36" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8549,73 +8546,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="31">
+      <c r="AB36" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC36" s="31" t="str">
+      <c r="AC36" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD36" s="32"/>
+      <c r="AD36" s="25"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="31" t="s">
+      <c r="B37" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="34" t="s">
+      <c r="E37" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="34" t="s">
+      <c r="G37" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I37" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J37" s="36">
+      <c r="H37" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K37" s="36"/>
-      <c r="L37" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N37" s="36"/>
-      <c r="O37" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P37" s="36">
+      <c r="K37" s="31"/>
+      <c r="L37" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N37" s="31"/>
+      <c r="O37" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q37" s="36"/>
-      <c r="R37" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
-      <c r="U37" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="31">
+      <c r="Q37" s="31"/>
+      <c r="R37" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8631,75 +8628,75 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC37" s="31" t="str">
+      <c r="AC37" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD37" s="32"/>
+      <c r="AD37" s="25"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="31" t="s">
+      <c r="B38" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F38" s="34" t="s">
+      <c r="E38" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H38" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J38" s="36">
-        <v>46274.0</v>
-      </c>
-      <c r="K38" s="36">
+      <c r="G38" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="46">
+        <v>46277.0</v>
+      </c>
+      <c r="K38" s="31">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="M38" s="36">
+      <c r="L38" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="31">
+        <v>46283.0</v>
+      </c>
+      <c r="N38" s="31"/>
+      <c r="O38" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P38" s="31">
         <v>46277.0</v>
       </c>
-      <c r="N38" s="36"/>
-      <c r="O38" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P38" s="36">
-        <v>46277.0</v>
-      </c>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S38" s="36"/>
-      <c r="T38" s="36"/>
-      <c r="U38" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="31">
+      <c r="Q38" s="31"/>
+      <c r="R38" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V38" s="31"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="24">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8713,75 +8710,75 @@
       </c>
       <c r="AA38" s="39">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB38" s="31">
+        <v>46283</v>
+      </c>
+      <c r="AB38" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC38" s="31" t="str">
+        <v>6</v>
+      </c>
+      <c r="AC38" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD38" s="32"/>
+      <c r="AD38" s="25"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="31" t="s">
+      <c r="B39" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="34" t="s">
+      <c r="E39" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I39" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J39" s="36">
+      <c r="G39" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K39" s="36"/>
-      <c r="L39" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="36">
+      <c r="K39" s="31"/>
+      <c r="L39" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="31">
         <v>46283.0</v>
       </c>
-      <c r="N39" s="36"/>
-      <c r="O39" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P39" s="36">
+      <c r="N39" s="31"/>
+      <c r="O39" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="31">
         <v>46283.0</v>
       </c>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
-      <c r="U39" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="31">
+      <c r="Q39" s="31"/>
+      <c r="R39" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8797,73 +8794,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB39" s="31">
+      <c r="AB39" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC39" s="31" t="str">
+      <c r="AC39" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD39" s="32"/>
+      <c r="AD39" s="25"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="31" t="s">
+      <c r="B40" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="34" t="s">
+      <c r="E40" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H40" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I40" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J40" s="36">
+      <c r="G40" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K40" s="36"/>
-      <c r="L40" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="36">
+      <c r="K40" s="31"/>
+      <c r="L40" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M40" s="31">
         <v>46283.0</v>
       </c>
-      <c r="N40" s="36"/>
-      <c r="O40" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P40" s="36">
+      <c r="N40" s="31"/>
+      <c r="O40" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P40" s="31">
         <v>46283.0</v>
       </c>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S40" s="36"/>
-      <c r="T40" s="36"/>
-      <c r="U40" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="31">
+      <c r="Q40" s="31"/>
+      <c r="R40" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8879,73 +8876,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB40" s="31">
+      <c r="AB40" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC40" s="31" t="str">
+      <c r="AC40" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD40" s="32"/>
+      <c r="AD40" s="25"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="31" t="s">
+      <c r="B41" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="34" t="s">
+      <c r="E41" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H41" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I41" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J41" s="36">
+      <c r="G41" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K41" s="36"/>
-      <c r="L41" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="36">
+      <c r="K41" s="31"/>
+      <c r="L41" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" s="31">
         <v>46283.0</v>
       </c>
-      <c r="N41" s="36"/>
-      <c r="O41" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P41" s="36">
+      <c r="N41" s="31"/>
+      <c r="O41" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P41" s="31">
         <v>46283.0</v>
       </c>
-      <c r="Q41" s="36"/>
-      <c r="R41" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
-      <c r="U41" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="31">
+      <c r="Q41" s="31"/>
+      <c r="R41" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8961,73 +8958,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC41" s="31" t="str">
+      <c r="AC41" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD41" s="32"/>
+      <c r="AD41" s="25"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="B42" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="34" t="s">
+      <c r="E42" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J42" s="36">
+      <c r="G42" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="31">
         <v>46283.0</v>
       </c>
-      <c r="K42" s="36"/>
-      <c r="L42" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" s="36">
+      <c r="K42" s="31"/>
+      <c r="L42" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" s="31">
         <v>46283.0</v>
       </c>
-      <c r="N42" s="36"/>
-      <c r="O42" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P42" s="36">
+      <c r="N42" s="31"/>
+      <c r="O42" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P42" s="31">
         <v>46283.0</v>
       </c>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S42" s="36"/>
-      <c r="T42" s="36"/>
-      <c r="U42" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
-      <c r="X42" s="31">
+      <c r="Q42" s="31"/>
+      <c r="R42" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -9043,79 +9040,79 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB42" s="31">
+      <c r="AB42" s="24">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AC42" s="31" t="str">
+      <c r="AC42" s="24" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD42" s="32"/>
+      <c r="AD42" s="25"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="24" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="31" t="s">
+      <c r="B43" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="34" t="s">
+      <c r="E43" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H43" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I43" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J43" s="36">
-        <v>46274.0</v>
-      </c>
-      <c r="K43" s="36">
+      <c r="G43" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="46">
+        <v>46277.0</v>
+      </c>
+      <c r="K43" s="31">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M43" s="36">
-        <v>46275.0</v>
-      </c>
-      <c r="N43" s="36">
+      <c r="L43" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43" s="46">
+        <v>46277.0</v>
+      </c>
+      <c r="N43" s="31">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P43" s="36">
+      <c r="O43" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="31">
         <v>46276.0</v>
       </c>
-      <c r="Q43" s="36">
+      <c r="Q43" s="31">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
-      <c r="U43" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="31">
+      <c r="R43" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="24">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9131,73 +9128,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="31" t="str">
+      <c r="AB43" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="31" t="str">
+      <c r="AC43" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="32"/>
+      <c r="AD43" s="25"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="31" t="s">
+      <c r="B44" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F44" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="H44" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I44" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J44" s="36">
-        <v>46274.0</v>
-      </c>
-      <c r="K44" s="36">
+      <c r="E44" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J44" s="46">
+        <v>46277.0</v>
+      </c>
+      <c r="K44" s="31">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="M44" s="36">
+      <c r="L44" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="31">
         <v>46276.0</v>
       </c>
-      <c r="N44" s="36"/>
-      <c r="O44" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-      <c r="U44" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="31">
+      <c r="N44" s="31"/>
+      <c r="O44" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+      <c r="U44" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="24">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9213,15 +9210,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="24">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="AC44" s="31" t="str">
+      <c r="AC44" s="24" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="32"/>
+      <c r="AD44" s="25"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
@@ -10308,13 +10305,13 @@
   </sheetData>
   <autoFilter ref="$A$3:$AD$44"/>
   <mergeCells count="8">
+    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="X2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="I4:I44 I46:I1000 L4:L44 L46:L1000 O4:O44 O46:O1000 R4:R44 R46:R1000 U4:U44 U46:U1000">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -35,30 +35,30 @@
     <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
   </si>
   <si>
+    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
+  </si>
+  <si>
+    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
+  </si>
+  <si>
     <t>Estatus</t>
   </si>
   <si>
-    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
-  </si>
-  <si>
-    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
   </si>
   <si>
     <t>Factor avance</t>
   </si>
   <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
-  </si>
-  <si>
     <t>Módulos</t>
   </si>
   <si>
     <t>Prioridad</t>
   </si>
   <si>
-    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
-  </si>
-  <si>
     <t>Áreas / Frentes</t>
   </si>
   <si>
@@ -71,169 +71,265 @@
     <t>No iniciado</t>
   </si>
   <si>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>INDICADORES CLAVE</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
     <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
   </si>
   <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>AVANCE POR MÓDULO</t>
   </si>
   <si>
     <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
   </si>
   <si>
-    <t>1. Llenado de plantilla</t>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
   </si>
   <si>
     <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
   </si>
   <si>
-    <t>En proceso</t>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
   </si>
   <si>
     <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
   </si>
   <si>
-    <t>Compras (P2P)</t>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
+  </si>
+  <si>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
+  </si>
+  <si>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>Activos Fijos / Patrimonio</t>
+  </si>
+  <si>
+    <t>6. Cerrado</t>
+  </si>
+  <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
+  </si>
+  <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
+    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+  </si>
+  <si>
+    <t>3. Valores de estatus permitidos</t>
+  </si>
+  <si>
+    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+  </si>
+  <si>
+    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
     <t>IDENTIFICACIÓN Y RESPONSABLES</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
-  </si>
-  <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
-  </si>
-  <si>
-    <t>2. Revisión y validación</t>
-  </si>
-  <si>
-    <t>INDICADORES CLAVE</t>
-  </si>
-  <si>
-    <t>Completado</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
+    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
+  </si>
+  <si>
+    <t>4. Lectura del semáforo</t>
+  </si>
+  <si>
+    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
+  </si>
+  <si>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
+  </si>
+  <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+  </si>
+  <si>
+    <t>PMO / Consultoría</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
   </si>
   <si>
     <t>E1 · LLENADO</t>
   </si>
   <si>
-    <t>3. Carga en repositorio Oracle</t>
-  </si>
-  <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
-  </si>
-  <si>
-    <t>Inventarios (D2B)</t>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
+  </si>
+  <si>
+    <t>5. Conexión con el tablero HTML</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
+  </si>
+  <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
+    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
+  </si>
+  <si>
+    <t>E3 Repositorio OK</t>
   </si>
   <si>
     <t>E2 · REVISIÓN</t>
   </si>
   <si>
-    <t>AVANCE POR MÓDULO</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
-  </si>
-  <si>
-    <t>Almacén / Inventarios</t>
-  </si>
-  <si>
-    <t>4. Ambiente Sandbox</t>
+    <t>E4 Sandbox OK</t>
+  </si>
+  <si>
+    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
+  </si>
+  <si>
+    <t>E5 Productivo OK</t>
+  </si>
+  <si>
+    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
+  </si>
+  <si>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
+  </si>
+  <si>
+    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
   </si>
   <si>
     <t>E3 · REPOSITORIO ORACLE</t>
   </si>
   <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
+    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
     <t>E4 · SANDBOX</t>
   </si>
   <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
-    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
-  </si>
-  <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
+    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
+  </si>
+  <si>
+    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
+  </si>
+  <si>
+    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
     <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
-    <t>3. Valores de estatus permitidos</t>
-  </si>
-  <si>
-    <t>Activos Fijos (FA)</t>
+    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
+  </si>
+  <si>
+    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
+  </si>
+  <si>
+    <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
     <t>SEGUIMIENTO AUTOMÁTICO</t>
   </si>
   <si>
-    <t>Activos Fijos / Patrimonio</t>
-  </si>
-  <si>
-    <t>6. Cerrado</t>
-  </si>
-  <si>
-    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
-    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
-  </si>
-  <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+    <t>VTA-01</t>
   </si>
   <si>
     <t>Código</t>
@@ -245,19 +341,13 @@
     <t>Área Responsable</t>
   </si>
   <si>
-    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
-  </si>
-  <si>
     <t>Key User</t>
   </si>
   <si>
-    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
-  </si>
-  <si>
     <t>Consultor Oracle</t>
   </si>
   <si>
-    <t>4. Lectura del semáforo</t>
+    <t>300 MX Clientes (Final)</t>
   </si>
   <si>
     <t>E1 Llenado</t>
@@ -272,31 +362,25 @@
     <t>E2 Revisión</t>
   </si>
   <si>
-    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
+    <t>Itzel Bárcena</t>
   </si>
   <si>
     <t>E2 F. Compromiso</t>
   </si>
   <si>
-    <t>PMO / Consultoría</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
-  </si>
-  <si>
     <t>E2 F. Real</t>
   </si>
   <si>
     <t>E3 Repositorio</t>
   </si>
   <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
-  </si>
-  <si>
     <t>E3 F. Compromiso</t>
   </si>
   <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+    <t>Revisor / Consultor</t>
+  </si>
+  <si>
+    <t>Brandon Hernández</t>
   </si>
   <si>
     <t>E3 F. Real</t>
@@ -305,166 +389,85 @@
     <t>E4 Sandbox</t>
   </si>
   <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
     <t>E4 F. Compromiso</t>
   </si>
   <si>
     <t>E4 F. Real</t>
   </si>
   <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
-  </si>
-  <si>
     <t>E5 Productivo</t>
   </si>
   <si>
-    <t>Plantillas</t>
-  </si>
-  <si>
-    <t>5. Conexión con el tablero HTML</t>
-  </si>
-  <si>
     <t>E5 F. Compromiso</t>
   </si>
   <si>
-    <t>% Avance</t>
-  </si>
-  <si>
     <t>E5 F. Real</t>
   </si>
   <si>
     <t>Etapa #</t>
   </si>
   <si>
-    <t>E1 Llenado OK</t>
-  </si>
-  <si>
     <t>Etapa Actual</t>
   </si>
   <si>
-    <t>E2 Revisión OK</t>
-  </si>
-  <si>
-    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
-  </si>
-  <si>
-    <t>E3 Repositorio OK</t>
-  </si>
-  <si>
     <t>Próx. Compromiso</t>
   </si>
   <si>
     <t>Días Restantes</t>
   </si>
   <si>
-    <t>E4 Sandbox OK</t>
-  </si>
-  <si>
-    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
-  </si>
-  <si>
     <t>Semáforo</t>
   </si>
   <si>
-    <t>E5 Productivo OK</t>
-  </si>
-  <si>
-    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
-  </si>
-  <si>
     <t>Observaciones / Bloqueos</t>
   </si>
   <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
     <t>FIN-01</t>
   </si>
   <si>
-    <t>Avance global ponderado</t>
-  </si>
-  <si>
-    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
-  </si>
-  <si>
-    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
+    <t>26/05/2026</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
     <t>ESTEVEZ - Clases</t>
   </si>
   <si>
-    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
   </si>
   <si>
     <t>Angelica Ramirez</t>
   </si>
   <si>
-    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
-    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
-  </si>
-  <si>
-    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
-  </si>
-  <si>
-    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
-  </si>
-  <si>
-    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
-  </si>
-  <si>
-    <t>7. Ejemplo de captura correcta de una fila</t>
-  </si>
-  <si>
-    <t>VTA-01</t>
-  </si>
-  <si>
-    <t>300 MX Clientes (Final)</t>
-  </si>
-  <si>
-    <t>Itzel Bárcena</t>
-  </si>
-  <si>
-    <t>Revisor / Consultor</t>
-  </si>
-  <si>
-    <t>Brandon Hernández</t>
-  </si>
-  <si>
     <t>Llenado completado</t>
   </si>
   <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
-    <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
-  </si>
-  <si>
     <t>Llenado en proceso</t>
   </si>
   <si>
+    <t>Sin iniciar</t>
+  </si>
+  <si>
     <t>FIN-02</t>
   </si>
   <si>
     <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
   </si>
   <si>
-    <t>Sin iniciar</t>
+    <t>Bloqueadas</t>
   </si>
   <si>
     <t>FIN-03</t>
@@ -473,7 +476,7 @@
     <t>ESTEVEZ - Departamentos</t>
   </si>
   <si>
-    <t>Bloqueadas</t>
+    <t>Vencidas</t>
   </si>
   <si>
     <t>FIN-04</t>
@@ -482,7 +485,7 @@
     <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
-    <t>Vencidas</t>
+    <t>En riesgo (≤7 días)</t>
   </si>
   <si>
     <t>FIN-05</t>
@@ -491,25 +494,22 @@
     <t>ESTEVEZ - Ubicaciones</t>
   </si>
   <si>
-    <t>En riesgo (≤7 días)</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
+    <t>Sin fecha compromiso</t>
+  </si>
+  <si>
+    <t>Cerradas (productivo)</t>
+  </si>
+  <si>
+    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
+  </si>
+  <si>
     <t>FIN-06</t>
   </si>
   <si>
     <t>ESTEVEZ - Impuestos y Retenciones MX</t>
-  </si>
-  <si>
-    <t>Sin fecha compromiso</t>
-  </si>
-  <si>
-    <t>Cerradas (productivo)</t>
-  </si>
-  <si>
-    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
   </si>
   <si>
     <t>Etapa</t>
@@ -875,8 +875,19 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="15.0"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -893,12 +904,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
-      <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -911,11 +916,6 @@
     </font>
     <font/>
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF667085"/>
@@ -924,7 +924,7 @@
     <font>
       <b/>
       <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -935,12 +935,7 @@
     <font>
       <b/>
       <sz val="9.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -952,6 +947,11 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1076,65 +1076,50 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -1142,16 +1127,31 @@
     <xf borderId="5" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1163,16 +1163,16 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1513,326 +1513,326 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="10" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 12/09/2026</v>
+        <v> Actualizado al: 15/09/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="10"/>
-      <c r="E5" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="10"/>
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="12"/>
+      <c r="E5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="22">
+      <c r="A6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="19">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>113</v>
+      <c r="E6" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="26">
+      <c r="A7" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="23">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3329268293</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="32">
+        <v>0.3609756098</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.725</v>
-      </c>
-      <c r="H7" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>5</v>
-      </c>
-      <c r="K7" s="32">
+        <v>6</v>
+      </c>
+      <c r="K7" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="22">
+      <c r="A8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="19">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>12</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="32">
+        <v>15</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.625</v>
-      </c>
-      <c r="H8" s="32">
+        <v>0.525</v>
+      </c>
+      <c r="H8" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>2</v>
-      </c>
-      <c r="I8" s="32">
+        <v>1</v>
+      </c>
+      <c r="I8" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="22">
+      <c r="B9" s="17"/>
+      <c r="C9" s="19">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
-        <v>29</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="32">
+        <v>26</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="22">
+      <c r="A10" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="19">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="E10" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="H10" s="32">
+        <v>0.252173913</v>
+      </c>
+      <c r="H10" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="32">
+        <v>4</v>
+      </c>
+      <c r="I10" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="22">
+      <c r="A11" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="32">
+      <c r="E11" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3416666667</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="22">
+      <c r="A12" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="19">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
-        <v>1</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="32">
+        <v>5</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="29">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="30">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="29">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="22">
+      <c r="A13" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="19">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>155</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="G13" s="42">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3329268293</v>
+        <v>0.3609756098</v>
       </c>
       <c r="H13" s="41">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I13" s="41">
         <f t="shared" si="1"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="J13" s="41">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="41">
         <f t="shared" si="1"/>
@@ -1867,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="22">
+      <c r="A14" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="19">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="22">
+      <c r="A15" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="10"/>
+      <c r="E18" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19">
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="F19" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="44" t="s">
+      <c r="F19" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="43" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="32">
+      <c r="E20" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="29">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
-        <v>29</v>
-      </c>
-      <c r="G20" s="33">
+        <v>26</v>
+      </c>
+      <c r="G20" s="30">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.7073170732</v>
+        <v>0.6341463415</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="32">
+      <c r="E21" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="29">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
-        <v>4</v>
-      </c>
-      <c r="G21" s="33">
-        <f t="shared" si="2"/>
-        <v>0.09756097561</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="32">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
-        <v>1</v>
-      </c>
-      <c r="G22" s="33">
-        <f t="shared" si="2"/>
-        <v>0.0243902439</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="32">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
         <v>7</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G21" s="30">
         <f t="shared" si="2"/>
         <v>0.1707317073</v>
       </c>
     </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="E22" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="29">
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="E23" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="29">
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
+        <v>8</v>
+      </c>
+      <c r="G23" s="30">
+        <f t="shared" si="2"/>
+        <v>0.1951219512</v>
+      </c>
+    </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="32">
+      <c r="E24" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="29">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="32">
+      <c r="E25" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="29">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2983,370 +2983,370 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>14</v>
+      <c r="A4" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="s">
-        <v>18</v>
+      <c r="A5" s="14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
-        <v>20</v>
+      <c r="A6" s="14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="s">
-        <v>22</v>
+      <c r="A7" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="10"/>
+      <c r="A9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="s">
-        <v>36</v>
+      <c r="A10" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="s">
-        <v>38</v>
+      <c r="A11" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="s">
-        <v>43</v>
+      <c r="A12" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="s">
-        <v>47</v>
+      <c r="A13" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="s">
-        <v>49</v>
+      <c r="A14" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="s">
-        <v>53</v>
+      <c r="A15" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="14" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="10"/>
+      <c r="A24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="12"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="12" t="s">
-        <v>81</v>
+      <c r="A25" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>84</v>
+      <c r="A26" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12" t="s">
-        <v>87</v>
+      <c r="A27" s="14" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="12" t="s">
-        <v>89</v>
+      <c r="A28" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="12" t="s">
-        <v>92</v>
+      <c r="A29" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="12" t="s">
-        <v>95</v>
+      <c r="A30" s="14" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="10"/>
+      <c r="A32" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="12" t="s">
-        <v>106</v>
+      <c r="A33" s="14" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12" t="s">
-        <v>111</v>
+      <c r="A34" s="14" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="12" t="s">
-        <v>114</v>
+      <c r="A35" s="14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12" t="s">
-        <v>118</v>
+      <c r="A36" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="12" t="s">
-        <v>119</v>
+      <c r="A37" s="14" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="10"/>
+      <c r="A39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="12" t="s">
-        <v>124</v>
+      <c r="A40" s="14" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="12" t="s">
-        <v>126</v>
+      <c r="A41" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>127</v>
+      <c r="A42" s="14" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="12" t="s">
-        <v>128</v>
+      <c r="A43" s="14" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="12" t="s">
-        <v>129</v>
+      <c r="A44" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="10"/>
+      <c r="A46" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="12"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="35" t="s">
+      <c r="A47" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="35" t="s">
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="35" t="s">
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="35" t="s">
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="35" t="s">
+      <c r="C58" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="C58" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4373,242 +4373,242 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="11">
         <v>0.0</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="2"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="11">
         <v>0.4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="B5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3">
         <v>1.0</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
         <v>0.0</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="3"/>
       <c r="L9" s="11">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5633,240 +5633,240 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="12"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2" s="8"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="10"/>
+      <c r="A2" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="V2" s="9"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="12"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="C3" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="U3" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="V3" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z3" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="V3" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="X3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z3" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA3" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC3" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="AD3" s="19" t="s">
-        <v>115</v>
+      <c r="AA3" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="27" t="s">
+      <c r="A4" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H4" s="24" t="s">
+      <c r="F4" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="J4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="31">
+      <c r="L4" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="31">
+      <c r="O4" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="24">
+      <c r="R4" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="31">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,79 +5882,79 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="24" t="str">
+      <c r="AB4" s="31" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="24" t="str">
+      <c r="AC4" s="31" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="25"/>
+      <c r="AD4" s="32"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="25" t="s">
+      <c r="A5" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="B5" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="24" t="s">
+      <c r="F5" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="31">
+      <c r="J5" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="31">
+      <c r="L5" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="36">
         <v>46269.0</v>
       </c>
-      <c r="N5" s="31">
+      <c r="N5" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" s="31">
+      <c r="O5" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="36">
         <v>46269.0</v>
       </c>
-      <c r="Q5" s="31">
+      <c r="Q5" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R5" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="24">
+      <c r="R5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5970,79 +5970,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="24" t="str">
+      <c r="AB5" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC5" s="24" t="str">
+      <c r="AC5" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD5" s="25"/>
+      <c r="AD5" s="32"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="25" t="s">
+      <c r="A6" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="B6" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="24" t="s">
+      <c r="F6" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="31">
+      <c r="J6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="31">
+      <c r="L6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N6" s="31">
+      <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="31">
+      <c r="O6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q6" s="31">
+      <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="24">
+      <c r="R6" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6058,79 +6058,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="24" t="str">
+      <c r="AB6" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="24" t="str">
+      <c r="AC6" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="25"/>
+      <c r="AD6" s="32"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="B7" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="J7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="31">
+      <c r="L7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="31">
+      <c r="O7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q7" s="31">
+      <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="24">
+      <c r="R7" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6146,79 +6146,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="24" t="str">
+      <c r="AB7" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="24" t="str">
+      <c r="AC7" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="25"/>
+      <c r="AD7" s="32"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="25" t="s">
+      <c r="A8" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="B8" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="24" t="s">
+      <c r="F8" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="31">
+      <c r="J8" s="36">
         <v>46272.0</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="36">
         <v>46272.0</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="31">
+      <c r="L8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="36">
         <v>46273.0</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="36">
         <v>46272.0</v>
       </c>
-      <c r="O8" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="31">
+      <c r="O8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="36">
         <v>46273.0</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="36">
         <v>46272.0</v>
       </c>
-      <c r="R8" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="24">
+      <c r="R8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6234,138 +6234,140 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="24" t="str">
+      <c r="AB8" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="24" t="str">
+      <c r="AC8" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="25"/>
+      <c r="AD8" s="32"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="27" t="s">
+      <c r="A9" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="24" t="s">
+      <c r="F9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="31">
+      <c r="J9" s="36">
         <v>46274.0</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L9" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="31">
+      <c r="L9" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N9" s="31">
+      <c r="N9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="O9" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="P9" s="31">
+      <c r="O9" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="24">
+      <c r="Q9" s="36">
+        <v>46277.0</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="31">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="37" t="str">
         <f t="array" ref="Y9">INDEX(Cat_Etapas,$X9)</f>
-        <v>3. Carga en repositorio Oracle</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z9" s="38">
         <f t="array" ref="Z9">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I9,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L9,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O9,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R9,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U9,Cat_Estatus,0)),0),4)</f>
-        <v>0.6</v>
-      </c>
-      <c r="AA9" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA9" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB9" s="24">
+        <v/>
+      </c>
+      <c r="AB9" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC9" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AC9" s="31" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD9" s="25"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD9" s="32"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>23</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>26</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="31">
+      <c r="H10" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="36">
         <v>46272.0</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="36">
         <v>46272.0</v>
       </c>
-      <c r="L10" s="43" t="s">
-        <v>21</v>
+      <c r="L10" s="44" t="s">
+        <v>20</v>
       </c>
       <c r="M10" s="46">
         <v>46277.0</v>
@@ -6373,112 +6375,112 @@
       <c r="N10" s="46">
         <v>46277.0</v>
       </c>
-      <c r="O10" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="P10" s="31">
+      <c r="O10" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="24">
+      <c r="Q10" s="36"/>
+      <c r="R10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="31">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="37" t="str">
         <f t="array" ref="Y10">INDEX(Cat_Etapas,$X10)</f>
-        <v>2. Revisión y validación</v>
+        <v>1. Llenado de plantilla</v>
       </c>
       <c r="Z10" s="38">
         <f t="array" ref="Z10">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I10,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L10,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O10,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R10,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U10,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AA10" s="39">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB10" s="24">
+        <v>46272</v>
+      </c>
+      <c r="AB10" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="24" t="str">
+        <v>-8</v>
+      </c>
+      <c r="AC10" s="31" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD10" s="25"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD10" s="32"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="29" t="s">
+      <c r="E11" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="31">
+      <c r="J11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="31">
+      <c r="L11" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="N11" s="31">
+      <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="31">
+      <c r="O11" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="24">
+      <c r="R11" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6494,75 +6496,75 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="24" t="str">
+      <c r="AB11" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="24" t="str">
+      <c r="AC11" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="25"/>
+      <c r="AD11" s="32"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="24" t="s">
+      <c r="A12" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="27" t="s">
-        <v>33</v>
+      <c r="E12" s="33" t="s">
+        <v>30</v>
       </c>
       <c r="F12" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="31">
+      <c r="J12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="31">
+      <c r="L12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N12" s="31"/>
-      <c r="O12" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="31">
+      <c r="N12" s="36"/>
+      <c r="O12" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="24">
+      <c r="Q12" s="36"/>
+      <c r="R12" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6578,73 +6580,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="24">
+      <c r="AB12" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC12" s="24" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC12" s="31" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD12" s="25"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD12" s="32"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="27" t="s">
-        <v>33</v>
+      <c r="E13" s="33" t="s">
+        <v>30</v>
       </c>
       <c r="F13" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="31">
+      <c r="H13" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="36">
         <v>46277.0</v>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="31">
+      <c r="K13" s="36"/>
+      <c r="L13" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N13" s="31"/>
-      <c r="O13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="31">
+      <c r="N13" s="36"/>
+      <c r="O13" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="24">
+      <c r="Q13" s="36"/>
+      <c r="R13" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6660,73 +6662,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="24">
+      <c r="AB13" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC13" s="24" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC13" s="31" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD13" s="25"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD13" s="32"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="24" t="s">
+      <c r="B14" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>33</v>
+      <c r="E14" s="33" t="s">
+        <v>30</v>
       </c>
       <c r="F14" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="31">
+      <c r="H14" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="36">
         <v>46277.0</v>
       </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M14" s="31">
+      <c r="K14" s="36"/>
+      <c r="L14" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N14" s="31"/>
-      <c r="O14" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P14" s="31">
+      <c r="N14" s="36"/>
+      <c r="O14" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V14" s="31"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="24">
+      <c r="Q14" s="36"/>
+      <c r="R14" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6742,319 +6744,319 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB14" s="24">
+      <c r="AB14" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="24" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC14" s="31" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD14" s="25"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD14" s="32"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="24" t="s">
+      <c r="B15" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="30" t="s">
+      <c r="E15" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="31">
+      <c r="J15" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M15" s="31">
+      <c r="K15" s="36"/>
+      <c r="L15" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N15" s="31"/>
-      <c r="O15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P15" s="31">
+      <c r="N15" s="36"/>
+      <c r="O15" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="24">
+      <c r="Q15" s="36"/>
+      <c r="R15" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="37" t="str">
         <f t="array" ref="Y15">INDEX(Cat_Etapas,$X15)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z15" s="38">
         <f t="array" ref="Z15">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I15,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L15,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O15,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R15,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U15,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" s="39">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="24">
+      <c r="AB15" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC15" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD15" s="25"/>
+      <c r="AD15" s="32"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="B16" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="30" t="s">
+      <c r="E16" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="31">
+      <c r="J16" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M16" s="31">
+      <c r="K16" s="36"/>
+      <c r="L16" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N16" s="31"/>
-      <c r="O16" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P16" s="31">
+      <c r="N16" s="36"/>
+      <c r="O16" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="24">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" s="37" t="str">
         <f t="array" ref="Y16">INDEX(Cat_Etapas,$X16)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z16" s="38">
         <f t="array" ref="Z16">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I16,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L16,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O16,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R16,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U16,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA16" s="39">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="24">
+      <c r="AB16" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC16" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC16" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD16" s="25"/>
+      <c r="AD16" s="32"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="B17" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="30" t="s">
+      <c r="E17" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="31">
+      <c r="J17" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M17" s="31">
+      <c r="K17" s="36"/>
+      <c r="L17" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P17" s="31">
+      <c r="N17" s="36"/>
+      <c r="O17" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="24">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="36"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="37" t="str">
         <f t="array" ref="Y17">INDEX(Cat_Etapas,$X17)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z17" s="38">
         <f t="array" ref="Z17">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I17,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L17,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O17,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R17,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U17,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA17" s="39">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="24">
+      <c r="AB17" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC17" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD17" s="25"/>
+      <c r="AD17" s="32"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="24" t="s">
+      <c r="B18" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="30" t="s">
+      <c r="E18" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="31">
+      <c r="H18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K18" s="31"/>
-      <c r="L18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="31">
+      <c r="K18" s="36"/>
+      <c r="L18" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N18" s="31"/>
-      <c r="O18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P18" s="31">
+      <c r="N18" s="36"/>
+      <c r="O18" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="24">
+      <c r="Q18" s="36"/>
+      <c r="R18" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7070,155 +7072,155 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="24">
+      <c r="AB18" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC18" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD18" s="25"/>
+      <c r="AD18" s="32"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="24" t="s">
+      <c r="B19" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="30" t="s">
+      <c r="E19" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="31">
+      <c r="J19" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K19" s="31"/>
-      <c r="L19" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M19" s="31">
+      <c r="K19" s="36"/>
+      <c r="L19" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N19" s="31"/>
-      <c r="O19" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P19" s="31">
+      <c r="N19" s="36"/>
+      <c r="O19" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="24">
+      <c r="Q19" s="36"/>
+      <c r="R19" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="37" t="str">
         <f t="array" ref="Y19">INDEX(Cat_Etapas,$X19)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z19" s="38">
         <f t="array" ref="Z19">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I19,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L19,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O19,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R19,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U19,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA19" s="39">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="24">
+      <c r="AB19" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC19" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC19" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD19" s="25"/>
+      <c r="AD19" s="32"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="24" t="s">
+      <c r="B20" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="30" t="s">
+      <c r="E20" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="31">
+      <c r="H20" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M20" s="31">
+      <c r="K20" s="36"/>
+      <c r="L20" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N20" s="31"/>
-      <c r="O20" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P20" s="31">
+      <c r="N20" s="36"/>
+      <c r="O20" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="24">
+      <c r="Q20" s="36"/>
+      <c r="R20" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7234,73 +7236,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="24">
+      <c r="AB20" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC20" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD20" s="25"/>
+      <c r="AD20" s="32"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="24" t="s">
+      <c r="B21" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="30" t="s">
+      <c r="E21" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="31">
+      <c r="H21" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K21" s="31"/>
-      <c r="L21" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M21" s="31">
+      <c r="K21" s="36"/>
+      <c r="L21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N21" s="31"/>
-      <c r="O21" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P21" s="31">
+      <c r="N21" s="36"/>
+      <c r="O21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="24">
+      <c r="Q21" s="36"/>
+      <c r="R21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7316,73 +7318,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="24">
+      <c r="AB21" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC21" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD21" s="25"/>
+      <c r="AD21" s="32"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="24" t="s">
+      <c r="B22" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="30" t="s">
+      <c r="E22" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="31">
+      <c r="H22" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K22" s="31"/>
-      <c r="L22" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M22" s="31">
+      <c r="K22" s="36"/>
+      <c r="L22" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N22" s="31"/>
-      <c r="O22" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P22" s="31">
+      <c r="N22" s="36"/>
+      <c r="O22" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="24">
+      <c r="Q22" s="36"/>
+      <c r="R22" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7398,73 +7400,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="24">
+      <c r="AB22" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC22" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD22" s="25"/>
+      <c r="AD22" s="32"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="30" t="s">
+      <c r="E23" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="31">
+      <c r="H23" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M23" s="31">
+      <c r="K23" s="36"/>
+      <c r="L23" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N23" s="31"/>
-      <c r="O23" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P23" s="31">
+      <c r="N23" s="36"/>
+      <c r="O23" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P23" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="24">
+      <c r="Q23" s="36"/>
+      <c r="R23" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7480,73 +7482,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="24">
+      <c r="AB23" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC23" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD23" s="25"/>
+      <c r="AD23" s="32"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="30" t="s">
+      <c r="E24" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="31">
+      <c r="H24" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M24" s="31">
+      <c r="K24" s="36"/>
+      <c r="L24" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N24" s="31"/>
-      <c r="O24" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P24" s="31">
+      <c r="N24" s="36"/>
+      <c r="O24" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="24">
+      <c r="Q24" s="36"/>
+      <c r="R24" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7562,73 +7564,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="24">
+      <c r="AB24" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC24" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD24" s="25"/>
+      <c r="AD24" s="32"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="24" t="s">
+      <c r="B25" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="30" t="s">
+      <c r="E25" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="G25" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="31">
+      <c r="H25" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M25" s="31">
+      <c r="K25" s="36"/>
+      <c r="L25" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N25" s="31"/>
-      <c r="O25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P25" s="31">
+      <c r="N25" s="36"/>
+      <c r="O25" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="24">
+      <c r="Q25" s="36"/>
+      <c r="R25" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7644,73 +7646,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="24">
+      <c r="AB25" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC25" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC25" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD25" s="25"/>
+      <c r="AD25" s="32"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="30" t="s">
+      <c r="E26" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="30" t="s">
+      <c r="G26" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="31">
+      <c r="H26" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K26" s="31"/>
-      <c r="L26" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M26" s="31">
+      <c r="K26" s="36"/>
+      <c r="L26" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N26" s="31"/>
-      <c r="O26" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P26" s="31">
+      <c r="N26" s="36"/>
+      <c r="O26" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="24">
+      <c r="Q26" s="36"/>
+      <c r="R26" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7726,73 +7728,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="24">
+      <c r="AB26" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC26" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD26" s="25"/>
+      <c r="AD26" s="32"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="30" t="s">
+      <c r="E27" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="31">
+      <c r="H27" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K27" s="31"/>
-      <c r="L27" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M27" s="31">
+      <c r="K27" s="36"/>
+      <c r="L27" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N27" s="31"/>
-      <c r="O27" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P27" s="31">
+      <c r="N27" s="36"/>
+      <c r="O27" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P27" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="24">
+      <c r="Q27" s="36"/>
+      <c r="R27" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7808,73 +7810,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="24">
+      <c r="AB27" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC27" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD27" s="25"/>
+      <c r="AD27" s="32"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="24" t="s">
+      <c r="B28" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="30" t="s">
+      <c r="E28" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="31">
+      <c r="H28" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M28" s="31">
+      <c r="K28" s="36"/>
+      <c r="L28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N28" s="31"/>
-      <c r="O28" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P28" s="31">
+      <c r="N28" s="36"/>
+      <c r="O28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="24">
+      <c r="Q28" s="36"/>
+      <c r="R28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7890,73 +7892,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="24">
+      <c r="AB28" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC28" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC28" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD28" s="25"/>
+      <c r="AD28" s="32"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="30" t="s">
+      <c r="E29" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="30" t="s">
+      <c r="G29" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="31">
+      <c r="H29" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M29" s="31">
+      <c r="K29" s="36"/>
+      <c r="L29" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N29" s="31"/>
-      <c r="O29" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" s="31">
+      <c r="N29" s="36"/>
+      <c r="O29" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="24">
+      <c r="Q29" s="36"/>
+      <c r="R29" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="36"/>
+      <c r="W29" s="36"/>
+      <c r="X29" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7972,73 +7974,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="24">
+      <c r="AB29" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC29" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD29" s="25"/>
+      <c r="AD29" s="32"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="24" t="s">
+      <c r="B30" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="30" t="s">
+      <c r="E30" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="30" t="s">
+      <c r="G30" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="31">
+      <c r="H30" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K30" s="31"/>
-      <c r="L30" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M30" s="31">
+      <c r="K30" s="36"/>
+      <c r="L30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N30" s="31"/>
-      <c r="O30" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P30" s="31">
+      <c r="N30" s="36"/>
+      <c r="O30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="24">
+      <c r="Q30" s="36"/>
+      <c r="R30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8054,73 +8056,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="24">
+      <c r="AB30" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC30" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC30" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD30" s="25"/>
+      <c r="AD30" s="32"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="B31" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="30" t="s">
+      <c r="E31" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="30" t="s">
+      <c r="G31" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="31">
+      <c r="H31" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K31" s="31"/>
-      <c r="L31" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M31" s="31">
+      <c r="K31" s="36"/>
+      <c r="L31" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N31" s="31"/>
-      <c r="O31" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P31" s="31">
+      <c r="N31" s="36"/>
+      <c r="O31" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P31" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="24">
+      <c r="Q31" s="36"/>
+      <c r="R31" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8136,73 +8138,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="24">
+      <c r="AB31" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC31" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC31" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD31" s="25"/>
+      <c r="AD31" s="32"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="24" t="s">
+      <c r="B32" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="30" t="s">
+      <c r="E32" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="31">
+      <c r="H32" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M32" s="31">
+      <c r="K32" s="36"/>
+      <c r="L32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P32" s="31">
+      <c r="N32" s="36"/>
+      <c r="O32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P32" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="24">
+      <c r="Q32" s="36"/>
+      <c r="R32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V32" s="36"/>
+      <c r="W32" s="36"/>
+      <c r="X32" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8218,73 +8220,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="24">
+      <c r="AB32" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC32" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD32" s="25"/>
+      <c r="AD32" s="32"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="24" t="s">
+      <c r="B33" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="30" t="s">
+      <c r="E33" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" s="31">
+      <c r="H33" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K33" s="31"/>
-      <c r="L33" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M33" s="31">
+      <c r="K33" s="36"/>
+      <c r="L33" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N33" s="31"/>
-      <c r="O33" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P33" s="31">
+      <c r="N33" s="36"/>
+      <c r="O33" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P33" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="24">
+      <c r="Q33" s="36"/>
+      <c r="R33" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8300,73 +8302,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="24">
+      <c r="AB33" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC33" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD33" s="25"/>
+      <c r="AD33" s="32"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="24" t="s">
+      <c r="B34" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="30" t="s">
+      <c r="E34" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G34" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="31">
+      <c r="H34" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K34" s="31"/>
-      <c r="L34" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M34" s="31">
+      <c r="K34" s="36"/>
+      <c r="L34" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N34" s="31"/>
-      <c r="O34" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" s="31">
+      <c r="N34" s="36"/>
+      <c r="O34" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="24">
+      <c r="Q34" s="36"/>
+      <c r="R34" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8382,73 +8384,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="24">
+      <c r="AB34" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC34" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC34" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD34" s="25"/>
+      <c r="AD34" s="32"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="24" t="s">
+      <c r="B35" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="30" t="s">
+      <c r="E35" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="30" t="s">
+      <c r="G35" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J35" s="31">
+      <c r="H35" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M35" s="31">
+      <c r="K35" s="36"/>
+      <c r="L35" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N35" s="31"/>
-      <c r="O35" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P35" s="31">
+      <c r="N35" s="36"/>
+      <c r="O35" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="24">
+      <c r="Q35" s="36"/>
+      <c r="R35" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V35" s="36"/>
+      <c r="W35" s="36"/>
+      <c r="X35" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8464,73 +8466,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="24">
+      <c r="AB35" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC35" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD35" s="25"/>
+      <c r="AD35" s="32"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="24" t="s">
+      <c r="B36" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="30" t="s">
+      <c r="E36" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="30" t="s">
+      <c r="G36" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="31">
+      <c r="H36" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K36" s="31"/>
-      <c r="L36" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M36" s="31">
+      <c r="K36" s="36"/>
+      <c r="L36" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N36" s="31"/>
-      <c r="O36" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P36" s="31">
+      <c r="N36" s="36"/>
+      <c r="O36" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="24">
+      <c r="Q36" s="36"/>
+      <c r="R36" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8546,73 +8548,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="24">
+      <c r="AB36" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC36" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC36" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD36" s="25"/>
+      <c r="AD36" s="32"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="B37" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="30" t="s">
+      <c r="E37" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="30" t="s">
+      <c r="G37" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" s="31">
+      <c r="H37" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K37" s="31"/>
-      <c r="L37" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M37" s="31">
+      <c r="K37" s="36"/>
+      <c r="L37" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N37" s="31"/>
-      <c r="O37" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P37" s="31">
+      <c r="N37" s="36"/>
+      <c r="O37" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="24">
+      <c r="Q37" s="36"/>
+      <c r="R37" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8628,75 +8630,75 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="24">
+      <c r="AB37" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC37" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC37" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD37" s="25"/>
+      <c r="AD37" s="32"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="24" t="s">
+      <c r="B38" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" s="29" t="s">
+      <c r="E38" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G38" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H38" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="31" t="s">
         <v>25</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="J38" s="46">
         <v>46277.0</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="31">
+      <c r="L38" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N38" s="31"/>
-      <c r="O38" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P38" s="31">
+      <c r="N38" s="36"/>
+      <c r="O38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P38" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S38" s="31"/>
-      <c r="T38" s="31"/>
-      <c r="U38" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V38" s="31"/>
-      <c r="W38" s="31"/>
-      <c r="X38" s="24">
+      <c r="Q38" s="36"/>
+      <c r="R38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8712,73 +8714,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB38" s="24">
+      <c r="AB38" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC38" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD38" s="25"/>
+      <c r="AD38" s="32"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="24" t="s">
+      <c r="B39" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="30" t="s">
+      <c r="G39" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" s="31">
+      <c r="H39" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M39" s="31">
+      <c r="K39" s="36"/>
+      <c r="L39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N39" s="31"/>
-      <c r="O39" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P39" s="31">
+      <c r="N39" s="36"/>
+      <c r="O39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="24">
+      <c r="Q39" s="36"/>
+      <c r="R39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8794,73 +8796,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB39" s="24">
+      <c r="AB39" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC39" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC39" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD39" s="25"/>
+      <c r="AD39" s="32"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="24" t="s">
+      <c r="B40" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="29" t="s">
+      <c r="E40" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="30" t="s">
+      <c r="G40" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" s="31">
+      <c r="H40" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K40" s="31"/>
-      <c r="L40" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M40" s="31">
+      <c r="K40" s="36"/>
+      <c r="L40" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N40" s="31"/>
-      <c r="O40" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P40" s="31">
+      <c r="N40" s="36"/>
+      <c r="O40" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V40" s="31"/>
-      <c r="W40" s="31"/>
-      <c r="X40" s="24">
+      <c r="Q40" s="36"/>
+      <c r="R40" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
+      <c r="X40" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8876,73 +8878,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB40" s="24">
+      <c r="AB40" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC40" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC40" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD40" s="25"/>
+      <c r="AD40" s="32"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="24" t="s">
+      <c r="B41" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F41" s="29" t="s">
+      <c r="E41" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="30" t="s">
+      <c r="G41" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="31">
+      <c r="H41" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K41" s="31"/>
-      <c r="L41" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M41" s="31">
+      <c r="K41" s="36"/>
+      <c r="L41" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N41" s="31"/>
-      <c r="O41" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P41" s="31">
+      <c r="N41" s="36"/>
+      <c r="O41" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S41" s="31"/>
-      <c r="T41" s="31"/>
-      <c r="U41" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V41" s="31"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="24">
+      <c r="Q41" s="36"/>
+      <c r="R41" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" s="36"/>
+      <c r="W41" s="36"/>
+      <c r="X41" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8958,73 +8960,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB41" s="24">
+      <c r="AB41" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC41" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD41" s="25"/>
+      <c r="AD41" s="32"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="24" t="s">
+      <c r="B42" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F42" s="29" t="s">
+      <c r="E42" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="G42" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" s="31">
+      <c r="H42" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M42" s="31">
+      <c r="K42" s="36"/>
+      <c r="L42" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N42" s="31"/>
-      <c r="O42" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P42" s="31">
+      <c r="N42" s="36"/>
+      <c r="O42" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="24">
+      <c r="Q42" s="36"/>
+      <c r="R42" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="36"/>
+      <c r="W42" s="36"/>
+      <c r="X42" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -9040,79 +9042,79 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB42" s="24">
+      <c r="AB42" s="31">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AC42" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC42" s="31" t="str">
         <f t="shared" si="4"/>
         <v>En riesgo</v>
       </c>
-      <c r="AD42" s="25"/>
+      <c r="AD42" s="32"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="24" t="s">
+      <c r="B43" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="29" t="s">
+      <c r="E43" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="30" t="s">
+      <c r="G43" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="24" t="s">
+      <c r="H43" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="31" t="s">
         <v>25</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="J43" s="46">
         <v>46277.0</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="24" t="s">
-        <v>30</v>
+      <c r="L43" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="M43" s="46">
         <v>46277.0</v>
       </c>
-      <c r="N43" s="31">
+      <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P43" s="31">
+      <c r="O43" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V43" s="31"/>
-      <c r="W43" s="31"/>
-      <c r="X43" s="24">
+      <c r="R43" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+      <c r="U43" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" s="36"/>
+      <c r="W43" s="36"/>
+      <c r="X43" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9128,73 +9130,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="24" t="str">
+      <c r="AB43" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="24" t="str">
+      <c r="AC43" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="25"/>
+      <c r="AD43" s="32"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="24" t="s">
+      <c r="A44" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="24" t="s">
+      <c r="B44" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="25" t="s">
+      <c r="D44" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G44" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H44" s="24" t="s">
+      <c r="E44" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="31" t="s">
         <v>25</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="J44" s="46">
         <v>46277.0</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="31">
+      <c r="L44" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="36">
         <v>46276.0</v>
       </c>
-      <c r="N44" s="31"/>
-      <c r="O44" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="S44" s="31"/>
-      <c r="T44" s="31"/>
-      <c r="U44" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="V44" s="31"/>
-      <c r="W44" s="31"/>
-      <c r="X44" s="24">
+      <c r="N44" s="36"/>
+      <c r="O44" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9210,15 +9212,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="24">
+      <c r="AB44" s="31">
         <f t="shared" si="3"/>
-        <v>-1</v>
-      </c>
-      <c r="AC44" s="24" t="str">
+        <v>-4</v>
+      </c>
+      <c r="AC44" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="25"/>
+      <c r="AD44" s="32"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -32,39 +32,39 @@
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
   <si>
+    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
+  </si>
+  <si>
     <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
   </si>
   <si>
-    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
+  </si>
+  <si>
+    <t>Factor avance</t>
+  </si>
+  <si>
+    <t>Módulos</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Áreas / Frentes</t>
+  </si>
+  <si>
+    <t>Etapas</t>
   </si>
   <si>
     <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
   </si>
   <si>
-    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
-  </si>
-  <si>
-    <t>Estatus</t>
-  </si>
-  <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
-  </si>
-  <si>
-    <t>Factor avance</t>
-  </si>
-  <si>
-    <t>Módulos</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
-    <t>Áreas / Frentes</t>
-  </si>
-  <si>
-    <t>Etapas</t>
-  </si>
-  <si>
     <t>Peso etapa</t>
   </si>
   <si>
@@ -74,66 +74,72 @@
     <t>Finanzas (R2R)</t>
   </si>
   <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
+  </si>
+  <si>
     <t>INDICADORES CLAVE</t>
   </si>
   <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
-    <t>1. Llenado de plantilla</t>
-  </si>
-  <si>
-    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>Compras (P2P)</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
-  </si>
-  <si>
-    <t>2. Revisión y validación</t>
+    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
   </si>
   <si>
     <t>Completado</t>
   </si>
   <si>
+    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
     <t>AVANCE POR MÓDULO</t>
   </si>
   <si>
-    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
-  </si>
-  <si>
     <t>Baja</t>
   </si>
   <si>
@@ -143,24 +149,24 @@
     <t>4. Ambiente Sandbox</t>
   </si>
   <si>
-    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
-  </si>
-  <si>
     <t>No aplica</t>
   </si>
   <si>
     <t>Manufactura (MFG)</t>
   </si>
   <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
-  </si>
-  <si>
     <t>Manufactura / Producción</t>
   </si>
   <si>
     <t>5. Ambiente Productivo</t>
   </si>
   <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+  </si>
+  <si>
     <t>Activos Fijos (FA)</t>
   </si>
   <si>
@@ -170,39 +176,51 @@
     <t>6. Cerrado</t>
   </si>
   <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>Suma de pesos (debe ser 100%)</t>
   </si>
   <si>
     <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
   </si>
   <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
-  </si>
-  <si>
     <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
   </si>
   <si>
+    <t>E1 · LLENADO</t>
+  </si>
+  <si>
     <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
   </si>
   <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
     <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
   </si>
   <si>
     <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
   </si>
   <si>
+    <t>E2 · REVISIÓN</t>
+  </si>
+  <si>
     <t>3. Valores de estatus permitidos</t>
   </si>
   <si>
+    <t>E3 · REPOSITORIO ORACLE</t>
+  </si>
+  <si>
+    <t>PMO / Consultoría</t>
+  </si>
+  <si>
     <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
   </si>
   <si>
+    <t>E4 · SANDBOX</t>
+  </si>
+  <si>
     <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
   </si>
   <si>
@@ -212,37 +230,76 @@
     <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
-    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+    <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
     <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
   </si>
   <si>
+    <t>Módulo</t>
+  </si>
+  <si>
     <t>4. Lectura del semáforo</t>
   </si>
   <si>
+    <t>SEGUIMIENTO AUTOMÁTICO</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
+  </si>
+  <si>
     <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
   </si>
   <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
     <t>•  En riesgo — faltan 7 días o menos.</t>
   </si>
   <si>
+    <t>E3 Repositorio OK</t>
+  </si>
+  <si>
+    <t>E4 Sandbox OK</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>E5 Productivo OK</t>
+  </si>
+  <si>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
     <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
   </si>
   <si>
+    <t>Plantilla</t>
+  </si>
+  <si>
+    <t>Área Responsable</t>
+  </si>
+  <si>
     <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
   </si>
   <si>
-    <t>PMO / Consultoría</t>
-  </si>
-  <si>
-    <t>Módulo</t>
+    <t>Key User</t>
   </si>
   <si>
     <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
   </si>
   <si>
-    <t>E1 · LLENADO</t>
+    <t>Consultor Oracle</t>
   </si>
   <si>
     <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
@@ -251,55 +308,88 @@
     <t>5. Conexión con el tablero HTML</t>
   </si>
   <si>
-    <t>Plantillas</t>
-  </si>
-  <si>
-    <t>% Avance</t>
-  </si>
-  <si>
-    <t>E1 Llenado OK</t>
-  </si>
-  <si>
-    <t>E2 Revisión OK</t>
+    <t>E1 Llenado</t>
+  </si>
+  <si>
+    <t>E1 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E1 F. Real</t>
+  </si>
+  <si>
+    <t>E2 Revisión</t>
+  </si>
+  <si>
+    <t>E2 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E2 F. Real</t>
+  </si>
+  <si>
+    <t>E3 Repositorio</t>
   </si>
   <si>
     <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
-    <t>E3 Repositorio OK</t>
-  </si>
-  <si>
-    <t>E2 · REVISIÓN</t>
-  </si>
-  <si>
-    <t>E4 Sandbox OK</t>
+    <t>E3 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E3 F. Real</t>
+  </si>
+  <si>
+    <t>E4 Sandbox</t>
   </si>
   <si>
     <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
   </si>
   <si>
-    <t>E5 Productivo OK</t>
+    <t>E4 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E4 F. Real</t>
+  </si>
+  <si>
+    <t>E5 Productivo</t>
   </si>
   <si>
     <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
   </si>
   <si>
-    <t>Avance global ponderado</t>
+    <t>E5 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E5 F. Real</t>
+  </si>
+  <si>
+    <t>Etapa #</t>
   </si>
   <si>
     <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
   </si>
   <si>
+    <t>Etapa Actual</t>
+  </si>
+  <si>
     <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
   </si>
   <si>
-    <t>E3 · REPOSITORIO ORACLE</t>
+    <t>Próx. Compromiso</t>
+  </si>
+  <si>
+    <t>Días Restantes</t>
   </si>
   <si>
     <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
-    <t>E4 · SANDBOX</t>
+    <t>Semáforo</t>
+  </si>
+  <si>
+    <t>Observaciones / Bloqueos</t>
+  </si>
+  <si>
+    <t>FIN-01</t>
   </si>
   <si>
     <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
@@ -308,10 +398,13 @@
     <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
-    <t>E5 · PRODUCTIVO</t>
+    <t>ESTEVEZ - Clases</t>
   </si>
   <si>
     <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
@@ -323,159 +416,66 @@
     <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
-    <t>SEGUIMIENTO AUTOMÁTICO</t>
-  </si>
-  <si>
-    <t>ID</t>
+    <t>Angelica Ramirez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
     <t>VTA-01</t>
   </si>
   <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Plantilla</t>
-  </si>
-  <si>
-    <t>Área Responsable</t>
-  </si>
-  <si>
-    <t>Key User</t>
-  </si>
-  <si>
-    <t>Consultor Oracle</t>
-  </si>
-  <si>
     <t>300 MX Clientes (Final)</t>
   </si>
   <si>
-    <t>E1 Llenado</t>
-  </si>
-  <si>
-    <t>E1 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E1 F. Real</t>
-  </si>
-  <si>
-    <t>E2 Revisión</t>
-  </si>
-  <si>
     <t>Itzel Bárcena</t>
   </si>
   <si>
-    <t>E2 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E2 F. Real</t>
-  </si>
-  <si>
-    <t>E3 Repositorio</t>
-  </si>
-  <si>
-    <t>E3 F. Compromiso</t>
-  </si>
-  <si>
     <t>Revisor / Consultor</t>
   </si>
   <si>
     <t>Brandon Hernández</t>
   </si>
   <si>
-    <t>E3 F. Real</t>
-  </si>
-  <si>
-    <t>E4 Sandbox</t>
-  </si>
-  <si>
-    <t>E4 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E4 F. Real</t>
-  </si>
-  <si>
-    <t>E5 Productivo</t>
-  </si>
-  <si>
-    <t>E5 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E5 F. Real</t>
-  </si>
-  <si>
-    <t>Etapa #</t>
-  </si>
-  <si>
-    <t>Etapa Actual</t>
-  </si>
-  <si>
-    <t>Próx. Compromiso</t>
-  </si>
-  <si>
-    <t>Días Restantes</t>
-  </si>
-  <si>
-    <t>Semáforo</t>
-  </si>
-  <si>
-    <t>Observaciones / Bloqueos</t>
-  </si>
-  <si>
     <t>15/05/2026</t>
   </si>
   <si>
-    <t>FIN-01</t>
-  </si>
-  <si>
     <t>26/05/2026</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>28/08/2026</t>
   </si>
   <si>
-    <t>ESTEVEZ - Clases</t>
-  </si>
-  <si>
     <t>Observaciones</t>
   </si>
   <si>
     <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
   </si>
   <si>
-    <t>Angelica Ramirez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fredy Sanchez </t>
-  </si>
-  <si>
     <t>Llenado completado</t>
   </si>
   <si>
     <t>Llenado en proceso</t>
   </si>
   <si>
+    <t>FIN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+  </si>
+  <si>
     <t>Sin iniciar</t>
   </si>
   <si>
-    <t>FIN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+    <t>FIN-03</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Departamentos</t>
   </si>
   <si>
     <t>Bloqueadas</t>
   </si>
   <si>
-    <t>FIN-03</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Departamentos</t>
-  </si>
-  <si>
     <t>Vencidas</t>
   </si>
   <si>
@@ -488,15 +488,15 @@
     <t>En riesgo (≤7 días)</t>
   </si>
   <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
     <t>FIN-05</t>
   </si>
   <si>
     <t>ESTEVEZ - Ubicaciones</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
     <t>Sin fecha compromiso</t>
   </si>
   <si>
@@ -506,16 +506,16 @@
     <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
   </si>
   <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>% del total</t>
+  </si>
+  <si>
     <t>FIN-06</t>
   </si>
   <si>
     <t>ESTEVEZ - Impuestos y Retenciones MX</t>
-  </si>
-  <si>
-    <t>Etapa</t>
-  </si>
-  <si>
-    <t>% del total</t>
   </si>
   <si>
     <t>CMP-01</t>
@@ -904,21 +904,27 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font/>
     <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF667085"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -933,9 +939,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -947,11 +952,6 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F4E79"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1079,80 +1079,86 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1163,17 +1169,11 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1514,28 +1514,28 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="str">
+      <c r="A3" s="11" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 15/09/2026</v>
+        <v> Actualizado al: 21/09/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>15</v>
+      <c r="A5" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="12"/>
-      <c r="E5" s="13" t="s">
-        <v>26</v>
+      <c r="E5" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
@@ -1546,438 +1546,438 @@
       <c r="L5" s="12"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="19">
+      <c r="A6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="20">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="20" t="s">
+      <c r="I6" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="L6" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="20" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="23">
+      <c r="A7" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="24">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3609756098</v>
-      </c>
-      <c r="E7" s="27" t="s">
+        <v>0.3475609756</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.75</v>
-      </c>
-      <c r="H7" s="29">
+        <v>0.6583333333</v>
+      </c>
+      <c r="H7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>6</v>
-      </c>
-      <c r="I7" s="29">
+        <v>5</v>
+      </c>
+      <c r="I7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
-        <v>6</v>
-      </c>
-      <c r="J7" s="29">
+        <v>5</v>
+      </c>
+      <c r="J7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>6</v>
-      </c>
-      <c r="K7" s="29">
+        <v>5</v>
+      </c>
+      <c r="K7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="19">
+      <c r="B8" s="18"/>
+      <c r="C8" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>15</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="29">
+        <v>14</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.525</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19">
+      <c r="B9" s="18"/>
+      <c r="C9" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
-        <v>26</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="29">
+        <v>27</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="19">
+      <c r="A10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="29">
+      <c r="E10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.252173913</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>4</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="29">
+      <c r="L10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="19">
+      <c r="A11" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="29">
+      <c r="E11" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3416666667</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="19">
+      <c r="B12" s="18"/>
+      <c r="C12" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
-        <v>5</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="29">
+        <v>34</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="19">
+      <c r="B13" s="18"/>
+      <c r="C13" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
-        <v>28</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13" s="41">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="43">
         <f>SUM(F7:F12)</f>
         <v>41</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="44">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3609756098</v>
-      </c>
-      <c r="H13" s="41">
+        <v>0.3475609756</v>
+      </c>
+      <c r="H13" s="43">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
-        <v>15</v>
-      </c>
-      <c r="I13" s="41">
+        <v>14</v>
+      </c>
+      <c r="I13" s="43">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J13" s="41">
+        <v>7</v>
+      </c>
+      <c r="J13" s="43">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K13" s="41">
+        <v>7</v>
+      </c>
+      <c r="K13" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="19">
+      <c r="B14" s="18"/>
+      <c r="C14" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19">
+      <c r="B15" s="18"/>
+      <c r="C15" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>158</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19">
-      <c r="E19" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="43" t="s">
-        <v>162</v>
+      <c r="E19" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="29">
+      <c r="E20" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
-        <v>26</v>
-      </c>
-      <c r="G20" s="30">
+        <v>27</v>
+      </c>
+      <c r="G20" s="31">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.6341463415</v>
+        <v>0.6585365854</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
         <v>7</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <f t="shared" si="2"/>
         <v>0.1707317073</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="29">
+      <c r="E22" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="29">
+      <c r="E23" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
-        <v>8</v>
-      </c>
-      <c r="G23" s="30">
+        <v>7</v>
+      </c>
+      <c r="G23" s="31">
         <f t="shared" si="2"/>
-        <v>0.1951219512</v>
+        <v>0.1707317073</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="29">
+      <c r="E25" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2984,12 +2984,12 @@
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>6</v>
+      <c r="A3" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2998,28 +2998,28 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="s">
-        <v>27</v>
+      <c r="A5" s="13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="s">
-        <v>34</v>
+      <c r="A6" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="s">
-        <v>38</v>
+      <c r="A7" s="13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>41</v>
+      <c r="A9" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -3028,38 +3028,38 @@
       <c r="F9" s="12"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
-        <v>47</v>
+      <c r="A10" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
-        <v>48</v>
+      <c r="A11" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>51</v>
+      <c r="A12" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>52</v>
+      <c r="A13" s="13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>54</v>
+      <c r="A14" s="13" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>55</v>
+      <c r="A15" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>56</v>
+      <c r="A17" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -3068,34 +3068,34 @@
       <c r="F17" s="12"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>57</v>
+      <c r="A18" s="13" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>58</v>
+      <c r="A19" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>59</v>
+      <c r="A20" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>60</v>
+      <c r="A21" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>62</v>
+      <c r="A22" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="s">
-        <v>63</v>
+      <c r="A24" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -3104,39 +3104,39 @@
       <c r="F24" s="12"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>64</v>
+      <c r="A25" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>65</v>
+      <c r="A26" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>66</v>
+      <c r="A27" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>67</v>
+      <c r="A28" s="13" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>70</v>
+      <c r="A29" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>72</v>
+      <c r="A30" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="8" t="s">
-        <v>73</v>
+      <c r="A32" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -3145,34 +3145,34 @@
       <c r="F32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>78</v>
+      <c r="A33" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>82</v>
+      <c r="A34" s="13" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>84</v>
+      <c r="A35" s="13" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>86</v>
+      <c r="A36" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>87</v>
+      <c r="A37" s="13" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="8" t="s">
-        <v>89</v>
+      <c r="A39" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -3181,34 +3181,34 @@
       <c r="F39" s="12"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>91</v>
+      <c r="A40" s="13" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="14" t="s">
-        <v>92</v>
+      <c r="A41" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>93</v>
+      <c r="A42" s="13" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="14" t="s">
-        <v>95</v>
+      <c r="A43" s="13" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>96</v>
+      <c r="A44" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="8" t="s">
-        <v>97</v>
+      <c r="A46" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -3217,136 +3217,136 @@
       <c r="F46" s="12"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
+      <c r="A47" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
+      <c r="C48" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
+      <c r="A49" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
+      <c r="A50" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
+      <c r="A51" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
+      <c r="A52" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
+      <c r="A53" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
+      <c r="A54" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
+      <c r="A55" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="A56" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
+      <c r="A57" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
+      <c r="A58" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4387,26 +4387,26 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="6" t="s">
@@ -4417,7 +4417,7 @@
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>0.0</v>
       </c>
       <c r="C3" s="3"/>
@@ -4425,32 +4425,32 @@
         <v>14</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="11" t="s">
-        <v>16</v>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="L3" s="11">
+      <c r="L3" s="8">
         <v>0.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3">
         <v>0.5</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
@@ -4471,26 +4471,26 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
@@ -4499,26 +4499,26 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>0.0</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3">
@@ -4527,14 +4527,14 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -4556,17 +4556,17 @@
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3">
@@ -4582,14 +4582,14 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="15" t="s">
-        <v>50</v>
+      <c r="J9" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="11">
+      <c r="L9" s="8">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
@@ -4603,7 +4603,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -5633,8 +5633,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>3</v>
+      <c r="A1" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5667,8 +5667,8 @@
       <c r="AD1" s="12"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="18" t="s">
-        <v>61</v>
+      <c r="A2" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -5677,33 +5677,33 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="21" t="s">
-        <v>71</v>
+      <c r="I2" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="12"/>
-      <c r="L2" s="21" t="s">
-        <v>80</v>
+      <c r="L2" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="12"/>
-      <c r="O2" s="21" t="s">
-        <v>88</v>
+      <c r="O2" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="12"/>
-      <c r="R2" s="21" t="s">
-        <v>90</v>
+      <c r="R2" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="12"/>
-      <c r="U2" s="21" t="s">
-        <v>94</v>
+      <c r="U2" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="12"/>
-      <c r="X2" s="18" t="s">
-        <v>98</v>
+      <c r="X2" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
@@ -5713,124 +5713,124 @@
       <c r="AD2" s="12"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="25" t="s">
+      <c r="P3" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="Q3" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="R3" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="28" t="s">
+      <c r="S3" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="25" t="s">
+      <c r="T3" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="U3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="K3" s="25" t="s">
+      <c r="V3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="W3" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="M3" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="N3" s="25" t="s">
+      <c r="X3" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y3" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O3" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="P3" s="25" t="s">
+      <c r="Z3" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="AB3" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC3" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="AD3" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="25" t="s">
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="T3" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="U3" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="V3" s="25" t="s">
+      <c r="B4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="W3" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="X3" s="25" t="s">
+      <c r="D4" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="Y3" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z3" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA3" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB3" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="AC3" s="25" t="s">
+      <c r="E4" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="AD3" s="25" t="s">
+      <c r="G4" s="33" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="31" t="s">
-        <v>25</v>
+      <c r="I4" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J4" s="36">
         <v>46268.0</v>
@@ -5838,8 +5838,8 @@
       <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="31" t="s">
-        <v>25</v>
+      <c r="L4" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="M4" s="36">
         <v>46268.0</v>
@@ -5847,8 +5847,8 @@
       <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="31" t="s">
-        <v>25</v>
+      <c r="O4" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="P4" s="36">
         <v>46268.0</v>
@@ -5856,17 +5856,17 @@
       <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="31" t="s">
+      <c r="R4" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
-      <c r="U4" s="31" t="s">
+      <c r="U4" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
-      <c r="X4" s="31">
+      <c r="X4" s="26">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,131 +5882,121 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="31" t="str">
+      <c r="AB4" s="26" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="31" t="str">
+      <c r="AC4" s="26" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="32"/>
+      <c r="AD4" s="28"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H5" s="31" t="s">
+      <c r="E5" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="36">
-        <v>46268.0</v>
-      </c>
-      <c r="K5" s="36">
-        <v>46268.0</v>
-      </c>
-      <c r="L5" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="36">
-        <v>46269.0</v>
-      </c>
-      <c r="N5" s="36">
-        <v>46269.0</v>
-      </c>
-      <c r="O5" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="36">
-        <v>46269.0</v>
-      </c>
-      <c r="Q5" s="36">
-        <v>46269.0</v>
-      </c>
-      <c r="R5" s="31" t="s">
+      <c r="I5" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="41">
+        <v>46282.0</v>
+      </c>
+      <c r="K5" s="41"/>
+      <c r="L5" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="41"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="40" t="s">
         <v>13</v>
       </c>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="31" t="s">
+      <c r="U5" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V5" s="36"/>
       <c r="W5" s="36"/>
-      <c r="X5" s="31">
+      <c r="X5" s="26">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="37" t="str">
         <f t="array" ref="Y5">INDEX(Cat_Etapas,$X5)</f>
-        <v>4. Ambiente Sandbox</v>
+        <v>1. Llenado de plantilla</v>
       </c>
       <c r="Z5" s="38">
         <f t="array" ref="Z5">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I5,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L5,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O5,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R5,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U5,Cat_Estatus,0)),0),4)</f>
-        <v>0.75</v>
-      </c>
-      <c r="AA5" s="39" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="AA5" s="39">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB5" s="31" t="str">
+        <v>46282</v>
+      </c>
+      <c r="AB5" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC5" s="31" t="str">
+        <v>-4</v>
+      </c>
+      <c r="AC5" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>Sin fecha</v>
-      </c>
-      <c r="AD5" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD5" s="28"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="31" t="s">
+      <c r="E6" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="31" t="s">
-        <v>25</v>
+      <c r="I6" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J6" s="36">
         <v>46268.0</v>
@@ -6014,8 +6004,8 @@
       <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="31" t="s">
-        <v>25</v>
+      <c r="L6" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="M6" s="36">
         <v>46268.0</v>
@@ -6023,8 +6013,8 @@
       <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="31" t="s">
-        <v>25</v>
+      <c r="O6" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="P6" s="36">
         <v>46268.0</v>
@@ -6032,17 +6022,17 @@
       <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="31" t="s">
+      <c r="R6" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="31" t="s">
+      <c r="U6" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V6" s="36"/>
       <c r="W6" s="36"/>
-      <c r="X6" s="31">
+      <c r="X6" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6058,43 +6048,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="31" t="str">
+      <c r="AB6" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="31" t="str">
+      <c r="AC6" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="32"/>
+      <c r="AD6" s="28"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="32" t="s">
+      <c r="C7" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" s="31" t="s">
+      <c r="E7" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="31" t="s">
-        <v>25</v>
+      <c r="I7" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J7" s="36">
         <v>46268.0</v>
@@ -6102,8 +6092,8 @@
       <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>25</v>
+      <c r="L7" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="M7" s="36">
         <v>46268.0</v>
@@ -6111,8 +6101,8 @@
       <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="31" t="s">
-        <v>25</v>
+      <c r="O7" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="P7" s="36">
         <v>46268.0</v>
@@ -6120,17 +6110,17 @@
       <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="31" t="s">
+      <c r="R7" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
-      <c r="U7" s="31" t="s">
+      <c r="U7" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V7" s="36"/>
       <c r="W7" s="36"/>
-      <c r="X7" s="31">
+      <c r="X7" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6146,79 +6136,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="31" t="str">
+      <c r="AB7" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="31" t="str">
+      <c r="AC7" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="32"/>
+      <c r="AD7" s="28"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H8" s="31" t="s">
+      <c r="C8" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="36">
-        <v>46272.0</v>
-      </c>
-      <c r="K8" s="36">
-        <v>46272.0</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="36">
-        <v>46273.0</v>
-      </c>
-      <c r="N8" s="36">
-        <v>46272.0</v>
-      </c>
-      <c r="O8" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="36">
-        <v>46273.0</v>
-      </c>
-      <c r="Q8" s="36">
-        <v>46272.0</v>
-      </c>
-      <c r="R8" s="31" t="s">
+      <c r="I8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="41">
+        <v>46282.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>46283.0</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="41">
+        <v>46283.0</v>
+      </c>
+      <c r="N8" s="41">
+        <v>46283.0</v>
+      </c>
+      <c r="O8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="41">
+        <v>46283.0</v>
+      </c>
+      <c r="Q8" s="41">
+        <v>46283.0</v>
+      </c>
+      <c r="R8" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
-      <c r="U8" s="31" t="s">
+      <c r="U8" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
-      <c r="X8" s="31">
+      <c r="X8" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6234,43 +6224,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="31" t="str">
+      <c r="AB8" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="31" t="str">
+      <c r="AC8" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="32"/>
+      <c r="AD8" s="28"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="31" t="s">
+      <c r="A9" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="C9" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>25</v>
+      <c r="I9" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J9" s="36">
         <v>46274.0</v>
@@ -6278,8 +6268,8 @@
       <c r="K9" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L9" s="44" t="s">
-        <v>25</v>
+      <c r="L9" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="M9" s="36">
         <v>46277.0</v>
@@ -6287,8 +6277,8 @@
       <c r="N9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="O9" s="44" t="s">
-        <v>25</v>
+      <c r="O9" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="P9" s="36">
         <v>46277.0</v>
@@ -6296,17 +6286,17 @@
       <c r="Q9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="31" t="s">
+      <c r="R9" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
-      <c r="U9" s="31" t="s">
+      <c r="U9" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V9" s="36"/>
       <c r="W9" s="36"/>
-      <c r="X9" s="31">
+      <c r="X9" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6322,43 +6312,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="31" t="str">
+      <c r="AB9" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="31" t="str">
+      <c r="AC9" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="32"/>
+      <c r="AD9" s="28"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="44" t="s">
-        <v>20</v>
+      <c r="I10" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="J10" s="36">
         <v>46272.0</v>
@@ -6366,33 +6356,33 @@
       <c r="K10" s="36">
         <v>46272.0</v>
       </c>
-      <c r="L10" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="46">
+      <c r="L10" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="41">
         <v>46277.0</v>
       </c>
-      <c r="N10" s="46">
+      <c r="N10" s="41">
         <v>46277.0</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="O10" s="40" t="s">
         <v>13</v>
       </c>
       <c r="P10" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q10" s="36"/>
-      <c r="R10" s="31" t="s">
+      <c r="R10" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
-      <c r="U10" s="31" t="s">
+      <c r="U10" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="36"/>
-      <c r="X10" s="31">
+      <c r="X10" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6408,43 +6398,43 @@
         <f t="shared" si="2"/>
         <v>46272</v>
       </c>
-      <c r="AB10" s="31">
+      <c r="AB10" s="26">
         <f t="shared" si="3"/>
-        <v>-8</v>
-      </c>
-      <c r="AC10" s="31" t="str">
+        <v>-14</v>
+      </c>
+      <c r="AC10" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD10" s="32"/>
+      <c r="AD10" s="28"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="34" t="s">
+      <c r="E11" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="31" t="s">
-        <v>25</v>
+      <c r="I11" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J11" s="36">
         <v>46268.0</v>
@@ -6452,8 +6442,8 @@
       <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>25</v>
+      <c r="L11" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="M11" s="36">
         <v>46269.0</v>
@@ -6461,8 +6451,8 @@
       <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="31" t="s">
-        <v>25</v>
+      <c r="O11" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="P11" s="36">
         <v>46269.0</v>
@@ -6470,17 +6460,17 @@
       <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="31" t="s">
+      <c r="R11" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
-      <c r="U11" s="31" t="s">
+      <c r="U11" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V11" s="36"/>
       <c r="W11" s="36"/>
-      <c r="X11" s="31">
+      <c r="X11" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6496,43 +6486,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="31" t="str">
+      <c r="AB11" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="31" t="str">
+      <c r="AC11" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="32"/>
+      <c r="AD11" s="28"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="A12" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="45" t="s">
+      <c r="E12" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="31" t="s">
-        <v>25</v>
+      <c r="I12" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J12" s="36">
         <v>46274.0</v>
@@ -6540,31 +6530,31 @@
       <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="31" t="s">
-        <v>20</v>
+      <c r="L12" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="M12" s="36">
         <v>46277.0</v>
       </c>
       <c r="N12" s="36"/>
-      <c r="O12" s="31" t="s">
+      <c r="O12" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P12" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q12" s="36"/>
-      <c r="R12" s="31" t="s">
+      <c r="R12" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="31" t="s">
+      <c r="U12" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V12" s="36"/>
       <c r="W12" s="36"/>
-      <c r="X12" s="31">
+      <c r="X12" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6580,73 +6570,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="31">
+      <c r="AB12" s="26">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC12" s="31" t="str">
+        <v>-9</v>
+      </c>
+      <c r="AC12" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD12" s="32"/>
+      <c r="AD12" s="28"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="45" t="s">
+      <c r="E13" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="31" t="s">
-        <v>20</v>
+      <c r="I13" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J13" s="36">
         <v>46277.0</v>
       </c>
       <c r="K13" s="36"/>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M13" s="36">
         <v>46277.0</v>
       </c>
       <c r="N13" s="36"/>
-      <c r="O13" s="31" t="s">
+      <c r="O13" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P13" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q13" s="36"/>
-      <c r="R13" s="31" t="s">
+      <c r="R13" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
-      <c r="U13" s="31" t="s">
+      <c r="U13" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V13" s="36"/>
       <c r="W13" s="36"/>
-      <c r="X13" s="31">
+      <c r="X13" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6662,73 +6652,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="31">
+      <c r="AB13" s="26">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC13" s="31" t="str">
+        <v>-9</v>
+      </c>
+      <c r="AC13" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD13" s="32"/>
+      <c r="AD13" s="28"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="45" t="s">
+      <c r="E14" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="31" t="s">
-        <v>20</v>
+      <c r="I14" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J14" s="36">
         <v>46277.0</v>
       </c>
       <c r="K14" s="36"/>
-      <c r="L14" s="31" t="s">
+      <c r="L14" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M14" s="36">
         <v>46283.0</v>
       </c>
       <c r="N14" s="36"/>
-      <c r="O14" s="31" t="s">
+      <c r="O14" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P14" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q14" s="36"/>
-      <c r="R14" s="31" t="s">
+      <c r="R14" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S14" s="36"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="31" t="s">
+      <c r="U14" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V14" s="36"/>
       <c r="W14" s="36"/>
-      <c r="X14" s="31">
+      <c r="X14" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6744,73 +6734,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB14" s="31">
+      <c r="AB14" s="26">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC14" s="31" t="str">
+        <v>-9</v>
+      </c>
+      <c r="AC14" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD14" s="32"/>
+      <c r="AD14" s="28"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="35" t="s">
+      <c r="E15" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="44" t="s">
-        <v>25</v>
+      <c r="I15" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="J15" s="36">
         <v>46283.0</v>
       </c>
       <c r="K15" s="36"/>
-      <c r="L15" s="44" t="s">
-        <v>20</v>
+      <c r="L15" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="M15" s="36">
         <v>46283.0</v>
       </c>
       <c r="N15" s="36"/>
-      <c r="O15" s="31" t="s">
+      <c r="O15" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P15" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q15" s="36"/>
-      <c r="R15" s="31" t="s">
+      <c r="R15" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S15" s="36"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="31" t="s">
+      <c r="U15" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V15" s="36"/>
       <c r="W15" s="36"/>
-      <c r="X15" s="31">
+      <c r="X15" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6826,73 +6816,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="31">
+      <c r="AB15" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC15" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC15" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD15" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD15" s="28"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="35" t="s">
+      <c r="E16" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="44" t="s">
-        <v>25</v>
+      <c r="I16" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="J16" s="36">
         <v>46283.0</v>
       </c>
       <c r="K16" s="36"/>
-      <c r="L16" s="44" t="s">
-        <v>20</v>
+      <c r="L16" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="M16" s="36">
         <v>46283.0</v>
       </c>
       <c r="N16" s="36"/>
-      <c r="O16" s="31" t="s">
+      <c r="O16" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P16" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q16" s="36"/>
-      <c r="R16" s="31" t="s">
+      <c r="R16" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S16" s="36"/>
       <c r="T16" s="36"/>
-      <c r="U16" s="31" t="s">
+      <c r="U16" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V16" s="36"/>
       <c r="W16" s="36"/>
-      <c r="X16" s="31">
+      <c r="X16" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6908,73 +6898,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="31">
+      <c r="AB16" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC16" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC16" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD16" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD16" s="28"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="35" t="s">
+      <c r="E17" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="44" t="s">
-        <v>25</v>
+      <c r="I17" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="J17" s="36">
         <v>46283.0</v>
       </c>
       <c r="K17" s="36"/>
-      <c r="L17" s="44" t="s">
-        <v>20</v>
+      <c r="L17" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="M17" s="36">
         <v>46283.0</v>
       </c>
       <c r="N17" s="36"/>
-      <c r="O17" s="31" t="s">
+      <c r="O17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P17" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q17" s="36"/>
-      <c r="R17" s="31" t="s">
+      <c r="R17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
-      <c r="U17" s="31" t="s">
+      <c r="U17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="36"/>
-      <c r="X17" s="31">
+      <c r="X17" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6990,73 +6980,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="31">
+      <c r="AB17" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC17" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC17" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD17" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD17" s="28"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="35" t="s">
+      <c r="E18" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="31" t="s">
-        <v>20</v>
+      <c r="I18" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J18" s="36">
         <v>46283.0</v>
       </c>
       <c r="K18" s="36"/>
-      <c r="L18" s="31" t="s">
+      <c r="L18" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M18" s="36">
         <v>46283.0</v>
       </c>
       <c r="N18" s="36"/>
-      <c r="O18" s="31" t="s">
+      <c r="O18" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P18" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q18" s="36"/>
-      <c r="R18" s="31" t="s">
+      <c r="R18" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
-      <c r="U18" s="31" t="s">
+      <c r="U18" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V18" s="36"/>
       <c r="W18" s="36"/>
-      <c r="X18" s="31">
+      <c r="X18" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7072,73 +7062,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="31">
+      <c r="AB18" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC18" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC18" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD18" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD18" s="28"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="35" t="s">
+      <c r="E19" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="44" t="s">
-        <v>25</v>
+      <c r="I19" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="J19" s="36">
         <v>46283.0</v>
       </c>
       <c r="K19" s="36"/>
-      <c r="L19" s="44" t="s">
-        <v>20</v>
+      <c r="L19" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="M19" s="36">
         <v>46283.0</v>
       </c>
       <c r="N19" s="36"/>
-      <c r="O19" s="31" t="s">
+      <c r="O19" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P19" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q19" s="36"/>
-      <c r="R19" s="31" t="s">
+      <c r="R19" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S19" s="36"/>
       <c r="T19" s="36"/>
-      <c r="U19" s="31" t="s">
+      <c r="U19" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V19" s="36"/>
       <c r="W19" s="36"/>
-      <c r="X19" s="31">
+      <c r="X19" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7154,73 +7144,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="31">
+      <c r="AB19" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC19" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC19" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD19" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD19" s="28"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="35" t="s">
+      <c r="E20" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="31" t="s">
-        <v>20</v>
+      <c r="I20" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J20" s="36">
         <v>46283.0</v>
       </c>
       <c r="K20" s="36"/>
-      <c r="L20" s="31" t="s">
+      <c r="L20" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M20" s="36">
         <v>46283.0</v>
       </c>
       <c r="N20" s="36"/>
-      <c r="O20" s="31" t="s">
+      <c r="O20" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P20" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="31" t="s">
+      <c r="R20" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S20" s="36"/>
       <c r="T20" s="36"/>
-      <c r="U20" s="31" t="s">
+      <c r="U20" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="36"/>
-      <c r="X20" s="31">
+      <c r="X20" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7236,73 +7226,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC20" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC20" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD20" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD20" s="28"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="35" t="s">
+      <c r="E21" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="31" t="s">
-        <v>20</v>
+      <c r="I21" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J21" s="36">
         <v>46283.0</v>
       </c>
       <c r="K21" s="36"/>
-      <c r="L21" s="31" t="s">
+      <c r="L21" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M21" s="36">
         <v>46283.0</v>
       </c>
       <c r="N21" s="36"/>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P21" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q21" s="36"/>
-      <c r="R21" s="31" t="s">
+      <c r="R21" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S21" s="36"/>
       <c r="T21" s="36"/>
-      <c r="U21" s="31" t="s">
+      <c r="U21" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V21" s="36"/>
       <c r="W21" s="36"/>
-      <c r="X21" s="31">
+      <c r="X21" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7318,73 +7308,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC21" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC21" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD21" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD21" s="28"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="35" t="s">
+      <c r="E22" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I22" s="31" t="s">
-        <v>20</v>
+      <c r="I22" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J22" s="36">
         <v>46283.0</v>
       </c>
       <c r="K22" s="36"/>
-      <c r="L22" s="31" t="s">
+      <c r="L22" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M22" s="36">
         <v>46283.0</v>
       </c>
       <c r="N22" s="36"/>
-      <c r="O22" s="31" t="s">
+      <c r="O22" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P22" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q22" s="36"/>
-      <c r="R22" s="31" t="s">
+      <c r="R22" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S22" s="36"/>
       <c r="T22" s="36"/>
-      <c r="U22" s="31" t="s">
+      <c r="U22" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V22" s="36"/>
       <c r="W22" s="36"/>
-      <c r="X22" s="31">
+      <c r="X22" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7400,73 +7390,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="31">
+      <c r="AB22" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC22" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC22" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD22" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD22" s="28"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="31" t="s">
+      <c r="B23" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="35" t="s">
+      <c r="E23" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="31" t="s">
-        <v>20</v>
+      <c r="I23" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J23" s="36">
         <v>46283.0</v>
       </c>
       <c r="K23" s="36"/>
-      <c r="L23" s="31" t="s">
+      <c r="L23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M23" s="36">
         <v>46283.0</v>
       </c>
       <c r="N23" s="36"/>
-      <c r="O23" s="31" t="s">
+      <c r="O23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P23" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q23" s="36"/>
-      <c r="R23" s="31" t="s">
+      <c r="R23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S23" s="36"/>
       <c r="T23" s="36"/>
-      <c r="U23" s="31" t="s">
+      <c r="U23" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V23" s="36"/>
       <c r="W23" s="36"/>
-      <c r="X23" s="31">
+      <c r="X23" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7482,73 +7472,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="31">
+      <c r="AB23" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC23" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC23" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD23" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD23" s="28"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="31" t="s">
+      <c r="B24" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="35" t="s">
+      <c r="E24" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="31" t="s">
-        <v>20</v>
+      <c r="I24" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J24" s="36">
         <v>46283.0</v>
       </c>
       <c r="K24" s="36"/>
-      <c r="L24" s="31" t="s">
+      <c r="L24" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M24" s="36">
         <v>46283.0</v>
       </c>
       <c r="N24" s="36"/>
-      <c r="O24" s="31" t="s">
+      <c r="O24" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P24" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q24" s="36"/>
-      <c r="R24" s="31" t="s">
+      <c r="R24" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S24" s="36"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="31" t="s">
+      <c r="U24" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V24" s="36"/>
       <c r="W24" s="36"/>
-      <c r="X24" s="31">
+      <c r="X24" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7564,73 +7554,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC24" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC24" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD24" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD24" s="28"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="31" t="s">
+      <c r="B25" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="35" t="s">
+      <c r="E25" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="31" t="s">
-        <v>20</v>
+      <c r="I25" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J25" s="36">
         <v>46283.0</v>
       </c>
       <c r="K25" s="36"/>
-      <c r="L25" s="31" t="s">
+      <c r="L25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M25" s="36">
         <v>46283.0</v>
       </c>
       <c r="N25" s="36"/>
-      <c r="O25" s="31" t="s">
+      <c r="O25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P25" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q25" s="36"/>
-      <c r="R25" s="31" t="s">
+      <c r="R25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S25" s="36"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="31" t="s">
+      <c r="U25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V25" s="36"/>
       <c r="W25" s="36"/>
-      <c r="X25" s="31">
+      <c r="X25" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7646,73 +7636,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="31">
+      <c r="AB25" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC25" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC25" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD25" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD25" s="28"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="31" t="s">
+      <c r="B26" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="35" t="s">
+      <c r="E26" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="31" t="s">
-        <v>20</v>
+      <c r="I26" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J26" s="36">
         <v>46283.0</v>
       </c>
       <c r="K26" s="36"/>
-      <c r="L26" s="31" t="s">
+      <c r="L26" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M26" s="36">
         <v>46283.0</v>
       </c>
       <c r="N26" s="36"/>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P26" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q26" s="36"/>
-      <c r="R26" s="31" t="s">
+      <c r="R26" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S26" s="36"/>
       <c r="T26" s="36"/>
-      <c r="U26" s="31" t="s">
+      <c r="U26" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V26" s="36"/>
       <c r="W26" s="36"/>
-      <c r="X26" s="31">
+      <c r="X26" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7728,73 +7718,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="31">
+      <c r="AB26" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC26" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC26" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD26" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD26" s="28"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="35" t="s">
+      <c r="E27" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="31" t="s">
-        <v>20</v>
+      <c r="I27" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J27" s="36">
         <v>46283.0</v>
       </c>
       <c r="K27" s="36"/>
-      <c r="L27" s="31" t="s">
+      <c r="L27" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="36">
         <v>46283.0</v>
       </c>
       <c r="N27" s="36"/>
-      <c r="O27" s="31" t="s">
+      <c r="O27" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P27" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="31" t="s">
+      <c r="R27" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S27" s="36"/>
       <c r="T27" s="36"/>
-      <c r="U27" s="31" t="s">
+      <c r="U27" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V27" s="36"/>
       <c r="W27" s="36"/>
-      <c r="X27" s="31">
+      <c r="X27" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7810,73 +7800,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC27" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC27" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD27" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD27" s="28"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="31" t="s">
+      <c r="B28" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="35" t="s">
+      <c r="E28" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="31" t="s">
-        <v>20</v>
+      <c r="I28" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J28" s="36">
         <v>46283.0</v>
       </c>
       <c r="K28" s="36"/>
-      <c r="L28" s="31" t="s">
+      <c r="L28" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M28" s="36">
         <v>46283.0</v>
       </c>
       <c r="N28" s="36"/>
-      <c r="O28" s="31" t="s">
+      <c r="O28" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P28" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q28" s="36"/>
-      <c r="R28" s="31" t="s">
+      <c r="R28" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="36"/>
       <c r="T28" s="36"/>
-      <c r="U28" s="31" t="s">
+      <c r="U28" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V28" s="36"/>
       <c r="W28" s="36"/>
-      <c r="X28" s="31">
+      <c r="X28" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7892,73 +7882,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="31">
+      <c r="AB28" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC28" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC28" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD28" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD28" s="28"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="B29" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="35" t="s">
+      <c r="E29" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="31" t="s">
-        <v>20</v>
+      <c r="I29" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J29" s="36">
         <v>46283.0</v>
       </c>
       <c r="K29" s="36"/>
-      <c r="L29" s="31" t="s">
+      <c r="L29" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M29" s="36">
         <v>46283.0</v>
       </c>
       <c r="N29" s="36"/>
-      <c r="O29" s="31" t="s">
+      <c r="O29" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P29" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q29" s="36"/>
-      <c r="R29" s="31" t="s">
+      <c r="R29" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S29" s="36"/>
       <c r="T29" s="36"/>
-      <c r="U29" s="31" t="s">
+      <c r="U29" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V29" s="36"/>
       <c r="W29" s="36"/>
-      <c r="X29" s="31">
+      <c r="X29" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7974,73 +7964,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="31">
+      <c r="AB29" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC29" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC29" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD29" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD29" s="28"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="35" t="s">
+      <c r="E30" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="31" t="s">
-        <v>20</v>
+      <c r="I30" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J30" s="36">
         <v>46283.0</v>
       </c>
       <c r="K30" s="36"/>
-      <c r="L30" s="31" t="s">
+      <c r="L30" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M30" s="36">
         <v>46283.0</v>
       </c>
       <c r="N30" s="36"/>
-      <c r="O30" s="31" t="s">
+      <c r="O30" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P30" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q30" s="36"/>
-      <c r="R30" s="31" t="s">
+      <c r="R30" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S30" s="36"/>
       <c r="T30" s="36"/>
-      <c r="U30" s="31" t="s">
+      <c r="U30" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V30" s="36"/>
       <c r="W30" s="36"/>
-      <c r="X30" s="31">
+      <c r="X30" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8056,73 +8046,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="31">
+      <c r="AB30" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC30" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC30" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD30" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD30" s="28"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="31" t="s">
+      <c r="B31" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="35" t="s">
+      <c r="E31" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="35" t="s">
+      <c r="G31" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I31" s="31" t="s">
-        <v>20</v>
+      <c r="I31" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J31" s="36">
         <v>46283.0</v>
       </c>
       <c r="K31" s="36"/>
-      <c r="L31" s="31" t="s">
+      <c r="L31" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M31" s="36">
         <v>46283.0</v>
       </c>
       <c r="N31" s="36"/>
-      <c r="O31" s="31" t="s">
+      <c r="O31" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P31" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q31" s="36"/>
-      <c r="R31" s="31" t="s">
+      <c r="R31" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S31" s="36"/>
       <c r="T31" s="36"/>
-      <c r="U31" s="31" t="s">
+      <c r="U31" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V31" s="36"/>
       <c r="W31" s="36"/>
-      <c r="X31" s="31">
+      <c r="X31" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8138,73 +8128,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="31">
+      <c r="AB31" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC31" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC31" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD31" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD31" s="28"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="31" t="s">
+      <c r="B32" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="35" t="s">
+      <c r="E32" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="35" t="s">
+      <c r="G32" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="31" t="s">
-        <v>20</v>
+      <c r="I32" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J32" s="36">
         <v>46283.0</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="31" t="s">
+      <c r="L32" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M32" s="36">
         <v>46283.0</v>
       </c>
       <c r="N32" s="36"/>
-      <c r="O32" s="31" t="s">
+      <c r="O32" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P32" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q32" s="36"/>
-      <c r="R32" s="31" t="s">
+      <c r="R32" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S32" s="36"/>
       <c r="T32" s="36"/>
-      <c r="U32" s="31" t="s">
+      <c r="U32" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V32" s="36"/>
       <c r="W32" s="36"/>
-      <c r="X32" s="31">
+      <c r="X32" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8220,73 +8210,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="31">
+      <c r="AB32" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC32" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC32" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD32" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD32" s="28"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="31" t="s">
+      <c r="B33" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="35" t="s">
+      <c r="E33" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="31" t="s">
-        <v>20</v>
+      <c r="I33" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J33" s="36">
         <v>46283.0</v>
       </c>
       <c r="K33" s="36"/>
-      <c r="L33" s="31" t="s">
+      <c r="L33" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M33" s="36">
         <v>46283.0</v>
       </c>
       <c r="N33" s="36"/>
-      <c r="O33" s="31" t="s">
+      <c r="O33" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P33" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q33" s="36"/>
-      <c r="R33" s="31" t="s">
+      <c r="R33" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
-      <c r="U33" s="31" t="s">
+      <c r="U33" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V33" s="36"/>
       <c r="W33" s="36"/>
-      <c r="X33" s="31">
+      <c r="X33" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8302,73 +8292,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="31">
+      <c r="AB33" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC33" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC33" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD33" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD33" s="28"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="31" t="s">
+      <c r="B34" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="35" t="s">
+      <c r="E34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="35" t="s">
+      <c r="G34" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="31" t="s">
-        <v>20</v>
+      <c r="I34" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J34" s="36">
         <v>46283.0</v>
       </c>
       <c r="K34" s="36"/>
-      <c r="L34" s="31" t="s">
+      <c r="L34" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M34" s="36">
         <v>46283.0</v>
       </c>
       <c r="N34" s="36"/>
-      <c r="O34" s="31" t="s">
+      <c r="O34" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P34" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q34" s="36"/>
-      <c r="R34" s="31" t="s">
+      <c r="R34" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S34" s="36"/>
       <c r="T34" s="36"/>
-      <c r="U34" s="31" t="s">
+      <c r="U34" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V34" s="36"/>
       <c r="W34" s="36"/>
-      <c r="X34" s="31">
+      <c r="X34" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8384,73 +8374,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="31">
+      <c r="AB34" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC34" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC34" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD34" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD34" s="28"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="B35" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="35" t="s">
+      <c r="E35" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="31" t="s">
-        <v>20</v>
+      <c r="I35" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J35" s="36">
         <v>46283.0</v>
       </c>
       <c r="K35" s="36"/>
-      <c r="L35" s="31" t="s">
+      <c r="L35" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M35" s="36">
         <v>46283.0</v>
       </c>
       <c r="N35" s="36"/>
-      <c r="O35" s="31" t="s">
+      <c r="O35" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P35" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q35" s="36"/>
-      <c r="R35" s="31" t="s">
+      <c r="R35" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
-      <c r="U35" s="31" t="s">
+      <c r="U35" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V35" s="36"/>
       <c r="W35" s="36"/>
-      <c r="X35" s="31">
+      <c r="X35" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8466,73 +8456,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="31">
+      <c r="AB35" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC35" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC35" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD35" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD35" s="28"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="B36" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="35" t="s">
+      <c r="E36" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="35" t="s">
+      <c r="G36" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="31" t="s">
-        <v>20</v>
+      <c r="I36" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J36" s="36">
         <v>46283.0</v>
       </c>
       <c r="K36" s="36"/>
-      <c r="L36" s="31" t="s">
+      <c r="L36" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M36" s="36">
         <v>46283.0</v>
       </c>
       <c r="N36" s="36"/>
-      <c r="O36" s="31" t="s">
+      <c r="O36" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P36" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q36" s="36"/>
-      <c r="R36" s="31" t="s">
+      <c r="R36" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S36" s="36"/>
       <c r="T36" s="36"/>
-      <c r="U36" s="31" t="s">
+      <c r="U36" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V36" s="36"/>
       <c r="W36" s="36"/>
-      <c r="X36" s="31">
+      <c r="X36" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8548,73 +8538,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="31">
+      <c r="AB36" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC36" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC36" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD36" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD36" s="28"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="31" t="s">
+      <c r="B37" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="35" t="s">
+      <c r="E37" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G37" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="31" t="s">
-        <v>20</v>
+      <c r="I37" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J37" s="36">
         <v>46283.0</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="31" t="s">
+      <c r="L37" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M37" s="36">
         <v>46283.0</v>
       </c>
       <c r="N37" s="36"/>
-      <c r="O37" s="31" t="s">
+      <c r="O37" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P37" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q37" s="36"/>
-      <c r="R37" s="31" t="s">
+      <c r="R37" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
-      <c r="U37" s="31" t="s">
+      <c r="U37" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V37" s="36"/>
       <c r="W37" s="36"/>
-      <c r="X37" s="31">
+      <c r="X37" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8630,75 +8620,75 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC37" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC37" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD37" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD37" s="28"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="31" t="s">
+      <c r="B38" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="34" t="s">
+      <c r="F38" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" s="46">
+      <c r="I38" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="41">
         <v>46277.0</v>
       </c>
       <c r="K38" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="31" t="s">
-        <v>20</v>
+      <c r="L38" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="M38" s="36">
         <v>46283.0</v>
       </c>
       <c r="N38" s="36"/>
-      <c r="O38" s="31" t="s">
+      <c r="O38" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P38" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="31" t="s">
+      <c r="R38" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S38" s="36"/>
       <c r="T38" s="36"/>
-      <c r="U38" s="31" t="s">
+      <c r="U38" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V38" s="36"/>
       <c r="W38" s="36"/>
-      <c r="X38" s="31">
+      <c r="X38" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8714,73 +8704,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC38" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC38" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD38" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD38" s="28"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="31" t="s">
+      <c r="B39" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="35" t="s">
+      <c r="G39" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I39" s="31" t="s">
-        <v>20</v>
+      <c r="I39" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J39" s="36">
         <v>46283.0</v>
       </c>
       <c r="K39" s="36"/>
-      <c r="L39" s="31" t="s">
+      <c r="L39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M39" s="36">
         <v>46283.0</v>
       </c>
       <c r="N39" s="36"/>
-      <c r="O39" s="31" t="s">
+      <c r="O39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P39" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q39" s="36"/>
-      <c r="R39" s="31" t="s">
+      <c r="R39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
-      <c r="U39" s="31" t="s">
+      <c r="U39" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V39" s="36"/>
       <c r="W39" s="36"/>
-      <c r="X39" s="31">
+      <c r="X39" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8796,73 +8786,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB39" s="31">
+      <c r="AB39" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC39" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC39" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD39" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD39" s="28"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="31" t="s">
+      <c r="B40" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="34" t="s">
+      <c r="F40" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I40" s="31" t="s">
-        <v>20</v>
+      <c r="I40" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J40" s="36">
         <v>46283.0</v>
       </c>
       <c r="K40" s="36"/>
-      <c r="L40" s="31" t="s">
+      <c r="L40" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M40" s="36">
         <v>46283.0</v>
       </c>
       <c r="N40" s="36"/>
-      <c r="O40" s="31" t="s">
+      <c r="O40" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P40" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q40" s="36"/>
-      <c r="R40" s="31" t="s">
+      <c r="R40" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
-      <c r="U40" s="31" t="s">
+      <c r="U40" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V40" s="36"/>
       <c r="W40" s="36"/>
-      <c r="X40" s="31">
+      <c r="X40" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8878,73 +8868,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB40" s="31">
+      <c r="AB40" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC40" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC40" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD40" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD40" s="28"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="31" t="s">
+      <c r="B41" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="34" t="s">
+      <c r="F41" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="35" t="s">
+      <c r="G41" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="31" t="s">
-        <v>20</v>
+      <c r="I41" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J41" s="36">
         <v>46283.0</v>
       </c>
       <c r="K41" s="36"/>
-      <c r="L41" s="31" t="s">
+      <c r="L41" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M41" s="36">
         <v>46283.0</v>
       </c>
       <c r="N41" s="36"/>
-      <c r="O41" s="31" t="s">
+      <c r="O41" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P41" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q41" s="36"/>
-      <c r="R41" s="31" t="s">
+      <c r="R41" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
-      <c r="U41" s="31" t="s">
+      <c r="U41" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V41" s="36"/>
       <c r="W41" s="36"/>
-      <c r="X41" s="31">
+      <c r="X41" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8960,73 +8950,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC41" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC41" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD41" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD41" s="28"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="B42" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="34" t="s">
+      <c r="F42" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="31" t="s">
+      <c r="H42" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I42" s="31" t="s">
-        <v>20</v>
+      <c r="I42" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="J42" s="36">
         <v>46283.0</v>
       </c>
       <c r="K42" s="36"/>
-      <c r="L42" s="31" t="s">
+      <c r="L42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="M42" s="36">
         <v>46283.0</v>
       </c>
       <c r="N42" s="36"/>
-      <c r="O42" s="31" t="s">
+      <c r="O42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P42" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q42" s="36"/>
-      <c r="R42" s="31" t="s">
+      <c r="R42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S42" s="36"/>
       <c r="T42" s="36"/>
-      <c r="U42" s="31" t="s">
+      <c r="U42" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V42" s="36"/>
       <c r="W42" s="36"/>
-      <c r="X42" s="31">
+      <c r="X42" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -9042,61 +9032,61 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB42" s="31">
+      <c r="AB42" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AC42" s="31" t="str">
+        <v>-3</v>
+      </c>
+      <c r="AC42" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>En riesgo</v>
-      </c>
-      <c r="AD42" s="32"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD42" s="28"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="31" t="s">
+      <c r="B43" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="33" t="s">
+      <c r="E43" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="34" t="s">
+      <c r="F43" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G43" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" s="46">
+      <c r="I43" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="41">
         <v>46277.0</v>
       </c>
       <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" s="46">
+      <c r="L43" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="41">
         <v>46277.0</v>
       </c>
       <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="31" t="s">
-        <v>25</v>
+      <c r="O43" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="P43" s="36">
         <v>46276.0</v>
@@ -9104,17 +9094,17 @@
       <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="31" t="s">
+      <c r="R43" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
-      <c r="U43" s="31" t="s">
+      <c r="U43" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V43" s="36"/>
       <c r="W43" s="36"/>
-      <c r="X43" s="31">
+      <c r="X43" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9130,73 +9120,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="31" t="str">
+      <c r="AB43" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="31" t="str">
+      <c r="AC43" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="32"/>
+      <c r="AD43" s="28"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="31" t="s">
+      <c r="B44" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G44" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="H44" s="31" t="s">
+      <c r="E44" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="46">
+      <c r="I44" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="41">
         <v>46277.0</v>
       </c>
       <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="31" t="s">
-        <v>20</v>
+      <c r="L44" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="M44" s="36">
         <v>46276.0</v>
       </c>
       <c r="N44" s="36"/>
-      <c r="O44" s="31" t="s">
+      <c r="O44" s="26" t="s">
         <v>13</v>
       </c>
       <c r="P44" s="36"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="31" t="s">
+      <c r="R44" s="26" t="s">
         <v>13</v>
       </c>
       <c r="S44" s="36"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="31" t="s">
+      <c r="U44" s="26" t="s">
         <v>13</v>
       </c>
       <c r="V44" s="36"/>
       <c r="W44" s="36"/>
-      <c r="X44" s="31">
+      <c r="X44" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9212,15 +9202,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="26">
         <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
-      <c r="AC44" s="31" t="str">
+        <v>-10</v>
+      </c>
+      <c r="AC44" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="32"/>
+      <c r="AD44" s="28"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -29,24 +29,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="274">
   <si>
+    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
+  </si>
+  <si>
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
   <si>
-    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
-  </si>
-  <si>
-    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
-  </si>
-  <si>
-    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
   </si>
   <si>
     <t>Estatus</t>
   </si>
   <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
-  </si>
-  <si>
     <t>Factor avance</t>
   </si>
   <si>
@@ -62,252 +62,288 @@
     <t>Etapas</t>
   </si>
   <si>
+    <t>Peso etapa</t>
+  </si>
+  <si>
+    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
+  </si>
+  <si>
+    <t>No iniciado</t>
+  </si>
+  <si>
+    <t>INDICADORES CLAVE</t>
+  </si>
+  <si>
+    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+  </si>
+  <si>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
+    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>AVANCE POR MÓDULO</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
+  </si>
+  <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
+  </si>
+  <si>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+  </si>
+  <si>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>Activos Fijos / Patrimonio</t>
+  </si>
+  <si>
+    <t>6. Cerrado</t>
+  </si>
+  <si>
+    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
+  </si>
+  <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
     <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
   </si>
   <si>
-    <t>Peso etapa</t>
-  </si>
-  <si>
-    <t>No iniciado</t>
-  </si>
-  <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
-    <t>1. Llenado de plantilla</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
-  </si>
-  <si>
-    <t>Compras (P2P)</t>
-  </si>
-  <si>
-    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
-  </si>
-  <si>
-    <t>2. Revisión y validación</t>
-  </si>
-  <si>
-    <t>INDICADORES CLAVE</t>
-  </si>
-  <si>
-    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
-  </si>
-  <si>
-    <t>Completado</t>
-  </si>
-  <si>
-    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
-  </si>
-  <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>AVANCE POR MÓDULO</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Almacén / Inventarios</t>
-  </si>
-  <si>
-    <t>4. Ambiente Sandbox</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
-  </si>
-  <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
-  </si>
-  <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+  </si>
+  <si>
+    <t>3. Valores de estatus permitidos</t>
+  </si>
+  <si>
+    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+  </si>
+  <si>
+    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
+  </si>
+  <si>
+    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
+  </si>
+  <si>
+    <t>PMO / Consultoría</t>
+  </si>
+  <si>
+    <t>4. Lectura del semáforo</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
+  </si>
+  <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+  </si>
+  <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
+    <t>E3 Repositorio OK</t>
+  </si>
+  <si>
+    <t>E4 Sandbox OK</t>
+  </si>
+  <si>
+    <t>E5 Productivo OK</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+  </si>
+  <si>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
+  </si>
+  <si>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
   </si>
   <si>
     <t>IDENTIFICACIÓN Y RESPONSABLES</t>
   </si>
   <si>
-    <t>Activos Fijos (FA)</t>
-  </si>
-  <si>
-    <t>Activos Fijos / Patrimonio</t>
-  </si>
-  <si>
-    <t>6. Cerrado</t>
-  </si>
-  <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
-  </si>
-  <si>
-    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
+    <t>5. Conexión con el tablero HTML</t>
+  </si>
+  <si>
+    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
     <t>E1 · LLENADO</t>
   </si>
   <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
-  </si>
-  <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
-  </si>
-  <si>
-    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
+  </si>
+  <si>
+    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
+  </si>
+  <si>
+    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
+  </si>
+  <si>
+    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
   </si>
   <si>
     <t>E2 · REVISIÓN</t>
   </si>
   <si>
-    <t>3. Valores de estatus permitidos</t>
+    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
     <t>E3 · REPOSITORIO ORACLE</t>
   </si>
   <si>
-    <t>PMO / Consultoría</t>
-  </si>
-  <si>
-    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
-  </si>
-  <si>
     <t>E4 · SANDBOX</t>
   </si>
   <si>
-    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
+    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
+  </si>
+  <si>
+    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
   </si>
   <si>
     <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
-    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
-  </si>
-  <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>4. Lectura del semáforo</t>
+    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
     <t>SEGUIMIENTO AUTOMÁTICO</t>
   </si>
   <si>
-    <t>Plantillas</t>
-  </si>
-  <si>
-    <t>% Avance</t>
-  </si>
-  <si>
-    <t>E1 Llenado OK</t>
-  </si>
-  <si>
-    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
-  </si>
-  <si>
-    <t>E2 Revisión OK</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
-  </si>
-  <si>
-    <t>E3 Repositorio OK</t>
-  </si>
-  <si>
-    <t>E4 Sandbox OK</t>
+    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
+  </si>
+  <si>
+    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>E5 Productivo OK</t>
-  </si>
-  <si>
-    <t>Avance global ponderado</t>
+    <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
     <t>Código</t>
   </si>
   <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
-  </si>
-  <si>
     <t>Plantilla</t>
   </si>
   <si>
     <t>Área Responsable</t>
   </si>
   <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
-  </si>
-  <si>
     <t>Key User</t>
   </si>
   <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
     <t>Consultor Oracle</t>
   </si>
   <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
-  </si>
-  <si>
-    <t>5. Conexión con el tablero HTML</t>
-  </si>
-  <si>
     <t>E1 Llenado</t>
   </si>
   <si>
@@ -320,6 +356,9 @@
     <t>E2 Revisión</t>
   </si>
   <si>
+    <t>VTA-01</t>
+  </si>
+  <si>
     <t>E2 F. Compromiso</t>
   </si>
   <si>
@@ -329,9 +368,6 @@
     <t>E3 Repositorio</t>
   </si>
   <si>
-    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
-  </si>
-  <si>
     <t>E3 F. Compromiso</t>
   </si>
   <si>
@@ -341,9 +377,6 @@
     <t>E4 Sandbox</t>
   </si>
   <si>
-    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
-  </si>
-  <si>
     <t>E4 F. Compromiso</t>
   </si>
   <si>
@@ -353,9 +386,6 @@
     <t>E5 Productivo</t>
   </si>
   <si>
-    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
-  </si>
-  <si>
     <t>E5 F. Compromiso</t>
   </si>
   <si>
@@ -365,24 +395,15 @@
     <t>Etapa #</t>
   </si>
   <si>
-    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
-  </si>
-  <si>
     <t>Etapa Actual</t>
   </si>
   <si>
-    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
-  </si>
-  <si>
     <t>Próx. Compromiso</t>
   </si>
   <si>
     <t>Días Restantes</t>
   </si>
   <si>
-    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
-  </si>
-  <si>
     <t>Semáforo</t>
   </si>
   <si>
@@ -392,51 +413,30 @@
     <t>FIN-01</t>
   </si>
   <si>
-    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
-  </si>
-  <si>
-    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
+    <t>300 MX Clientes (Final)</t>
+  </si>
+  <si>
+    <t>Itzel Bárcena</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
-    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
+    <t>Revisor / Consultor</t>
+  </si>
+  <si>
+    <t>Brandon Hernández</t>
   </si>
   <si>
     <t>ESTEVEZ - Clases</t>
   </si>
   <si>
-    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
-  </si>
-  <si>
-    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
-  </si>
-  <si>
-    <t>7. Ejemplo de captura correcta de una fila</t>
-  </si>
-  <si>
     <t>Angelica Ramirez</t>
   </si>
   <si>
     <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
-    <t>VTA-01</t>
-  </si>
-  <si>
-    <t>300 MX Clientes (Final)</t>
-  </si>
-  <si>
-    <t>Itzel Bárcena</t>
-  </si>
-  <si>
-    <t>Revisor / Consultor</t>
-  </si>
-  <si>
-    <t>Brandon Hernández</t>
-  </si>
-  <si>
     <t>15/05/2026</t>
   </si>
   <si>
@@ -458,13 +458,19 @@
     <t>Llenado en proceso</t>
   </si>
   <si>
+    <t>Sin iniciar</t>
+  </si>
+  <si>
     <t>FIN-02</t>
   </si>
   <si>
     <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
   </si>
   <si>
-    <t>Sin iniciar</t>
+    <t>Bloqueadas</t>
+  </si>
+  <si>
+    <t>Vencidas</t>
   </si>
   <si>
     <t>FIN-03</t>
@@ -473,43 +479,37 @@
     <t>ESTEVEZ - Departamentos</t>
   </si>
   <si>
-    <t>Bloqueadas</t>
-  </si>
-  <si>
-    <t>Vencidas</t>
+    <t>En riesgo (≤7 días)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>FIN-04</t>
   </si>
   <si>
+    <t>Sin fecha compromiso</t>
+  </si>
+  <si>
     <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
-    <t>En riesgo (≤7 días)</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>Cerradas (productivo)</t>
+  </si>
+  <si>
+    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>% del total</t>
   </si>
   <si>
     <t>FIN-05</t>
   </si>
   <si>
     <t>ESTEVEZ - Ubicaciones</t>
-  </si>
-  <si>
-    <t>Sin fecha compromiso</t>
-  </si>
-  <si>
-    <t>Cerradas (productivo)</t>
-  </si>
-  <si>
-    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
-  </si>
-  <si>
-    <t>Etapa</t>
-  </si>
-  <si>
-    <t>% del total</t>
   </si>
   <si>
     <t>FIN-06</t>
@@ -870,19 +870,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="15.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="14.0"/>
       <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -892,14 +887,13 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
       <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -911,7 +905,7 @@
     <font/>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
@@ -922,10 +916,9 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -934,13 +927,15 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="9.0"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -952,6 +947,11 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -981,14 +981,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B2A4A"/>
-        <bgColor rgb="FF0B2A4A"/>
+        <fgColor rgb="FF16406B"/>
+        <bgColor rgb="FF16406B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16406B"/>
-        <bgColor rgb="FF16406B"/>
+        <fgColor rgb="FF0B2A4A"/>
+        <bgColor rgb="FF0B2A4A"/>
       </patternFill>
     </fill>
     <fill>
@@ -1014,16 +1014,16 @@
     <border/>
     <border>
       <left/>
-      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <top/>
       <bottom/>
     </border>
     <border>
       <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
+      <right/>
       <top/>
       <bottom/>
     </border>
@@ -1079,85 +1079,85 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1169,10 +1169,10 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1513,329 +1513,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="str">
+      <c r="A3" s="9" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 21/09/2026</v>
+        <v> Actualizado al: 24/09/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="10"/>
+      <c r="E5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="12"/>
-      <c r="E5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="12"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="20">
+      <c r="A6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="18">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="I6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="K6" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="L6" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="21" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="24">
+      <c r="B7" s="15"/>
+      <c r="C7" s="21">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3475609756</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="27">
+        <v>0.3548780488</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.6583333333</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="20">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>14</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="27">
+        <v>15</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.525</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="20">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
-        <v>27</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="27">
+        <v>26</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="20">
+      <c r="A10" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.252173913</v>
-      </c>
-      <c r="H10" s="27">
+        <v>0.2652173913</v>
+      </c>
+      <c r="H10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>4</v>
-      </c>
-      <c r="I10" s="27">
+        <v>5</v>
+      </c>
+      <c r="I10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="20">
+      <c r="A11" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="27">
+      <c r="E11" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3416666667</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="20">
+      <c r="A12" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
         <v>34</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="28">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="20">
+      <c r="A13" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F13" s="43">
         <f>SUM(F7:F12)</f>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="G13" s="44">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3475609756</v>
+        <v>0.3548780488</v>
       </c>
       <c r="H13" s="43">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="43">
         <f t="shared" si="1"/>
@@ -1867,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="20">
+      <c r="A14" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
         <v>7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="20">
+      <c r="A15" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="12"/>
+      <c r="E18" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19">
       <c r="E19" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="27">
+      <c r="E20" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
-        <v>27</v>
-      </c>
-      <c r="G20" s="31">
+        <v>26</v>
+      </c>
+      <c r="G20" s="28">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.6585365854</v>
+        <v>0.6341463415</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
+        <v>8</v>
+      </c>
+      <c r="G21" s="28">
+        <f t="shared" si="2"/>
+        <v>0.1951219512</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="E22" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="24">
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="E23" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="24">
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
         <v>7</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G23" s="28">
         <f t="shared" si="2"/>
         <v>0.1707317073</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="27">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="E24" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="24">
+        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G24" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="27">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
-        <v>7</v>
-      </c>
-      <c r="G23" s="31">
-        <f t="shared" si="2"/>
-        <v>0.1707317073</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="27">
-        <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="31">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2983,370 +2983,370 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>3</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
-        <v>19</v>
+      <c r="A4" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>21</v>
+      <c r="A5" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>26</v>
+      <c r="A6" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>28</v>
+      <c r="A7" s="11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="12"/>
+      <c r="A9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>44</v>
+      <c r="A10" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="s">
-        <v>52</v>
+      <c r="A11" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
+    <row r="15">
+      <c r="A15" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
+    <row r="17">
+      <c r="A17" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>66</v>
+      <c r="A21" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>68</v>
+      <c r="A22" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="13" t="s">
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="13" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="13" t="s">
-        <v>91</v>
+      <c r="A30" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="12"/>
+      <c r="A32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="13" t="s">
-        <v>100</v>
+      <c r="A33" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="13" t="s">
-        <v>104</v>
+      <c r="A34" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="13" t="s">
-        <v>108</v>
+      <c r="A35" s="11" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="13" t="s">
-        <v>112</v>
+      <c r="A36" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="13" t="s">
-        <v>114</v>
+      <c r="A37" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="12"/>
+      <c r="A39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="10"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="13" t="s">
-        <v>121</v>
+      <c r="A40" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="13" t="s">
-        <v>122</v>
+      <c r="A41" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="13" t="s">
-        <v>124</v>
+      <c r="A42" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13" t="s">
-        <v>126</v>
+      <c r="A43" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="13" t="s">
-        <v>127</v>
+      <c r="A44" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="10"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="34" t="s">
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" s="34" t="s">
+      <c r="C51" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="34" t="s">
+      <c r="A54" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" s="34" t="s">
+      <c r="A55" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
+      <c r="A56" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="34" t="s">
+      <c r="A57" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="32" t="s">
+      <c r="A58" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4370,245 +4370,245 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
+      <c r="K2" s="5"/>
+      <c r="L2" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="8">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="12">
         <v>0.0</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="8">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="12">
         <v>0.4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="5">
         <v>0.5</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="5">
         <v>1.0</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5">
         <v>0.15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
+      <c r="K8" s="5"/>
+      <c r="L8" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="3"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="8">
+        <v>52</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="12">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5633,204 +5633,204 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="10"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="9"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="12"/>
+      <c r="A2" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" s="7"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" s="7"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="10"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="22" t="s">
+      <c r="A3" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="N3" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="O3" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="S3" s="22" t="s">
+      <c r="I3" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="J3" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="K3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="V3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="W3" s="22" t="s">
+      <c r="L3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="M3" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="X3" s="22" t="s">
+      <c r="N3" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="O3" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA3" s="22" t="s">
+      <c r="Q3" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="AB3" s="22" t="s">
+      <c r="S3" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="AC3" s="22" t="s">
+      <c r="T3" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="U3" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="AD3" s="22" t="s">
+      <c r="V3" s="25" t="s">
         <v>119</v>
       </c>
+      <c r="W3" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="29" t="s">
+      <c r="A4" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="33" t="s">
+      <c r="C4" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>27</v>
+      <c r="D4" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J4" s="36">
         <v>46268.0</v>
@@ -5838,8 +5838,8 @@
       <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="26" t="s">
-        <v>27</v>
+      <c r="L4" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M4" s="36">
         <v>46268.0</v>
@@ -5847,8 +5847,8 @@
       <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>27</v>
+      <c r="O4" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P4" s="36">
         <v>46268.0</v>
@@ -5856,17 +5856,17 @@
       <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="R4" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
-      <c r="X4" s="26">
+      <c r="X4" s="31">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,43 +5882,43 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="26" t="str">
+      <c r="AB4" s="31" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="26" t="str">
+      <c r="AC4" s="31" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="28"/>
+      <c r="AD4" s="32"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="28" t="s">
+      <c r="A5" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="B5" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>22</v>
+      <c r="D5" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J5" s="41">
         <v>46282.0</v>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="26" t="s">
+      <c r="U5" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V5" s="36"/>
       <c r="W5" s="36"/>
-      <c r="X5" s="26">
+      <c r="X5" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -5960,43 +5960,43 @@
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AB5" s="31">
         <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
-      <c r="AC5" s="26" t="str">
+        <v>-7</v>
+      </c>
+      <c r="AC5" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD5" s="28"/>
+      <c r="AD5" s="32"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="A6" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="33" t="s">
+      <c r="C6" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>27</v>
+      <c r="D6" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J6" s="36">
         <v>46268.0</v>
@@ -6004,8 +6004,8 @@
       <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>27</v>
+      <c r="L6" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M6" s="36">
         <v>46268.0</v>
@@ -6013,8 +6013,8 @@
       <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="26" t="s">
-        <v>27</v>
+      <c r="O6" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P6" s="36">
         <v>46268.0</v>
@@ -6022,17 +6022,17 @@
       <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="R6" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="26" t="s">
+      <c r="U6" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V6" s="36"/>
       <c r="W6" s="36"/>
-      <c r="X6" s="26">
+      <c r="X6" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6048,43 +6048,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="26" t="str">
+      <c r="AB6" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="26" t="str">
+      <c r="AC6" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="28"/>
+      <c r="AD6" s="32"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="29" t="s">
+      <c r="A7" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="33" t="s">
+      <c r="C7" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>27</v>
+      <c r="D7" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J7" s="36">
         <v>46268.0</v>
@@ -6092,8 +6092,8 @@
       <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="26" t="s">
-        <v>27</v>
+      <c r="L7" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M7" s="36">
         <v>46268.0</v>
@@ -6101,8 +6101,8 @@
       <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>27</v>
+      <c r="O7" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P7" s="36">
         <v>46268.0</v>
@@ -6110,17 +6110,17 @@
       <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="26" t="s">
+      <c r="R7" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
-      <c r="U7" s="26" t="s">
+      <c r="U7" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V7" s="36"/>
       <c r="W7" s="36"/>
-      <c r="X7" s="26">
+      <c r="X7" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6136,43 +6136,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="26" t="str">
+      <c r="AB7" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="26" t="str">
+      <c r="AC7" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="28"/>
+      <c r="AD7" s="32"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="29" t="s">
+      <c r="A8" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="33" t="s">
+      <c r="C8" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>27</v>
+      <c r="D8" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J8" s="41">
         <v>46282.0</v>
@@ -6180,8 +6180,8 @@
       <c r="K8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="L8" s="26" t="s">
-        <v>27</v>
+      <c r="L8" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M8" s="41">
         <v>46283.0</v>
@@ -6189,8 +6189,8 @@
       <c r="N8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="O8" s="26" t="s">
-        <v>27</v>
+      <c r="O8" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P8" s="41">
         <v>46283.0</v>
@@ -6198,17 +6198,17 @@
       <c r="Q8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="R8" s="26" t="s">
+      <c r="R8" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
-      <c r="U8" s="26" t="s">
+      <c r="U8" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
-      <c r="X8" s="26">
+      <c r="X8" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6224,43 +6224,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="26" t="str">
+      <c r="AB8" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="26" t="str">
+      <c r="AC8" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="28"/>
+      <c r="AD8" s="32"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="B9" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>27</v>
+      <c r="E9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J9" s="36">
         <v>46274.0</v>
@@ -6269,7 +6269,7 @@
         <v>46274.0</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M9" s="36">
         <v>46277.0</v>
@@ -6278,7 +6278,7 @@
         <v>46277.0</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P9" s="36">
         <v>46277.0</v>
@@ -6286,17 +6286,17 @@
       <c r="Q9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="26" t="s">
+      <c r="R9" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
-      <c r="U9" s="26" t="s">
+      <c r="U9" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V9" s="36"/>
       <c r="W9" s="36"/>
-      <c r="X9" s="26">
+      <c r="X9" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6312,43 +6312,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="26" t="str">
+      <c r="AB9" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="26" t="str">
+      <c r="AC9" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="28"/>
+      <c r="AD9" s="32"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>23</v>
+      <c r="E10" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>22</v>
+      <c r="H10" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J10" s="36">
         <v>46272.0</v>
@@ -6357,7 +6357,7 @@
         <v>46272.0</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M10" s="41">
         <v>46277.0</v>
@@ -6372,17 +6372,17 @@
         <v>46277.0</v>
       </c>
       <c r="Q10" s="36"/>
-      <c r="R10" s="26" t="s">
+      <c r="R10" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
-      <c r="U10" s="26" t="s">
+      <c r="U10" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="36"/>
-      <c r="X10" s="26">
+      <c r="X10" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6398,43 +6398,43 @@
         <f t="shared" si="2"/>
         <v>46272</v>
       </c>
-      <c r="AB10" s="26">
+      <c r="AB10" s="31">
         <f t="shared" si="3"/>
-        <v>-14</v>
-      </c>
-      <c r="AC10" s="26" t="str">
+        <v>-17</v>
+      </c>
+      <c r="AC10" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD10" s="28"/>
+      <c r="AD10" s="32"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="30" t="s">
+      <c r="E11" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>27</v>
+      <c r="H11" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J11" s="36">
         <v>46268.0</v>
@@ -6442,8 +6442,8 @@
       <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>27</v>
+      <c r="L11" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M11" s="36">
         <v>46269.0</v>
@@ -6451,8 +6451,8 @@
       <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="26" t="s">
-        <v>27</v>
+      <c r="O11" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P11" s="36">
         <v>46269.0</v>
@@ -6460,17 +6460,17 @@
       <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="26" t="s">
+      <c r="R11" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
-      <c r="U11" s="26" t="s">
+      <c r="U11" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V11" s="36"/>
       <c r="W11" s="36"/>
-      <c r="X11" s="26">
+      <c r="X11" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6486,43 +6486,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="26" t="str">
+      <c r="AB11" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="26" t="str">
+      <c r="AC11" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="28"/>
+      <c r="AD11" s="32"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="A12" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="29" t="s">
-        <v>31</v>
+      <c r="E12" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>27</v>
+      <c r="H12" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J12" s="36">
         <v>46274.0</v>
@@ -6530,31 +6530,31 @@
       <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="26" t="s">
-        <v>18</v>
+      <c r="L12" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="M12" s="36">
         <v>46277.0</v>
       </c>
       <c r="N12" s="36"/>
-      <c r="O12" s="26" t="s">
+      <c r="O12" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P12" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q12" s="36"/>
-      <c r="R12" s="26" t="s">
+      <c r="R12" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="26" t="s">
+      <c r="U12" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V12" s="36"/>
       <c r="W12" s="36"/>
-      <c r="X12" s="26">
+      <c r="X12" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6570,73 +6570,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="31">
         <f t="shared" si="3"/>
-        <v>-9</v>
-      </c>
-      <c r="AC12" s="26" t="str">
+        <v>-12</v>
+      </c>
+      <c r="AC12" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD12" s="28"/>
+      <c r="AD12" s="32"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>31</v>
+      <c r="E13" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>18</v>
+      <c r="H13" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J13" s="36">
         <v>46277.0</v>
       </c>
       <c r="K13" s="36"/>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M13" s="36">
         <v>46277.0</v>
       </c>
       <c r="N13" s="36"/>
-      <c r="O13" s="26" t="s">
+      <c r="O13" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P13" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q13" s="36"/>
-      <c r="R13" s="26" t="s">
+      <c r="R13" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
-      <c r="U13" s="26" t="s">
+      <c r="U13" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V13" s="36"/>
       <c r="W13" s="36"/>
-      <c r="X13" s="26">
+      <c r="X13" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6652,73 +6652,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="26">
+      <c r="AB13" s="31">
         <f t="shared" si="3"/>
-        <v>-9</v>
-      </c>
-      <c r="AC13" s="26" t="str">
+        <v>-12</v>
+      </c>
+      <c r="AC13" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD13" s="28"/>
+      <c r="AD13" s="32"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>31</v>
+      <c r="E14" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>18</v>
+      <c r="H14" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J14" s="36">
         <v>46277.0</v>
       </c>
       <c r="K14" s="36"/>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M14" s="36">
         <v>46283.0</v>
       </c>
       <c r="N14" s="36"/>
-      <c r="O14" s="26" t="s">
+      <c r="O14" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P14" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q14" s="36"/>
-      <c r="R14" s="26" t="s">
+      <c r="R14" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S14" s="36"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="26" t="s">
+      <c r="U14" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V14" s="36"/>
       <c r="W14" s="36"/>
-      <c r="X14" s="26">
+      <c r="X14" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6734,73 +6734,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB14" s="26">
+      <c r="AB14" s="31">
         <f t="shared" si="3"/>
-        <v>-9</v>
-      </c>
-      <c r="AC14" s="26" t="str">
+        <v>-12</v>
+      </c>
+      <c r="AC14" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD14" s="28"/>
+      <c r="AD14" s="32"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="33" t="s">
+      <c r="E15" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>22</v>
+      <c r="H15" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" s="36">
         <v>46283.0</v>
       </c>
       <c r="K15" s="36"/>
       <c r="L15" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M15" s="36">
         <v>46283.0</v>
       </c>
       <c r="N15" s="36"/>
-      <c r="O15" s="26" t="s">
+      <c r="O15" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P15" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q15" s="36"/>
-      <c r="R15" s="26" t="s">
+      <c r="R15" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S15" s="36"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="26" t="s">
+      <c r="U15" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V15" s="36"/>
       <c r="W15" s="36"/>
-      <c r="X15" s="26">
+      <c r="X15" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6816,73 +6816,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC15" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC15" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD15" s="28"/>
+      <c r="AD15" s="32"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="33" t="s">
+      <c r="E16" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="26" t="s">
-        <v>22</v>
+      <c r="H16" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J16" s="36">
         <v>46283.0</v>
       </c>
       <c r="K16" s="36"/>
       <c r="L16" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M16" s="36">
         <v>46283.0</v>
       </c>
       <c r="N16" s="36"/>
-      <c r="O16" s="26" t="s">
+      <c r="O16" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P16" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q16" s="36"/>
-      <c r="R16" s="26" t="s">
+      <c r="R16" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S16" s="36"/>
       <c r="T16" s="36"/>
-      <c r="U16" s="26" t="s">
+      <c r="U16" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V16" s="36"/>
       <c r="W16" s="36"/>
-      <c r="X16" s="26">
+      <c r="X16" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6898,73 +6898,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="26">
+      <c r="AB16" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC16" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC16" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD16" s="28"/>
+      <c r="AD16" s="32"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="33" t="s">
+      <c r="E17" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>22</v>
+      <c r="H17" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="36">
         <v>46283.0</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M17" s="36">
         <v>46283.0</v>
       </c>
       <c r="N17" s="36"/>
-      <c r="O17" s="26" t="s">
+      <c r="O17" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P17" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q17" s="36"/>
-      <c r="R17" s="26" t="s">
+      <c r="R17" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
-      <c r="U17" s="26" t="s">
+      <c r="U17" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="36"/>
-      <c r="X17" s="26">
+      <c r="X17" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6980,73 +6980,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="26">
+      <c r="AB17" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC17" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC17" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD17" s="28"/>
+      <c r="AD17" s="32"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="33" t="s">
+      <c r="E18" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>18</v>
+      <c r="H18" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J18" s="36">
         <v>46283.0</v>
       </c>
       <c r="K18" s="36"/>
-      <c r="L18" s="26" t="s">
+      <c r="L18" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M18" s="36">
         <v>46283.0</v>
       </c>
       <c r="N18" s="36"/>
-      <c r="O18" s="26" t="s">
+      <c r="O18" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P18" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q18" s="36"/>
-      <c r="R18" s="26" t="s">
+      <c r="R18" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
-      <c r="U18" s="26" t="s">
+      <c r="U18" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V18" s="36"/>
       <c r="W18" s="36"/>
-      <c r="X18" s="26">
+      <c r="X18" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7062,73 +7062,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="26">
+      <c r="AB18" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC18" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC18" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD18" s="28"/>
+      <c r="AD18" s="32"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="33" t="s">
+      <c r="E19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="26" t="s">
-        <v>22</v>
+      <c r="H19" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J19" s="36">
         <v>46283.0</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M19" s="36">
         <v>46283.0</v>
       </c>
       <c r="N19" s="36"/>
-      <c r="O19" s="26" t="s">
+      <c r="O19" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P19" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q19" s="36"/>
-      <c r="R19" s="26" t="s">
+      <c r="R19" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S19" s="36"/>
       <c r="T19" s="36"/>
-      <c r="U19" s="26" t="s">
+      <c r="U19" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V19" s="36"/>
       <c r="W19" s="36"/>
-      <c r="X19" s="26">
+      <c r="X19" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7144,73 +7144,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="26">
+      <c r="AB19" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC19" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC19" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD19" s="28"/>
+      <c r="AD19" s="32"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="33" t="s">
+      <c r="E20" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>18</v>
+      <c r="H20" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J20" s="36">
         <v>46283.0</v>
       </c>
       <c r="K20" s="36"/>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M20" s="36">
         <v>46283.0</v>
       </c>
       <c r="N20" s="36"/>
-      <c r="O20" s="26" t="s">
+      <c r="O20" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P20" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="26" t="s">
+      <c r="R20" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S20" s="36"/>
       <c r="T20" s="36"/>
-      <c r="U20" s="26" t="s">
+      <c r="U20" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="36"/>
-      <c r="X20" s="26">
+      <c r="X20" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7226,155 +7226,155 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="26">
+      <c r="AB20" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC20" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC20" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD20" s="28"/>
+      <c r="AD20" s="32"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="33" t="s">
+      <c r="E21" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>18</v>
+      <c r="H21" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>29</v>
       </c>
       <c r="J21" s="36">
         <v>46283.0</v>
       </c>
       <c r="K21" s="36"/>
-      <c r="L21" s="26" t="s">
-        <v>13</v>
+      <c r="L21" s="40" t="s">
+        <v>21</v>
       </c>
       <c r="M21" s="36">
         <v>46283.0</v>
       </c>
       <c r="N21" s="36"/>
-      <c r="O21" s="26" t="s">
+      <c r="O21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P21" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q21" s="36"/>
-      <c r="R21" s="26" t="s">
+      <c r="R21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S21" s="36"/>
       <c r="T21" s="36"/>
-      <c r="U21" s="26" t="s">
+      <c r="U21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V21" s="36"/>
       <c r="W21" s="36"/>
-      <c r="X21" s="26">
+      <c r="X21" s="31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" s="37" t="str">
         <f t="array" ref="Y21">INDEX(Cat_Etapas,$X21)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z21" s="38">
         <f t="array" ref="Z21">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I21,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L21,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O21,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R21,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U21,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA21" s="39">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="26">
+      <c r="AB21" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC21" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC21" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD21" s="28"/>
+      <c r="AD21" s="32"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="33" t="s">
+      <c r="E22" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>18</v>
+      <c r="H22" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J22" s="36">
         <v>46283.0</v>
       </c>
       <c r="K22" s="36"/>
-      <c r="L22" s="26" t="s">
+      <c r="L22" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M22" s="36">
         <v>46283.0</v>
       </c>
       <c r="N22" s="36"/>
-      <c r="O22" s="26" t="s">
+      <c r="O22" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P22" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q22" s="36"/>
-      <c r="R22" s="26" t="s">
+      <c r="R22" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S22" s="36"/>
       <c r="T22" s="36"/>
-      <c r="U22" s="26" t="s">
+      <c r="U22" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V22" s="36"/>
       <c r="W22" s="36"/>
-      <c r="X22" s="26">
+      <c r="X22" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7390,73 +7390,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="26">
+      <c r="AB22" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC22" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC22" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD22" s="28"/>
+      <c r="AD22" s="32"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="33" t="s">
+      <c r="E23" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>18</v>
+      <c r="H23" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J23" s="36">
         <v>46283.0</v>
       </c>
       <c r="K23" s="36"/>
-      <c r="L23" s="26" t="s">
+      <c r="L23" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M23" s="36">
         <v>46283.0</v>
       </c>
       <c r="N23" s="36"/>
-      <c r="O23" s="26" t="s">
+      <c r="O23" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P23" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q23" s="36"/>
-      <c r="R23" s="26" t="s">
+      <c r="R23" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S23" s="36"/>
       <c r="T23" s="36"/>
-      <c r="U23" s="26" t="s">
+      <c r="U23" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V23" s="36"/>
       <c r="W23" s="36"/>
-      <c r="X23" s="26">
+      <c r="X23" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7472,73 +7472,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="26">
+      <c r="AB23" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC23" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC23" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD23" s="28"/>
+      <c r="AD23" s="32"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="33" t="s">
+      <c r="E24" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>18</v>
+      <c r="H24" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J24" s="36">
         <v>46283.0</v>
       </c>
       <c r="K24" s="36"/>
-      <c r="L24" s="26" t="s">
+      <c r="L24" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M24" s="36">
         <v>46283.0</v>
       </c>
       <c r="N24" s="36"/>
-      <c r="O24" s="26" t="s">
+      <c r="O24" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P24" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q24" s="36"/>
-      <c r="R24" s="26" t="s">
+      <c r="R24" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S24" s="36"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="26" t="s">
+      <c r="U24" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V24" s="36"/>
       <c r="W24" s="36"/>
-      <c r="X24" s="26">
+      <c r="X24" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7554,73 +7554,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="26">
+      <c r="AB24" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC24" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC24" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD24" s="28"/>
+      <c r="AD24" s="32"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="33" t="s">
+      <c r="E25" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>18</v>
+      <c r="H25" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J25" s="36">
         <v>46283.0</v>
       </c>
       <c r="K25" s="36"/>
-      <c r="L25" s="26" t="s">
+      <c r="L25" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M25" s="36">
         <v>46283.0</v>
       </c>
       <c r="N25" s="36"/>
-      <c r="O25" s="26" t="s">
+      <c r="O25" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P25" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q25" s="36"/>
-      <c r="R25" s="26" t="s">
+      <c r="R25" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S25" s="36"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="26" t="s">
+      <c r="U25" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V25" s="36"/>
       <c r="W25" s="36"/>
-      <c r="X25" s="26">
+      <c r="X25" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7636,73 +7636,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="26">
+      <c r="AB25" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC25" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC25" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD25" s="28"/>
+      <c r="AD25" s="32"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="33" t="s">
+      <c r="E26" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="33" t="s">
+      <c r="G26" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>18</v>
+      <c r="H26" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J26" s="36">
         <v>46283.0</v>
       </c>
       <c r="K26" s="36"/>
-      <c r="L26" s="26" t="s">
+      <c r="L26" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M26" s="36">
         <v>46283.0</v>
       </c>
       <c r="N26" s="36"/>
-      <c r="O26" s="26" t="s">
+      <c r="O26" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P26" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q26" s="36"/>
-      <c r="R26" s="26" t="s">
+      <c r="R26" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S26" s="36"/>
       <c r="T26" s="36"/>
-      <c r="U26" s="26" t="s">
+      <c r="U26" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V26" s="36"/>
       <c r="W26" s="36"/>
-      <c r="X26" s="26">
+      <c r="X26" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7718,73 +7718,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="26">
+      <c r="AB26" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC26" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC26" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD26" s="28"/>
+      <c r="AD26" s="32"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="33" t="s">
+      <c r="E27" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>18</v>
+      <c r="H27" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J27" s="36">
         <v>46283.0</v>
       </c>
       <c r="K27" s="36"/>
-      <c r="L27" s="26" t="s">
+      <c r="L27" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="36">
         <v>46283.0</v>
       </c>
       <c r="N27" s="36"/>
-      <c r="O27" s="26" t="s">
+      <c r="O27" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P27" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="26" t="s">
+      <c r="R27" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S27" s="36"/>
       <c r="T27" s="36"/>
-      <c r="U27" s="26" t="s">
+      <c r="U27" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V27" s="36"/>
       <c r="W27" s="36"/>
-      <c r="X27" s="26">
+      <c r="X27" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7800,73 +7800,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="26">
+      <c r="AB27" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC27" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC27" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD27" s="28"/>
+      <c r="AD27" s="32"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="33" t="s">
+      <c r="E28" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="33" t="s">
+      <c r="G28" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>18</v>
+      <c r="H28" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J28" s="36">
         <v>46283.0</v>
       </c>
       <c r="K28" s="36"/>
-      <c r="L28" s="26" t="s">
+      <c r="L28" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M28" s="36">
         <v>46283.0</v>
       </c>
       <c r="N28" s="36"/>
-      <c r="O28" s="26" t="s">
+      <c r="O28" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P28" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q28" s="36"/>
-      <c r="R28" s="26" t="s">
+      <c r="R28" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="36"/>
       <c r="T28" s="36"/>
-      <c r="U28" s="26" t="s">
+      <c r="U28" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V28" s="36"/>
       <c r="W28" s="36"/>
-      <c r="X28" s="26">
+      <c r="X28" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7882,73 +7882,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="26">
+      <c r="AB28" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC28" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC28" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD28" s="28"/>
+      <c r="AD28" s="32"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="33" t="s">
+      <c r="E29" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>18</v>
+      <c r="H29" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J29" s="36">
         <v>46283.0</v>
       </c>
       <c r="K29" s="36"/>
-      <c r="L29" s="26" t="s">
+      <c r="L29" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M29" s="36">
         <v>46283.0</v>
       </c>
       <c r="N29" s="36"/>
-      <c r="O29" s="26" t="s">
+      <c r="O29" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P29" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q29" s="36"/>
-      <c r="R29" s="26" t="s">
+      <c r="R29" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S29" s="36"/>
       <c r="T29" s="36"/>
-      <c r="U29" s="26" t="s">
+      <c r="U29" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V29" s="36"/>
       <c r="W29" s="36"/>
-      <c r="X29" s="26">
+      <c r="X29" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7964,73 +7964,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="26">
+      <c r="AB29" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC29" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC29" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD29" s="28"/>
+      <c r="AD29" s="32"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="33" t="s">
+      <c r="E30" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="33" t="s">
+      <c r="G30" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>18</v>
+      <c r="H30" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J30" s="36">
         <v>46283.0</v>
       </c>
       <c r="K30" s="36"/>
-      <c r="L30" s="26" t="s">
+      <c r="L30" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M30" s="36">
         <v>46283.0</v>
       </c>
       <c r="N30" s="36"/>
-      <c r="O30" s="26" t="s">
+      <c r="O30" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P30" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q30" s="36"/>
-      <c r="R30" s="26" t="s">
+      <c r="R30" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S30" s="36"/>
       <c r="T30" s="36"/>
-      <c r="U30" s="26" t="s">
+      <c r="U30" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V30" s="36"/>
       <c r="W30" s="36"/>
-      <c r="X30" s="26">
+      <c r="X30" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8046,73 +8046,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="26">
+      <c r="AB30" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC30" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC30" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD30" s="28"/>
+      <c r="AD30" s="32"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="33" t="s">
+      <c r="E31" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>18</v>
+      <c r="H31" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J31" s="36">
         <v>46283.0</v>
       </c>
       <c r="K31" s="36"/>
-      <c r="L31" s="26" t="s">
+      <c r="L31" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M31" s="36">
         <v>46283.0</v>
       </c>
       <c r="N31" s="36"/>
-      <c r="O31" s="26" t="s">
+      <c r="O31" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P31" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q31" s="36"/>
-      <c r="R31" s="26" t="s">
+      <c r="R31" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S31" s="36"/>
       <c r="T31" s="36"/>
-      <c r="U31" s="26" t="s">
+      <c r="U31" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V31" s="36"/>
       <c r="W31" s="36"/>
-      <c r="X31" s="26">
+      <c r="X31" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8128,73 +8128,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="26">
+      <c r="AB31" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC31" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC31" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD31" s="28"/>
+      <c r="AD31" s="32"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="33" t="s">
+      <c r="E32" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>18</v>
+      <c r="H32" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J32" s="36">
         <v>46283.0</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="26" t="s">
+      <c r="L32" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M32" s="36">
         <v>46283.0</v>
       </c>
       <c r="N32" s="36"/>
-      <c r="O32" s="26" t="s">
+      <c r="O32" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P32" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q32" s="36"/>
-      <c r="R32" s="26" t="s">
+      <c r="R32" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S32" s="36"/>
       <c r="T32" s="36"/>
-      <c r="U32" s="26" t="s">
+      <c r="U32" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V32" s="36"/>
       <c r="W32" s="36"/>
-      <c r="X32" s="26">
+      <c r="X32" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8210,73 +8210,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="26">
+      <c r="AB32" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC32" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC32" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD32" s="28"/>
+      <c r="AD32" s="32"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="33" t="s">
+      <c r="E33" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>18</v>
+      <c r="H33" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J33" s="36">
         <v>46283.0</v>
       </c>
       <c r="K33" s="36"/>
-      <c r="L33" s="26" t="s">
+      <c r="L33" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M33" s="36">
         <v>46283.0</v>
       </c>
       <c r="N33" s="36"/>
-      <c r="O33" s="26" t="s">
+      <c r="O33" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P33" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q33" s="36"/>
-      <c r="R33" s="26" t="s">
+      <c r="R33" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
-      <c r="U33" s="26" t="s">
+      <c r="U33" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V33" s="36"/>
       <c r="W33" s="36"/>
-      <c r="X33" s="26">
+      <c r="X33" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8292,73 +8292,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="26">
+      <c r="AB33" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC33" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC33" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD33" s="28"/>
+      <c r="AD33" s="32"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="33" t="s">
+      <c r="E34" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="33" t="s">
+      <c r="G34" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>18</v>
+      <c r="H34" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J34" s="36">
         <v>46283.0</v>
       </c>
       <c r="K34" s="36"/>
-      <c r="L34" s="26" t="s">
+      <c r="L34" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M34" s="36">
         <v>46283.0</v>
       </c>
       <c r="N34" s="36"/>
-      <c r="O34" s="26" t="s">
+      <c r="O34" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P34" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q34" s="36"/>
-      <c r="R34" s="26" t="s">
+      <c r="R34" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S34" s="36"/>
       <c r="T34" s="36"/>
-      <c r="U34" s="26" t="s">
+      <c r="U34" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V34" s="36"/>
       <c r="W34" s="36"/>
-      <c r="X34" s="26">
+      <c r="X34" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8374,73 +8374,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="26">
+      <c r="AB34" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC34" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC34" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD34" s="28"/>
+      <c r="AD34" s="32"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="33" t="s">
+      <c r="E35" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>18</v>
+      <c r="H35" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J35" s="36">
         <v>46283.0</v>
       </c>
       <c r="K35" s="36"/>
-      <c r="L35" s="26" t="s">
+      <c r="L35" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M35" s="36">
         <v>46283.0</v>
       </c>
       <c r="N35" s="36"/>
-      <c r="O35" s="26" t="s">
+      <c r="O35" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P35" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q35" s="36"/>
-      <c r="R35" s="26" t="s">
+      <c r="R35" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
-      <c r="U35" s="26" t="s">
+      <c r="U35" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V35" s="36"/>
       <c r="W35" s="36"/>
-      <c r="X35" s="26">
+      <c r="X35" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8456,73 +8456,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="26">
+      <c r="AB35" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC35" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC35" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD35" s="28"/>
+      <c r="AD35" s="32"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="33" t="s">
+      <c r="E36" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>18</v>
+      <c r="H36" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J36" s="36">
         <v>46283.0</v>
       </c>
       <c r="K36" s="36"/>
-      <c r="L36" s="26" t="s">
+      <c r="L36" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M36" s="36">
         <v>46283.0</v>
       </c>
       <c r="N36" s="36"/>
-      <c r="O36" s="26" t="s">
+      <c r="O36" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P36" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q36" s="36"/>
-      <c r="R36" s="26" t="s">
+      <c r="R36" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S36" s="36"/>
       <c r="T36" s="36"/>
-      <c r="U36" s="26" t="s">
+      <c r="U36" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V36" s="36"/>
       <c r="W36" s="36"/>
-      <c r="X36" s="26">
+      <c r="X36" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8538,73 +8538,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="26">
+      <c r="AB36" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC36" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC36" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD36" s="28"/>
+      <c r="AD36" s="32"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="33" t="s">
+      <c r="E37" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="33" t="s">
+      <c r="G37" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>18</v>
+      <c r="H37" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J37" s="36">
         <v>46283.0</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="26" t="s">
+      <c r="L37" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M37" s="36">
         <v>46283.0</v>
       </c>
       <c r="N37" s="36"/>
-      <c r="O37" s="26" t="s">
+      <c r="O37" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P37" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q37" s="36"/>
-      <c r="R37" s="26" t="s">
+      <c r="R37" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
-      <c r="U37" s="26" t="s">
+      <c r="U37" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V37" s="36"/>
       <c r="W37" s="36"/>
-      <c r="X37" s="26">
+      <c r="X37" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8620,43 +8620,43 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="26">
+      <c r="AB37" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC37" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC37" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD37" s="28"/>
+      <c r="AD37" s="32"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="33" t="s">
+      <c r="G38" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>27</v>
+      <c r="H38" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J38" s="41">
         <v>46277.0</v>
@@ -8664,31 +8664,31 @@
       <c r="K38" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="26" t="s">
-        <v>18</v>
+      <c r="L38" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="M38" s="36">
         <v>46283.0</v>
       </c>
       <c r="N38" s="36"/>
-      <c r="O38" s="26" t="s">
+      <c r="O38" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P38" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="26" t="s">
+      <c r="R38" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S38" s="36"/>
       <c r="T38" s="36"/>
-      <c r="U38" s="26" t="s">
+      <c r="U38" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V38" s="36"/>
       <c r="W38" s="36"/>
-      <c r="X38" s="26">
+      <c r="X38" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8704,73 +8704,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB38" s="26">
+      <c r="AB38" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC38" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC38" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD38" s="28"/>
+      <c r="AD38" s="32"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="26" t="s">
+      <c r="B39" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="30" t="s">
+      <c r="F39" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>18</v>
+      <c r="H39" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J39" s="36">
         <v>46283.0</v>
       </c>
       <c r="K39" s="36"/>
-      <c r="L39" s="26" t="s">
+      <c r="L39" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M39" s="36">
         <v>46283.0</v>
       </c>
       <c r="N39" s="36"/>
-      <c r="O39" s="26" t="s">
+      <c r="O39" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P39" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q39" s="36"/>
-      <c r="R39" s="26" t="s">
+      <c r="R39" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
-      <c r="U39" s="26" t="s">
+      <c r="U39" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V39" s="36"/>
       <c r="W39" s="36"/>
-      <c r="X39" s="26">
+      <c r="X39" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8786,73 +8786,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB39" s="26">
+      <c r="AB39" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC39" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC39" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD39" s="28"/>
+      <c r="AD39" s="32"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="26" t="s">
+      <c r="B40" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>18</v>
+      <c r="H40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J40" s="36">
         <v>46283.0</v>
       </c>
       <c r="K40" s="36"/>
-      <c r="L40" s="26" t="s">
+      <c r="L40" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M40" s="36">
         <v>46283.0</v>
       </c>
       <c r="N40" s="36"/>
-      <c r="O40" s="26" t="s">
+      <c r="O40" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P40" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q40" s="36"/>
-      <c r="R40" s="26" t="s">
+      <c r="R40" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
-      <c r="U40" s="26" t="s">
+      <c r="U40" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V40" s="36"/>
       <c r="W40" s="36"/>
-      <c r="X40" s="26">
+      <c r="X40" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8868,73 +8868,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB40" s="26">
+      <c r="AB40" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC40" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC40" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD40" s="28"/>
+      <c r="AD40" s="32"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="26" t="s">
+      <c r="B41" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="30" t="s">
+      <c r="F41" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>18</v>
+      <c r="H41" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J41" s="36">
         <v>46283.0</v>
       </c>
       <c r="K41" s="36"/>
-      <c r="L41" s="26" t="s">
+      <c r="L41" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M41" s="36">
         <v>46283.0</v>
       </c>
       <c r="N41" s="36"/>
-      <c r="O41" s="26" t="s">
+      <c r="O41" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P41" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q41" s="36"/>
-      <c r="R41" s="26" t="s">
+      <c r="R41" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
-      <c r="U41" s="26" t="s">
+      <c r="U41" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V41" s="36"/>
       <c r="W41" s="36"/>
-      <c r="X41" s="26">
+      <c r="X41" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8950,73 +8950,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB41" s="26">
+      <c r="AB41" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC41" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC41" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD41" s="28"/>
+      <c r="AD41" s="32"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="26" t="s">
+      <c r="B42" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>18</v>
+      <c r="H42" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="J42" s="36">
         <v>46283.0</v>
       </c>
       <c r="K42" s="36"/>
-      <c r="L42" s="26" t="s">
+      <c r="L42" s="31" t="s">
         <v>13</v>
       </c>
       <c r="M42" s="36">
         <v>46283.0</v>
       </c>
       <c r="N42" s="36"/>
-      <c r="O42" s="26" t="s">
+      <c r="O42" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P42" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q42" s="36"/>
-      <c r="R42" s="26" t="s">
+      <c r="R42" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S42" s="36"/>
       <c r="T42" s="36"/>
-      <c r="U42" s="26" t="s">
+      <c r="U42" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V42" s="36"/>
       <c r="W42" s="36"/>
-      <c r="X42" s="26">
+      <c r="X42" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -9032,43 +9032,43 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB42" s="26">
+      <c r="AB42" s="31">
         <f t="shared" si="3"/>
-        <v>-3</v>
-      </c>
-      <c r="AC42" s="26" t="str">
+        <v>-6</v>
+      </c>
+      <c r="AC42" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD42" s="28"/>
+      <c r="AD42" s="32"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="26" t="s">
+      <c r="B43" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="29" t="s">
+      <c r="E43" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="F43" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="33" t="s">
+      <c r="G43" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>27</v>
+      <c r="H43" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J43" s="41">
         <v>46277.0</v>
@@ -9076,8 +9076,8 @@
       <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="26" t="s">
-        <v>27</v>
+      <c r="L43" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="M43" s="41">
         <v>46277.0</v>
@@ -9085,8 +9085,8 @@
       <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="26" t="s">
-        <v>27</v>
+      <c r="O43" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="P43" s="36">
         <v>46276.0</v>
@@ -9094,17 +9094,17 @@
       <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="26" t="s">
+      <c r="R43" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
-      <c r="U43" s="26" t="s">
+      <c r="U43" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V43" s="36"/>
       <c r="W43" s="36"/>
-      <c r="X43" s="26">
+      <c r="X43" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9120,43 +9120,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="26" t="str">
+      <c r="AB43" s="31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="26" t="str">
+      <c r="AC43" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="28"/>
+      <c r="AD43" s="32"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G44" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>27</v>
+      <c r="F44" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="J44" s="41">
         <v>46277.0</v>
@@ -9164,29 +9164,29 @@
       <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="26" t="s">
-        <v>18</v>
+      <c r="L44" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="M44" s="36">
         <v>46276.0</v>
       </c>
       <c r="N44" s="36"/>
-      <c r="O44" s="26" t="s">
+      <c r="O44" s="31" t="s">
         <v>13</v>
       </c>
       <c r="P44" s="36"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="26" t="s">
+      <c r="R44" s="31" t="s">
         <v>13</v>
       </c>
       <c r="S44" s="36"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="26" t="s">
+      <c r="U44" s="31" t="s">
         <v>13</v>
       </c>
       <c r="V44" s="36"/>
       <c r="W44" s="36"/>
-      <c r="X44" s="26">
+      <c r="X44" s="31">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9202,15 +9202,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="26">
+      <c r="AB44" s="31">
         <f t="shared" si="3"/>
-        <v>-10</v>
-      </c>
-      <c r="AC44" s="26" t="str">
+        <v>-13</v>
+      </c>
+      <c r="AC44" s="31" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="28"/>
+      <c r="AD44" s="32"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -32,21 +32,30 @@
     <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
   </si>
   <si>
+    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
+  </si>
+  <si>
     <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
   </si>
   <si>
-    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
-  </si>
-  <si>
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
   <si>
     <t>1. ¿Qué se captura y qué se calcula solo?</t>
   </si>
   <si>
+    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
+  </si>
+  <si>
     <t>Estatus</t>
   </si>
   <si>
+    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
+  </si>
+  <si>
+    <t>INDICADORES CLAVE</t>
+  </si>
+  <si>
     <t>Factor avance</t>
   </si>
   <si>
@@ -56,25 +65,31 @@
     <t>Prioridad</t>
   </si>
   <si>
+    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+  </si>
+  <si>
     <t>Áreas / Frentes</t>
   </si>
   <si>
     <t>Etapas</t>
   </si>
   <si>
+    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
+  </si>
+  <si>
     <t>Peso etapa</t>
   </si>
   <si>
-    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
-  </si>
-  <si>
     <t>No iniciado</t>
   </si>
   <si>
-    <t>INDICADORES CLAVE</t>
-  </si>
-  <si>
-    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+  </si>
+  <si>
+    <t>AVANCE POR MÓDULO</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
   </si>
   <si>
     <t>Finanzas (R2R)</t>
@@ -89,13 +104,10 @@
     <t>1. Llenado de plantilla</t>
   </si>
   <si>
-    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
-  </si>
-  <si>
     <t>En proceso</t>
   </si>
   <si>
-    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
   </si>
   <si>
     <t>Compras (P2P)</t>
@@ -104,24 +116,27 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>AVANCE POR MÓDULO</t>
-  </si>
-  <si>
     <t>Compras / Abastecimiento</t>
   </si>
   <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
   </si>
   <si>
     <t>2. Revisión y validación</t>
   </si>
   <si>
+    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
+  </si>
+  <si>
     <t>Completado</t>
   </si>
   <si>
     <t>Ventas (O2C)</t>
   </si>
   <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
     <t>Media</t>
   </si>
   <si>
@@ -131,18 +146,33 @@
     <t>3. Carga en repositorio Oracle</t>
   </si>
   <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
+    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+  </si>
+  <si>
     <t>Bloqueado</t>
   </si>
   <si>
+    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+  </si>
+  <si>
     <t>Inventarios (D2B)</t>
   </si>
   <si>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
     <t>Almacén / Inventarios</t>
   </si>
   <si>
+    <t>3. Valores de estatus permitidos</t>
+  </si>
+  <si>
     <t>4. Ambiente Sandbox</t>
   </si>
   <si>
@@ -152,288 +182,258 @@
     <t>Manufactura (MFG)</t>
   </si>
   <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
-  </si>
-  <si>
     <t>Manufactura / Producción</t>
   </si>
   <si>
     <t>5. Ambiente Productivo</t>
   </si>
   <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+  </si>
+  <si>
+    <t>E1 · LLENADO</t>
   </si>
   <si>
     <t>Activos Fijos (FA)</t>
   </si>
   <si>
+    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
+  </si>
+  <si>
     <t>Activos Fijos / Patrimonio</t>
   </si>
   <si>
     <t>6. Cerrado</t>
   </si>
   <si>
-    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
-  </si>
-  <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
     <t>Capital Humano</t>
   </si>
   <si>
+    <t>E2 · REVISIÓN</t>
+  </si>
+  <si>
     <t>Suma de pesos (debe ser 100%)</t>
   </si>
   <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
-  </si>
-  <si>
-    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
-  </si>
-  <si>
-    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
-  </si>
-  <si>
-    <t>3. Valores de estatus permitidos</t>
-  </si>
-  <si>
-    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
-  </si>
-  <si>
-    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
-  </si>
-  <si>
     <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
   </si>
   <si>
+    <t>4. Lectura del semáforo</t>
+  </si>
+  <si>
+    <t>E3 · REPOSITORIO ORACLE</t>
+  </si>
+  <si>
+    <t>E4 · SANDBOX</t>
+  </si>
+  <si>
+    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
+  </si>
+  <si>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+  </si>
+  <si>
+    <t>E5 · PRODUCTIVO</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>SEGUIMIENTO AUTOMÁTICO</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
+  </si>
+  <si>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
+  </si>
+  <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
+    <t>E3 Repositorio OK</t>
+  </si>
+  <si>
+    <t>5. Conexión con el tablero HTML</t>
+  </si>
+  <si>
+    <t>E4 Sandbox OK</t>
+  </si>
+  <si>
+    <t>E5 Productivo OK</t>
+  </si>
+  <si>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>PMO / Consultoría</t>
   </si>
   <si>
-    <t>4. Lectura del semáforo</t>
-  </si>
-  <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
-  </si>
-  <si>
-    <t>Plantillas</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
-  </si>
-  <si>
-    <t>% Avance</t>
-  </si>
-  <si>
-    <t>E1 Llenado OK</t>
-  </si>
-  <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
-  </si>
-  <si>
-    <t>E2 Revisión OK</t>
-  </si>
-  <si>
-    <t>E3 Repositorio OK</t>
-  </si>
-  <si>
-    <t>E4 Sandbox OK</t>
-  </si>
-  <si>
-    <t>E5 Productivo OK</t>
-  </si>
-  <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
-  </si>
-  <si>
-    <t>Avance global ponderado</t>
-  </si>
-  <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
-  </si>
-  <si>
-    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
-  </si>
-  <si>
-    <t>5. Conexión con el tablero HTML</t>
-  </si>
-  <si>
     <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
-    <t>E1 · LLENADO</t>
-  </si>
-  <si>
     <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
   </si>
   <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Plantilla</t>
+  </si>
+  <si>
+    <t>Área Responsable</t>
+  </si>
+  <si>
     <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
   </si>
   <si>
+    <t>Key User</t>
+  </si>
+  <si>
     <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
   </si>
   <si>
+    <t>Consultor Oracle</t>
+  </si>
+  <si>
     <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
   </si>
   <si>
-    <t>E2 · REVISIÓN</t>
-  </si>
-  <si>
     <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
-    <t>E3 · REPOSITORIO ORACLE</t>
-  </si>
-  <si>
-    <t>E4 · SANDBOX</t>
+    <t>E1 Llenado</t>
+  </si>
+  <si>
+    <t>E1 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E1 F. Real</t>
+  </si>
+  <si>
+    <t>E2 Revisión</t>
+  </si>
+  <si>
+    <t>E2 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E2 F. Real</t>
   </si>
   <si>
     <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
   </si>
   <si>
+    <t>E3 Repositorio</t>
+  </si>
+  <si>
+    <t>E3 F. Compromiso</t>
+  </si>
+  <si>
     <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
   </si>
   <si>
-    <t>E5 · PRODUCTIVO</t>
+    <t>E3 F. Real</t>
+  </si>
+  <si>
+    <t>E4 Sandbox</t>
+  </si>
+  <si>
+    <t>E4 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E4 F. Real</t>
   </si>
   <si>
     <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
-    <t>SEGUIMIENTO AUTOMÁTICO</t>
+    <t>E5 Productivo</t>
+  </si>
+  <si>
+    <t>E5 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E5 F. Real</t>
   </si>
   <si>
     <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
   </si>
   <si>
+    <t>Etapa #</t>
+  </si>
+  <si>
+    <t>Etapa Actual</t>
+  </si>
+  <si>
     <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>Próx. Compromiso</t>
   </si>
   <si>
     <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Plantilla</t>
-  </si>
-  <si>
-    <t>Área Responsable</t>
-  </si>
-  <si>
-    <t>Key User</t>
-  </si>
-  <si>
-    <t>Consultor Oracle</t>
-  </si>
-  <si>
-    <t>E1 Llenado</t>
-  </si>
-  <si>
-    <t>E1 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E1 F. Real</t>
-  </si>
-  <si>
-    <t>E2 Revisión</t>
+    <t>Días Restantes</t>
+  </si>
+  <si>
+    <t>Semáforo</t>
+  </si>
+  <si>
+    <t>Observaciones / Bloqueos</t>
+  </si>
+  <si>
+    <t>FIN-01</t>
   </si>
   <si>
     <t>VTA-01</t>
   </si>
   <si>
-    <t>E2 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E2 F. Real</t>
-  </si>
-  <si>
-    <t>E3 Repositorio</t>
-  </si>
-  <si>
-    <t>E3 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E3 F. Real</t>
-  </si>
-  <si>
-    <t>E4 Sandbox</t>
-  </si>
-  <si>
-    <t>E4 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E4 F. Real</t>
-  </si>
-  <si>
-    <t>E5 Productivo</t>
-  </si>
-  <si>
-    <t>E5 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E5 F. Real</t>
-  </si>
-  <si>
-    <t>Etapa #</t>
-  </si>
-  <si>
-    <t>Etapa Actual</t>
-  </si>
-  <si>
-    <t>Próx. Compromiso</t>
-  </si>
-  <si>
-    <t>Días Restantes</t>
-  </si>
-  <si>
-    <t>Semáforo</t>
-  </si>
-  <si>
-    <t>Observaciones / Bloqueos</t>
-  </si>
-  <si>
-    <t>FIN-01</t>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Clases</t>
   </si>
   <si>
     <t>300 MX Clientes (Final)</t>
   </si>
   <si>
+    <t>Angelica Ramirez</t>
+  </si>
+  <si>
     <t>Itzel Bárcena</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Revisor / Consultor</t>
   </si>
   <si>
     <t>Brandon Hernández</t>
   </si>
   <si>
-    <t>ESTEVEZ - Clases</t>
-  </si>
-  <si>
-    <t>Angelica Ramirez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
@@ -458,64 +458,64 @@
     <t>Llenado en proceso</t>
   </si>
   <si>
+    <t>FIN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+  </si>
+  <si>
     <t>Sin iniciar</t>
   </si>
   <si>
-    <t>FIN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
-  </si>
-  <si>
     <t>Bloqueadas</t>
   </si>
   <si>
+    <t>FIN-03</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Departamentos</t>
+  </si>
+  <si>
     <t>Vencidas</t>
   </si>
   <si>
-    <t>FIN-03</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Departamentos</t>
+    <t>FIN-04</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
     <t>En riesgo (≤7 días)</t>
   </si>
   <si>
+    <t>FIN-05</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>FIN-04</t>
+    <t>ESTEVEZ - Ubicaciones</t>
   </si>
   <si>
     <t>Sin fecha compromiso</t>
   </si>
   <si>
-    <t>ESTEVEZ - Plantilla Subsidiarias</t>
-  </si>
-  <si>
     <t>Cerradas (productivo)</t>
   </si>
   <si>
     <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
   </si>
   <si>
+    <t>FIN-06</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Impuestos y Retenciones MX</t>
+  </si>
+  <si>
     <t>Etapa</t>
   </si>
   <si>
     <t>% del total</t>
-  </si>
-  <si>
-    <t>FIN-05</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Ubicaciones</t>
-  </si>
-  <si>
-    <t>FIN-06</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Impuestos y Retenciones MX</t>
   </si>
   <si>
     <t>CMP-01</t>
@@ -875,14 +875,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -904,26 +904,15 @@
     </font>
     <font/>
     <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9.0"/>
-      <color theme="1"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -939,6 +928,22 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -947,11 +952,6 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F4E79"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1022,12 +1022,12 @@
       <bottom/>
     </border>
     <border>
-      <left/>
       <right/>
       <top/>
       <bottom/>
     </border>
     <border>
+      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -1080,84 +1080,84 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1169,10 +1169,10 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1518,24 +1518,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
+      <c r="A3" s="8" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 24/09/2026</v>
+        <v> Actualizado al: 03/10/2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="10"/>
+      <c r="C5" s="9"/>
       <c r="E5" s="13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -1543,299 +1543,299 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="18">
+      <c r="B6" s="17"/>
+      <c r="C6" s="20">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" s="19" t="s">
+      <c r="E6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>74</v>
       </c>
+      <c r="G6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="21">
+      <c r="A7" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="24">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3548780488</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="24">
+        <v>0.3682926829</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.6583333333</v>
-      </c>
-      <c r="H7" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>5</v>
-      </c>
-      <c r="I7" s="24">
+        <v>6</v>
+      </c>
+      <c r="I7" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
-        <v>5</v>
-      </c>
-      <c r="J7" s="24">
+        <v>6</v>
+      </c>
+      <c r="J7" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>5</v>
-      </c>
-      <c r="K7" s="24">
+        <v>6</v>
+      </c>
+      <c r="K7" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="18">
+      <c r="B8" s="17"/>
+      <c r="C8" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>15</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="24">
+        <v>16</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.525</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="18">
+      <c r="B9" s="17"/>
+      <c r="C9" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
-        <v>26</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="24">
+        <v>25</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="18">
+      <c r="A10" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="24">
+      <c r="E10" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.2652173913</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="18">
+      <c r="B11" s="17"/>
+      <c r="C11" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="24">
+      <c r="E11" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.3416666667</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="18">
+      <c r="A12" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
-        <v>34</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="24">
+        <v>33</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="28">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="33">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="28">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="18">
+      <c r="A13" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F13" s="43">
         <f>SUM(F7:F12)</f>
@@ -1843,19 +1843,19 @@
       </c>
       <c r="G13" s="44">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3548780488</v>
+        <v>0.3682926829</v>
       </c>
       <c r="H13" s="43">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="43">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" s="43">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="43">
         <f t="shared" si="1"/>
@@ -1867,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="18">
+      <c r="A14" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="18">
+      <c r="A15" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
+      <c r="G18" s="9"/>
     </row>
     <row r="19">
       <c r="E19" s="45" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="24">
+      <c r="E20" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
-        <v>26</v>
-      </c>
-      <c r="G20" s="28">
+        <v>25</v>
+      </c>
+      <c r="G20" s="33">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.6341463415</v>
+        <v>0.6097560976</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="24">
+      <c r="E21" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
         <v>8</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="33">
         <f t="shared" si="2"/>
         <v>0.1951219512</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="24">
+      <c r="E22" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="24">
+      <c r="E23" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
-        <v>7</v>
-      </c>
-      <c r="G23" s="28">
+        <v>8</v>
+      </c>
+      <c r="G23" s="33">
         <f t="shared" si="2"/>
-        <v>0.1707317073</v>
+        <v>0.1951219512</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="24">
+      <c r="E24" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="24">
+      <c r="E25" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="28">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2983,8 +2983,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2995,86 +2995,86 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="10"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="10"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -3089,139 +3089,139 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="10"/>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
-      <c r="F39" s="10"/>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="11" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="10"/>
+      <c r="F46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="27" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D47" s="30"/>
       <c r="E47" s="30"/>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="27" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D48" s="30"/>
       <c r="E48" s="30"/>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="27" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D49" s="30"/>
       <c r="E49" s="30"/>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="27" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D50" s="30"/>
       <c r="E50" s="30"/>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D51" s="30"/>
       <c r="E51" s="30"/>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="30"/>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="27" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
@@ -3295,7 +3295,7 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>136</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="27" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C55" s="29" t="s">
         <v>137</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="27" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C57" s="29" t="s">
         <v>138</v>
@@ -4386,83 +4386,83 @@
       <c r="L1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="8" t="s">
-        <v>7</v>
+      <c r="D2" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="8" t="s">
-        <v>8</v>
+      <c r="F2" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="8" t="s">
-        <v>9</v>
+      <c r="H2" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="8" t="s">
-        <v>10</v>
+      <c r="J2" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="8" t="s">
-        <v>11</v>
+      <c r="L2" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="12">
+        <v>17</v>
+      </c>
+      <c r="B3" s="14">
         <v>0.0</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>17</v>
+      <c r="F3" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="12">
+      <c r="L3" s="14">
         <v>0.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" s="5">
         <v>0.5</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5">
@@ -4471,26 +4471,26 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" s="5">
         <v>1.0</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5">
@@ -4499,26 +4499,26 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B6" s="5">
         <v>0.0</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5">
@@ -4527,24 +4527,24 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B7" s="5">
         <v>1.0</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5">
@@ -4556,17 +4556,17 @@
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5">
@@ -4582,14 +4582,14 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="16" t="s">
-        <v>52</v>
+      <c r="J9" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="12">
+      <c r="L9" s="14">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
@@ -4603,7 +4603,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -5633,8 +5633,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>54</v>
+      <c r="A1" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5664,11 +5664,11 @@
       <c r="AA1" s="7"/>
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
-      <c r="AD1" s="10"/>
+      <c r="AD1" s="9"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>79</v>
+      <c r="A2" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5676,161 +5676,161 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="22" t="s">
-        <v>82</v>
+      <c r="H2" s="9"/>
+      <c r="I2" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="J2" s="7"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="22" t="s">
-        <v>87</v>
+      <c r="K2" s="9"/>
+      <c r="L2" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="M2" s="7"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="22" t="s">
-        <v>89</v>
+      <c r="N2" s="9"/>
+      <c r="O2" s="18" t="s">
+        <v>66</v>
       </c>
       <c r="P2" s="7"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="22" t="s">
-        <v>90</v>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="S2" s="7"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="22" t="s">
-        <v>93</v>
+      <c r="T2" s="9"/>
+      <c r="U2" s="18" t="s">
+        <v>72</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="20" t="s">
-        <v>95</v>
+      <c r="W2" s="9"/>
+      <c r="X2" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
-      <c r="AD2" s="10"/>
+      <c r="AD2" s="9"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="25" t="s">
+      <c r="A3" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="K3" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="L3" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="M3" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="N3" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="J3" s="25" t="s">
+      <c r="O3" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="P3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="L3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="M3" s="25" t="s">
+      <c r="Q3" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="R3" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="S3" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="T3" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="P3" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q3" s="25" t="s">
+      <c r="U3" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="V3" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="W3" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="T3" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="25" t="s">
+      <c r="X3" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="V3" s="25" t="s">
+      <c r="Y3" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="X3" s="25" t="s">
+      <c r="Z3" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA3" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="Y3" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA3" s="25" t="s">
+      <c r="AB3" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AC3" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="AC3" s="25" t="s">
+      <c r="AD3" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="25" t="s">
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4" s="26" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>18</v>
+      <c r="B4" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>29</v>
+      <c r="H4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J4" s="36">
         <v>46268.0</v>
@@ -5838,8 +5838,8 @@
       <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="31" t="s">
-        <v>29</v>
+      <c r="L4" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="M4" s="36">
         <v>46268.0</v>
@@ -5847,8 +5847,8 @@
       <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="31" t="s">
-        <v>29</v>
+      <c r="O4" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="P4" s="36">
         <v>46268.0</v>
@@ -5856,17 +5856,17 @@
       <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="31" t="s">
-        <v>13</v>
+      <c r="R4" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
-      <c r="U4" s="31" t="s">
-        <v>13</v>
+      <c r="U4" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
-      <c r="X4" s="31">
+      <c r="X4" s="26">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,121 +5882,123 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="31" t="str">
+      <c r="AB4" s="26" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="31" t="str">
+      <c r="AC4" s="26" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="32"/>
+      <c r="AD4" s="31"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>18</v>
+      <c r="E5" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="31" t="s">
-        <v>24</v>
+      <c r="H5" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="41">
         <v>46282.0</v>
       </c>
-      <c r="K5" s="41"/>
+      <c r="K5" s="41">
+        <v>46298.0</v>
+      </c>
       <c r="L5" s="40" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="M5" s="41"/>
       <c r="N5" s="36"/>
       <c r="O5" s="40" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="P5" s="41"/>
       <c r="Q5" s="36"/>
       <c r="R5" s="40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="31" t="s">
-        <v>13</v>
+      <c r="U5" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V5" s="36"/>
       <c r="W5" s="36"/>
-      <c r="X5" s="31">
+      <c r="X5" s="26">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" s="37" t="str">
         <f t="array" ref="Y5">INDEX(Cat_Etapas,$X5)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z5" s="38">
         <f t="array" ref="Z5">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I5,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L5,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O5,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R5,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U5,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA5" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA5" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46282</v>
-      </c>
-      <c r="AB5" s="31">
+        <v/>
+      </c>
+      <c r="AB5" s="26" t="str">
         <f t="shared" si="3"/>
-        <v>-7</v>
-      </c>
-      <c r="AC5" s="31" t="str">
+        <v/>
+      </c>
+      <c r="AC5" s="26" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD5" s="32"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD5" s="31"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>18</v>
+      <c r="E6" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>29</v>
+      <c r="H6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J6" s="36">
         <v>46268.0</v>
@@ -6004,8 +6006,8 @@
       <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="31" t="s">
-        <v>29</v>
+      <c r="L6" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="M6" s="36">
         <v>46268.0</v>
@@ -6013,8 +6015,8 @@
       <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="31" t="s">
-        <v>29</v>
+      <c r="O6" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="P6" s="36">
         <v>46268.0</v>
@@ -6022,17 +6024,17 @@
       <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="31" t="s">
-        <v>13</v>
+      <c r="R6" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="31" t="s">
-        <v>13</v>
+      <c r="U6" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V6" s="36"/>
       <c r="W6" s="36"/>
-      <c r="X6" s="31">
+      <c r="X6" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6048,43 +6050,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="31" t="str">
+      <c r="AB6" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="31" t="str">
+      <c r="AC6" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="32"/>
+      <c r="AD6" s="31"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>18</v>
+      <c r="A7" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H7" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>29</v>
+      <c r="H7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J7" s="36">
         <v>46268.0</v>
@@ -6092,8 +6094,8 @@
       <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>29</v>
+      <c r="L7" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="M7" s="36">
         <v>46268.0</v>
@@ -6101,8 +6103,8 @@
       <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="31" t="s">
-        <v>29</v>
+      <c r="O7" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="P7" s="36">
         <v>46268.0</v>
@@ -6110,17 +6112,17 @@
       <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="31" t="s">
-        <v>13</v>
+      <c r="R7" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
-      <c r="U7" s="31" t="s">
-        <v>13</v>
+      <c r="U7" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V7" s="36"/>
       <c r="W7" s="36"/>
-      <c r="X7" s="31">
+      <c r="X7" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6136,52 +6138,50 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="31" t="str">
+      <c r="AB7" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="31" t="str">
+      <c r="AC7" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="32"/>
+      <c r="AD7" s="31"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>18</v>
+      <c r="A8" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>29</v>
+      <c r="H8" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="J8" s="41">
-        <v>46282.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>46283.0</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>29</v>
+        <v>46302.0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="M8" s="41">
         <v>46283.0</v>
@@ -6189,8 +6189,8 @@
       <c r="N8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="O8" s="31" t="s">
-        <v>29</v>
+      <c r="O8" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="P8" s="41">
         <v>46283.0</v>
@@ -6198,17 +6198,17 @@
       <c r="Q8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="R8" s="31" t="s">
-        <v>13</v>
+      <c r="R8" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
-      <c r="U8" s="31" t="s">
-        <v>13</v>
+      <c r="U8" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
-      <c r="X8" s="31">
+      <c r="X8" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6224,43 +6224,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="31" t="str">
+      <c r="AB8" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="31" t="str">
+      <c r="AC8" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="32"/>
+      <c r="AD8" s="31"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>18</v>
+      <c r="A9" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>29</v>
+      <c r="H9" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J9" s="36">
         <v>46274.0</v>
@@ -6269,7 +6269,7 @@
         <v>46274.0</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M9" s="36">
         <v>46277.0</v>
@@ -6278,7 +6278,7 @@
         <v>46277.0</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P9" s="36">
         <v>46277.0</v>
@@ -6286,17 +6286,17 @@
       <c r="Q9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="31" t="s">
-        <v>13</v>
+      <c r="R9" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
-      <c r="U9" s="31" t="s">
-        <v>13</v>
+      <c r="U9" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V9" s="36"/>
       <c r="W9" s="36"/>
-      <c r="X9" s="31">
+      <c r="X9" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6312,31 +6312,31 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="31" t="str">
+      <c r="AB9" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="31" t="str">
+      <c r="AC9" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="32"/>
+      <c r="AD9" s="31"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>26</v>
+      <c r="E10" s="32" t="s">
+        <v>29</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>166</v>
@@ -6344,11 +6344,11 @@
       <c r="G10" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>24</v>
+      <c r="H10" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" s="36">
         <v>46272.0</v>
@@ -6357,7 +6357,7 @@
         <v>46272.0</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M10" s="41">
         <v>46277.0</v>
@@ -6366,23 +6366,23 @@
         <v>46277.0</v>
       </c>
       <c r="O10" s="40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P10" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q10" s="36"/>
-      <c r="R10" s="31" t="s">
-        <v>13</v>
+      <c r="R10" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
-      <c r="U10" s="31" t="s">
-        <v>13</v>
+      <c r="U10" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="36"/>
-      <c r="X10" s="31">
+      <c r="X10" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6398,31 +6398,31 @@
         <f t="shared" si="2"/>
         <v>46272</v>
       </c>
-      <c r="AB10" s="31">
+      <c r="AB10" s="26">
         <f t="shared" si="3"/>
-        <v>-17</v>
-      </c>
-      <c r="AC10" s="31" t="str">
+        <v>-26</v>
+      </c>
+      <c r="AC10" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD10" s="32"/>
+      <c r="AD10" s="31"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>51</v>
+      <c r="E11" s="32" t="s">
+        <v>61</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>171</v>
@@ -6430,11 +6430,11 @@
       <c r="G11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>29</v>
+      <c r="H11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J11" s="36">
         <v>46268.0</v>
@@ -6442,8 +6442,8 @@
       <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>29</v>
+      <c r="L11" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="M11" s="36">
         <v>46269.0</v>
@@ -6451,8 +6451,8 @@
       <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="31" t="s">
-        <v>29</v>
+      <c r="O11" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="P11" s="36">
         <v>46269.0</v>
@@ -6460,17 +6460,17 @@
       <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="31" t="s">
-        <v>13</v>
+      <c r="R11" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
-      <c r="U11" s="31" t="s">
-        <v>13</v>
+      <c r="U11" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V11" s="36"/>
       <c r="W11" s="36"/>
-      <c r="X11" s="31">
+      <c r="X11" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6486,31 +6486,31 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="31" t="str">
+      <c r="AB11" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="31" t="str">
+      <c r="AC11" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="32"/>
+      <c r="AD11" s="31"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="A12" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="33" t="s">
-        <v>32</v>
+      <c r="E12" s="32" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>174</v>
@@ -6518,11 +6518,11 @@
       <c r="G12" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>29</v>
+      <c r="H12" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J12" s="36">
         <v>46274.0</v>
@@ -6530,31 +6530,31 @@
       <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="31" t="s">
-        <v>21</v>
+      <c r="L12" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="M12" s="36">
         <v>46277.0</v>
       </c>
       <c r="N12" s="36"/>
-      <c r="O12" s="31" t="s">
-        <v>13</v>
+      <c r="O12" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P12" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q12" s="36"/>
-      <c r="R12" s="31" t="s">
-        <v>13</v>
+      <c r="R12" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="31" t="s">
-        <v>13</v>
+      <c r="U12" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V12" s="36"/>
       <c r="W12" s="36"/>
-      <c r="X12" s="31">
+      <c r="X12" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6570,31 +6570,31 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="31">
+      <c r="AB12" s="26">
         <f t="shared" si="3"/>
-        <v>-12</v>
-      </c>
-      <c r="AC12" s="31" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC12" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD12" s="32"/>
+      <c r="AD12" s="31"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>32</v>
+      <c r="E13" s="32" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>174</v>
@@ -6602,41 +6602,41 @@
       <c r="G13" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>21</v>
+      <c r="H13" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J13" s="36">
         <v>46277.0</v>
       </c>
       <c r="K13" s="36"/>
-      <c r="L13" s="31" t="s">
-        <v>13</v>
+      <c r="L13" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M13" s="36">
         <v>46277.0</v>
       </c>
       <c r="N13" s="36"/>
-      <c r="O13" s="31" t="s">
-        <v>13</v>
+      <c r="O13" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P13" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q13" s="36"/>
-      <c r="R13" s="31" t="s">
-        <v>13</v>
+      <c r="R13" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
-      <c r="U13" s="31" t="s">
-        <v>13</v>
+      <c r="U13" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V13" s="36"/>
       <c r="W13" s="36"/>
-      <c r="X13" s="31">
+      <c r="X13" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6652,31 +6652,31 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="31">
+      <c r="AB13" s="26">
         <f t="shared" si="3"/>
-        <v>-12</v>
-      </c>
-      <c r="AC13" s="31" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC13" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD13" s="32"/>
+      <c r="AD13" s="31"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="33" t="s">
-        <v>32</v>
+      <c r="E14" s="32" t="s">
+        <v>37</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>174</v>
@@ -6684,41 +6684,41 @@
       <c r="G14" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>21</v>
+      <c r="H14" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J14" s="36">
         <v>46277.0</v>
       </c>
       <c r="K14" s="36"/>
-      <c r="L14" s="31" t="s">
-        <v>13</v>
+      <c r="L14" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M14" s="36">
         <v>46283.0</v>
       </c>
       <c r="N14" s="36"/>
-      <c r="O14" s="31" t="s">
-        <v>13</v>
+      <c r="O14" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P14" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q14" s="36"/>
-      <c r="R14" s="31" t="s">
-        <v>13</v>
+      <c r="R14" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S14" s="36"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="31" t="s">
-        <v>13</v>
+      <c r="U14" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V14" s="36"/>
       <c r="W14" s="36"/>
-      <c r="X14" s="31">
+      <c r="X14" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6734,31 +6734,31 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB14" s="31">
+      <c r="AB14" s="26">
         <f t="shared" si="3"/>
-        <v>-12</v>
-      </c>
-      <c r="AC14" s="31" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC14" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD14" s="32"/>
+      <c r="AD14" s="31"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="33" t="s">
-        <v>37</v>
+      <c r="E15" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F15" s="35" t="s">
         <v>185</v>
@@ -6766,41 +6766,41 @@
       <c r="G15" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>24</v>
+      <c r="H15" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J15" s="36">
         <v>46283.0</v>
       </c>
       <c r="K15" s="36"/>
       <c r="L15" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M15" s="36">
         <v>46283.0</v>
       </c>
       <c r="N15" s="36"/>
-      <c r="O15" s="31" t="s">
-        <v>13</v>
+      <c r="O15" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P15" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q15" s="36"/>
-      <c r="R15" s="31" t="s">
-        <v>13</v>
+      <c r="R15" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S15" s="36"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="31" t="s">
-        <v>13</v>
+      <c r="U15" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V15" s="36"/>
       <c r="W15" s="36"/>
-      <c r="X15" s="31">
+      <c r="X15" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6816,31 +6816,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="31">
+      <c r="AB15" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC15" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC15" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD15" s="32"/>
+      <c r="AD15" s="31"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>37</v>
+      <c r="E16" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F16" s="35" t="s">
         <v>185</v>
@@ -6848,41 +6848,41 @@
       <c r="G16" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="31" t="s">
-        <v>24</v>
+      <c r="H16" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J16" s="36">
         <v>46283.0</v>
       </c>
       <c r="K16" s="36"/>
       <c r="L16" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M16" s="36">
         <v>46283.0</v>
       </c>
       <c r="N16" s="36"/>
-      <c r="O16" s="31" t="s">
-        <v>13</v>
+      <c r="O16" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P16" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q16" s="36"/>
-      <c r="R16" s="31" t="s">
-        <v>13</v>
+      <c r="R16" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S16" s="36"/>
       <c r="T16" s="36"/>
-      <c r="U16" s="31" t="s">
-        <v>13</v>
+      <c r="U16" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V16" s="36"/>
       <c r="W16" s="36"/>
-      <c r="X16" s="31">
+      <c r="X16" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6898,31 +6898,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="31">
+      <c r="AB16" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC16" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC16" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD16" s="32"/>
+      <c r="AD16" s="31"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>37</v>
+      <c r="E17" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F17" s="35" t="s">
         <v>185</v>
@@ -6930,41 +6930,41 @@
       <c r="G17" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="31" t="s">
-        <v>24</v>
+      <c r="H17" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" s="36">
         <v>46283.0</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M17" s="36">
         <v>46283.0</v>
       </c>
       <c r="N17" s="36"/>
-      <c r="O17" s="31" t="s">
-        <v>13</v>
+      <c r="O17" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P17" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q17" s="36"/>
-      <c r="R17" s="31" t="s">
-        <v>13</v>
+      <c r="R17" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
-      <c r="U17" s="31" t="s">
-        <v>13</v>
+      <c r="U17" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="36"/>
-      <c r="X17" s="31">
+      <c r="X17" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6980,31 +6980,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="31">
+      <c r="AB17" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC17" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC17" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD17" s="32"/>
+      <c r="AD17" s="31"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>37</v>
+      <c r="E18" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F18" s="35" t="s">
         <v>185</v>
@@ -7012,41 +7012,41 @@
       <c r="G18" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>21</v>
+      <c r="H18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J18" s="36">
         <v>46283.0</v>
       </c>
       <c r="K18" s="36"/>
-      <c r="L18" s="31" t="s">
-        <v>13</v>
+      <c r="L18" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M18" s="36">
         <v>46283.0</v>
       </c>
       <c r="N18" s="36"/>
-      <c r="O18" s="31" t="s">
-        <v>13</v>
+      <c r="O18" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P18" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q18" s="36"/>
-      <c r="R18" s="31" t="s">
-        <v>13</v>
+      <c r="R18" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
-      <c r="U18" s="31" t="s">
-        <v>13</v>
+      <c r="U18" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V18" s="36"/>
       <c r="W18" s="36"/>
-      <c r="X18" s="31">
+      <c r="X18" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7062,31 +7062,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="31">
+      <c r="AB18" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC18" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC18" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD18" s="32"/>
+      <c r="AD18" s="31"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>37</v>
+      <c r="E19" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F19" s="35" t="s">
         <v>185</v>
@@ -7094,41 +7094,41 @@
       <c r="G19" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="31" t="s">
-        <v>24</v>
+      <c r="H19" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J19" s="36">
         <v>46283.0</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M19" s="36">
         <v>46283.0</v>
       </c>
       <c r="N19" s="36"/>
-      <c r="O19" s="31" t="s">
-        <v>13</v>
+      <c r="O19" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P19" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q19" s="36"/>
-      <c r="R19" s="31" t="s">
-        <v>13</v>
+      <c r="R19" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S19" s="36"/>
       <c r="T19" s="36"/>
-      <c r="U19" s="31" t="s">
-        <v>13</v>
+      <c r="U19" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V19" s="36"/>
       <c r="W19" s="36"/>
-      <c r="X19" s="31">
+      <c r="X19" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7144,31 +7144,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="31">
+      <c r="AB19" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC19" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC19" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD19" s="32"/>
+      <c r="AD19" s="31"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="33" t="s">
-        <v>37</v>
+      <c r="E20" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F20" s="35" t="s">
         <v>185</v>
@@ -7176,41 +7176,41 @@
       <c r="G20" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>21</v>
+      <c r="H20" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J20" s="36">
         <v>46283.0</v>
       </c>
       <c r="K20" s="36"/>
-      <c r="L20" s="31" t="s">
-        <v>13</v>
+      <c r="L20" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M20" s="36">
         <v>46283.0</v>
       </c>
       <c r="N20" s="36"/>
-      <c r="O20" s="31" t="s">
-        <v>13</v>
+      <c r="O20" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P20" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="31" t="s">
-        <v>13</v>
+      <c r="R20" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S20" s="36"/>
       <c r="T20" s="36"/>
-      <c r="U20" s="31" t="s">
-        <v>13</v>
+      <c r="U20" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="36"/>
-      <c r="X20" s="31">
+      <c r="X20" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7226,31 +7226,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC20" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC20" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD20" s="32"/>
+      <c r="AD20" s="31"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>37</v>
+      <c r="E21" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F21" s="35" t="s">
         <v>185</v>
@@ -7258,41 +7258,41 @@
       <c r="G21" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="31" t="s">
-        <v>24</v>
+      <c r="H21" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J21" s="36">
         <v>46283.0</v>
       </c>
       <c r="K21" s="36"/>
       <c r="L21" s="40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M21" s="36">
         <v>46283.0</v>
       </c>
       <c r="N21" s="36"/>
-      <c r="O21" s="31" t="s">
-        <v>13</v>
+      <c r="O21" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P21" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q21" s="36"/>
-      <c r="R21" s="31" t="s">
-        <v>13</v>
+      <c r="R21" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S21" s="36"/>
       <c r="T21" s="36"/>
-      <c r="U21" s="31" t="s">
-        <v>13</v>
+      <c r="U21" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V21" s="36"/>
       <c r="W21" s="36"/>
-      <c r="X21" s="31">
+      <c r="X21" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7308,31 +7308,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC21" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC21" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD21" s="32"/>
+      <c r="AD21" s="31"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="33" t="s">
-        <v>37</v>
+      <c r="E22" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F22" s="35" t="s">
         <v>185</v>
@@ -7340,41 +7340,41 @@
       <c r="G22" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="31" t="s">
-        <v>21</v>
+      <c r="H22" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J22" s="36">
         <v>46283.0</v>
       </c>
       <c r="K22" s="36"/>
-      <c r="L22" s="31" t="s">
-        <v>13</v>
+      <c r="L22" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="36">
         <v>46283.0</v>
       </c>
       <c r="N22" s="36"/>
-      <c r="O22" s="31" t="s">
-        <v>13</v>
+      <c r="O22" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P22" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q22" s="36"/>
-      <c r="R22" s="31" t="s">
-        <v>13</v>
+      <c r="R22" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S22" s="36"/>
       <c r="T22" s="36"/>
-      <c r="U22" s="31" t="s">
-        <v>13</v>
+      <c r="U22" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V22" s="36"/>
       <c r="W22" s="36"/>
-      <c r="X22" s="31">
+      <c r="X22" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7390,31 +7390,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="31">
+      <c r="AB22" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC22" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC22" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD22" s="32"/>
+      <c r="AD22" s="31"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="31" t="s">
+      <c r="B23" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="33" t="s">
-        <v>37</v>
+      <c r="E23" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F23" s="35" t="s">
         <v>185</v>
@@ -7422,41 +7422,41 @@
       <c r="G23" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>21</v>
+      <c r="H23" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J23" s="36">
         <v>46283.0</v>
       </c>
       <c r="K23" s="36"/>
-      <c r="L23" s="31" t="s">
-        <v>13</v>
+      <c r="L23" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M23" s="36">
         <v>46283.0</v>
       </c>
       <c r="N23" s="36"/>
-      <c r="O23" s="31" t="s">
-        <v>13</v>
+      <c r="O23" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P23" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q23" s="36"/>
-      <c r="R23" s="31" t="s">
-        <v>13</v>
+      <c r="R23" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S23" s="36"/>
       <c r="T23" s="36"/>
-      <c r="U23" s="31" t="s">
-        <v>13</v>
+      <c r="U23" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V23" s="36"/>
       <c r="W23" s="36"/>
-      <c r="X23" s="31">
+      <c r="X23" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7472,31 +7472,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="31">
+      <c r="AB23" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC23" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC23" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD23" s="32"/>
+      <c r="AD23" s="31"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="31" t="s">
+      <c r="B24" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>37</v>
+      <c r="E24" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F24" s="35" t="s">
         <v>185</v>
@@ -7504,41 +7504,41 @@
       <c r="G24" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>21</v>
+      <c r="H24" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J24" s="36">
         <v>46283.0</v>
       </c>
       <c r="K24" s="36"/>
-      <c r="L24" s="31" t="s">
-        <v>13</v>
+      <c r="L24" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M24" s="36">
         <v>46283.0</v>
       </c>
       <c r="N24" s="36"/>
-      <c r="O24" s="31" t="s">
-        <v>13</v>
+      <c r="O24" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P24" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q24" s="36"/>
-      <c r="R24" s="31" t="s">
-        <v>13</v>
+      <c r="R24" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S24" s="36"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="31" t="s">
-        <v>13</v>
+      <c r="U24" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V24" s="36"/>
       <c r="W24" s="36"/>
-      <c r="X24" s="31">
+      <c r="X24" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7554,31 +7554,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC24" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC24" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD24" s="32"/>
+      <c r="AD24" s="31"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="31" t="s">
+      <c r="B25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="33" t="s">
-        <v>37</v>
+      <c r="E25" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F25" s="35" t="s">
         <v>185</v>
@@ -7586,41 +7586,41 @@
       <c r="G25" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>21</v>
+      <c r="H25" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J25" s="36">
         <v>46283.0</v>
       </c>
       <c r="K25" s="36"/>
-      <c r="L25" s="31" t="s">
-        <v>13</v>
+      <c r="L25" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M25" s="36">
         <v>46283.0</v>
       </c>
       <c r="N25" s="36"/>
-      <c r="O25" s="31" t="s">
-        <v>13</v>
+      <c r="O25" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P25" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q25" s="36"/>
-      <c r="R25" s="31" t="s">
-        <v>13</v>
+      <c r="R25" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S25" s="36"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="31" t="s">
-        <v>13</v>
+      <c r="U25" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V25" s="36"/>
       <c r="W25" s="36"/>
-      <c r="X25" s="31">
+      <c r="X25" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7636,31 +7636,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="31">
+      <c r="AB25" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC25" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC25" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD25" s="32"/>
+      <c r="AD25" s="31"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="31" t="s">
+      <c r="B26" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="33" t="s">
-        <v>37</v>
+      <c r="E26" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F26" s="35" t="s">
         <v>185</v>
@@ -7668,41 +7668,41 @@
       <c r="G26" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>21</v>
+      <c r="H26" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J26" s="36">
         <v>46283.0</v>
       </c>
       <c r="K26" s="36"/>
-      <c r="L26" s="31" t="s">
-        <v>13</v>
+      <c r="L26" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M26" s="36">
         <v>46283.0</v>
       </c>
       <c r="N26" s="36"/>
-      <c r="O26" s="31" t="s">
-        <v>13</v>
+      <c r="O26" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P26" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q26" s="36"/>
-      <c r="R26" s="31" t="s">
-        <v>13</v>
+      <c r="R26" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S26" s="36"/>
       <c r="T26" s="36"/>
-      <c r="U26" s="31" t="s">
-        <v>13</v>
+      <c r="U26" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V26" s="36"/>
       <c r="W26" s="36"/>
-      <c r="X26" s="31">
+      <c r="X26" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7718,31 +7718,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="31">
+      <c r="AB26" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC26" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC26" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD26" s="32"/>
+      <c r="AD26" s="31"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="33" t="s">
-        <v>37</v>
+      <c r="E27" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F27" s="35" t="s">
         <v>185</v>
@@ -7750,41 +7750,41 @@
       <c r="G27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="31" t="s">
-        <v>21</v>
+      <c r="H27" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J27" s="36">
         <v>46283.0</v>
       </c>
       <c r="K27" s="36"/>
-      <c r="L27" s="31" t="s">
-        <v>13</v>
+      <c r="L27" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M27" s="36">
         <v>46283.0</v>
       </c>
       <c r="N27" s="36"/>
-      <c r="O27" s="31" t="s">
-        <v>13</v>
+      <c r="O27" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P27" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="31" t="s">
-        <v>13</v>
+      <c r="R27" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S27" s="36"/>
       <c r="T27" s="36"/>
-      <c r="U27" s="31" t="s">
-        <v>13</v>
+      <c r="U27" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V27" s="36"/>
       <c r="W27" s="36"/>
-      <c r="X27" s="31">
+      <c r="X27" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7800,31 +7800,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC27" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC27" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD27" s="32"/>
+      <c r="AD27" s="31"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="31" t="s">
+      <c r="B28" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>37</v>
+      <c r="E28" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F28" s="35" t="s">
         <v>185</v>
@@ -7832,41 +7832,41 @@
       <c r="G28" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>21</v>
+      <c r="H28" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J28" s="36">
         <v>46283.0</v>
       </c>
       <c r="K28" s="36"/>
-      <c r="L28" s="31" t="s">
-        <v>13</v>
+      <c r="L28" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M28" s="36">
         <v>46283.0</v>
       </c>
       <c r="N28" s="36"/>
-      <c r="O28" s="31" t="s">
-        <v>13</v>
+      <c r="O28" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P28" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q28" s="36"/>
-      <c r="R28" s="31" t="s">
-        <v>13</v>
+      <c r="R28" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S28" s="36"/>
       <c r="T28" s="36"/>
-      <c r="U28" s="31" t="s">
-        <v>13</v>
+      <c r="U28" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V28" s="36"/>
       <c r="W28" s="36"/>
-      <c r="X28" s="31">
+      <c r="X28" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7882,31 +7882,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="31">
+      <c r="AB28" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC28" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC28" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD28" s="32"/>
+      <c r="AD28" s="31"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="B29" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>37</v>
+      <c r="E29" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F29" s="35" t="s">
         <v>185</v>
@@ -7914,41 +7914,41 @@
       <c r="G29" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="31" t="s">
-        <v>21</v>
+      <c r="H29" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J29" s="36">
         <v>46283.0</v>
       </c>
       <c r="K29" s="36"/>
-      <c r="L29" s="31" t="s">
-        <v>13</v>
+      <c r="L29" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M29" s="36">
         <v>46283.0</v>
       </c>
       <c r="N29" s="36"/>
-      <c r="O29" s="31" t="s">
-        <v>13</v>
+      <c r="O29" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P29" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q29" s="36"/>
-      <c r="R29" s="31" t="s">
-        <v>13</v>
+      <c r="R29" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S29" s="36"/>
       <c r="T29" s="36"/>
-      <c r="U29" s="31" t="s">
-        <v>13</v>
+      <c r="U29" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V29" s="36"/>
       <c r="W29" s="36"/>
-      <c r="X29" s="31">
+      <c r="X29" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7964,31 +7964,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="31">
+      <c r="AB29" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC29" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC29" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD29" s="32"/>
+      <c r="AD29" s="31"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>37</v>
+      <c r="E30" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F30" s="35" t="s">
         <v>185</v>
@@ -7996,41 +7996,41 @@
       <c r="G30" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="31" t="s">
-        <v>21</v>
+      <c r="H30" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J30" s="36">
         <v>46283.0</v>
       </c>
       <c r="K30" s="36"/>
-      <c r="L30" s="31" t="s">
-        <v>13</v>
+      <c r="L30" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M30" s="36">
         <v>46283.0</v>
       </c>
       <c r="N30" s="36"/>
-      <c r="O30" s="31" t="s">
-        <v>13</v>
+      <c r="O30" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P30" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q30" s="36"/>
-      <c r="R30" s="31" t="s">
-        <v>13</v>
+      <c r="R30" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S30" s="36"/>
       <c r="T30" s="36"/>
-      <c r="U30" s="31" t="s">
-        <v>13</v>
+      <c r="U30" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V30" s="36"/>
       <c r="W30" s="36"/>
-      <c r="X30" s="31">
+      <c r="X30" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8046,31 +8046,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="31">
+      <c r="AB30" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC30" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC30" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD30" s="32"/>
+      <c r="AD30" s="31"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="31" t="s">
+      <c r="B31" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>37</v>
+      <c r="E31" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F31" s="35" t="s">
         <v>185</v>
@@ -8078,41 +8078,41 @@
       <c r="G31" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="31" t="s">
-        <v>21</v>
+      <c r="H31" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J31" s="36">
         <v>46283.0</v>
       </c>
       <c r="K31" s="36"/>
-      <c r="L31" s="31" t="s">
-        <v>13</v>
+      <c r="L31" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M31" s="36">
         <v>46283.0</v>
       </c>
       <c r="N31" s="36"/>
-      <c r="O31" s="31" t="s">
-        <v>13</v>
+      <c r="O31" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P31" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q31" s="36"/>
-      <c r="R31" s="31" t="s">
-        <v>13</v>
+      <c r="R31" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S31" s="36"/>
       <c r="T31" s="36"/>
-      <c r="U31" s="31" t="s">
-        <v>13</v>
+      <c r="U31" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V31" s="36"/>
       <c r="W31" s="36"/>
-      <c r="X31" s="31">
+      <c r="X31" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8128,31 +8128,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="31">
+      <c r="AB31" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC31" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC31" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD31" s="32"/>
+      <c r="AD31" s="31"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="31" t="s">
+      <c r="B32" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>37</v>
+      <c r="E32" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F32" s="35" t="s">
         <v>185</v>
@@ -8160,41 +8160,41 @@
       <c r="G32" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="31" t="s">
-        <v>21</v>
+      <c r="H32" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J32" s="36">
         <v>46283.0</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="31" t="s">
-        <v>13</v>
+      <c r="L32" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M32" s="36">
         <v>46283.0</v>
       </c>
       <c r="N32" s="36"/>
-      <c r="O32" s="31" t="s">
-        <v>13</v>
+      <c r="O32" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P32" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q32" s="36"/>
-      <c r="R32" s="31" t="s">
-        <v>13</v>
+      <c r="R32" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S32" s="36"/>
       <c r="T32" s="36"/>
-      <c r="U32" s="31" t="s">
-        <v>13</v>
+      <c r="U32" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V32" s="36"/>
       <c r="W32" s="36"/>
-      <c r="X32" s="31">
+      <c r="X32" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8210,31 +8210,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="31">
+      <c r="AB32" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC32" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC32" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD32" s="32"/>
+      <c r="AD32" s="31"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="31" t="s">
+      <c r="B33" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="33" t="s">
-        <v>37</v>
+      <c r="E33" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F33" s="35" t="s">
         <v>185</v>
@@ -8242,41 +8242,41 @@
       <c r="G33" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="31" t="s">
-        <v>21</v>
+      <c r="H33" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J33" s="36">
         <v>46283.0</v>
       </c>
       <c r="K33" s="36"/>
-      <c r="L33" s="31" t="s">
-        <v>13</v>
+      <c r="L33" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M33" s="36">
         <v>46283.0</v>
       </c>
       <c r="N33" s="36"/>
-      <c r="O33" s="31" t="s">
-        <v>13</v>
+      <c r="O33" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P33" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q33" s="36"/>
-      <c r="R33" s="31" t="s">
-        <v>13</v>
+      <c r="R33" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
-      <c r="U33" s="31" t="s">
-        <v>13</v>
+      <c r="U33" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V33" s="36"/>
       <c r="W33" s="36"/>
-      <c r="X33" s="31">
+      <c r="X33" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8292,31 +8292,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="31">
+      <c r="AB33" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC33" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC33" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD33" s="32"/>
+      <c r="AD33" s="31"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="31" t="s">
+      <c r="B34" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>37</v>
+      <c r="E34" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F34" s="35" t="s">
         <v>185</v>
@@ -8324,41 +8324,41 @@
       <c r="G34" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="31" t="s">
-        <v>21</v>
+      <c r="H34" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J34" s="36">
         <v>46283.0</v>
       </c>
       <c r="K34" s="36"/>
-      <c r="L34" s="31" t="s">
-        <v>13</v>
+      <c r="L34" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="36">
         <v>46283.0</v>
       </c>
       <c r="N34" s="36"/>
-      <c r="O34" s="31" t="s">
-        <v>13</v>
+      <c r="O34" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P34" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q34" s="36"/>
-      <c r="R34" s="31" t="s">
-        <v>13</v>
+      <c r="R34" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S34" s="36"/>
       <c r="T34" s="36"/>
-      <c r="U34" s="31" t="s">
-        <v>13</v>
+      <c r="U34" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V34" s="36"/>
       <c r="W34" s="36"/>
-      <c r="X34" s="31">
+      <c r="X34" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8374,31 +8374,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="31">
+      <c r="AB34" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC34" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC34" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD34" s="32"/>
+      <c r="AD34" s="31"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="B35" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>37</v>
+      <c r="E35" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F35" s="35" t="s">
         <v>185</v>
@@ -8406,41 +8406,41 @@
       <c r="G35" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="31" t="s">
-        <v>21</v>
+      <c r="H35" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J35" s="36">
         <v>46283.0</v>
       </c>
       <c r="K35" s="36"/>
-      <c r="L35" s="31" t="s">
-        <v>13</v>
+      <c r="L35" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M35" s="36">
         <v>46283.0</v>
       </c>
       <c r="N35" s="36"/>
-      <c r="O35" s="31" t="s">
-        <v>13</v>
+      <c r="O35" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P35" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q35" s="36"/>
-      <c r="R35" s="31" t="s">
-        <v>13</v>
+      <c r="R35" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
-      <c r="U35" s="31" t="s">
-        <v>13</v>
+      <c r="U35" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V35" s="36"/>
       <c r="W35" s="36"/>
-      <c r="X35" s="31">
+      <c r="X35" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8456,31 +8456,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="31">
+      <c r="AB35" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC35" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC35" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD35" s="32"/>
+      <c r="AD35" s="31"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="B36" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>37</v>
+      <c r="E36" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F36" s="35" t="s">
         <v>185</v>
@@ -8488,41 +8488,41 @@
       <c r="G36" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="31" t="s">
-        <v>21</v>
+      <c r="H36" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J36" s="36">
         <v>46283.0</v>
       </c>
       <c r="K36" s="36"/>
-      <c r="L36" s="31" t="s">
-        <v>13</v>
+      <c r="L36" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M36" s="36">
         <v>46283.0</v>
       </c>
       <c r="N36" s="36"/>
-      <c r="O36" s="31" t="s">
-        <v>13</v>
+      <c r="O36" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P36" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q36" s="36"/>
-      <c r="R36" s="31" t="s">
-        <v>13</v>
+      <c r="R36" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S36" s="36"/>
       <c r="T36" s="36"/>
-      <c r="U36" s="31" t="s">
-        <v>13</v>
+      <c r="U36" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V36" s="36"/>
       <c r="W36" s="36"/>
-      <c r="X36" s="31">
+      <c r="X36" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8538,31 +8538,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="31">
+      <c r="AB36" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC36" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC36" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD36" s="32"/>
+      <c r="AD36" s="31"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="31" t="s">
+      <c r="B37" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>37</v>
+      <c r="E37" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="F37" s="35" t="s">
         <v>185</v>
@@ -8570,41 +8570,41 @@
       <c r="G37" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="31" t="s">
-        <v>21</v>
+      <c r="H37" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J37" s="36">
         <v>46283.0</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="31" t="s">
-        <v>13</v>
+      <c r="L37" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M37" s="36">
         <v>46283.0</v>
       </c>
       <c r="N37" s="36"/>
-      <c r="O37" s="31" t="s">
-        <v>13</v>
+      <c r="O37" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P37" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q37" s="36"/>
-      <c r="R37" s="31" t="s">
-        <v>13</v>
+      <c r="R37" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
-      <c r="U37" s="31" t="s">
-        <v>13</v>
+      <c r="U37" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V37" s="36"/>
       <c r="W37" s="36"/>
-      <c r="X37" s="31">
+      <c r="X37" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8620,31 +8620,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC37" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC37" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD37" s="32"/>
+      <c r="AD37" s="31"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="31" t="s">
+      <c r="B38" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="33" t="s">
-        <v>42</v>
+      <c r="E38" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F38" s="34" t="s">
         <v>255</v>
@@ -8652,11 +8652,11 @@
       <c r="G38" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>29</v>
+      <c r="H38" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J38" s="41">
         <v>46277.0</v>
@@ -8664,31 +8664,31 @@
       <c r="K38" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="31" t="s">
-        <v>21</v>
+      <c r="L38" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="M38" s="36">
         <v>46283.0</v>
       </c>
       <c r="N38" s="36"/>
-      <c r="O38" s="31" t="s">
-        <v>13</v>
+      <c r="O38" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P38" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="31" t="s">
-        <v>13</v>
+      <c r="R38" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S38" s="36"/>
       <c r="T38" s="36"/>
-      <c r="U38" s="31" t="s">
-        <v>13</v>
+      <c r="U38" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V38" s="36"/>
       <c r="W38" s="36"/>
-      <c r="X38" s="31">
+      <c r="X38" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8704,31 +8704,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC38" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC38" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD38" s="32"/>
+      <c r="AD38" s="31"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="31" t="s">
+      <c r="B39" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="33" t="s">
-        <v>42</v>
+      <c r="E39" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F39" s="34" t="s">
         <v>255</v>
@@ -8736,41 +8736,41 @@
       <c r="G39" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39" s="31" t="s">
-        <v>21</v>
+      <c r="H39" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J39" s="36">
         <v>46283.0</v>
       </c>
       <c r="K39" s="36"/>
-      <c r="L39" s="31" t="s">
-        <v>13</v>
+      <c r="L39" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M39" s="36">
         <v>46283.0</v>
       </c>
       <c r="N39" s="36"/>
-      <c r="O39" s="31" t="s">
-        <v>13</v>
+      <c r="O39" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P39" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q39" s="36"/>
-      <c r="R39" s="31" t="s">
-        <v>13</v>
+      <c r="R39" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
-      <c r="U39" s="31" t="s">
-        <v>13</v>
+      <c r="U39" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V39" s="36"/>
       <c r="W39" s="36"/>
-      <c r="X39" s="31">
+      <c r="X39" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8786,31 +8786,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB39" s="31">
+      <c r="AB39" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC39" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC39" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD39" s="32"/>
+      <c r="AD39" s="31"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="31" t="s">
+      <c r="B40" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>42</v>
+      <c r="E40" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F40" s="34" t="s">
         <v>255</v>
@@ -8818,41 +8818,41 @@
       <c r="G40" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="31" t="s">
-        <v>21</v>
+      <c r="H40" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J40" s="36">
         <v>46283.0</v>
       </c>
       <c r="K40" s="36"/>
-      <c r="L40" s="31" t="s">
-        <v>13</v>
+      <c r="L40" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M40" s="36">
         <v>46283.0</v>
       </c>
       <c r="N40" s="36"/>
-      <c r="O40" s="31" t="s">
-        <v>13</v>
+      <c r="O40" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P40" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q40" s="36"/>
-      <c r="R40" s="31" t="s">
-        <v>13</v>
+      <c r="R40" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
-      <c r="U40" s="31" t="s">
-        <v>13</v>
+      <c r="U40" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V40" s="36"/>
       <c r="W40" s="36"/>
-      <c r="X40" s="31">
+      <c r="X40" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8868,31 +8868,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB40" s="31">
+      <c r="AB40" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC40" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC40" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD40" s="32"/>
+      <c r="AD40" s="31"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="31" t="s">
+      <c r="B41" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="33" t="s">
-        <v>42</v>
+      <c r="E41" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F41" s="34" t="s">
         <v>255</v>
@@ -8900,41 +8900,41 @@
       <c r="G41" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="31" t="s">
-        <v>21</v>
+      <c r="H41" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J41" s="36">
         <v>46283.0</v>
       </c>
       <c r="K41" s="36"/>
-      <c r="L41" s="31" t="s">
-        <v>13</v>
+      <c r="L41" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M41" s="36">
         <v>46283.0</v>
       </c>
       <c r="N41" s="36"/>
-      <c r="O41" s="31" t="s">
-        <v>13</v>
+      <c r="O41" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P41" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q41" s="36"/>
-      <c r="R41" s="31" t="s">
-        <v>13</v>
+      <c r="R41" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
-      <c r="U41" s="31" t="s">
-        <v>13</v>
+      <c r="U41" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V41" s="36"/>
       <c r="W41" s="36"/>
-      <c r="X41" s="31">
+      <c r="X41" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8950,31 +8950,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC41" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC41" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD41" s="32"/>
+      <c r="AD41" s="31"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="B42" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="33" t="s">
-        <v>42</v>
+      <c r="E42" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F42" s="34" t="s">
         <v>255</v>
@@ -8982,41 +8982,41 @@
       <c r="G42" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>21</v>
+      <c r="H42" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="J42" s="36">
         <v>46283.0</v>
       </c>
       <c r="K42" s="36"/>
-      <c r="L42" s="31" t="s">
-        <v>13</v>
+      <c r="L42" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="M42" s="36">
         <v>46283.0</v>
       </c>
       <c r="N42" s="36"/>
-      <c r="O42" s="31" t="s">
-        <v>13</v>
+      <c r="O42" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P42" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q42" s="36"/>
-      <c r="R42" s="31" t="s">
-        <v>13</v>
+      <c r="R42" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S42" s="36"/>
       <c r="T42" s="36"/>
-      <c r="U42" s="31" t="s">
-        <v>13</v>
+      <c r="U42" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V42" s="36"/>
       <c r="W42" s="36"/>
-      <c r="X42" s="31">
+      <c r="X42" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -9032,31 +9032,31 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB42" s="31">
+      <c r="AB42" s="26">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AC42" s="31" t="str">
+        <v>-15</v>
+      </c>
+      <c r="AC42" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD42" s="32"/>
+      <c r="AD42" s="31"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="31" t="s">
+      <c r="B43" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="33" t="s">
-        <v>42</v>
+      <c r="E43" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="F43" s="34" t="s">
         <v>255</v>
@@ -9064,11 +9064,11 @@
       <c r="G43" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="31" t="s">
-        <v>29</v>
+      <c r="H43" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J43" s="41">
         <v>46277.0</v>
@@ -9076,8 +9076,8 @@
       <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="31" t="s">
-        <v>29</v>
+      <c r="L43" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="M43" s="41">
         <v>46277.0</v>
@@ -9085,8 +9085,8 @@
       <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="31" t="s">
-        <v>29</v>
+      <c r="O43" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="P43" s="36">
         <v>46276.0</v>
@@ -9094,17 +9094,17 @@
       <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="31" t="s">
-        <v>13</v>
+      <c r="R43" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
-      <c r="U43" s="31" t="s">
-        <v>13</v>
+      <c r="U43" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V43" s="36"/>
       <c r="W43" s="36"/>
-      <c r="X43" s="31">
+      <c r="X43" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9120,43 +9120,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="31" t="str">
+      <c r="AB43" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="31" t="str">
+      <c r="AC43" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="32"/>
+      <c r="AD43" s="31"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="31" t="s">
+      <c r="B44" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="33" t="s">
-        <v>47</v>
+      <c r="E44" s="32" t="s">
+        <v>57</v>
       </c>
       <c r="F44" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H44" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="31" t="s">
-        <v>29</v>
+      <c r="H44" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="J44" s="41">
         <v>46277.0</v>
@@ -9164,29 +9164,29 @@
       <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="31" t="s">
-        <v>21</v>
+      <c r="L44" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="M44" s="36">
         <v>46276.0</v>
       </c>
       <c r="N44" s="36"/>
-      <c r="O44" s="31" t="s">
-        <v>13</v>
+      <c r="O44" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="P44" s="36"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="31" t="s">
-        <v>13</v>
+      <c r="R44" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="S44" s="36"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="31" t="s">
-        <v>13</v>
+      <c r="U44" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="V44" s="36"/>
       <c r="W44" s="36"/>
-      <c r="X44" s="31">
+      <c r="X44" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9202,15 +9202,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="26">
         <f t="shared" si="3"/>
-        <v>-13</v>
-      </c>
-      <c r="AC44" s="31" t="str">
+        <v>-22</v>
+      </c>
+      <c r="AC44" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="32"/>
+      <c r="AD44" s="31"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -29,18 +29,18 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="274">
   <si>
+    <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
+  </si>
+  <si>
     <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
   </si>
   <si>
+    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+  </si>
+  <si>
     <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
   </si>
   <si>
-    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
-  </si>
-  <si>
-    <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
-  </si>
-  <si>
     <t>1. ¿Qué se captura y qué se calcula solo?</t>
   </si>
   <si>
@@ -50,160 +50,205 @@
     <t>Estatus</t>
   </si>
   <si>
+    <t>Factor avance</t>
+  </si>
+  <si>
+    <t>Módulos</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Áreas / Frentes</t>
+  </si>
+  <si>
+    <t>Etapas</t>
+  </si>
+  <si>
+    <t>Peso etapa</t>
+  </si>
+  <si>
+    <t>No iniciado</t>
+  </si>
+  <si>
+    <t>INDICADORES CLAVE</t>
+  </si>
+  <si>
     <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
   </si>
   <si>
-    <t>INDICADORES CLAVE</t>
-  </si>
-  <si>
-    <t>Factor avance</t>
-  </si>
-  <si>
-    <t>Módulos</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
+    <t>AVANCE POR MÓDULO</t>
   </si>
   <si>
     <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
   </si>
   <si>
-    <t>Áreas / Frentes</t>
-  </si>
-  <si>
-    <t>Etapas</t>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>Alta</t>
   </si>
   <si>
     <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
   </si>
   <si>
-    <t>Peso etapa</t>
-  </si>
-  <si>
-    <t>No iniciado</t>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
   </si>
   <si>
     <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
   </si>
   <si>
-    <t>AVANCE POR MÓDULO</t>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
   </si>
   <si>
     <t>2. Etapas del flujo y su peso en el avance</t>
   </si>
   <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
-    <t>1. Llenado de plantilla</t>
-  </si>
-  <si>
-    <t>En proceso</t>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
+  </si>
+  <si>
+    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
   </si>
   <si>
     <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
   </si>
   <si>
-    <t>Compras (P2P)</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
   </si>
   <si>
     <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
   </si>
   <si>
-    <t>2. Revisión y validación</t>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
   </si>
   <si>
     <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
   </si>
   <si>
-    <t>Completado</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>E1 · LLENADO</t>
+  </si>
+  <si>
+    <t>Activos Fijos / Patrimonio</t>
   </si>
   <si>
     <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
+    <t>6. Cerrado</t>
+  </si>
+  <si>
+    <t>Módulo</t>
   </si>
   <si>
     <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
   </si>
   <si>
-    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
   </si>
   <si>
     <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
   </si>
   <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Almacén / Inventarios</t>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
+    <t>E2 · REVISIÓN</t>
+  </si>
+  <si>
+    <t>E3 Repositorio OK</t>
+  </si>
+  <si>
+    <t>E4 Sandbox OK</t>
   </si>
   <si>
     <t>3. Valores de estatus permitidos</t>
   </si>
   <si>
-    <t>4. Ambiente Sandbox</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
-  </si>
-  <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
+    <t>E5 Productivo OK</t>
+  </si>
+  <si>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>E3 · REPOSITORIO ORACLE</t>
+  </si>
+  <si>
+    <t>E4 · SANDBOX</t>
   </si>
   <si>
     <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
   </si>
   <si>
-    <t>E1 · LLENADO</t>
-  </si>
-  <si>
-    <t>Activos Fijos (FA)</t>
-  </si>
-  <si>
     <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
   </si>
   <si>
-    <t>Activos Fijos / Patrimonio</t>
-  </si>
-  <si>
-    <t>6. Cerrado</t>
+    <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
     <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
@@ -212,13 +257,10 @@
     <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
-    <t>E2 · REVISIÓN</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
+    <t>SEGUIMIENTO AUTOMÁTICO</t>
+  </si>
+  <si>
+    <t>PMO / Consultoría</t>
   </si>
   <si>
     <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
@@ -227,97 +269,127 @@
     <t>4. Lectura del semáforo</t>
   </si>
   <si>
-    <t>E3 · REPOSITORIO ORACLE</t>
-  </si>
-  <si>
-    <t>E4 · SANDBOX</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Plantilla</t>
   </si>
   <si>
     <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
   </si>
   <si>
+    <t>Área Responsable</t>
+  </si>
+  <si>
+    <t>Key User</t>
+  </si>
+  <si>
     <t>•  En riesgo — faltan 7 días o menos.</t>
   </si>
   <si>
-    <t>Módulo</t>
+    <t>Consultor Oracle</t>
   </si>
   <si>
     <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
   </si>
   <si>
-    <t>E5 · PRODUCTIVO</t>
+    <t>E1 Llenado</t>
   </si>
   <si>
     <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
   </si>
   <si>
-    <t>Plantillas</t>
+    <t>E1 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E1 F. Real</t>
+  </si>
+  <si>
+    <t>E2 Revisión</t>
+  </si>
+  <si>
+    <t>E2 F. Compromiso</t>
   </si>
   <si>
     <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
   </si>
   <si>
-    <t>% Avance</t>
-  </si>
-  <si>
-    <t>SEGUIMIENTO AUTOMÁTICO</t>
-  </si>
-  <si>
-    <t>E1 Llenado OK</t>
+    <t>E2 F. Real</t>
+  </si>
+  <si>
+    <t>E3 Repositorio</t>
+  </si>
+  <si>
+    <t>E3 F. Compromiso</t>
   </si>
   <si>
     <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
   </si>
   <si>
-    <t>E2 Revisión OK</t>
-  </si>
-  <si>
-    <t>E3 Repositorio OK</t>
+    <t>E3 F. Real</t>
+  </si>
+  <si>
+    <t>E4 Sandbox</t>
+  </si>
+  <si>
+    <t>E4 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E4 F. Real</t>
+  </si>
+  <si>
+    <t>E5 Productivo</t>
   </si>
   <si>
     <t>5. Conexión con el tablero HTML</t>
   </si>
   <si>
-    <t>E4 Sandbox OK</t>
-  </si>
-  <si>
-    <t>E5 Productivo OK</t>
-  </si>
-  <si>
-    <t>Avance global ponderado</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>PMO / Consultoría</t>
+    <t>E5 F. Compromiso</t>
+  </si>
+  <si>
+    <t>E5 F. Real</t>
+  </si>
+  <si>
+    <t>Etapa #</t>
+  </si>
+  <si>
+    <t>Etapa Actual</t>
+  </si>
+  <si>
+    <t>Próx. Compromiso</t>
+  </si>
+  <si>
+    <t>Días Restantes</t>
+  </si>
+  <si>
+    <t>Semáforo</t>
+  </si>
+  <si>
+    <t>Observaciones / Bloqueos</t>
   </si>
   <si>
     <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
+    <t>FIN-01</t>
+  </si>
+  <si>
     <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
   </si>
   <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Plantilla</t>
-  </si>
-  <si>
-    <t>Área Responsable</t>
-  </si>
-  <si>
     <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
   </si>
   <si>
-    <t>Key User</t>
+    <t>—</t>
   </si>
   <si>
     <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
   </si>
   <si>
-    <t>Consultor Oracle</t>
+    <t>ESTEVEZ - Clases</t>
   </si>
   <si>
     <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
@@ -326,117 +398,51 @@
     <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
-    <t>E1 Llenado</t>
-  </si>
-  <si>
-    <t>E1 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E1 F. Real</t>
-  </si>
-  <si>
-    <t>E2 Revisión</t>
-  </si>
-  <si>
-    <t>E2 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E2 F. Real</t>
+    <t>Angelica Ramirez</t>
   </si>
   <si>
     <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
   </si>
   <si>
-    <t>E3 Repositorio</t>
-  </si>
-  <si>
-    <t>E3 F. Compromiso</t>
+    <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
     <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
   </si>
   <si>
-    <t>E3 F. Real</t>
-  </si>
-  <si>
-    <t>E4 Sandbox</t>
-  </si>
-  <si>
-    <t>E4 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E4 F. Real</t>
+    <t>Llenado completado</t>
   </si>
   <si>
     <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
-    <t>E5 Productivo</t>
-  </si>
-  <si>
-    <t>E5 F. Compromiso</t>
-  </si>
-  <si>
-    <t>E5 F. Real</t>
-  </si>
-  <si>
     <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
   </si>
   <si>
-    <t>Etapa #</t>
-  </si>
-  <si>
-    <t>Etapa Actual</t>
-  </si>
-  <si>
     <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
-    <t>Próx. Compromiso</t>
-  </si>
-  <si>
     <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
-    <t>Días Restantes</t>
-  </si>
-  <si>
-    <t>Semáforo</t>
-  </si>
-  <si>
-    <t>Observaciones / Bloqueos</t>
-  </si>
-  <si>
-    <t>FIN-01</t>
-  </si>
-  <si>
     <t>VTA-01</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Clases</t>
-  </si>
-  <si>
     <t>300 MX Clientes (Final)</t>
   </si>
   <si>
-    <t>Angelica Ramirez</t>
-  </si>
-  <si>
     <t>Itzel Bárcena</t>
   </si>
   <si>
     <t>Revisor / Consultor</t>
   </si>
   <si>
+    <t>Llenado en proceso</t>
+  </si>
+  <si>
     <t>Brandon Hernández</t>
   </si>
   <si>
-    <t xml:space="preserve">Fredy Sanchez </t>
-  </si>
-  <si>
     <t>15/05/2026</t>
   </si>
   <si>
@@ -452,10 +458,13 @@
     <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
   </si>
   <si>
-    <t>Llenado completado</t>
-  </si>
-  <si>
-    <t>Llenado en proceso</t>
+    <t>Sin iniciar</t>
+  </si>
+  <si>
+    <t>Bloqueadas</t>
+  </si>
+  <si>
+    <t>Vencidas</t>
   </si>
   <si>
     <t>FIN-02</t>
@@ -464,10 +473,25 @@
     <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
   </si>
   <si>
-    <t>Sin iniciar</t>
-  </si>
-  <si>
-    <t>Bloqueadas</t>
+    <t>En riesgo (≤7 días)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Sin fecha compromiso</t>
+  </si>
+  <si>
+    <t>Cerradas (productivo)</t>
+  </si>
+  <si>
+    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>% del total</t>
   </si>
   <si>
     <t>FIN-03</t>
@@ -476,46 +500,22 @@
     <t>ESTEVEZ - Departamentos</t>
   </si>
   <si>
-    <t>Vencidas</t>
-  </si>
-  <si>
     <t>FIN-04</t>
   </si>
   <si>
     <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
-    <t>En riesgo (≤7 días)</t>
-  </si>
-  <si>
     <t>FIN-05</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
     <t>ESTEVEZ - Ubicaciones</t>
   </si>
   <si>
-    <t>Sin fecha compromiso</t>
-  </si>
-  <si>
-    <t>Cerradas (productivo)</t>
-  </si>
-  <si>
-    <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
-  </si>
-  <si>
     <t>FIN-06</t>
   </si>
   <si>
     <t>ESTEVEZ - Impuestos y Retenciones MX</t>
-  </si>
-  <si>
-    <t>Etapa</t>
-  </si>
-  <si>
-    <t>% del total</t>
   </si>
   <si>
     <t>CMP-01</t>
@@ -870,13 +870,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="11.0"/>
       <color rgb="FF0B2A4A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -887,7 +882,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="15.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
     </font>
@@ -897,16 +892,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font/>
-    <font>
-      <i/>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -921,16 +914,23 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font/>
     <font>
-      <b/>
-      <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
+      <i/>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -1018,16 +1018,16 @@
       <bottom/>
     </border>
     <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
+      <left/>
       <right/>
       <top/>
       <bottom/>
     </border>
     <border>
-      <left/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <right/>
       <top/>
       <bottom/>
@@ -1079,62 +1079,59 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1145,6 +1142,9 @@
     <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1169,7 +1169,7 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1513,329 +1513,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="str">
+      <c r="A3" s="10" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 03/10/2026</v>
+        <v> Actualizado al: 09/10/2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="11"/>
       <c r="E5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="20">
+        <v>27</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="18">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>84</v>
+      <c r="E6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="24">
+        <v>68</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="22">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3682926829</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="28">
+        <v>0.4475609756</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.75</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="20">
+        <v>127</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>16</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="28">
+        <v>23</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.525</v>
-      </c>
-      <c r="H8" s="28">
+        <v>0.625</v>
+      </c>
+      <c r="H8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="I8" s="28">
+        <v>2</v>
+      </c>
+      <c r="I8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="20">
+        <v>136</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
-        <v>25</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="28">
+        <v>18</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3</v>
-      </c>
-      <c r="H9" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="I9" s="28">
+        <v>3</v>
+      </c>
+      <c r="I9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="20">
+        <v>143</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="18">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="28">
+      <c r="E10" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.2652173913</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="20">
+        <v>144</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="28">
+      <c r="E11" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3416666667</v>
-      </c>
-      <c r="H11" s="28">
+        <v>0.75</v>
+      </c>
+      <c r="H11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
-        <v>2</v>
-      </c>
-      <c r="I11" s="28">
+        <v>6</v>
+      </c>
+      <c r="I11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="28">
+        <v>6</v>
+      </c>
+      <c r="J11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="28">
+        <v>6</v>
+      </c>
+      <c r="K11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="20">
+        <v>145</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
-        <v>33</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="28">
+        <v>28</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="27">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="20">
+        <v>148</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F13" s="43">
         <f>SUM(F7:F12)</f>
@@ -1843,19 +1843,19 @@
       </c>
       <c r="G13" s="44">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.3682926829</v>
+        <v>0.4475609756</v>
       </c>
       <c r="H13" s="43">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I13" s="43">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" s="43">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K13" s="43">
         <f t="shared" si="1"/>
@@ -1868,116 +1868,116 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="20">
+        <v>150</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="20">
+        <v>151</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="18">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
+        <v>152</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19">
       <c r="E19" s="45" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="28">
+      <c r="E20" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
-        <v>25</v>
-      </c>
-      <c r="G20" s="33">
+        <v>18</v>
+      </c>
+      <c r="G20" s="27">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
-        <v>0.6097560976</v>
+        <v>0.4390243902</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="28">
+      <c r="E21" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
-        <v>8</v>
-      </c>
-      <c r="G21" s="33">
+        <v>10</v>
+      </c>
+      <c r="G21" s="27">
         <f t="shared" si="2"/>
-        <v>0.1951219512</v>
+        <v>0.243902439</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="28">
+      <c r="E22" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="28">
+      <c r="E23" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
-        <v>8</v>
-      </c>
-      <c r="G23" s="33">
+        <v>13</v>
+      </c>
+      <c r="G23" s="27">
         <f t="shared" si="2"/>
-        <v>0.1951219512</v>
+        <v>0.3170731707</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="28">
+      <c r="E24" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" s="28">
+      <c r="E25" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2983,7 +2983,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2991,362 +2991,362 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>7</v>
+      <c r="A4" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>12</v>
+      <c r="A5" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="s">
-        <v>15</v>
+      <c r="A6" s="14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="s">
-        <v>18</v>
+      <c r="A7" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>26</v>
+      <c r="A10" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="s">
-        <v>30</v>
+      <c r="A11" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>32</v>
+      <c r="A12" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="s">
-        <v>35</v>
+      <c r="A13" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>39</v>
+      <c r="A14" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="s">
-        <v>42</v>
+      <c r="A15" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="9"/>
+        <v>66</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>53</v>
+      <c r="A18" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="s">
-        <v>56</v>
+      <c r="A19" s="14" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>59</v>
+      <c r="A20" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="11" t="s">
-        <v>60</v>
+      <c r="A21" s="14" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>64</v>
+      <c r="A22" s="14" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="9"/>
+        <v>79</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="11" t="s">
-        <v>68</v>
+      <c r="A25" s="14" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>69</v>
+      <c r="A26" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="11" t="s">
-        <v>71</v>
+      <c r="A27" s="14" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>73</v>
+      <c r="A28" s="14" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>75</v>
+      <c r="A29" s="14" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>79</v>
+      <c r="A30" s="14" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="9"/>
+        <v>105</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>88</v>
+      <c r="A33" s="14" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>89</v>
+      <c r="A34" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>93</v>
+      <c r="A35" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>95</v>
+      <c r="A36" s="14" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="11" t="s">
-        <v>97</v>
+      <c r="A37" s="14" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="11" t="s">
-        <v>105</v>
+      <c r="A40" s="14" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="11" t="s">
-        <v>108</v>
+      <c r="A41" s="14" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="11" t="s">
-        <v>113</v>
+      <c r="A42" s="14" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="11" t="s">
-        <v>117</v>
+      <c r="A43" s="14" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="11" t="s">
-        <v>120</v>
+      <c r="A44" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="9"/>
+        <v>131</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
+      <c r="A47" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
+      <c r="A48" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="27" t="s">
+      <c r="C54" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
+      <c r="C57" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C58" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
+      <c r="A58" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4370,245 +4370,245 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="10" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="10" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="14">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="12">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.0</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="14">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4">
         <v>1.0</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4">
         <v>0.0</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="14">
+      <c r="K9" s="4"/>
+      <c r="L9" s="12">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5633,240 +5633,240 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="11"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="V2" s="9"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="11"/>
+    </row>
+    <row r="3" ht="33.75" customHeight="1">
+      <c r="A3" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="S2" s="7"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V2" s="7"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="9"/>
-    </row>
-    <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="K3" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="L3" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="N3" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="22" t="s">
+      <c r="O3" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="R3" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="S3" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="T3" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="U3" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="V3" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="W3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="X3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y3" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="Z3" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA3" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="AB3" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="AC3" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="U3" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="V3" s="22" t="s">
+      <c r="AD3" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="W3" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="22" t="s">
+      <c r="B4" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA3" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB3" s="22" t="s">
+      <c r="D4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AC3" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD3" s="22" t="s">
+      <c r="G4" s="32" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="36">
+      <c r="H4" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="36">
+      <c r="L4" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="36">
+      <c r="O4" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="33">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="26">
+      <c r="R4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="28">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,43 +5882,43 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="26" t="str">
+      <c r="AB4" s="28" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="26" t="str">
+      <c r="AC4" s="28" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="31"/>
+      <c r="AD4" s="29"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>28</v>
+      <c r="A5" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J5" s="41">
         <v>46282.0</v>
@@ -5927,26 +5927,26 @@
         <v>46298.0</v>
       </c>
       <c r="L5" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="36"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P5" s="41"/>
-      <c r="Q5" s="36"/>
+      <c r="Q5" s="33"/>
       <c r="R5" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="26">
+        <v>13</v>
+      </c>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5962,79 +5962,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="26" t="str">
+      <c r="AB5" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC5" s="26" t="str">
+      <c r="AC5" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD5" s="31"/>
+      <c r="AD5" s="29"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="36">
+      <c r="A6" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="36">
+      <c r="L6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="36">
+      <c r="O6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="33">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="26">
+      <c r="R6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6050,79 +6050,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="26" t="str">
+      <c r="AB6" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="26" t="str">
+      <c r="AC6" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="31"/>
+      <c r="AD6" s="29"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="36">
+      <c r="A7" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="36">
+      <c r="L7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="36">
+      <c r="O7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="Q7" s="36">
+      <c r="Q7" s="33">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="26">
+      <c r="R7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6138,50 +6138,50 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="26" t="str">
+      <c r="AB7" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="26" t="str">
+      <c r="AC7" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="31"/>
+      <c r="AD7" s="29"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>28</v>
+      <c r="A8" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J8" s="41">
         <v>46302.0</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M8" s="41">
         <v>46283.0</v>
@@ -6190,7 +6190,7 @@
         <v>46283.0</v>
       </c>
       <c r="O8" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P8" s="41">
         <v>46283.0</v>
@@ -6198,17 +6198,17 @@
       <c r="Q8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="R8" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="26">
+      <c r="R8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6224,79 +6224,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="26" t="str">
+      <c r="AB8" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="26" t="str">
+      <c r="AC8" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="31"/>
+      <c r="AD8" s="29"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="36">
+      <c r="A9" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="33">
         <v>46274.0</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="33">
         <v>46274.0</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="36">
+        <v>30</v>
+      </c>
+      <c r="M9" s="33">
         <v>46277.0</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="33">
         <v>46277.0</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" s="36">
+        <v>30</v>
+      </c>
+      <c r="P9" s="33">
         <v>46277.0</v>
       </c>
-      <c r="Q9" s="36">
+      <c r="Q9" s="33">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="26">
+      <c r="R9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6312,52 +6312,52 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="26" t="str">
+      <c r="AB9" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="26" t="str">
+      <c r="AC9" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="31"/>
+      <c r="AD9" s="29"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>29</v>
+      <c r="E10" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>28</v>
+      <c r="H10" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="36">
+        <v>30</v>
+      </c>
+      <c r="J10" s="33">
         <v>46272.0</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="33">
         <v>46272.0</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M10" s="41">
         <v>46277.0</v>
@@ -6366,111 +6366,111 @@
         <v>46277.0</v>
       </c>
       <c r="O10" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="P10" s="36">
+        <v>13</v>
+      </c>
+      <c r="P10" s="33">
         <v>46277.0</v>
       </c>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="26">
+      <c r="Q10" s="33"/>
+      <c r="R10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="37" t="str">
         <f t="array" ref="Y10">INDEX(Cat_Etapas,$X10)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z10" s="38">
         <f t="array" ref="Z10">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I10,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L10,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O10,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R10,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U10,Cat_Estatus,0)),0),4)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AA10" s="39">
         <f t="shared" si="2"/>
-        <v>46272</v>
-      </c>
-      <c r="AB10" s="26">
+        <v>46277</v>
+      </c>
+      <c r="AB10" s="28">
         <f t="shared" si="3"/>
-        <v>-26</v>
-      </c>
-      <c r="AC10" s="26" t="str">
+        <v>-27</v>
+      </c>
+      <c r="AC10" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD10" s="31"/>
+      <c r="AD10" s="29"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="34" t="s">
+      <c r="E11" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="36">
+      <c r="H11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="33">
         <v>46268.0</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="33">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="36">
+      <c r="L11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="33">
         <v>46269.0</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="33">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="36">
+      <c r="O11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="33">
         <v>46269.0</v>
       </c>
-      <c r="Q11" s="36">
+      <c r="Q11" s="33">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="26">
+      <c r="R11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6486,75 +6486,75 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="26" t="str">
+      <c r="AB11" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="26" t="str">
+      <c r="AC11" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="31"/>
+      <c r="AD11" s="29"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="30" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>37</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="36">
+      <c r="H12" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="33">
         <v>46274.0</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="33">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="36">
+      <c r="L12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="33">
         <v>46277.0</v>
       </c>
-      <c r="N12" s="36"/>
-      <c r="O12" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P12" s="36">
+      <c r="N12" s="33"/>
+      <c r="O12" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="26">
+      <c r="Q12" s="33"/>
+      <c r="R12" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6570,237 +6570,239 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC12" s="26" t="str">
+        <v>-27</v>
+      </c>
+      <c r="AC12" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD12" s="31"/>
+      <c r="AD12" s="29"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="30" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="36">
+      <c r="H13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="33">
         <v>46277.0</v>
       </c>
-      <c r="K13" s="36"/>
-      <c r="L13" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="36">
+      <c r="K13" s="41">
+        <v>46303.0</v>
+      </c>
+      <c r="L13" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="33">
         <v>46277.0</v>
       </c>
-      <c r="N13" s="36"/>
-      <c r="O13" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P13" s="36">
+      <c r="N13" s="33"/>
+      <c r="O13" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="26">
+      <c r="Q13" s="33"/>
+      <c r="R13" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="37" t="str">
         <f t="array" ref="Y13">INDEX(Cat_Etapas,$X13)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>2. Revisión y validación</v>
       </c>
       <c r="Z13" s="38">
         <f t="array" ref="Z13">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I13,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L13,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O13,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R13,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U13,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA13" s="39">
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="26">
+      <c r="AB13" s="28">
+        <f t="shared" si="3"/>
+        <v>-27</v>
+      </c>
+      <c r="AC13" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v>Vencido</v>
+      </c>
+      <c r="AD13" s="29"/>
+    </row>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="33">
+        <v>46277.0</v>
+      </c>
+      <c r="K14" s="33"/>
+      <c r="L14" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="33">
+        <v>46283.0</v>
+      </c>
+      <c r="N14" s="33"/>
+      <c r="O14" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="33">
+        <v>46276.0</v>
+      </c>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="28">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y14" s="37" t="str">
+        <f t="array" ref="Y14">INDEX(Cat_Etapas,$X14)</f>
+        <v>2. Revisión y validación</v>
+      </c>
+      <c r="Z14" s="38">
+        <f t="array" ref="Z14">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I14,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L14,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O14,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R14,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U14,Cat_Estatus,0)),0),4)</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA14" s="39">
+        <f t="shared" si="2"/>
+        <v>46283</v>
+      </c>
+      <c r="AB14" s="28">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC13" s="26" t="str">
+      <c r="AC14" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD13" s="31"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="32" t="s">
+      <c r="AD14" s="29"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1">
+      <c r="A15" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="36">
-        <v>46277.0</v>
-      </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="36">
+      <c r="C15" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N14" s="36"/>
-      <c r="O14" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="36">
+      <c r="K15" s="33"/>
+      <c r="L15" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="33">
+        <v>46283.0</v>
+      </c>
+      <c r="N15" s="33"/>
+      <c r="O15" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y14" s="37" t="str">
-        <f t="array" ref="Y14">INDEX(Cat_Etapas,$X14)</f>
-        <v>1. Llenado de plantilla</v>
-      </c>
-      <c r="Z14" s="38">
-        <f t="array" ref="Z14">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I14,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L14,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O14,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R14,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U14,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA14" s="39">
-        <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB14" s="26">
-        <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC14" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD14" s="31"/>
-    </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="36">
-        <v>46283.0</v>
-      </c>
-      <c r="K15" s="36"/>
-      <c r="L15" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="36">
-        <v>46283.0</v>
-      </c>
-      <c r="N15" s="36"/>
-      <c r="O15" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="36">
-        <v>46276.0</v>
-      </c>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S15" s="36"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="26">
+      <c r="Q15" s="33"/>
+      <c r="R15" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6816,73 +6818,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC15" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC15" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD15" s="31"/>
+      <c r="AD15" s="29"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="35" t="s">
+      <c r="E16" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="26" t="s">
-        <v>28</v>
+      <c r="H16" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="36">
+        <v>30</v>
+      </c>
+      <c r="J16" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K16" s="36"/>
+      <c r="K16" s="33"/>
       <c r="L16" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="36">
+        <v>22</v>
+      </c>
+      <c r="M16" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N16" s="36"/>
-      <c r="O16" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="36">
+      <c r="N16" s="33"/>
+      <c r="O16" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="26">
+      <c r="Q16" s="33"/>
+      <c r="R16" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6898,73 +6900,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="26">
+      <c r="AB16" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC16" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC16" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD16" s="31"/>
+      <c r="AD16" s="29"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="35" t="s">
+      <c r="E17" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>28</v>
+      <c r="H17" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="36">
+        <v>30</v>
+      </c>
+      <c r="J17" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K17" s="36"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="36">
+        <v>22</v>
+      </c>
+      <c r="M17" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N17" s="36"/>
-      <c r="O17" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P17" s="36">
+      <c r="N17" s="33"/>
+      <c r="O17" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="26">
+      <c r="Q17" s="33"/>
+      <c r="R17" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6980,73 +6982,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="26">
+      <c r="AB17" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC17" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC17" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD17" s="31"/>
+      <c r="AD17" s="29"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="B18" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="35" t="s">
+      <c r="E18" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="36">
+      <c r="H18" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K18" s="36"/>
-      <c r="L18" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" s="36">
+      <c r="K18" s="33"/>
+      <c r="L18" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N18" s="36"/>
-      <c r="O18" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P18" s="36">
+      <c r="N18" s="33"/>
+      <c r="O18" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="26">
+      <c r="Q18" s="33"/>
+      <c r="R18" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7062,73 +7064,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="26">
+      <c r="AB18" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC18" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC18" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD18" s="31"/>
+      <c r="AD18" s="29"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="B19" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="35" t="s">
+      <c r="E19" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="26" t="s">
-        <v>28</v>
+      <c r="H19" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="36">
+        <v>30</v>
+      </c>
+      <c r="J19" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K19" s="36"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="36">
+        <v>22</v>
+      </c>
+      <c r="M19" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N19" s="36"/>
-      <c r="O19" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P19" s="36">
+      <c r="N19" s="33"/>
+      <c r="O19" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="26">
+      <c r="Q19" s="33"/>
+      <c r="R19" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7144,73 +7146,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="26">
+      <c r="AB19" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC19" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC19" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD19" s="31"/>
+      <c r="AD19" s="29"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="26" t="s">
+      <c r="B20" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="35" t="s">
+      <c r="E20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="36">
+      <c r="H20" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="36">
+      <c r="K20" s="33"/>
+      <c r="L20" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N20" s="36"/>
-      <c r="O20" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P20" s="36">
+      <c r="N20" s="33"/>
+      <c r="O20" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="26">
+      <c r="Q20" s="33"/>
+      <c r="R20" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="33"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7226,73 +7228,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="26">
+      <c r="AB20" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC20" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC20" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD20" s="31"/>
+      <c r="AD20" s="29"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="26" t="s">
+      <c r="B21" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="35" t="s">
+      <c r="E21" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>28</v>
+      <c r="H21" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="36">
+        <v>30</v>
+      </c>
+      <c r="J21" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K21" s="36"/>
+      <c r="K21" s="33"/>
       <c r="L21" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="36">
+        <v>22</v>
+      </c>
+      <c r="M21" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N21" s="36"/>
-      <c r="O21" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="36">
+      <c r="N21" s="33"/>
+      <c r="O21" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="26">
+      <c r="Q21" s="33"/>
+      <c r="R21" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7308,73 +7310,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="26">
+      <c r="AB21" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC21" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC21" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD21" s="31"/>
+      <c r="AD21" s="29"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="B22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="35" t="s">
+      <c r="E22" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="36">
+      <c r="H22" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="36">
+      <c r="K22" s="33"/>
+      <c r="L22" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N22" s="36"/>
-      <c r="O22" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="36">
+      <c r="N22" s="33"/>
+      <c r="O22" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="26">
+      <c r="Q22" s="33"/>
+      <c r="R22" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7390,73 +7392,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="26">
+      <c r="AB22" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC22" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC22" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD22" s="31"/>
+      <c r="AD22" s="29"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="26" t="s">
+      <c r="B23" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="35" t="s">
+      <c r="E23" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" s="36">
+      <c r="H23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K23" s="36"/>
-      <c r="L23" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="36">
+      <c r="K23" s="33"/>
+      <c r="L23" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N23" s="36"/>
-      <c r="O23" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P23" s="36">
+      <c r="N23" s="33"/>
+      <c r="O23" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P23" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S23" s="36"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="26">
+      <c r="Q23" s="33"/>
+      <c r="R23" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7472,73 +7474,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="26">
+      <c r="AB23" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC23" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC23" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD23" s="31"/>
+      <c r="AD23" s="29"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="26" t="s">
+      <c r="B24" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="35" t="s">
+      <c r="E24" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="H24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K24" s="36"/>
-      <c r="L24" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="36">
+      <c r="K24" s="33"/>
+      <c r="L24" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N24" s="36"/>
-      <c r="O24" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P24" s="36">
+      <c r="N24" s="33"/>
+      <c r="O24" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S24" s="36"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="26">
+      <c r="Q24" s="33"/>
+      <c r="R24" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7554,73 +7556,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="26">
+      <c r="AB24" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC24" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC24" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD24" s="31"/>
+      <c r="AD24" s="29"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="26" t="s">
+      <c r="B25" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="35" t="s">
+      <c r="E25" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" s="36">
+      <c r="H25" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="36">
+      <c r="K25" s="33"/>
+      <c r="L25" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N25" s="36"/>
-      <c r="O25" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P25" s="36">
+      <c r="N25" s="33"/>
+      <c r="O25" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="26">
+      <c r="Q25" s="33"/>
+      <c r="R25" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7636,73 +7638,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="26">
+      <c r="AB25" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC25" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC25" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD25" s="31"/>
+      <c r="AD25" s="29"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="26" t="s">
+      <c r="B26" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" s="35" t="s">
+      <c r="E26" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="36">
+      <c r="H26" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M26" s="36">
+      <c r="K26" s="33"/>
+      <c r="L26" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N26" s="36"/>
-      <c r="O26" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P26" s="36">
+      <c r="N26" s="33"/>
+      <c r="O26" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="26">
+      <c r="Q26" s="33"/>
+      <c r="R26" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7718,73 +7720,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="26">
+      <c r="AB26" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC26" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC26" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD26" s="31"/>
+      <c r="AD26" s="29"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="B27" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="35" t="s">
+      <c r="E27" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="36">
+      <c r="H27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K27" s="36"/>
-      <c r="L27" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M27" s="36">
+      <c r="K27" s="33"/>
+      <c r="L27" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N27" s="36"/>
-      <c r="O27" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P27" s="36">
+      <c r="N27" s="33"/>
+      <c r="O27" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P27" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="26">
+      <c r="Q27" s="33"/>
+      <c r="R27" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7800,73 +7802,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="26">
+      <c r="AB27" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC27" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC27" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD27" s="31"/>
+      <c r="AD27" s="29"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="26" t="s">
+      <c r="B28" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="35" t="s">
+      <c r="E28" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="36">
+      <c r="H28" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M28" s="36">
+      <c r="K28" s="33"/>
+      <c r="L28" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N28" s="36"/>
-      <c r="O28" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P28" s="36">
+      <c r="N28" s="33"/>
+      <c r="O28" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S28" s="36"/>
-      <c r="T28" s="36"/>
-      <c r="U28" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="26">
+      <c r="Q28" s="33"/>
+      <c r="R28" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7882,73 +7884,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="26">
+      <c r="AB28" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC28" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC28" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD28" s="31"/>
+      <c r="AD28" s="29"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="26" t="s">
+      <c r="B29" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="35" t="s">
+      <c r="E29" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="36">
+      <c r="H29" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K29" s="36"/>
-      <c r="L29" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M29" s="36">
+      <c r="K29" s="33"/>
+      <c r="L29" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N29" s="36"/>
-      <c r="O29" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P29" s="36">
+      <c r="N29" s="33"/>
+      <c r="O29" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q29" s="36"/>
-      <c r="R29" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S29" s="36"/>
-      <c r="T29" s="36"/>
-      <c r="U29" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
-      <c r="X29" s="26">
+      <c r="Q29" s="33"/>
+      <c r="R29" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7964,73 +7966,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="26">
+      <c r="AB29" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC29" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC29" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD29" s="31"/>
+      <c r="AD29" s="29"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="26" t="s">
+      <c r="B30" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="35" t="s">
+      <c r="E30" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="36">
+      <c r="H30" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K30" s="36"/>
-      <c r="L30" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M30" s="36">
+      <c r="K30" s="33"/>
+      <c r="L30" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N30" s="36"/>
-      <c r="O30" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P30" s="36">
+      <c r="N30" s="33"/>
+      <c r="O30" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="26">
+      <c r="Q30" s="33"/>
+      <c r="R30" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8046,73 +8048,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="26">
+      <c r="AB30" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC30" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC30" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD30" s="31"/>
+      <c r="AD30" s="29"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="26" t="s">
+      <c r="B31" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="35" t="s">
+      <c r="E31" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="35" t="s">
+      <c r="G31" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="36">
+      <c r="H31" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K31" s="36"/>
-      <c r="L31" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="36">
+      <c r="K31" s="33"/>
+      <c r="L31" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N31" s="36"/>
-      <c r="O31" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P31" s="36">
+      <c r="N31" s="33"/>
+      <c r="O31" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P31" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q31" s="36"/>
-      <c r="R31" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S31" s="36"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="26">
+      <c r="Q31" s="33"/>
+      <c r="R31" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8128,73 +8130,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="26">
+      <c r="AB31" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC31" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC31" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD31" s="31"/>
+      <c r="AD31" s="29"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="26" t="s">
+      <c r="B32" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="35" t="s">
+      <c r="E32" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="35" t="s">
+      <c r="G32" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="36">
+      <c r="H32" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M32" s="36">
+      <c r="K32" s="33"/>
+      <c r="L32" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N32" s="36"/>
-      <c r="O32" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P32" s="36">
+      <c r="N32" s="33"/>
+      <c r="O32" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P32" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="26">
+      <c r="Q32" s="33"/>
+      <c r="R32" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S32" s="33"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8210,73 +8212,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="26">
+      <c r="AB32" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC32" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC32" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD32" s="31"/>
+      <c r="AD32" s="29"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="26" t="s">
+      <c r="B33" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="35" t="s">
+      <c r="E33" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="36">
+      <c r="H33" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33" s="36">
+      <c r="K33" s="33"/>
+      <c r="L33" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P33" s="36">
+      <c r="N33" s="33"/>
+      <c r="O33" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P33" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="26">
+      <c r="Q33" s="33"/>
+      <c r="R33" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+      <c r="U33" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8292,73 +8294,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="26">
+      <c r="AB33" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC33" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC33" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD33" s="31"/>
+      <c r="AD33" s="29"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="26" t="s">
+      <c r="B34" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" s="35" t="s">
+      <c r="E34" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="35" t="s">
+      <c r="G34" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" s="36">
+      <c r="H34" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M34" s="36">
+      <c r="K34" s="33"/>
+      <c r="L34" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N34" s="36"/>
-      <c r="O34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P34" s="36">
+      <c r="N34" s="33"/>
+      <c r="O34" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="26">
+      <c r="Q34" s="33"/>
+      <c r="R34" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8374,73 +8376,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="26">
+      <c r="AB34" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC34" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC34" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD34" s="31"/>
+      <c r="AD34" s="29"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="26" t="s">
+      <c r="B35" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="35" t="s">
+      <c r="E35" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" s="36">
+      <c r="H35" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K35" s="36"/>
-      <c r="L35" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="36">
+      <c r="K35" s="33"/>
+      <c r="L35" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N35" s="36"/>
-      <c r="O35" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P35" s="36">
+      <c r="N35" s="33"/>
+      <c r="O35" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="26">
+      <c r="Q35" s="33"/>
+      <c r="R35" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8456,73 +8458,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="26">
+      <c r="AB35" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC35" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC35" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD35" s="31"/>
+      <c r="AD35" s="29"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="26" t="s">
+      <c r="B36" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" s="35" t="s">
+      <c r="E36" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="35" t="s">
+      <c r="G36" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="36">
+      <c r="H36" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K36" s="36"/>
-      <c r="L36" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M36" s="36">
+      <c r="K36" s="33"/>
+      <c r="L36" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N36" s="36"/>
-      <c r="O36" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P36" s="36">
+      <c r="N36" s="33"/>
+      <c r="O36" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="26">
+      <c r="Q36" s="33"/>
+      <c r="R36" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8538,73 +8540,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="26">
+      <c r="AB36" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC36" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC36" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD36" s="31"/>
+      <c r="AD36" s="29"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="26" t="s">
+      <c r="B37" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" s="35" t="s">
+      <c r="E37" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G37" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="36">
+      <c r="H37" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K37" s="36"/>
-      <c r="L37" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M37" s="36">
+      <c r="K37" s="33"/>
+      <c r="L37" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N37" s="36"/>
-      <c r="O37" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P37" s="36">
+      <c r="N37" s="33"/>
+      <c r="O37" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q37" s="36"/>
-      <c r="R37" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
-      <c r="U37" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="26">
+      <c r="Q37" s="33"/>
+      <c r="R37" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8620,491 +8622,491 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="26">
+      <c r="AB37" s="28">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC37" s="26" t="str">
+        <v>-21</v>
+      </c>
+      <c r="AC37" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD37" s="31"/>
+      <c r="AD37" s="29"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" s="34" t="s">
+      <c r="E38" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>33</v>
+      <c r="H38" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J38" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K38" s="36">
+      <c r="K38" s="33">
         <v>46276.0</v>
       </c>
-      <c r="L38" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" s="36">
+      <c r="L38" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N38" s="36"/>
-      <c r="O38" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P38" s="36">
+      <c r="N38" s="33"/>
+      <c r="O38" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" s="33">
         <v>46277.0</v>
       </c>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S38" s="36"/>
-      <c r="T38" s="36"/>
-      <c r="U38" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="26">
+      <c r="Q38" s="33"/>
+      <c r="R38" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="37" t="str">
         <f t="array" ref="Y38">INDEX(Cat_Etapas,$X38)</f>
-        <v>2. Revisión y validación</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z38" s="38">
         <f t="array" ref="Z38">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I38,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L38,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O38,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R38,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U38,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA38" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA38" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB38" s="26">
+        <v/>
+      </c>
+      <c r="AB38" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC38" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC38" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD38" s="31"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD38" s="29"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="26" t="s">
+      <c r="B39" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" s="34" t="s">
+      <c r="E39" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="35" t="s">
+      <c r="G39" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="36">
+      <c r="H39" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K39" s="36"/>
-      <c r="L39" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M39" s="36">
+      <c r="K39" s="33"/>
+      <c r="L39" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N39" s="36"/>
-      <c r="O39" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P39" s="36">
+      <c r="N39" s="33"/>
+      <c r="O39" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="33">
         <v>46283.0</v>
       </c>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
-      <c r="U39" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="26">
+      <c r="Q39" s="33"/>
+      <c r="R39" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="37" t="str">
         <f t="array" ref="Y39">INDEX(Cat_Etapas,$X39)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z39" s="38">
         <f t="array" ref="Z39">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I39,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L39,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O39,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R39,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U39,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA39" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA39" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB39" s="26">
+        <v/>
+      </c>
+      <c r="AB39" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC39" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC39" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD39" s="31"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD39" s="29"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="26" t="s">
+      <c r="B40" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" s="34" t="s">
+      <c r="E40" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J40" s="36">
+      <c r="H40" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K40" s="36"/>
-      <c r="L40" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M40" s="36">
+      <c r="K40" s="33"/>
+      <c r="L40" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N40" s="36"/>
-      <c r="O40" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P40" s="36">
+      <c r="N40" s="33"/>
+      <c r="O40" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="33">
         <v>46283.0</v>
       </c>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S40" s="36"/>
-      <c r="T40" s="36"/>
-      <c r="U40" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="26">
+      <c r="Q40" s="33"/>
+      <c r="R40" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y40" s="37" t="str">
         <f t="array" ref="Y40">INDEX(Cat_Etapas,$X40)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z40" s="38">
         <f t="array" ref="Z40">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I40,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L40,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O40,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R40,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U40,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA40" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA40" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB40" s="26">
+        <v/>
+      </c>
+      <c r="AB40" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC40" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC40" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD40" s="31"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD40" s="29"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="26" t="s">
+      <c r="B41" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="34" t="s">
+      <c r="E41" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="35" t="s">
+      <c r="G41" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" s="36">
+      <c r="H41" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K41" s="36"/>
-      <c r="L41" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M41" s="36">
+      <c r="K41" s="33"/>
+      <c r="L41" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N41" s="36"/>
-      <c r="O41" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P41" s="36">
+      <c r="N41" s="33"/>
+      <c r="O41" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="33">
         <v>46283.0</v>
       </c>
-      <c r="Q41" s="36"/>
-      <c r="R41" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
-      <c r="U41" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="26">
+      <c r="Q41" s="33"/>
+      <c r="R41" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y41" s="37" t="str">
         <f t="array" ref="Y41">INDEX(Cat_Etapas,$X41)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z41" s="38">
         <f t="array" ref="Z41">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I41,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L41,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O41,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R41,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U41,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA41" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA41" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB41" s="26">
+        <v/>
+      </c>
+      <c r="AB41" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC41" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC41" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD41" s="31"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD41" s="29"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="26" t="s">
+      <c r="B42" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42" s="34" t="s">
+      <c r="E42" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="36">
+      <c r="H42" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" s="33">
         <v>46283.0</v>
       </c>
-      <c r="K42" s="36"/>
-      <c r="L42" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M42" s="36">
+      <c r="K42" s="33"/>
+      <c r="L42" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42" s="33">
         <v>46283.0</v>
       </c>
-      <c r="N42" s="36"/>
-      <c r="O42" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P42" s="36">
+      <c r="N42" s="33"/>
+      <c r="O42" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" s="33">
         <v>46283.0</v>
       </c>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S42" s="36"/>
-      <c r="T42" s="36"/>
-      <c r="U42" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
-      <c r="X42" s="26">
+      <c r="Q42" s="33"/>
+      <c r="R42" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="33"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="37" t="str">
         <f t="array" ref="Y42">INDEX(Cat_Etapas,$X42)</f>
-        <v>1. Llenado de plantilla</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z42" s="38">
         <f t="array" ref="Z42">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I42,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L42,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O42,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R42,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U42,Cat_Estatus,0)),0),4)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA42" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA42" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB42" s="26">
+        <v/>
+      </c>
+      <c r="AB42" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-15</v>
-      </c>
-      <c r="AC42" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC42" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD42" s="31"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD42" s="29"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="26" t="s">
+      <c r="B43" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F43" s="34" t="s">
+      <c r="E43" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G43" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>33</v>
+      <c r="H43" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J43" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K43" s="36">
+      <c r="K43" s="33">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="26" t="s">
-        <v>33</v>
+      <c r="L43" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M43" s="41">
         <v>46277.0</v>
       </c>
-      <c r="N43" s="36">
+      <c r="N43" s="33">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P43" s="36">
+      <c r="O43" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="33">
         <v>46276.0</v>
       </c>
-      <c r="Q43" s="36">
+      <c r="Q43" s="33">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
-      <c r="U43" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="26">
+      <c r="R43" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9120,73 +9122,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="26" t="str">
+      <c r="AB43" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="26" t="str">
+      <c r="AC43" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="31"/>
+      <c r="AD43" s="29"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="26" t="s">
+      <c r="B44" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="F44" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G44" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>33</v>
+      <c r="E44" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J44" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K44" s="36">
+      <c r="K44" s="33">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="36">
+      <c r="L44" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="33">
         <v>46276.0</v>
       </c>
-      <c r="N44" s="36"/>
-      <c r="O44" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-      <c r="U44" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="26">
+      <c r="N44" s="33"/>
+      <c r="O44" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9202,15 +9204,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="26">
+      <c r="AB44" s="28">
         <f t="shared" si="3"/>
-        <v>-22</v>
-      </c>
-      <c r="AC44" s="26" t="str">
+        <v>-28</v>
+      </c>
+      <c r="AC44" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="31"/>
+      <c r="AD44" s="29"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -32,21 +32,21 @@
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
   <si>
+    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+  </si>
+  <si>
     <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
   </si>
   <si>
-    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
+  </si>
+  <si>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
   </si>
   <si>
     <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
   </si>
   <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
-  </si>
-  <si>
-    <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
-  </si>
-  <si>
     <t>Estatus</t>
   </si>
   <si>
@@ -71,163 +71,223 @@
     <t>No iniciado</t>
   </si>
   <si>
+    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
+  </si>
+  <si>
+    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
+  </si>
+  <si>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
+    <t>1. Llenado de plantilla</t>
+  </si>
+  <si>
+    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>Compras (P2P)</t>
+  </si>
+  <si>
+    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
+  </si>
+  <si>
+    <t>2. Etapas del flujo y su peso en el avance</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>INDICADORES CLAVE</t>
   </si>
   <si>
-    <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
-  </si>
-  <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
-    <t>1. Llenado de plantilla</t>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
+  </si>
+  <si>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
+  </si>
+  <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
+  </si>
+  <si>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
+  </si>
+  <si>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
   </si>
   <si>
     <t>AVANCE POR MÓDULO</t>
   </si>
   <si>
-    <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>Compras (P2P)</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
+    <t>Activos Fijos / Patrimonio</t>
+  </si>
+  <si>
+    <t>E1 · LLENADO</t>
+  </si>
+  <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
+    <t>6. Cerrado</t>
+  </si>
+  <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+  </si>
+  <si>
+    <t>E2 · REVISIÓN</t>
   </si>
   <si>
     <t>Plantillas totales</t>
   </si>
   <si>
-    <t>2. Revisión y validación</t>
-  </si>
-  <si>
-    <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
-  </si>
-  <si>
-    <t>Completado</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
-  </si>
-  <si>
-    <t>2. Etapas del flujo y su peso en el avance</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Almacén / Inventarios</t>
-  </si>
-  <si>
-    <t>4. Ambiente Sandbox</t>
-  </si>
-  <si>
-    <t>IDENTIFICACIÓN Y RESPONSABLES</t>
-  </si>
-  <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
-  </si>
-  <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
-  </si>
-  <si>
-    <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
-  </si>
-  <si>
-    <t>Activos Fijos (FA)</t>
-  </si>
-  <si>
-    <t>E1 · LLENADO</t>
-  </si>
-  <si>
-    <t>Activos Fijos / Patrimonio</t>
-  </si>
-  <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
-  </si>
-  <si>
-    <t>6. Cerrado</t>
+    <t>3. Valores de estatus permitidos</t>
+  </si>
+  <si>
+    <t>E3 · REPOSITORIO ORACLE</t>
+  </si>
+  <si>
+    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+  </si>
+  <si>
+    <t>E4 · SANDBOX</t>
+  </si>
+  <si>
+    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+  </si>
+  <si>
+    <t>E5 · PRODUCTIVO</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
+  </si>
+  <si>
+    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
+  </si>
+  <si>
+    <t>SEGUIMIENTO AUTOMÁTICO</t>
+  </si>
+  <si>
+    <t>4. Lectura del semáforo</t>
   </si>
   <si>
     <t>Módulo</t>
   </si>
   <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
+  </si>
+  <si>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
   </si>
   <si>
     <t>Plantillas</t>
   </si>
   <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
     <t>% Avance</t>
   </si>
   <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+  </si>
+  <si>
     <t>E1 Llenado OK</t>
   </si>
   <si>
-    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
+    <t>Código</t>
   </si>
   <si>
     <t>E2 Revisión OK</t>
   </si>
   <si>
-    <t>E2 · REVISIÓN</t>
+    <t>Plantilla</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
   </si>
   <si>
     <t>E3 Repositorio OK</t>
   </si>
   <si>
+    <t>Área Responsable</t>
+  </si>
+  <si>
     <t>E4 Sandbox OK</t>
   </si>
   <si>
-    <t>3. Valores de estatus permitidos</t>
+    <t>Key User</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
   </si>
   <si>
     <t>E5 Productivo OK</t>
@@ -236,72 +296,21 @@
     <t>Avance global ponderado</t>
   </si>
   <si>
-    <t>E3 · REPOSITORIO ORACLE</t>
-  </si>
-  <si>
-    <t>E4 · SANDBOX</t>
-  </si>
-  <si>
-    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
-  </si>
-  <si>
-    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
-  </si>
-  <si>
-    <t>E5 · PRODUCTIVO</t>
-  </si>
-  <si>
-    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
-  </si>
-  <si>
-    <t>SEGUIMIENTO AUTOMÁTICO</t>
+    <t>Consultor Oracle</t>
+  </si>
+  <si>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
   </si>
   <si>
     <t>PMO / Consultoría</t>
   </si>
   <si>
-    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
-  </si>
-  <si>
-    <t>4. Lectura del semáforo</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Plantilla</t>
-  </si>
-  <si>
-    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
-  </si>
-  <si>
-    <t>Área Responsable</t>
-  </si>
-  <si>
-    <t>Key User</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
-  </si>
-  <si>
-    <t>Consultor Oracle</t>
-  </si>
-  <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
+    <t>5. Conexión con el tablero HTML</t>
   </si>
   <si>
     <t>E1 Llenado</t>
   </si>
   <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
-  </si>
-  <si>
     <t>E1 F. Compromiso</t>
   </si>
   <si>
@@ -311,24 +320,24 @@
     <t>E2 Revisión</t>
   </si>
   <si>
+    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
+  </si>
+  <si>
     <t>E2 F. Compromiso</t>
   </si>
   <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
     <t>E2 F. Real</t>
   </si>
   <si>
     <t>E3 Repositorio</t>
   </si>
   <si>
+    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
+  </si>
+  <si>
     <t>E3 F. Compromiso</t>
   </si>
   <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
-  </si>
-  <si>
     <t>E3 F. Real</t>
   </si>
   <si>
@@ -344,7 +353,7 @@
     <t>E5 Productivo</t>
   </si>
   <si>
-    <t>5. Conexión con el tablero HTML</t>
+    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
   </si>
   <si>
     <t>E5 F. Compromiso</t>
@@ -356,129 +365,126 @@
     <t>Etapa #</t>
   </si>
   <si>
+    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
+  </si>
+  <si>
     <t>Etapa Actual</t>
   </si>
   <si>
+    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
+  </si>
+  <si>
     <t>Próx. Compromiso</t>
   </si>
   <si>
     <t>Días Restantes</t>
   </si>
   <si>
+    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
+  </si>
+  <si>
     <t>Semáforo</t>
   </si>
   <si>
     <t>Observaciones / Bloqueos</t>
   </si>
   <si>
-    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
-  </si>
-  <si>
     <t>FIN-01</t>
   </si>
   <si>
-    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
-  </si>
-  <si>
-    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
+    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
+  </si>
+  <si>
+    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
+  </si>
+  <si>
+    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
+  </si>
+  <si>
+    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
+  </si>
+  <si>
+    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
-    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
+    <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
     <t>ESTEVEZ - Clases</t>
   </si>
   <si>
-    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
-  </si>
-  <si>
-    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
-  </si>
-  <si>
     <t>Angelica Ramirez</t>
   </si>
   <si>
-    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
+    <t>VTA-01</t>
   </si>
   <si>
     <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
-    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
+    <t>300 MX Clientes (Final)</t>
+  </si>
+  <si>
+    <t>Itzel Bárcena</t>
+  </si>
+  <si>
+    <t>Revisor / Consultor</t>
+  </si>
+  <si>
+    <t>Brandon Hernández</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
   </si>
   <si>
     <t>Llenado completado</t>
   </si>
   <si>
-    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
-  </si>
-  <si>
-    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
-  </si>
-  <si>
-    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
-  </si>
-  <si>
-    <t>7. Ejemplo de captura correcta de una fila</t>
-  </si>
-  <si>
-    <t>VTA-01</t>
-  </si>
-  <si>
-    <t>300 MX Clientes (Final)</t>
-  </si>
-  <si>
-    <t>Itzel Bárcena</t>
-  </si>
-  <si>
-    <t>Revisor / Consultor</t>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
   </si>
   <si>
     <t>Llenado en proceso</t>
   </si>
   <si>
-    <t>Brandon Hernández</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
-    <t>Duplicidad de RFC entre dos clientes: requiere definición del área.</t>
-  </si>
-  <si>
     <t>Sin iniciar</t>
   </si>
   <si>
     <t>Bloqueadas</t>
   </si>
   <si>
+    <t>FIN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+  </si>
+  <si>
     <t>Vencidas</t>
   </si>
   <si>
-    <t>FIN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
-  </si>
-  <si>
     <t>En riesgo (≤7 días)</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
+    <t>FIN-03</t>
+  </si>
+  <si>
+    <t>ESTEVEZ - Departamentos</t>
+  </si>
+  <si>
     <t>Sin fecha compromiso</t>
   </si>
   <si>
@@ -492,12 +498,6 @@
   </si>
   <si>
     <t>% del total</t>
-  </si>
-  <si>
-    <t>FIN-03</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Departamentos</t>
   </si>
   <si>
     <t>FIN-04</t>
@@ -892,6 +892,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF667085"/>
       <name val="Arial"/>
@@ -908,23 +914,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
     <font/>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF667085"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -937,6 +932,11 @@
       <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="9.0"/>
@@ -981,14 +981,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16406B"/>
-        <bgColor rgb="FF16406B"/>
+        <fgColor rgb="FF0B2A4A"/>
+        <bgColor rgb="FF0B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B2A4A"/>
-        <bgColor rgb="FF0B2A4A"/>
+        <fgColor rgb="FF16406B"/>
+        <bgColor rgb="FF16406B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1077,78 +1077,78 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1169,7 +1169,7 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1514,28 +1514,28 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>3</v>
+      <c r="A2" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="str">
+      <c r="A3" s="13" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
         <v> Actualizado al: 09/10/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>14</v>
+      <c r="A5" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="11"/>
-      <c r="E5" s="13" t="s">
-        <v>20</v>
+      <c r="C5" s="10"/>
+      <c r="E5" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
@@ -1543,294 +1543,294 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="L5" s="11"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="18">
+      <c r="A6" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>67</v>
+      <c r="E6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="22">
+      <c r="A7" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.4475609756</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.75</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="18">
+      <c r="A8" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>23</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="24">
+      <c r="E8" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.625</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="18">
+      <c r="A9" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
         <v>18</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="24">
+      <c r="E9" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>3</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="18">
+      <c r="B10" s="19"/>
+      <c r="C10" s="20">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="24">
+      <c r="E10" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.2652173913</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="18">
+      <c r="B11" s="19"/>
+      <c r="C11" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="24">
+      <c r="E11" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.75</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="18">
+      <c r="A12" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
         <v>28</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="24">
+      <c r="E12" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="27">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="29">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="27">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
@@ -1867,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="18">
+      <c r="A14" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="18">
+      <c r="A15" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="13" t="s">
-        <v>152</v>
+      <c r="E18" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="F18" s="9"/>
-      <c r="G18" s="11"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19">
       <c r="E19" s="45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
         <v>18</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="29">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
         <v>0.4390243902</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="24">
+      <c r="E21" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
         <v>10</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="29">
         <f t="shared" si="2"/>
         <v>0.243902439</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="24">
+      <c r="E22" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="24">
+      <c r="E23" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
         <v>13</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="29">
         <f t="shared" si="2"/>
         <v>0.3170731707</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="24">
+      <c r="E24" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="24">
+      <c r="E25" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="27">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2984,369 +2984,369 @@
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="11"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="14" t="s">
-        <v>25</v>
+      <c r="A6" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="s">
-        <v>29</v>
+      <c r="A7" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
-        <v>32</v>
+      <c r="A9" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
-        <v>42</v>
+      <c r="A10" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
-        <v>45</v>
+      <c r="A11" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>48</v>
+      <c r="A12" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>52</v>
+      <c r="A13" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>55</v>
+      <c r="A14" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>60</v>
+      <c r="A15" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>66</v>
+      <c r="A17" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>71</v>
+      <c r="A18" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>72</v>
+      <c r="A19" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>74</v>
+      <c r="A20" s="11" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>75</v>
+      <c r="A21" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>78</v>
+      <c r="A22" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>79</v>
+      <c r="A24" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="11"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>83</v>
+      <c r="A25" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="14" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="11" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>105</v>
+      <c r="A32" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="11"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="11" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6" t="s">
-        <v>122</v>
+      <c r="A39" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
-      <c r="F39" s="11"/>
+      <c r="F39" s="10"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="14" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="14" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>130</v>
+      <c r="A44" s="11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>131</v>
+      <c r="A46" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
-      <c r="F46" s="11"/>
+      <c r="F46" s="10"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C49" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="35" t="s">
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="35" t="s">
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="34" t="s">
+      <c r="C51" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="C51" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="35" t="s">
+      <c r="C52" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
+      <c r="A53" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="35" t="s">
+      <c r="A54" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="35" t="s">
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" s="35" t="s">
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="34" t="s">
+      <c r="C58" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="C58" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4386,30 +4386,30 @@
       <c r="L1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4443,14 +4443,14 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4">
         <v>0.5</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
@@ -4458,11 +4458,11 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4">
@@ -4471,26 +4471,26 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="4">
         <v>1.0</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4">
@@ -4499,26 +4499,26 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
         <v>0.0</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4">
@@ -4527,24 +4527,24 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4">
@@ -4556,17 +4556,17 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4">
@@ -4582,11 +4582,11 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="21" t="s">
-        <v>61</v>
+      <c r="J9" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="12">
@@ -4603,7 +4603,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -5633,8 +5633,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>5</v>
+      <c r="A1" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5664,11 +5664,11 @@
       <c r="AA1" s="9"/>
       <c r="AB1" s="9"/>
       <c r="AC1" s="9"/>
-      <c r="AD1" s="11"/>
+      <c r="AD1" s="10"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>41</v>
+      <c r="A2" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -5676,197 +5676,197 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="16" t="s">
         <v>50</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="20" t="s">
-        <v>63</v>
+      <c r="K2" s="10"/>
+      <c r="L2" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="20" t="s">
-        <v>69</v>
+      <c r="N2" s="10"/>
+      <c r="O2" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="P2" s="9"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="20" t="s">
-        <v>70</v>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="S2" s="9"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="20" t="s">
-        <v>73</v>
+      <c r="T2" s="10"/>
+      <c r="U2" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="V2" s="9"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="17" t="s">
-        <v>76</v>
+      <c r="W2" s="10"/>
+      <c r="X2" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9"/>
-      <c r="AD2" s="11"/>
+      <c r="AD2" s="10"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" s="25" t="s">
+      <c r="I3" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="J3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="K3" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="O3" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="P3" s="25" t="s">
+      <c r="M3" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="N3" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="R3" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="S3" s="25" t="s">
+      <c r="P3" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="T3" s="25" t="s">
+      <c r="Q3" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="U3" s="25" t="s">
+      <c r="R3" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="V3" s="25" t="s">
+      <c r="S3" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="T3" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="W3" s="25" t="s">
+      <c r="U3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="X3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y3" s="25" t="s">
+      <c r="V3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Z3" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA3" s="25" t="s">
+      <c r="W3" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="X3" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="AC3" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="AD3" s="25" t="s">
+      <c r="Y3" s="22" t="s">
         <v>113</v>
       </c>
+      <c r="Z3" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC3" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD3" s="22" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>120</v>
+      <c r="C4" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H4" s="28" t="s">
+      <c r="F4" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="33">
+      <c r="I4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="33">
+      <c r="L4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="33">
+      <c r="O4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="28">
+      <c r="R4" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="26">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,43 +5882,43 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="28" t="str">
+      <c r="AB4" s="26" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="28" t="str">
+      <c r="AC4" s="26" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="29"/>
+      <c r="AD4" s="28"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>146</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>147</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="28" t="s">
+      <c r="F5" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J5" s="41">
         <v>46282.0</v>
@@ -5927,26 +5927,26 @@
         <v>46298.0</v>
       </c>
       <c r="L5" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="33"/>
+      <c r="N5" s="36"/>
       <c r="O5" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P5" s="41"/>
-      <c r="Q5" s="33"/>
+      <c r="Q5" s="36"/>
       <c r="R5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="28">
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5962,79 +5962,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="28" t="str">
+      <c r="AB5" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC5" s="28" t="str">
+      <c r="AC5" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD5" s="29"/>
+      <c r="AD5" s="28"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>156</v>
+      <c r="C6" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="F6" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="33">
+      <c r="I6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="33">
+      <c r="L6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="33">
+      <c r="O6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q6" s="33">
+      <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="28">
+      <c r="R6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6050,79 +6050,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="28" t="str">
+      <c r="AB6" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="28" t="str">
+      <c r="AC6" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="29"/>
+      <c r="AD6" s="28"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>158</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="28" t="s">
+      <c r="F7" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="33">
+      <c r="I7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="33">
+      <c r="L7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="33">
+      <c r="O7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="Q7" s="33">
+      <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="28">
+      <c r="R7" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6138,50 +6138,50 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="28" t="str">
+      <c r="AB7" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="28" t="str">
+      <c r="AC7" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="29"/>
+      <c r="AD7" s="28"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="29" t="s">
+      <c r="C8" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>160</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="28" t="s">
+      <c r="F8" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J8" s="41">
         <v>46302.0</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M8" s="41">
         <v>46283.0</v>
@@ -6190,7 +6190,7 @@
         <v>46283.0</v>
       </c>
       <c r="O8" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P8" s="41">
         <v>46283.0</v>
@@ -6198,17 +6198,17 @@
       <c r="Q8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="R8" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="28">
+      <c r="R8" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6224,79 +6224,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="28" t="str">
+      <c r="AB8" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="28" t="str">
+      <c r="AC8" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="29"/>
+      <c r="AD8" s="28"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>162</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="28" t="s">
+      <c r="F9" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="33">
+      <c r="I9" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="36">
         <v>46274.0</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="36">
         <v>46274.0</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="33">
+        <v>28</v>
+      </c>
+      <c r="M9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="36">
         <v>46277.0</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="33">
+        <v>28</v>
+      </c>
+      <c r="P9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="28">
+      <c r="R9" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6312,52 +6312,52 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="28" t="str">
+      <c r="AB9" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="28" t="str">
+      <c r="AC9" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="29"/>
+      <c r="AD9" s="28"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="28" t="s">
         <v>165</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="33">
+        <v>28</v>
+      </c>
+      <c r="J10" s="36">
         <v>46272.0</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="36">
         <v>46272.0</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M10" s="41">
         <v>46277.0</v>
@@ -6368,21 +6368,21 @@
       <c r="O10" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="28">
+      <c r="Q10" s="36"/>
+      <c r="R10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6398,79 +6398,79 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB10" s="28">
+      <c r="AB10" s="26">
         <f t="shared" si="3"/>
         <v>-27</v>
       </c>
-      <c r="AC10" s="28" t="str">
+      <c r="AC10" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD10" s="29"/>
+      <c r="AD10" s="28"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="28" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="33">
+      <c r="I11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="33">
+      <c r="L11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="33">
+      <c r="O11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="Q11" s="33">
+      <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="28">
+      <c r="R11" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6486,75 +6486,75 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="28" t="str">
+      <c r="AB11" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="28" t="str">
+      <c r="AC11" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="29"/>
+      <c r="AD11" s="28"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="28" t="s">
+      <c r="A12" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="33">
+      <c r="I12" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="33">
+      <c r="L12" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N12" s="33"/>
-      <c r="O12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="33">
+      <c r="N12" s="36"/>
+      <c r="O12" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="28">
+      <c r="Q12" s="36"/>
+      <c r="R12" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6570,75 +6570,75 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB12" s="28">
+      <c r="AB12" s="26">
         <f t="shared" si="3"/>
         <v>-27</v>
       </c>
-      <c r="AC12" s="28" t="str">
+      <c r="AC12" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD12" s="29"/>
+      <c r="AD12" s="28"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="33">
+        <v>28</v>
+      </c>
+      <c r="J13" s="36">
         <v>46277.0</v>
       </c>
       <c r="K13" s="41">
         <v>46303.0</v>
       </c>
       <c r="L13" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="33">
+        <v>21</v>
+      </c>
+      <c r="M13" s="36">
         <v>46277.0</v>
       </c>
-      <c r="N13" s="33"/>
-      <c r="O13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="33">
+      <c r="N13" s="36"/>
+      <c r="O13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="28">
+      <c r="Q13" s="36"/>
+      <c r="R13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6654,73 +6654,73 @@
         <f t="shared" si="2"/>
         <v>46277</v>
       </c>
-      <c r="AB13" s="28">
+      <c r="AB13" s="26">
         <f t="shared" si="3"/>
         <v>-27</v>
       </c>
-      <c r="AC13" s="28" t="str">
+      <c r="AC13" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD13" s="29"/>
+      <c r="AD13" s="28"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="28" t="s">
         <v>181</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="33">
+        <v>28</v>
+      </c>
+      <c r="J14" s="36">
         <v>46277.0</v>
       </c>
-      <c r="K14" s="33"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="33">
+        <v>21</v>
+      </c>
+      <c r="M14" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N14" s="33"/>
-      <c r="O14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P14" s="33">
+      <c r="N14" s="36"/>
+      <c r="O14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="28">
+      <c r="Q14" s="36"/>
+      <c r="R14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6736,73 +6736,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB14" s="28">
+      <c r="AB14" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC14" s="28" t="str">
+      <c r="AC14" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD14" s="29"/>
+      <c r="AD14" s="28"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="28" t="s">
         <v>184</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="33">
+        <v>28</v>
+      </c>
+      <c r="J15" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K15" s="33"/>
+      <c r="K15" s="36"/>
       <c r="L15" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="33">
+        <v>21</v>
+      </c>
+      <c r="M15" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N15" s="33"/>
-      <c r="O15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P15" s="33">
+      <c r="N15" s="36"/>
+      <c r="O15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="28">
+      <c r="Q15" s="36"/>
+      <c r="R15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6818,73 +6818,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="28">
+      <c r="AB15" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC15" s="28" t="str">
+      <c r="AC15" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD15" s="29"/>
+      <c r="AD15" s="28"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="28" t="s">
         <v>189</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="H16" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="33">
+        <v>28</v>
+      </c>
+      <c r="J16" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K16" s="33"/>
+      <c r="K16" s="36"/>
       <c r="L16" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="33">
+        <v>21</v>
+      </c>
+      <c r="M16" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N16" s="33"/>
-      <c r="O16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P16" s="33">
+      <c r="N16" s="36"/>
+      <c r="O16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="28">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6900,73 +6900,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="28">
+      <c r="AB16" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC16" s="28" t="str">
+      <c r="AC16" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD16" s="29"/>
+      <c r="AD16" s="28"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="28" t="s">
+      <c r="B17" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="28" t="s">
         <v>192</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="33">
+        <v>28</v>
+      </c>
+      <c r="J17" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K17" s="33"/>
+      <c r="K17" s="36"/>
       <c r="L17" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" s="33">
+        <v>21</v>
+      </c>
+      <c r="M17" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N17" s="33"/>
-      <c r="O17" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P17" s="33">
+      <c r="N17" s="36"/>
+      <c r="O17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="28">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="36"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6982,73 +6982,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="28">
+      <c r="AB17" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC17" s="28" t="str">
+      <c r="AC17" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD17" s="29"/>
+      <c r="AD17" s="28"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="28" t="s">
         <v>195</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="33">
+      <c r="I18" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K18" s="33"/>
-      <c r="L18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="33">
+      <c r="K18" s="36"/>
+      <c r="L18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N18" s="33"/>
-      <c r="O18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P18" s="33">
+      <c r="N18" s="36"/>
+      <c r="O18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="28">
+      <c r="Q18" s="36"/>
+      <c r="R18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7064,73 +7064,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="28">
+      <c r="AB18" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC18" s="28" t="str">
+      <c r="AC18" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD18" s="29"/>
+      <c r="AD18" s="28"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="B19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="28" t="s">
         <v>198</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" s="33">
+        <v>28</v>
+      </c>
+      <c r="J19" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K19" s="33"/>
+      <c r="K19" s="36"/>
       <c r="L19" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="33">
+        <v>21</v>
+      </c>
+      <c r="M19" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N19" s="33"/>
-      <c r="O19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P19" s="33">
+      <c r="N19" s="36"/>
+      <c r="O19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="28">
+      <c r="Q19" s="36"/>
+      <c r="R19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7146,73 +7146,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="28">
+      <c r="AB19" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC19" s="28" t="str">
+      <c r="AC19" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD19" s="29"/>
+      <c r="AD19" s="28"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="28" t="s">
         <v>201</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="33">
+      <c r="I20" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K20" s="33"/>
-      <c r="L20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M20" s="33">
+      <c r="K20" s="36"/>
+      <c r="L20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N20" s="33"/>
-      <c r="O20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P20" s="33">
+      <c r="N20" s="36"/>
+      <c r="O20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="28">
+      <c r="Q20" s="36"/>
+      <c r="R20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7228,73 +7228,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="28">
+      <c r="AB20" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC20" s="28" t="str">
+      <c r="AC20" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD20" s="29"/>
+      <c r="AD20" s="28"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="28" t="s">
+      <c r="B21" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="28" t="s">
         <v>204</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J21" s="33">
+        <v>28</v>
+      </c>
+      <c r="J21" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K21" s="33"/>
+      <c r="K21" s="36"/>
       <c r="L21" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="33">
+        <v>21</v>
+      </c>
+      <c r="M21" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N21" s="33"/>
-      <c r="O21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P21" s="33">
+      <c r="N21" s="36"/>
+      <c r="O21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="28">
+      <c r="Q21" s="36"/>
+      <c r="R21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7310,73 +7310,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="28">
+      <c r="AB21" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC21" s="28" t="str">
+      <c r="AC21" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD21" s="29"/>
+      <c r="AD21" s="28"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="28" t="s">
+      <c r="B22" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="28" t="s">
         <v>207</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H22" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="33">
+      <c r="I22" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K22" s="33"/>
-      <c r="L22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M22" s="33">
+      <c r="K22" s="36"/>
+      <c r="L22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N22" s="33"/>
-      <c r="O22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P22" s="33">
+      <c r="N22" s="36"/>
+      <c r="O22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="28">
+      <c r="Q22" s="36"/>
+      <c r="R22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7392,73 +7392,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="28">
+      <c r="AB22" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC22" s="28" t="str">
+      <c r="AC22" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD22" s="29"/>
+      <c r="AD22" s="28"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="28" t="s">
+      <c r="B23" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="28" t="s">
         <v>210</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="28" t="s">
+      <c r="H23" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="33">
+      <c r="I23" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M23" s="33">
+      <c r="K23" s="36"/>
+      <c r="L23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N23" s="33"/>
-      <c r="O23" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P23" s="33">
+      <c r="N23" s="36"/>
+      <c r="O23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P23" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="28">
+      <c r="Q23" s="36"/>
+      <c r="R23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7474,73 +7474,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="28">
+      <c r="AB23" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC23" s="28" t="str">
+      <c r="AC23" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD23" s="29"/>
+      <c r="AD23" s="28"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="28" t="s">
+      <c r="B24" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="28" t="s">
         <v>213</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="33">
+      <c r="I24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K24" s="33"/>
-      <c r="L24" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M24" s="33">
+      <c r="K24" s="36"/>
+      <c r="L24" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N24" s="33"/>
-      <c r="O24" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P24" s="33">
+      <c r="N24" s="36"/>
+      <c r="O24" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="28">
+      <c r="Q24" s="36"/>
+      <c r="R24" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7556,73 +7556,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="28">
+      <c r="AB24" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC24" s="28" t="str">
+      <c r="AC24" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD24" s="29"/>
+      <c r="AD24" s="28"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="28" t="s">
+      <c r="B25" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="28" t="s">
         <v>216</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="33">
+      <c r="I25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K25" s="33"/>
-      <c r="L25" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M25" s="33">
+      <c r="K25" s="36"/>
+      <c r="L25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N25" s="33"/>
-      <c r="O25" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P25" s="33">
+      <c r="N25" s="36"/>
+      <c r="O25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="28">
+      <c r="Q25" s="36"/>
+      <c r="R25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7638,73 +7638,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="28">
+      <c r="AB25" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC25" s="28" t="str">
+      <c r="AC25" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD25" s="29"/>
+      <c r="AD25" s="28"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="28" t="s">
+      <c r="B26" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="28" t="s">
         <v>219</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="32" t="s">
+      <c r="G26" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="33">
+      <c r="I26" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M26" s="33">
+      <c r="K26" s="36"/>
+      <c r="L26" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N26" s="33"/>
-      <c r="O26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P26" s="33">
+      <c r="N26" s="36"/>
+      <c r="O26" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="28">
+      <c r="Q26" s="36"/>
+      <c r="R26" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7720,73 +7720,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="28">
+      <c r="AB26" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC26" s="28" t="str">
+      <c r="AC26" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD26" s="29"/>
+      <c r="AD26" s="28"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="28" t="s">
+      <c r="B27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="28" t="s">
         <v>222</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="33">
+      <c r="I27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K27" s="33"/>
-      <c r="L27" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M27" s="33">
+      <c r="K27" s="36"/>
+      <c r="L27" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N27" s="33"/>
-      <c r="O27" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P27" s="33">
+      <c r="N27" s="36"/>
+      <c r="O27" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P27" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="28">
+      <c r="Q27" s="36"/>
+      <c r="R27" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7802,73 +7802,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="28">
+      <c r="AB27" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC27" s="28" t="str">
+      <c r="AC27" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD27" s="29"/>
+      <c r="AD27" s="28"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="28" t="s">
+      <c r="B28" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="28" t="s">
         <v>225</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="33">
+      <c r="I28" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K28" s="33"/>
-      <c r="L28" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M28" s="33">
+      <c r="K28" s="36"/>
+      <c r="L28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N28" s="33"/>
-      <c r="O28" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P28" s="33">
+      <c r="N28" s="36"/>
+      <c r="O28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="28">
+      <c r="Q28" s="36"/>
+      <c r="R28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7884,73 +7884,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="28">
+      <c r="AB28" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC28" s="28" t="str">
+      <c r="AC28" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD28" s="29"/>
+      <c r="AD28" s="28"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="28" t="s">
+      <c r="B29" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="28" t="s">
         <v>228</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="33">
+      <c r="I29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K29" s="33"/>
-      <c r="L29" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M29" s="33">
+      <c r="K29" s="36"/>
+      <c r="L29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N29" s="33"/>
-      <c r="O29" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" s="33">
+      <c r="N29" s="36"/>
+      <c r="O29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S29" s="33"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="28">
+      <c r="Q29" s="36"/>
+      <c r="R29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="36"/>
+      <c r="W29" s="36"/>
+      <c r="X29" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7966,73 +7966,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="28">
+      <c r="AB29" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC29" s="28" t="str">
+      <c r="AC29" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD29" s="29"/>
+      <c r="AD29" s="28"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="28" t="s">
+      <c r="B30" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="28" t="s">
         <v>231</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="G30" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="H30" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="33">
+      <c r="I30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K30" s="33"/>
-      <c r="L30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M30" s="33">
+      <c r="K30" s="36"/>
+      <c r="L30" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N30" s="33"/>
-      <c r="O30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P30" s="33">
+      <c r="N30" s="36"/>
+      <c r="O30" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="28">
+      <c r="Q30" s="36"/>
+      <c r="R30" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8048,73 +8048,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="28">
+      <c r="AB30" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC30" s="28" t="str">
+      <c r="AC30" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD30" s="29"/>
+      <c r="AD30" s="28"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="28" t="s">
+      <c r="B31" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="28" t="s">
         <v>234</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="33">
+      <c r="I31" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M31" s="33">
+      <c r="K31" s="36"/>
+      <c r="L31" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N31" s="33"/>
-      <c r="O31" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P31" s="33">
+      <c r="N31" s="36"/>
+      <c r="O31" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P31" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="28">
+      <c r="Q31" s="36"/>
+      <c r="R31" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8130,73 +8130,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="28">
+      <c r="AB31" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC31" s="28" t="str">
+      <c r="AC31" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD31" s="29"/>
+      <c r="AD31" s="28"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="28" t="s">
+      <c r="B32" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="28" t="s">
         <v>237</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H32" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="33">
+      <c r="I32" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K32" s="33"/>
-      <c r="L32" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M32" s="33">
+      <c r="K32" s="36"/>
+      <c r="L32" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N32" s="33"/>
-      <c r="O32" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P32" s="33">
+      <c r="N32" s="36"/>
+      <c r="O32" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P32" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="28">
+      <c r="Q32" s="36"/>
+      <c r="R32" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V32" s="36"/>
+      <c r="W32" s="36"/>
+      <c r="X32" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8212,73 +8212,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="28">
+      <c r="AB32" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC32" s="28" t="str">
+      <c r="AC32" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD32" s="29"/>
+      <c r="AD32" s="28"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="28" t="s">
+      <c r="B33" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="28" t="s">
         <v>240</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H33" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="33">
+      <c r="I33" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K33" s="33"/>
-      <c r="L33" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M33" s="33">
+      <c r="K33" s="36"/>
+      <c r="L33" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N33" s="33"/>
-      <c r="O33" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P33" s="33">
+      <c r="N33" s="36"/>
+      <c r="O33" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P33" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="28">
+      <c r="Q33" s="36"/>
+      <c r="R33" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8294,73 +8294,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="28">
+      <c r="AB33" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC33" s="28" t="str">
+      <c r="AC33" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD33" s="29"/>
+      <c r="AD33" s="28"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="28" t="s">
+      <c r="B34" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="28" t="s">
         <v>243</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="33">
+      <c r="I34" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K34" s="33"/>
-      <c r="L34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M34" s="33">
+      <c r="K34" s="36"/>
+      <c r="L34" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N34" s="33"/>
-      <c r="O34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" s="33">
+      <c r="N34" s="36"/>
+      <c r="O34" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="28">
+      <c r="Q34" s="36"/>
+      <c r="R34" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8376,73 +8376,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="28">
+      <c r="AB34" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC34" s="28" t="str">
+      <c r="AC34" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD34" s="29"/>
+      <c r="AD34" s="28"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="28" t="s">
+      <c r="B35" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="28" t="s">
         <v>246</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="33">
+      <c r="I35" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K35" s="33"/>
-      <c r="L35" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M35" s="33">
+      <c r="K35" s="36"/>
+      <c r="L35" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N35" s="33"/>
-      <c r="O35" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P35" s="33">
+      <c r="N35" s="36"/>
+      <c r="O35" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="28">
+      <c r="Q35" s="36"/>
+      <c r="R35" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V35" s="36"/>
+      <c r="W35" s="36"/>
+      <c r="X35" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8458,73 +8458,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="28">
+      <c r="AB35" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC35" s="28" t="str">
+      <c r="AC35" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD35" s="29"/>
+      <c r="AD35" s="28"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="28" t="s">
+      <c r="B36" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="28" t="s">
         <v>249</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F36" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="28" t="s">
+      <c r="H36" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="33">
+      <c r="I36" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K36" s="33"/>
-      <c r="L36" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M36" s="33">
+      <c r="K36" s="36"/>
+      <c r="L36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N36" s="33"/>
-      <c r="O36" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P36" s="33">
+      <c r="N36" s="36"/>
+      <c r="O36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="28">
+      <c r="Q36" s="36"/>
+      <c r="R36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8540,73 +8540,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="28">
+      <c r="AB36" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC36" s="28" t="str">
+      <c r="AC36" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD36" s="29"/>
+      <c r="AD36" s="28"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="28" t="s">
+      <c r="B37" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="28" t="s">
         <v>252</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="28" t="s">
+      <c r="H37" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="33">
+      <c r="I37" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K37" s="33"/>
-      <c r="L37" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M37" s="33">
+      <c r="K37" s="36"/>
+      <c r="L37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N37" s="33"/>
-      <c r="O37" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P37" s="33">
+      <c r="N37" s="36"/>
+      <c r="O37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S37" s="33"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="28">
+      <c r="Q37" s="36"/>
+      <c r="R37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8622,75 +8622,75 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="28">
+      <c r="AB37" s="26">
         <f t="shared" si="3"/>
         <v>-21</v>
       </c>
-      <c r="AC37" s="28" t="str">
+      <c r="AC37" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD37" s="29"/>
+      <c r="AD37" s="28"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="28" t="s">
+      <c r="B38" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="28" t="s">
         <v>254</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="32" t="s">
+      <c r="G38" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="28" t="s">
+      <c r="H38" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="28" t="s">
-        <v>30</v>
+      <c r="I38" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="J38" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="36">
         <v>46276.0</v>
       </c>
       <c r="L38" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="33">
+        <v>28</v>
+      </c>
+      <c r="M38" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N38" s="33"/>
+      <c r="N38" s="36"/>
       <c r="O38" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P38" s="33">
+        <v>28</v>
+      </c>
+      <c r="P38" s="36">
         <v>46277.0</v>
       </c>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="28">
+      <c r="Q38" s="36"/>
+      <c r="R38" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8706,73 +8706,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB38" s="28" t="str">
+      <c r="AB38" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC38" s="28" t="str">
+      <c r="AC38" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD38" s="29"/>
+      <c r="AD38" s="28"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="28" t="s">
+      <c r="B39" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="28" t="s">
         <v>258</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="G39" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="28" t="s">
+      <c r="H39" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J39" s="33">
+        <v>28</v>
+      </c>
+      <c r="J39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K39" s="33"/>
+      <c r="K39" s="36"/>
       <c r="L39" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M39" s="33">
+        <v>28</v>
+      </c>
+      <c r="M39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N39" s="33"/>
+      <c r="N39" s="36"/>
       <c r="O39" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P39" s="33">
+        <v>28</v>
+      </c>
+      <c r="P39" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="28">
+      <c r="Q39" s="36"/>
+      <c r="R39" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8788,73 +8788,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB39" s="28" t="str">
+      <c r="AB39" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC39" s="28" t="str">
+      <c r="AC39" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD39" s="29"/>
+      <c r="AD39" s="28"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="28" t="s">
+      <c r="B40" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="28" t="s">
         <v>261</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="32" t="s">
+      <c r="G40" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="28" t="s">
+      <c r="H40" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I40" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J40" s="33">
+        <v>28</v>
+      </c>
+      <c r="J40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K40" s="33"/>
+      <c r="K40" s="36"/>
       <c r="L40" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" s="33">
+        <v>28</v>
+      </c>
+      <c r="M40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N40" s="33"/>
+      <c r="N40" s="36"/>
       <c r="O40" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P40" s="33">
+        <v>28</v>
+      </c>
+      <c r="P40" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="28">
+      <c r="Q40" s="36"/>
+      <c r="R40" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
+      <c r="X40" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8870,73 +8870,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB40" s="28" t="str">
+      <c r="AB40" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC40" s="28" t="str">
+      <c r="AC40" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD40" s="29"/>
+      <c r="AD40" s="28"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="28" t="s">
+      <c r="B41" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="28" t="s">
         <v>264</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="32" t="s">
+      <c r="G41" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H41" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J41" s="33">
+        <v>28</v>
+      </c>
+      <c r="J41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K41" s="33"/>
+      <c r="K41" s="36"/>
       <c r="L41" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M41" s="33">
+        <v>28</v>
+      </c>
+      <c r="M41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N41" s="33"/>
+      <c r="N41" s="36"/>
       <c r="O41" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P41" s="33">
+        <v>28</v>
+      </c>
+      <c r="P41" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="28">
+      <c r="Q41" s="36"/>
+      <c r="R41" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" s="36"/>
+      <c r="W41" s="36"/>
+      <c r="X41" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8952,73 +8952,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB41" s="28" t="str">
+      <c r="AB41" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC41" s="28" t="str">
+      <c r="AC41" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD41" s="29"/>
+      <c r="AD41" s="28"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="28" t="s">
+      <c r="B42" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="28" t="s">
         <v>267</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="26" t="s">
         <v>24</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J42" s="33">
+        <v>28</v>
+      </c>
+      <c r="J42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="K42" s="33"/>
+      <c r="K42" s="36"/>
       <c r="L42" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M42" s="33">
+        <v>28</v>
+      </c>
+      <c r="M42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="N42" s="33"/>
+      <c r="N42" s="36"/>
       <c r="O42" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P42" s="33">
+        <v>28</v>
+      </c>
+      <c r="P42" s="36">
         <v>46283.0</v>
       </c>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="28">
+      <c r="Q42" s="36"/>
+      <c r="R42" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="36"/>
+      <c r="W42" s="36"/>
+      <c r="X42" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9034,79 +9034,79 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB42" s="28" t="str">
+      <c r="AB42" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC42" s="28" t="str">
+      <c r="AC42" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD42" s="29"/>
+      <c r="AD42" s="28"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="28" t="s">
+      <c r="B43" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="28" t="s">
         <v>270</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="G43" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="28" t="s">
+      <c r="H43" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="28" t="s">
-        <v>30</v>
+      <c r="I43" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="J43" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K43" s="33">
+      <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="28" t="s">
-        <v>30</v>
+      <c r="L43" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="M43" s="41">
         <v>46277.0</v>
       </c>
-      <c r="N43" s="33">
+      <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P43" s="33">
+      <c r="O43" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="Q43" s="33">
+      <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S43" s="33"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="28">
+      <c r="R43" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+      <c r="U43" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" s="36"/>
+      <c r="W43" s="36"/>
+      <c r="X43" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9122,73 +9122,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="28" t="str">
+      <c r="AB43" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="28" t="str">
+      <c r="AC43" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="29"/>
+      <c r="AD43" s="28"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="E44" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F44" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G44" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H44" s="28" t="s">
+      <c r="F44" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H44" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I44" s="28" t="s">
-        <v>30</v>
+      <c r="I44" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="J44" s="41">
         <v>46277.0</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="33">
+      <c r="L44" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="36">
         <v>46276.0</v>
       </c>
-      <c r="N44" s="33"/>
-      <c r="O44" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="28">
+      <c r="N44" s="36"/>
+      <c r="O44" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9204,15 +9204,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="28">
+      <c r="AB44" s="26">
         <f t="shared" si="3"/>
         <v>-28</v>
       </c>
-      <c r="AC44" s="28" t="str">
+      <c r="AC44" s="26" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="29"/>
+      <c r="AD44" s="28"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">

--- a/datos/Control_Plantillas_NetSuite_V1.xlsx
+++ b/datos/Control_Plantillas_NetSuite_V1.xlsx
@@ -29,30 +29,30 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="274">
   <si>
+    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+  </si>
+  <si>
+    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
+  </si>
+  <si>
     <t>CATÁLOGOS - No modificar sin autorización del PMO</t>
   </si>
   <si>
-    <t>INSTRUCTIVO DE USO — CONTROL DE PLANTILLAS ORACLE NETSUITE</t>
-  </si>
-  <si>
-    <t>TABLERO DE CONTROL — PLANTILLAS DE MIGRACIÓN ORACLE NETSUITE</t>
+    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
+  </si>
+  <si>
+    <t>1. ¿Qué se captura y qué se calcula solo?</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>Factor avance</t>
   </si>
   <si>
     <t>CONTROL DE PLANTILLAS DE MIGRACIÓN — ORACLE NETSUITE | ESTEVEZ.JOR</t>
   </si>
   <si>
-    <t>1. ¿Qué se captura y qué se calcula solo?</t>
-  </si>
-  <si>
-    <t>GRUPO ESTEVEZ · Etapa vigente: llenado de plantillas por áreas y Key Users</t>
-  </si>
-  <si>
-    <t>Estatus</t>
-  </si>
-  <si>
-    <t>Factor avance</t>
-  </si>
-  <si>
     <t>Módulos</t>
   </si>
   <si>
@@ -71,241 +71,259 @@
     <t>No iniciado</t>
   </si>
   <si>
+    <t>INDICADORES CLAVE</t>
+  </si>
+  <si>
+    <t>AVANCE POR MÓDULO</t>
+  </si>
+  <si>
+    <t>Plantillas totales</t>
+  </si>
+  <si>
     <t>•  Celdas con fondo AMARILLO: son las únicas que se capturan manualmente (Key User, Revisor y las fechas de compromiso / reales).</t>
   </si>
   <si>
+    <t>Finanzas (R2R)</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Finanzas / Contabilidad</t>
+  </si>
+  <si>
     <t>•  Columnas de estatus (E1 a E5): se seleccionan de la lista desplegable. No escribir texto libre.</t>
   </si>
   <si>
-    <t>Finanzas (R2R)</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Finanzas / Contabilidad</t>
-  </si>
-  <si>
     <t>1. Llenado de plantilla</t>
   </si>
   <si>
+    <t>En proceso</t>
+  </si>
+  <si>
     <t>•  Columnas X a AC (Etapa #, Etapa Actual, % Avance, Próx. Compromiso, Días Restantes y Semáforo): se calculan automáticamente. NO editar.</t>
   </si>
   <si>
-    <t>En proceso</t>
-  </si>
-  <si>
     <t>Compras (P2P)</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Compras / Abastecimiento</t>
+  </si>
+  <si>
+    <t>2. Revisión y validación</t>
+  </si>
+  <si>
     <t>•  La hoja Resumen_Ejecutivo se actualiza sola a partir de la hoja Control_Plantillas.</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Compras / Abastecimiento</t>
-  </si>
-  <si>
-    <t>2. Revisión y validación</t>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Ventas (O2C)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Comercial / Ventas</t>
+  </si>
+  <si>
+    <t>3. Carga en repositorio Oracle</t>
   </si>
   <si>
     <t>2. Etapas del flujo y su peso en el avance</t>
   </si>
   <si>
-    <t>Completado</t>
-  </si>
-  <si>
-    <t>Ventas (O2C)</t>
+    <t>Bloqueado</t>
+  </si>
+  <si>
+    <t>Inventarios (D2B)</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
+  </si>
+  <si>
+    <t>Almacén / Inventarios</t>
+  </si>
+  <si>
+    <t>4. Ambiente Sandbox</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Manufactura (MFG)</t>
+  </si>
+  <si>
+    <t>Manufactura / Producción</t>
+  </si>
+  <si>
+    <t>5. Ambiente Productivo</t>
+  </si>
+  <si>
+    <t>Activos Fijos (FA)</t>
+  </si>
+  <si>
+    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
+  </si>
+  <si>
+    <t>Activos Fijos / Patrimonio</t>
   </si>
   <si>
     <t>IDENTIFICACIÓN Y RESPONSABLES</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>INDICADORES CLAVE</t>
-  </si>
-  <si>
-    <t>Comercial / Ventas</t>
-  </si>
-  <si>
-    <t>3. Carga en repositorio Oracle</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
-  </si>
-  <si>
-    <t>Inventarios (D2B)</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Almacén / Inventarios</t>
-  </si>
-  <si>
-    <t>4. Ambiente Sandbox</t>
-  </si>
-  <si>
-    <t>•  E1 · Llenado de plantilla por el área / Key User .................... 40%</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>Manufactura (MFG)</t>
-  </si>
-  <si>
-    <t>Manufactura / Producción</t>
-  </si>
-  <si>
-    <t>•  E2 · Revisión y validación (PMO / consultoría) ..................... 20%</t>
-  </si>
-  <si>
-    <t>5. Ambiente Productivo</t>
-  </si>
-  <si>
-    <t>Activos Fijos (FA)</t>
+    <t>6. Cerrado</t>
   </si>
   <si>
     <t>•  E3 · Carga en el repositorio de Oracle ............................. 15%</t>
   </si>
   <si>
-    <t>AVANCE POR MÓDULO</t>
-  </si>
-  <si>
-    <t>Activos Fijos / Patrimonio</t>
+    <t>Capital Humano</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
+  </si>
+  <si>
+    <t>Suma de pesos (debe ser 100%)</t>
+  </si>
+  <si>
+    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+  </si>
+  <si>
+    <t>% Avance</t>
+  </si>
+  <si>
+    <t>E1 Llenado OK</t>
+  </si>
+  <si>
+    <t>3. Valores de estatus permitidos</t>
+  </si>
+  <si>
+    <t>E2 Revisión OK</t>
+  </si>
+  <si>
+    <t>E3 Repositorio OK</t>
+  </si>
+  <si>
+    <t>E4 Sandbox OK</t>
+  </si>
+  <si>
+    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+  </si>
+  <si>
+    <t>E5 Productivo OK</t>
   </si>
   <si>
     <t>E1 · LLENADO</t>
   </si>
   <si>
-    <t>•  E4 · Carga y validación en ambiente Sandbox ........................ 15%</t>
-  </si>
-  <si>
-    <t>6. Cerrado</t>
-  </si>
-  <si>
-    <t>•  E5 · Carga en ambiente Productivo .................................. 10%</t>
-  </si>
-  <si>
-    <t>Capital Humano</t>
-  </si>
-  <si>
-    <t>Suma de pesos (debe ser 100%)</t>
-  </si>
-  <si>
-    <t>•  Los pesos son editables en la hoja Catalogos (columna L). Deben sumar 100%.</t>
+    <t>Avance global ponderado</t>
+  </si>
+  <si>
+    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+  </si>
+  <si>
+    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
   </si>
   <si>
     <t>E2 · REVISIÓN</t>
   </si>
   <si>
-    <t>Plantillas totales</t>
-  </si>
-  <si>
-    <t>3. Valores de estatus permitidos</t>
+    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
+  </si>
+  <si>
+    <t>4. Lectura del semáforo</t>
   </si>
   <si>
     <t>E3 · REPOSITORIO ORACLE</t>
   </si>
   <si>
-    <t>•  No iniciado — la etapa aún no arranca (avance 0%).</t>
+    <t>PMO / Consultoría</t>
+  </si>
+  <si>
+    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
   </si>
   <si>
     <t>E4 · SANDBOX</t>
   </si>
   <si>
-    <t>•  En proceso — etapa iniciada sin concluir (avance 50% de su peso).</t>
-  </si>
-  <si>
-    <t>•  Completado — etapa concluida y con evidencia (avance 100% de su peso).</t>
+    <t>•  En riesgo — faltan 7 días o menos.</t>
+  </si>
+  <si>
+    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
   </si>
   <si>
     <t>E5 · PRODUCTIVO</t>
   </si>
   <si>
-    <t>•  Bloqueado — detenida por una dependencia o decisión. Documentar el motivo en Observaciones.</t>
-  </si>
-  <si>
-    <t>•  No aplica — la plantilla no requiere esa etapa. Cuenta como completada para el avance.</t>
+    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
+  </si>
+  <si>
+    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
+  </si>
+  <si>
+    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
   </si>
   <si>
     <t>SEGUIMIENTO AUTOMÁTICO</t>
   </si>
   <si>
-    <t>4. Lectura del semáforo</t>
-  </si>
-  <si>
-    <t>Módulo</t>
+    <t>5. Conexión con el tablero HTML</t>
+  </si>
+  <si>
+    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>•  En tiempo — faltan más de 7 días para la fecha compromiso de la etapa vigente.</t>
-  </si>
-  <si>
-    <t>•  En riesgo — faltan 7 días o menos.</t>
-  </si>
-  <si>
-    <t>Plantillas</t>
-  </si>
-  <si>
-    <t>% Avance</t>
-  </si>
-  <si>
-    <t>•  Vencido — la fecha compromiso ya pasó y la etapa sigue abierta.</t>
-  </si>
-  <si>
-    <t>E1 Llenado OK</t>
+    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
   </si>
   <si>
     <t>Código</t>
   </si>
   <si>
-    <t>E2 Revisión OK</t>
-  </si>
-  <si>
     <t>Plantilla</t>
   </si>
   <si>
-    <t>•  Bloqueado — existe al menos una etapa marcada como bloqueada.</t>
-  </si>
-  <si>
-    <t>E3 Repositorio OK</t>
+    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
   </si>
   <si>
     <t>Área Responsable</t>
   </si>
   <si>
-    <t>E4 Sandbox OK</t>
-  </si>
-  <si>
     <t>Key User</t>
   </si>
   <si>
-    <t>•  Sin fecha — falta capturar la fecha compromiso de la etapa vigente. Debe regularizarse.</t>
-  </si>
-  <si>
-    <t>E5 Productivo OK</t>
-  </si>
-  <si>
-    <t>Avance global ponderado</t>
+    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
   </si>
   <si>
     <t>Consultor Oracle</t>
   </si>
   <si>
-    <t>•  Cerrado — la plantilla llegó a ambiente productivo.</t>
-  </si>
-  <si>
-    <t>PMO / Consultoría</t>
-  </si>
-  <si>
-    <t>5. Conexión con el tablero HTML</t>
+    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
+  </si>
+  <si>
+    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
   </si>
   <si>
     <t>E1 Llenado</t>
@@ -320,21 +338,18 @@
     <t>E2 Revisión</t>
   </si>
   <si>
-    <t>•  Abrir el archivo Tablero_Plantillas_NetSuite.html en cualquier navegador.</t>
-  </si>
-  <si>
     <t>E2 F. Compromiso</t>
   </si>
   <si>
     <t>E2 F. Real</t>
   </si>
   <si>
+    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
+  </si>
+  <si>
     <t>E3 Repositorio</t>
   </si>
   <si>
-    <t>•  Arrastrar este archivo Excel sobre el tablero (o usar el botón Cargar archivo Excel).</t>
-  </si>
-  <si>
     <t>E3 F. Compromiso</t>
   </si>
   <si>
@@ -344,6 +359,9 @@
     <t>E4 Sandbox</t>
   </si>
   <si>
+    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
+  </si>
+  <si>
     <t>E4 F. Compromiso</t>
   </si>
   <si>
@@ -353,7 +371,7 @@
     <t>E5 Productivo</t>
   </si>
   <si>
-    <t>•  El tablero se regenera completo con la información más reciente: KPIs, avance por módulo, embudo de etapas y detalle filtrable.</t>
+    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
   </si>
   <si>
     <t>E5 F. Compromiso</t>
@@ -365,13 +383,13 @@
     <t>Etapa #</t>
   </si>
   <si>
-    <t>•  No se sube nada a internet: la lectura del archivo ocurre localmente en el navegador.</t>
+    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
   </si>
   <si>
     <t>Etapa Actual</t>
   </si>
   <si>
-    <t>•  Requisito: no cambiar los nombres de la hoja Control_Plantillas ni de los encabezados de la fila 3.</t>
+    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
   </si>
   <si>
     <t>Próx. Compromiso</t>
@@ -380,7 +398,7 @@
     <t>Días Restantes</t>
   </si>
   <si>
-    <t>6. Supuestos aplicados en la carga inicial (validar con las áreas)</t>
+    <t>7. Ejemplo de captura correcta de una fila</t>
   </si>
   <si>
     <t>Semáforo</t>
@@ -392,36 +410,21 @@
     <t>FIN-01</t>
   </si>
   <si>
-    <t>•  El inventario de plantillas se construyó a partir de las capturas del repositorio compartido (Finanzas, Compras, Ventas, Inventarios y Manufactura).</t>
-  </si>
-  <si>
-    <t>•  Se marcaron como Completado en E1 únicamente las plantillas cuyo nombre indica versión Final (COA MX, 300/310/320 MX). El resto quedó En proceso.</t>
-  </si>
-  <si>
-    <t>•  Activos Fijos se incluyó con tres plantillas tentativas: no se observó carpeta en el repositorio. Pendiente de confirmar con el área.</t>
-  </si>
-  <si>
-    <t>•  No se capturaron fechas compromiso porque no fueron proporcionadas. Es la primera acción a completar con cada Key User.</t>
-  </si>
-  <si>
-    <t>•  Las etapas E2 a E5 se inicializaron en No iniciado conforme al estatus reportado del proyecto.</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
-    <t>7. Ejemplo de captura correcta de una fila</t>
-  </si>
-  <si>
     <t>ESTEVEZ - Clases</t>
   </si>
   <si>
+    <t>VTA-01</t>
+  </si>
+  <si>
+    <t>Llenado completado</t>
+  </si>
+  <si>
     <t>Angelica Ramirez</t>
   </si>
   <si>
-    <t>VTA-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fredy Sanchez </t>
   </si>
   <si>
@@ -440,9 +443,6 @@
     <t>15/05/2026</t>
   </si>
   <si>
-    <t>Llenado completado</t>
-  </si>
-  <si>
     <t>26/05/2026</t>
   </si>
   <si>
@@ -461,49 +461,49 @@
     <t>Sin iniciar</t>
   </si>
   <si>
+    <t>FIN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
+  </si>
+  <si>
     <t>Bloqueadas</t>
   </si>
   <si>
-    <t>FIN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTEVEZ - COA MX Plan de Cuentas </t>
-  </si>
-  <si>
     <t>Vencidas</t>
   </si>
   <si>
+    <t>FIN-03</t>
+  </si>
+  <si>
     <t>En riesgo (≤7 días)</t>
   </si>
   <si>
+    <t>ESTEVEZ - Departamentos</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>FIN-03</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Departamentos</t>
-  </si>
-  <si>
     <t>Sin fecha compromiso</t>
   </si>
   <si>
     <t>Cerradas (productivo)</t>
   </si>
   <si>
+    <t>FIN-04</t>
+  </si>
+  <si>
     <t>DISTRIBUCIÓN POR ETAPA ACTUAL</t>
   </si>
   <si>
+    <t>ESTEVEZ - Plantilla Subsidiarias</t>
+  </si>
+  <si>
     <t>Etapa</t>
   </si>
   <si>
     <t>% del total</t>
-  </si>
-  <si>
-    <t>FIN-04</t>
-  </si>
-  <si>
-    <t>ESTEVEZ - Plantilla Subsidiarias</t>
   </si>
   <si>
     <t>FIN-05</t>
@@ -870,19 +870,24 @@
     </font>
     <font>
       <b/>
+      <sz val="15.0"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="14.0"/>
-      <color rgb="FF0B2A4A"/>
+      <sz val="10.0"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="14.0"/>
       <color rgb="FF0B2A4A"/>
       <name val="Arial"/>
     </font>
@@ -893,13 +898,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -909,17 +909,22 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
     </font>
     <font/>
     <font>
-      <i/>
-      <sz val="10.0"/>
-      <color rgb="FF667085"/>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -932,11 +937,6 @@
       <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="9.0"/>
@@ -1014,12 +1014,12 @@
     <border/>
     <border>
       <left/>
+      <right/>
       <top/>
       <bottom/>
     </border>
     <border>
       <left/>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -1077,78 +1077,78 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1169,7 +1169,7 @@
     <xf borderId="5" fillId="6" fontId="18" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1513,29 +1513,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="8" t="str">
         <f>" Actualizado al: "&amp;TEXT(TODAY(),"DD/MM/YYYY")</f>
-        <v> Actualizado al: 09/10/2026</v>
+        <v> Actualizado al: 12/10/2026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
-        <v>32</v>
+      <c r="A5" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="E5" s="15" t="s">
-        <v>48</v>
+      <c r="C5" s="11"/>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
@@ -1543,299 +1543,299 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17">
         <f>COUNTA(Control_Plantillas!$A$4:$A$59)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>87</v>
+      <c r="E6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24">
+      <c r="A7" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="22">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.4475609756</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="27">
+        <v>0.4719512195</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E7)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.75</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E7,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>23</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="27">
+      <c r="E8" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E8)</f>
         <v>2</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.625</v>
-      </c>
-      <c r="H8" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="H8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$L$4:$L$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="27">
+        <v>2</v>
+      </c>
+      <c r="J8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>1</v>
-      </c>
-      <c r="K8" s="27">
+        <v>2</v>
+      </c>
+      <c r="K8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E8,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20">
+      <c r="B9" s="16"/>
+      <c r="C9" s="17">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"En proceso")</f>
         <v>18</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E9)</f>
         <v>3</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="H9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>3</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$L$4:$L$59,"Completado")</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="27">
+        <v>3</v>
+      </c>
+      <c r="J9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$O$4:$O$59,"Completado")</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="27">
+        <v>3</v>
+      </c>
+      <c r="K9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E9,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20">
+      <c r="B10" s="16"/>
+      <c r="C10" s="17">
         <f>COUNTIF(Control_Plantillas!$I$4:$I$59,"No iniciado")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="27">
+      <c r="E10" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E10)</f>
         <v>23</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.2652173913</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>5</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E10,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20">
+      <c r="A11" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="27">
+      <c r="E11" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.75</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>6</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E11,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Vencido")</f>
-        <v>28</v>
-      </c>
-      <c r="E12" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="24">
         <f>COUNTIF(Control_Plantillas!$B$4:$B$59,$E12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="26">
         <f>IFERROR(AVERAGEIF(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$Z$4:$Z$59),0)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$I$4:$I$59,"Completado")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$L$4:$L$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$O$4:$O$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$R$4:$R$59,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="24">
         <f>COUNTIFS(Control_Plantillas!$B$4:$B$59,$E12,Control_Plantillas!$U$4:$U$59,"Completado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20">
+      <c r="A13" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"En riesgo")</f>
         <v>0</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F13" s="43">
         <f>SUM(F7:F12)</f>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G13" s="44">
         <f>IFERROR(AVERAGE(Control_Plantillas!$Z$4:$Z$59),0)</f>
-        <v>0.4475609756</v>
+        <v>0.4719512195</v>
       </c>
       <c r="H13" s="43">
         <f t="shared" ref="H13:L13" si="1">SUM(H7:H12)</f>
@@ -1851,11 +1851,11 @@
       </c>
       <c r="I13" s="43">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J13" s="43">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K13" s="43">
         <f t="shared" si="1"/>
@@ -1867,117 +1867,117 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Sin fecha")</f>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20">
+      <c r="B15" s="16"/>
+      <c r="C15" s="17">
         <f>COUNTIF(Control_Plantillas!$AC$4:$AC$59,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="15" t="s">
-        <v>154</v>
+      <c r="E18" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19">
       <c r="E19" s="45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="27">
+      <c r="E20" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E20)</f>
         <v>18</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="26">
         <f t="shared" ref="G20:G25" si="2">IFERROR($F20/SUM($F$20:$F$25),0)</f>
         <v>0.4390243902</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="E21" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E21)</f>
-        <v>10</v>
-      </c>
-      <c r="G21" s="29">
+        <v>6</v>
+      </c>
+      <c r="G21" s="26">
         <f t="shared" si="2"/>
-        <v>0.243902439</v>
+        <v>0.1463414634</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="E23" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="27">
+      <c r="E23" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E23)</f>
-        <v>13</v>
-      </c>
-      <c r="G23" s="29">
+        <v>17</v>
+      </c>
+      <c r="G23" s="26">
         <f t="shared" si="2"/>
-        <v>0.3170731707</v>
+        <v>0.4146341463</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="E25" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="27">
+      <c r="E25" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="24">
         <f>COUNTIF(Control_Plantillas!$Y$4:$Y$59,$E25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2983,7 +2983,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2995,358 +2995,358 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>14</v>
+      <c r="A4" s="14" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>15</v>
+      <c r="A5" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="s">
-        <v>20</v>
+      <c r="A6" s="14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="s">
-        <v>23</v>
+      <c r="A7" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>40</v>
+      <c r="A10" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="s">
-        <v>44</v>
+      <c r="A11" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>47</v>
+      <c r="A12" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="s">
-        <v>51</v>
+      <c r="A13" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>53</v>
+      <c r="A14" s="14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="s">
-        <v>56</v>
+      <c r="A15" s="14" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>61</v>
+      <c r="A18" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="s">
-        <v>63</v>
+      <c r="A19" s="14" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>64</v>
+      <c r="A20" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="11" t="s">
-        <v>66</v>
+      <c r="A21" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>67</v>
+      <c r="A22" s="14" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="11" t="s">
-        <v>72</v>
+      <c r="A25" s="14" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>73</v>
+      <c r="A26" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="11" t="s">
-        <v>76</v>
+      <c r="A27" s="14" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>81</v>
+      <c r="A28" s="14" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>86</v>
+      <c r="A29" s="14" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>90</v>
+      <c r="A30" s="14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="14" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
-      <c r="F39" s="10"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="11" t="s">
-        <v>121</v>
+      <c r="A40" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="11" t="s">
-        <v>122</v>
+      <c r="A41" s="14" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="11" t="s">
-        <v>123</v>
+      <c r="A42" s="14" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="11" t="s">
-        <v>124</v>
+      <c r="A43" s="14" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="11" t="s">
-        <v>125</v>
+      <c r="A44" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
-      <c r="F46" s="10"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
+      <c r="A47" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
+      <c r="A48" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
+      <c r="A49" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
+      <c r="A50" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="34" t="s">
+      <c r="A51" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
+      <c r="C51" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
+      <c r="C52" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
+      <c r="A53" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
+      <c r="A54" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" s="34" t="s">
+      <c r="A55" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
+      <c r="A56" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" s="34" t="s">
+      <c r="A57" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -4370,245 +4370,245 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="8" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="8" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="12">
         <v>0.0</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5"/>
       <c r="F3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="5"/>
       <c r="L3" s="12">
         <v>0.4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5">
         <v>0.5</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="5">
         <v>1.0</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5">
         <v>0.15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5">
         <v>0.15</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5">
         <v>1.0</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="17" t="s">
+      <c r="I9" s="5"/>
+      <c r="J9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="5"/>
       <c r="L9" s="12">
         <f>SUM(L3:L7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5633,8 +5633,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>3</v>
+      <c r="A1" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5664,11 +5664,11 @@
       <c r="AA1" s="9"/>
       <c r="AB1" s="9"/>
       <c r="AC1" s="9"/>
-      <c r="AD1" s="10"/>
+      <c r="AD1" s="11"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>30</v>
+      <c r="A2" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -5676,161 +5676,161 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="16" t="s">
-        <v>50</v>
+      <c r="H2" s="11"/>
+      <c r="I2" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="16" t="s">
-        <v>57</v>
+      <c r="K2" s="11"/>
+      <c r="L2" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="16" t="s">
-        <v>60</v>
+      <c r="N2" s="11"/>
+      <c r="O2" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="16" t="s">
-        <v>62</v>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="S2" s="9"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="16" t="s">
-        <v>65</v>
+      <c r="T2" s="11"/>
+      <c r="U2" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="14" t="s">
-        <v>68</v>
+      <c r="W2" s="11"/>
+      <c r="X2" s="20" t="s">
+        <v>85</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9"/>
-      <c r="AD2" s="10"/>
+      <c r="AD2" s="11"/>
     </row>
     <row r="3" ht="33.75" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="22" t="s">
+      <c r="A3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="N3" s="22" t="s">
+      <c r="I3" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="J3" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="K3" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="M3" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="N3" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="S3" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="T3" s="22" t="s">
+      <c r="O3" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="P3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="V3" s="22" t="s">
+      <c r="Q3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="R3" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="W3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="X3" s="22" t="s">
+      <c r="S3" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="T3" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="U3" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA3" s="22" t="s">
+      <c r="V3" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="AB3" s="22" t="s">
+      <c r="W3" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="AC3" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" s="22" t="s">
+      <c r="X3" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" s="25" t="s">
         <v>119</v>
       </c>
+      <c r="Z3" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="B4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="33" t="s">
+      <c r="E4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>28</v>
+      <c r="G4" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J4" s="36">
         <v>46268.0</v>
@@ -5838,8 +5838,8 @@
       <c r="K4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L4" s="26" t="s">
-        <v>28</v>
+      <c r="L4" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M4" s="36">
         <v>46268.0</v>
@@ -5847,8 +5847,8 @@
       <c r="N4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>28</v>
+      <c r="O4" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="P4" s="36">
         <v>46268.0</v>
@@ -5856,17 +5856,17 @@
       <c r="Q4" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="R4" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S4" s="36"/>
       <c r="T4" s="36"/>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
-      <c r="X4" s="26">
+      <c r="X4" s="28">
         <f t="shared" ref="X4:X44" si="1">IF(OR($U4="Completado",$U4="No aplica"),6,IF(OR($R4="Completado",$R4="No aplica"),5,IF(OR($O4="Completado",$O4="No aplica"),4,IF(OR($L4="Completado",$L4="No aplica"),3,IF(OR($I4="Completado",$I4="No aplica"),2,1)))))</f>
         <v>4</v>
       </c>
@@ -5882,43 +5882,43 @@
         <f t="shared" ref="AA4:AA44" si="2">IF($X4=6,"",IF(IFERROR(INDEX($I4:$V4,3*$X4-1),0)=0,"",INDEX($I4:$V4,3*$X4-1)))</f>
         <v/>
       </c>
-      <c r="AB4" s="26" t="str">
+      <c r="AB4" s="28" t="str">
         <f t="shared" ref="AB4:AB44" si="3">IF($AA4="","",$AA4-TODAY())</f>
         <v/>
       </c>
-      <c r="AC4" s="26" t="str">
+      <c r="AC4" s="28" t="str">
         <f t="shared" ref="AC4:AC44" si="4">IF($X4=6,"Cerrado",IF(OR($I4="Bloqueado",$L4="Bloqueado",$O4="Bloqueado",$R4="Bloqueado",$U4="Bloqueado"),"Bloqueado",IF($AA4="","Sin fecha",IF($AB4&lt;0,"Vencido",IF($AB4&lt;=7,"En riesgo","En tiempo")))))</f>
         <v>Sin fecha</v>
       </c>
-      <c r="AD4" s="28"/>
+      <c r="AD4" s="30"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G5" s="33" t="s">
+      <c r="E5" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>24</v>
+      <c r="G5" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5" s="41">
         <v>46282.0</v>
@@ -5927,12 +5927,12 @@
         <v>46298.0</v>
       </c>
       <c r="L5" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M5" s="41"/>
       <c r="N5" s="36"/>
       <c r="O5" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P5" s="41"/>
       <c r="Q5" s="36"/>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
-      <c r="U5" s="26" t="s">
+      <c r="U5" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V5" s="36"/>
       <c r="W5" s="36"/>
-      <c r="X5" s="26">
+      <c r="X5" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5962,43 +5962,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="26" t="str">
+      <c r="AB5" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC5" s="26" t="str">
+      <c r="AC5" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD5" s="28"/>
+      <c r="AD5" s="30"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="33" t="s">
+      <c r="E6" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>28</v>
+      <c r="G6" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J6" s="36">
         <v>46268.0</v>
@@ -6006,8 +6006,8 @@
       <c r="K6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L6" s="26" t="s">
-        <v>28</v>
+      <c r="L6" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M6" s="36">
         <v>46268.0</v>
@@ -6015,8 +6015,8 @@
       <c r="N6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O6" s="26" t="s">
-        <v>28</v>
+      <c r="O6" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="P6" s="36">
         <v>46268.0</v>
@@ -6024,17 +6024,17 @@
       <c r="Q6" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="R6" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-      <c r="U6" s="26" t="s">
+      <c r="U6" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V6" s="36"/>
       <c r="W6" s="36"/>
-      <c r="X6" s="26">
+      <c r="X6" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6050,43 +6050,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="26" t="str">
+      <c r="AB6" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC6" s="26" t="str">
+      <c r="AC6" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD6" s="28"/>
+      <c r="AD6" s="30"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="30" t="s">
+      <c r="A7" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="33" t="s">
+      <c r="C7" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>28</v>
+      <c r="G7" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J7" s="36">
         <v>46268.0</v>
@@ -6094,8 +6094,8 @@
       <c r="K7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L7" s="26" t="s">
-        <v>28</v>
+      <c r="L7" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M7" s="36">
         <v>46268.0</v>
@@ -6103,8 +6103,8 @@
       <c r="N7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>28</v>
+      <c r="O7" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="P7" s="36">
         <v>46268.0</v>
@@ -6112,17 +6112,17 @@
       <c r="Q7" s="36">
         <v>46268.0</v>
       </c>
-      <c r="R7" s="26" t="s">
+      <c r="R7" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S7" s="36"/>
       <c r="T7" s="36"/>
-      <c r="U7" s="26" t="s">
+      <c r="U7" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V7" s="36"/>
       <c r="W7" s="36"/>
-      <c r="X7" s="26">
+      <c r="X7" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6138,50 +6138,50 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="26" t="str">
+      <c r="AB7" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC7" s="26" t="str">
+      <c r="AC7" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD7" s="28"/>
+      <c r="AD7" s="30"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="B8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="33" t="s">
+      <c r="E8" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>24</v>
+      <c r="G8" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J8" s="41">
         <v>46302.0</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M8" s="41">
         <v>46283.0</v>
@@ -6190,7 +6190,7 @@
         <v>46283.0</v>
       </c>
       <c r="O8" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P8" s="41">
         <v>46283.0</v>
@@ -6198,17 +6198,17 @@
       <c r="Q8" s="41">
         <v>46283.0</v>
       </c>
-      <c r="R8" s="26" t="s">
+      <c r="R8" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
-      <c r="U8" s="26" t="s">
+      <c r="U8" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
-      <c r="X8" s="26">
+      <c r="X8" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6224,43 +6224,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="26" t="str">
+      <c r="AB8" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC8" s="26" t="str">
+      <c r="AC8" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD8" s="28"/>
+      <c r="AD8" s="30"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="B9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="33" t="s">
+      <c r="E9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>28</v>
+      <c r="G9" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J9" s="36">
         <v>46274.0</v>
@@ -6269,7 +6269,7 @@
         <v>46274.0</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M9" s="36">
         <v>46277.0</v>
@@ -6278,7 +6278,7 @@
         <v>46277.0</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P9" s="36">
         <v>46277.0</v>
@@ -6286,17 +6286,17 @@
       <c r="Q9" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R9" s="26" t="s">
+      <c r="R9" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
-      <c r="U9" s="26" t="s">
+      <c r="U9" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V9" s="36"/>
       <c r="W9" s="36"/>
-      <c r="X9" s="26">
+      <c r="X9" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6312,43 +6312,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="26" t="str">
+      <c r="AB9" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC9" s="26" t="str">
+      <c r="AC9" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD9" s="28"/>
+      <c r="AD9" s="30"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="30" t="s">
-        <v>25</v>
+      <c r="E10" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>24</v>
+      <c r="H10" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J10" s="36">
         <v>46272.0</v>
@@ -6357,7 +6357,7 @@
         <v>46272.0</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M10" s="41">
         <v>46277.0</v>
@@ -6366,75 +6366,75 @@
         <v>46277.0</v>
       </c>
       <c r="O10" s="40" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="P10" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q10" s="36"/>
-      <c r="R10" s="26" t="s">
+      <c r="R10" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
-      <c r="U10" s="26" t="s">
+      <c r="U10" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="36"/>
-      <c r="X10" s="26">
+      <c r="X10" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="37" t="str">
         <f t="array" ref="Y10">INDEX(Cat_Etapas,$X10)</f>
-        <v>2. Revisión y validación</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z10" s="38">
         <f t="array" ref="Z10">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I10,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L10,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O10,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R10,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U10,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA10" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA10" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB10" s="26">
+        <v/>
+      </c>
+      <c r="AB10" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-27</v>
-      </c>
-      <c r="AC10" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC10" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD10" s="28"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD10" s="30"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="32" t="s">
+      <c r="E11" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>28</v>
+      <c r="H11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J11" s="36">
         <v>46268.0</v>
@@ -6442,8 +6442,8 @@
       <c r="K11" s="36">
         <v>46268.0</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>28</v>
+      <c r="L11" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M11" s="36">
         <v>46269.0</v>
@@ -6451,8 +6451,8 @@
       <c r="N11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="O11" s="26" t="s">
-        <v>28</v>
+      <c r="O11" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="P11" s="36">
         <v>46269.0</v>
@@ -6460,17 +6460,17 @@
       <c r="Q11" s="36">
         <v>46269.0</v>
       </c>
-      <c r="R11" s="26" t="s">
+      <c r="R11" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
-      <c r="U11" s="26" t="s">
+      <c r="U11" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V11" s="36"/>
       <c r="W11" s="36"/>
-      <c r="X11" s="26">
+      <c r="X11" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6486,43 +6486,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="26" t="str">
+      <c r="AB11" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC11" s="26" t="str">
+      <c r="AC11" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD11" s="28"/>
+      <c r="AD11" s="30"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="A12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="33" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>28</v>
+      <c r="H12" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J12" s="36">
         <v>46274.0</v>
@@ -6530,83 +6530,83 @@
       <c r="K12" s="36">
         <v>46274.0</v>
       </c>
-      <c r="L12" s="26" t="s">
-        <v>21</v>
+      <c r="L12" s="40" t="s">
+        <v>30</v>
       </c>
       <c r="M12" s="36">
         <v>46277.0</v>
       </c>
       <c r="N12" s="36"/>
-      <c r="O12" s="26" t="s">
-        <v>13</v>
+      <c r="O12" s="40" t="s">
+        <v>30</v>
       </c>
       <c r="P12" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q12" s="36"/>
-      <c r="R12" s="26" t="s">
+      <c r="R12" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="26" t="s">
+      <c r="U12" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V12" s="36"/>
       <c r="W12" s="36"/>
-      <c r="X12" s="26">
+      <c r="X12" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" s="37" t="str">
         <f t="array" ref="Y12">INDEX(Cat_Etapas,$X12)</f>
-        <v>2. Revisión y validación</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z12" s="38">
         <f t="array" ref="Z12">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I12,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L12,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O12,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R12,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U12,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA12" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA12" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB12" s="26">
+        <v/>
+      </c>
+      <c r="AB12" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-27</v>
-      </c>
-      <c r="AC12" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC12" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD12" s="28"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD12" s="30"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="33" t="s">
         <v>33</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>24</v>
+      <c r="H13" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J13" s="36">
         <v>46277.0</v>
@@ -6615,194 +6615,194 @@
         <v>46303.0</v>
       </c>
       <c r="L13" s="40" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M13" s="36">
         <v>46277.0</v>
       </c>
       <c r="N13" s="36"/>
-      <c r="O13" s="26" t="s">
-        <v>13</v>
+      <c r="O13" s="40" t="s">
+        <v>30</v>
       </c>
       <c r="P13" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q13" s="36"/>
-      <c r="R13" s="26" t="s">
+      <c r="R13" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
-      <c r="U13" s="26" t="s">
+      <c r="U13" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V13" s="36"/>
       <c r="W13" s="36"/>
-      <c r="X13" s="26">
+      <c r="X13" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="37" t="str">
         <f t="array" ref="Y13">INDEX(Cat_Etapas,$X13)</f>
-        <v>2. Revisión y validación</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z13" s="38">
         <f t="array" ref="Z13">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I13,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L13,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O13,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R13,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U13,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA13" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA13" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46277</v>
-      </c>
-      <c r="AB13" s="26">
+        <v/>
+      </c>
+      <c r="AB13" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-27</v>
-      </c>
-      <c r="AC13" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC13" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD13" s="28"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD13" s="30"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="33" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="26" t="s">
-        <v>24</v>
+      <c r="H14" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I14" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J14" s="36">
         <v>46277.0</v>
       </c>
       <c r="K14" s="36"/>
       <c r="L14" s="40" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M14" s="36">
         <v>46283.0</v>
       </c>
       <c r="N14" s="36"/>
-      <c r="O14" s="26" t="s">
-        <v>13</v>
+      <c r="O14" s="40" t="s">
+        <v>30</v>
       </c>
       <c r="P14" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q14" s="36"/>
-      <c r="R14" s="26" t="s">
+      <c r="R14" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S14" s="36"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="26" t="s">
+      <c r="U14" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V14" s="36"/>
       <c r="W14" s="36"/>
-      <c r="X14" s="26">
+      <c r="X14" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="37" t="str">
         <f t="array" ref="Y14">INDEX(Cat_Etapas,$X14)</f>
-        <v>2. Revisión y validación</v>
+        <v>4. Ambiente Sandbox</v>
       </c>
       <c r="Z14" s="38">
         <f t="array" ref="Z14">ROUND(Catalogos!$L$3*IFERROR(INDEX(Cat_Factor,MATCH($I14,Cat_Estatus,0)),0)+Catalogos!$L$4*IFERROR(INDEX(Cat_Factor,MATCH($L14,Cat_Estatus,0)),0)+Catalogos!$L$5*IFERROR(INDEX(Cat_Factor,MATCH($O14,Cat_Estatus,0)),0)+Catalogos!$L$6*IFERROR(INDEX(Cat_Factor,MATCH($R14,Cat_Estatus,0)),0)+Catalogos!$L$7*IFERROR(INDEX(Cat_Factor,MATCH($U14,Cat_Estatus,0)),0),4)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA14" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="AA14" s="39" t="str">
         <f t="shared" si="2"/>
-        <v>46283</v>
-      </c>
-      <c r="AB14" s="26">
+        <v/>
+      </c>
+      <c r="AB14" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC14" s="26" t="str">
+        <v/>
+      </c>
+      <c r="AC14" s="28" t="str">
         <f t="shared" si="4"/>
-        <v>Vencido</v>
-      </c>
-      <c r="AD14" s="28"/>
+        <v>Sin fecha</v>
+      </c>
+      <c r="AD14" s="30"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="B15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="33" t="s">
+      <c r="E15" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>24</v>
+      <c r="H15" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J15" s="36">
         <v>46283.0</v>
       </c>
       <c r="K15" s="36"/>
       <c r="L15" s="40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M15" s="36">
         <v>46283.0</v>
       </c>
       <c r="N15" s="36"/>
-      <c r="O15" s="26" t="s">
+      <c r="O15" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P15" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q15" s="36"/>
-      <c r="R15" s="26" t="s">
+      <c r="R15" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S15" s="36"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="26" t="s">
+      <c r="U15" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V15" s="36"/>
       <c r="W15" s="36"/>
-      <c r="X15" s="26">
+      <c r="X15" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6818,73 +6818,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC15" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC15" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD15" s="28"/>
+      <c r="AD15" s="30"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="E16" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="33" t="s">
+      <c r="E16" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H16" s="26" t="s">
-        <v>24</v>
+      <c r="H16" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16" s="36">
         <v>46283.0</v>
       </c>
       <c r="K16" s="36"/>
       <c r="L16" s="40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M16" s="36">
         <v>46283.0</v>
       </c>
       <c r="N16" s="36"/>
-      <c r="O16" s="26" t="s">
+      <c r="O16" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P16" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q16" s="36"/>
-      <c r="R16" s="26" t="s">
+      <c r="R16" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S16" s="36"/>
       <c r="T16" s="36"/>
-      <c r="U16" s="26" t="s">
+      <c r="U16" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V16" s="36"/>
       <c r="W16" s="36"/>
-      <c r="X16" s="26">
+      <c r="X16" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6900,73 +6900,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB16" s="26">
+      <c r="AB16" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC16" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC16" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD16" s="28"/>
+      <c r="AD16" s="30"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="33" t="s">
+      <c r="E17" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>24</v>
+      <c r="H17" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J17" s="36">
         <v>46283.0</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M17" s="36">
         <v>46283.0</v>
       </c>
       <c r="N17" s="36"/>
-      <c r="O17" s="26" t="s">
+      <c r="O17" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P17" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q17" s="36"/>
-      <c r="R17" s="26" t="s">
+      <c r="R17" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
-      <c r="U17" s="26" t="s">
+      <c r="U17" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="36"/>
-      <c r="X17" s="26">
+      <c r="X17" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6982,73 +6982,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB17" s="26">
+      <c r="AB17" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC17" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC17" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD17" s="28"/>
+      <c r="AD17" s="30"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="B18" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="33" t="s">
+      <c r="E18" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>21</v>
+      <c r="H18" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J18" s="36">
         <v>46283.0</v>
       </c>
       <c r="K18" s="36"/>
-      <c r="L18" s="26" t="s">
+      <c r="L18" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M18" s="36">
         <v>46283.0</v>
       </c>
       <c r="N18" s="36"/>
-      <c r="O18" s="26" t="s">
+      <c r="O18" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P18" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q18" s="36"/>
-      <c r="R18" s="26" t="s">
+      <c r="R18" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
-      <c r="U18" s="26" t="s">
+      <c r="U18" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V18" s="36"/>
       <c r="W18" s="36"/>
-      <c r="X18" s="26">
+      <c r="X18" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7064,73 +7064,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB18" s="26">
+      <c r="AB18" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC18" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC18" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD18" s="28"/>
+      <c r="AD18" s="30"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="B19" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="33" t="s">
+      <c r="E19" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="26" t="s">
-        <v>24</v>
+      <c r="H19" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J19" s="36">
         <v>46283.0</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M19" s="36">
         <v>46283.0</v>
       </c>
       <c r="N19" s="36"/>
-      <c r="O19" s="26" t="s">
+      <c r="O19" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P19" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q19" s="36"/>
-      <c r="R19" s="26" t="s">
+      <c r="R19" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S19" s="36"/>
       <c r="T19" s="36"/>
-      <c r="U19" s="26" t="s">
+      <c r="U19" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V19" s="36"/>
       <c r="W19" s="36"/>
-      <c r="X19" s="26">
+      <c r="X19" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7146,73 +7146,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB19" s="26">
+      <c r="AB19" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC19" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC19" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD19" s="28"/>
+      <c r="AD19" s="30"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="26" t="s">
+      <c r="B20" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="33" t="s">
+      <c r="E20" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>21</v>
+      <c r="H20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J20" s="36">
         <v>46283.0</v>
       </c>
       <c r="K20" s="36"/>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M20" s="36">
         <v>46283.0</v>
       </c>
       <c r="N20" s="36"/>
-      <c r="O20" s="26" t="s">
+      <c r="O20" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P20" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="26" t="s">
+      <c r="R20" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S20" s="36"/>
       <c r="T20" s="36"/>
-      <c r="U20" s="26" t="s">
+      <c r="U20" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="36"/>
-      <c r="X20" s="26">
+      <c r="X20" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7228,73 +7228,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB20" s="26">
+      <c r="AB20" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC20" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC20" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD20" s="28"/>
+      <c r="AD20" s="30"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="26" t="s">
+      <c r="B21" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="33" t="s">
+      <c r="E21" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>24</v>
+      <c r="H21" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J21" s="36">
         <v>46283.0</v>
       </c>
       <c r="K21" s="36"/>
       <c r="L21" s="40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M21" s="36">
         <v>46283.0</v>
       </c>
       <c r="N21" s="36"/>
-      <c r="O21" s="26" t="s">
+      <c r="O21" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P21" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q21" s="36"/>
-      <c r="R21" s="26" t="s">
+      <c r="R21" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S21" s="36"/>
       <c r="T21" s="36"/>
-      <c r="U21" s="26" t="s">
+      <c r="U21" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V21" s="36"/>
       <c r="W21" s="36"/>
-      <c r="X21" s="26">
+      <c r="X21" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -7310,73 +7310,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB21" s="26">
+      <c r="AB21" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC21" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC21" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD21" s="28"/>
+      <c r="AD21" s="30"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="B22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="33" t="s">
+      <c r="E22" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>21</v>
+      <c r="H22" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J22" s="36">
         <v>46283.0</v>
       </c>
       <c r="K22" s="36"/>
-      <c r="L22" s="26" t="s">
+      <c r="L22" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M22" s="36">
         <v>46283.0</v>
       </c>
       <c r="N22" s="36"/>
-      <c r="O22" s="26" t="s">
+      <c r="O22" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P22" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q22" s="36"/>
-      <c r="R22" s="26" t="s">
+      <c r="R22" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S22" s="36"/>
       <c r="T22" s="36"/>
-      <c r="U22" s="26" t="s">
+      <c r="U22" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V22" s="36"/>
       <c r="W22" s="36"/>
-      <c r="X22" s="26">
+      <c r="X22" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7392,73 +7392,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB22" s="26">
+      <c r="AB22" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC22" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC22" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD22" s="28"/>
+      <c r="AD22" s="30"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="26" t="s">
+      <c r="B23" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="33" t="s">
+      <c r="E23" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H23" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>21</v>
+      <c r="H23" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J23" s="36">
         <v>46283.0</v>
       </c>
       <c r="K23" s="36"/>
-      <c r="L23" s="26" t="s">
+      <c r="L23" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M23" s="36">
         <v>46283.0</v>
       </c>
       <c r="N23" s="36"/>
-      <c r="O23" s="26" t="s">
+      <c r="O23" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P23" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q23" s="36"/>
-      <c r="R23" s="26" t="s">
+      <c r="R23" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S23" s="36"/>
       <c r="T23" s="36"/>
-      <c r="U23" s="26" t="s">
+      <c r="U23" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V23" s="36"/>
       <c r="W23" s="36"/>
-      <c r="X23" s="26">
+      <c r="X23" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7474,73 +7474,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB23" s="26">
+      <c r="AB23" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC23" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC23" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD23" s="28"/>
+      <c r="AD23" s="30"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="26" t="s">
+      <c r="B24" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="33" t="s">
+      <c r="E24" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>21</v>
+      <c r="H24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J24" s="36">
         <v>46283.0</v>
       </c>
       <c r="K24" s="36"/>
-      <c r="L24" s="26" t="s">
+      <c r="L24" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M24" s="36">
         <v>46283.0</v>
       </c>
       <c r="N24" s="36"/>
-      <c r="O24" s="26" t="s">
+      <c r="O24" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P24" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q24" s="36"/>
-      <c r="R24" s="26" t="s">
+      <c r="R24" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S24" s="36"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="26" t="s">
+      <c r="U24" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V24" s="36"/>
       <c r="W24" s="36"/>
-      <c r="X24" s="26">
+      <c r="X24" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7556,73 +7556,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB24" s="26">
+      <c r="AB24" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC24" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC24" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD24" s="28"/>
+      <c r="AD24" s="30"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="26" t="s">
+      <c r="B25" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="33" t="s">
+      <c r="E25" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>21</v>
+      <c r="H25" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J25" s="36">
         <v>46283.0</v>
       </c>
       <c r="K25" s="36"/>
-      <c r="L25" s="26" t="s">
+      <c r="L25" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M25" s="36">
         <v>46283.0</v>
       </c>
       <c r="N25" s="36"/>
-      <c r="O25" s="26" t="s">
+      <c r="O25" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P25" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q25" s="36"/>
-      <c r="R25" s="26" t="s">
+      <c r="R25" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S25" s="36"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="26" t="s">
+      <c r="U25" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V25" s="36"/>
       <c r="W25" s="36"/>
-      <c r="X25" s="26">
+      <c r="X25" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7638,73 +7638,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB25" s="26">
+      <c r="AB25" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC25" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC25" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD25" s="28"/>
+      <c r="AD25" s="30"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="26" t="s">
+      <c r="B26" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="33" t="s">
+      <c r="E26" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="33" t="s">
+      <c r="G26" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>21</v>
+      <c r="H26" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J26" s="36">
         <v>46283.0</v>
       </c>
       <c r="K26" s="36"/>
-      <c r="L26" s="26" t="s">
+      <c r="L26" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M26" s="36">
         <v>46283.0</v>
       </c>
       <c r="N26" s="36"/>
-      <c r="O26" s="26" t="s">
+      <c r="O26" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P26" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q26" s="36"/>
-      <c r="R26" s="26" t="s">
+      <c r="R26" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S26" s="36"/>
       <c r="T26" s="36"/>
-      <c r="U26" s="26" t="s">
+      <c r="U26" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V26" s="36"/>
       <c r="W26" s="36"/>
-      <c r="X26" s="26">
+      <c r="X26" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7720,73 +7720,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB26" s="26">
+      <c r="AB26" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC26" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC26" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD26" s="28"/>
+      <c r="AD26" s="30"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="B27" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="33" t="s">
+      <c r="E27" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>21</v>
+      <c r="H27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J27" s="36">
         <v>46283.0</v>
       </c>
       <c r="K27" s="36"/>
-      <c r="L27" s="26" t="s">
+      <c r="L27" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="36">
         <v>46283.0</v>
       </c>
       <c r="N27" s="36"/>
-      <c r="O27" s="26" t="s">
+      <c r="O27" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P27" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="26" t="s">
+      <c r="R27" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S27" s="36"/>
       <c r="T27" s="36"/>
-      <c r="U27" s="26" t="s">
+      <c r="U27" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V27" s="36"/>
       <c r="W27" s="36"/>
-      <c r="X27" s="26">
+      <c r="X27" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7802,73 +7802,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB27" s="26">
+      <c r="AB27" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC27" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC27" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD27" s="28"/>
+      <c r="AD27" s="30"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="26" t="s">
+      <c r="B28" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="E28" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="33" t="s">
+      <c r="E28" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="33" t="s">
+      <c r="G28" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>21</v>
+      <c r="H28" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J28" s="36">
         <v>46283.0</v>
       </c>
       <c r="K28" s="36"/>
-      <c r="L28" s="26" t="s">
+      <c r="L28" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M28" s="36">
         <v>46283.0</v>
       </c>
       <c r="N28" s="36"/>
-      <c r="O28" s="26" t="s">
+      <c r="O28" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P28" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q28" s="36"/>
-      <c r="R28" s="26" t="s">
+      <c r="R28" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="36"/>
       <c r="T28" s="36"/>
-      <c r="U28" s="26" t="s">
+      <c r="U28" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V28" s="36"/>
       <c r="W28" s="36"/>
-      <c r="X28" s="26">
+      <c r="X28" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7884,73 +7884,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB28" s="26">
+      <c r="AB28" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC28" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC28" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD28" s="28"/>
+      <c r="AD28" s="30"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="26" t="s">
+      <c r="B29" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="33" t="s">
+      <c r="E29" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>21</v>
+      <c r="H29" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J29" s="36">
         <v>46283.0</v>
       </c>
       <c r="K29" s="36"/>
-      <c r="L29" s="26" t="s">
+      <c r="L29" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M29" s="36">
         <v>46283.0</v>
       </c>
       <c r="N29" s="36"/>
-      <c r="O29" s="26" t="s">
+      <c r="O29" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P29" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q29" s="36"/>
-      <c r="R29" s="26" t="s">
+      <c r="R29" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S29" s="36"/>
       <c r="T29" s="36"/>
-      <c r="U29" s="26" t="s">
+      <c r="U29" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V29" s="36"/>
       <c r="W29" s="36"/>
-      <c r="X29" s="26">
+      <c r="X29" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -7966,73 +7966,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB29" s="26">
+      <c r="AB29" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC29" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC29" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD29" s="28"/>
+      <c r="AD29" s="30"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="26" t="s">
+      <c r="B30" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="E30" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="33" t="s">
+      <c r="E30" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="33" t="s">
+      <c r="G30" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>21</v>
+      <c r="H30" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J30" s="36">
         <v>46283.0</v>
       </c>
       <c r="K30" s="36"/>
-      <c r="L30" s="26" t="s">
+      <c r="L30" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M30" s="36">
         <v>46283.0</v>
       </c>
       <c r="N30" s="36"/>
-      <c r="O30" s="26" t="s">
+      <c r="O30" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P30" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q30" s="36"/>
-      <c r="R30" s="26" t="s">
+      <c r="R30" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S30" s="36"/>
       <c r="T30" s="36"/>
-      <c r="U30" s="26" t="s">
+      <c r="U30" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V30" s="36"/>
       <c r="W30" s="36"/>
-      <c r="X30" s="26">
+      <c r="X30" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8048,73 +8048,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB30" s="26">
+      <c r="AB30" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC30" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC30" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD30" s="28"/>
+      <c r="AD30" s="30"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="26" t="s">
+      <c r="B31" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="33" t="s">
+      <c r="E31" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>21</v>
+      <c r="H31" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J31" s="36">
         <v>46283.0</v>
       </c>
       <c r="K31" s="36"/>
-      <c r="L31" s="26" t="s">
+      <c r="L31" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M31" s="36">
         <v>46283.0</v>
       </c>
       <c r="N31" s="36"/>
-      <c r="O31" s="26" t="s">
+      <c r="O31" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P31" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q31" s="36"/>
-      <c r="R31" s="26" t="s">
+      <c r="R31" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S31" s="36"/>
       <c r="T31" s="36"/>
-      <c r="U31" s="26" t="s">
+      <c r="U31" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V31" s="36"/>
       <c r="W31" s="36"/>
-      <c r="X31" s="26">
+      <c r="X31" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8130,73 +8130,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB31" s="26">
+      <c r="AB31" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC31" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC31" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD31" s="28"/>
+      <c r="AD31" s="30"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="26" t="s">
+      <c r="B32" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="33" t="s">
+      <c r="E32" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>21</v>
+      <c r="H32" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J32" s="36">
         <v>46283.0</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="26" t="s">
+      <c r="L32" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M32" s="36">
         <v>46283.0</v>
       </c>
       <c r="N32" s="36"/>
-      <c r="O32" s="26" t="s">
+      <c r="O32" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P32" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q32" s="36"/>
-      <c r="R32" s="26" t="s">
+      <c r="R32" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S32" s="36"/>
       <c r="T32" s="36"/>
-      <c r="U32" s="26" t="s">
+      <c r="U32" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V32" s="36"/>
       <c r="W32" s="36"/>
-      <c r="X32" s="26">
+      <c r="X32" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8212,73 +8212,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB32" s="26">
+      <c r="AB32" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC32" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC32" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD32" s="28"/>
+      <c r="AD32" s="30"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="26" t="s">
+      <c r="B33" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="33" t="s">
+      <c r="E33" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>21</v>
+      <c r="H33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J33" s="36">
         <v>46283.0</v>
       </c>
       <c r="K33" s="36"/>
-      <c r="L33" s="26" t="s">
+      <c r="L33" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M33" s="36">
         <v>46283.0</v>
       </c>
       <c r="N33" s="36"/>
-      <c r="O33" s="26" t="s">
+      <c r="O33" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P33" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q33" s="36"/>
-      <c r="R33" s="26" t="s">
+      <c r="R33" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
-      <c r="U33" s="26" t="s">
+      <c r="U33" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V33" s="36"/>
       <c r="W33" s="36"/>
-      <c r="X33" s="26">
+      <c r="X33" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8294,73 +8294,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB33" s="26">
+      <c r="AB33" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC33" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC33" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD33" s="28"/>
+      <c r="AD33" s="30"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="26" t="s">
+      <c r="B34" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="33" t="s">
+      <c r="E34" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="33" t="s">
+      <c r="G34" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>21</v>
+      <c r="H34" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J34" s="36">
         <v>46283.0</v>
       </c>
       <c r="K34" s="36"/>
-      <c r="L34" s="26" t="s">
+      <c r="L34" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M34" s="36">
         <v>46283.0</v>
       </c>
       <c r="N34" s="36"/>
-      <c r="O34" s="26" t="s">
+      <c r="O34" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P34" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q34" s="36"/>
-      <c r="R34" s="26" t="s">
+      <c r="R34" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S34" s="36"/>
       <c r="T34" s="36"/>
-      <c r="U34" s="26" t="s">
+      <c r="U34" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V34" s="36"/>
       <c r="W34" s="36"/>
-      <c r="X34" s="26">
+      <c r="X34" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8376,73 +8376,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB34" s="26">
+      <c r="AB34" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC34" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC34" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD34" s="28"/>
+      <c r="AD34" s="30"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="26" t="s">
+      <c r="B35" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="33" t="s">
+      <c r="E35" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>21</v>
+      <c r="H35" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J35" s="36">
         <v>46283.0</v>
       </c>
       <c r="K35" s="36"/>
-      <c r="L35" s="26" t="s">
+      <c r="L35" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M35" s="36">
         <v>46283.0</v>
       </c>
       <c r="N35" s="36"/>
-      <c r="O35" s="26" t="s">
+      <c r="O35" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P35" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q35" s="36"/>
-      <c r="R35" s="26" t="s">
+      <c r="R35" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
-      <c r="U35" s="26" t="s">
+      <c r="U35" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V35" s="36"/>
       <c r="W35" s="36"/>
-      <c r="X35" s="26">
+      <c r="X35" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8458,73 +8458,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB35" s="26">
+      <c r="AB35" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC35" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC35" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD35" s="28"/>
+      <c r="AD35" s="30"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="26" t="s">
+      <c r="B36" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="33" t="s">
+      <c r="E36" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>21</v>
+      <c r="H36" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J36" s="36">
         <v>46283.0</v>
       </c>
       <c r="K36" s="36"/>
-      <c r="L36" s="26" t="s">
+      <c r="L36" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M36" s="36">
         <v>46283.0</v>
       </c>
       <c r="N36" s="36"/>
-      <c r="O36" s="26" t="s">
+      <c r="O36" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P36" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q36" s="36"/>
-      <c r="R36" s="26" t="s">
+      <c r="R36" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S36" s="36"/>
       <c r="T36" s="36"/>
-      <c r="U36" s="26" t="s">
+      <c r="U36" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V36" s="36"/>
       <c r="W36" s="36"/>
-      <c r="X36" s="26">
+      <c r="X36" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8540,73 +8540,73 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB36" s="26">
+      <c r="AB36" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC36" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC36" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD36" s="28"/>
+      <c r="AD36" s="30"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="26" t="s">
+      <c r="B37" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="33" t="s">
+      <c r="E37" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="33" t="s">
+      <c r="G37" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>21</v>
+      <c r="H37" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="J37" s="36">
         <v>46283.0</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="26" t="s">
+      <c r="L37" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M37" s="36">
         <v>46283.0</v>
       </c>
       <c r="N37" s="36"/>
-      <c r="O37" s="26" t="s">
+      <c r="O37" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P37" s="36">
         <v>46276.0</v>
       </c>
       <c r="Q37" s="36"/>
-      <c r="R37" s="26" t="s">
+      <c r="R37" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
-      <c r="U37" s="26" t="s">
+      <c r="U37" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V37" s="36"/>
       <c r="W37" s="36"/>
-      <c r="X37" s="26">
+      <c r="X37" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -8622,43 +8622,43 @@
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="AB37" s="26">
+      <c r="AB37" s="28">
         <f t="shared" si="3"/>
-        <v>-21</v>
-      </c>
-      <c r="AC37" s="26" t="str">
+        <v>-24</v>
+      </c>
+      <c r="AC37" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD37" s="28"/>
+      <c r="AD37" s="30"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="32" t="s">
+      <c r="E38" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G38" s="33" t="s">
+      <c r="G38" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>28</v>
+      <c r="H38" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J38" s="41">
         <v>46277.0</v>
@@ -8667,30 +8667,30 @@
         <v>46276.0</v>
       </c>
       <c r="L38" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M38" s="36">
         <v>46283.0</v>
       </c>
       <c r="N38" s="36"/>
       <c r="O38" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P38" s="36">
         <v>46277.0</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="26" t="s">
+      <c r="R38" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S38" s="36"/>
       <c r="T38" s="36"/>
-      <c r="U38" s="26" t="s">
+      <c r="U38" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V38" s="36"/>
       <c r="W38" s="36"/>
-      <c r="X38" s="26">
+      <c r="X38" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8706,73 +8706,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB38" s="26" t="str">
+      <c r="AB38" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC38" s="26" t="str">
+      <c r="AC38" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD38" s="28"/>
+      <c r="AD38" s="30"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="26" t="s">
+      <c r="B39" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E39" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="32" t="s">
+      <c r="E39" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="26" t="s">
-        <v>24</v>
+      <c r="H39" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J39" s="36">
         <v>46283.0</v>
       </c>
       <c r="K39" s="36"/>
       <c r="L39" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M39" s="36">
         <v>46283.0</v>
       </c>
       <c r="N39" s="36"/>
       <c r="O39" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P39" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q39" s="36"/>
-      <c r="R39" s="26" t="s">
+      <c r="R39" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
-      <c r="U39" s="26" t="s">
+      <c r="U39" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V39" s="36"/>
       <c r="W39" s="36"/>
-      <c r="X39" s="26">
+      <c r="X39" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8788,73 +8788,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB39" s="26" t="str">
+      <c r="AB39" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC39" s="26" t="str">
+      <c r="AC39" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD39" s="28"/>
+      <c r="AD39" s="30"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="26" t="s">
+      <c r="B40" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="32" t="s">
+      <c r="E40" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="26" t="s">
-        <v>24</v>
+      <c r="H40" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I40" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J40" s="36">
         <v>46283.0</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M40" s="36">
         <v>46283.0</v>
       </c>
       <c r="N40" s="36"/>
       <c r="O40" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P40" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q40" s="36"/>
-      <c r="R40" s="26" t="s">
+      <c r="R40" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
-      <c r="U40" s="26" t="s">
+      <c r="U40" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V40" s="36"/>
       <c r="W40" s="36"/>
-      <c r="X40" s="26">
+      <c r="X40" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8870,73 +8870,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB40" s="26" t="str">
+      <c r="AB40" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC40" s="26" t="str">
+      <c r="AC40" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD40" s="28"/>
+      <c r="AD40" s="30"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="26" t="s">
+      <c r="B41" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="32" t="s">
+      <c r="E41" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="26" t="s">
-        <v>24</v>
+      <c r="H41" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J41" s="36">
         <v>46283.0</v>
       </c>
       <c r="K41" s="36"/>
       <c r="L41" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M41" s="36">
         <v>46283.0</v>
       </c>
       <c r="N41" s="36"/>
       <c r="O41" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P41" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q41" s="36"/>
-      <c r="R41" s="26" t="s">
+      <c r="R41" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
-      <c r="U41" s="26" t="s">
+      <c r="U41" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V41" s="36"/>
       <c r="W41" s="36"/>
-      <c r="X41" s="26">
+      <c r="X41" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8952,73 +8952,73 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB41" s="26" t="str">
+      <c r="AB41" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC41" s="26" t="str">
+      <c r="AC41" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD41" s="28"/>
+      <c r="AD41" s="30"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="26" t="s">
+      <c r="B42" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="32" t="s">
+      <c r="E42" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="26" t="s">
-        <v>24</v>
+      <c r="H42" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J42" s="36">
         <v>46283.0</v>
       </c>
       <c r="K42" s="36"/>
       <c r="L42" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M42" s="36">
         <v>46283.0</v>
       </c>
       <c r="N42" s="36"/>
       <c r="O42" s="40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P42" s="36">
         <v>46283.0</v>
       </c>
       <c r="Q42" s="36"/>
-      <c r="R42" s="26" t="s">
+      <c r="R42" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S42" s="36"/>
       <c r="T42" s="36"/>
-      <c r="U42" s="26" t="s">
+      <c r="U42" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V42" s="36"/>
       <c r="W42" s="36"/>
-      <c r="X42" s="26">
+      <c r="X42" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9034,43 +9034,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB42" s="26" t="str">
+      <c r="AB42" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC42" s="26" t="str">
+      <c r="AC42" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD42" s="28"/>
+      <c r="AD42" s="30"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="26" t="s">
+      <c r="B43" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="E43" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="32" t="s">
+      <c r="E43" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="33" t="s">
+      <c r="G43" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>28</v>
+      <c r="H43" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J43" s="41">
         <v>46277.0</v>
@@ -9078,8 +9078,8 @@
       <c r="K43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="L43" s="26" t="s">
-        <v>28</v>
+      <c r="L43" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="M43" s="41">
         <v>46277.0</v>
@@ -9087,8 +9087,8 @@
       <c r="N43" s="36">
         <v>46276.0</v>
       </c>
-      <c r="O43" s="26" t="s">
-        <v>28</v>
+      <c r="O43" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="P43" s="36">
         <v>46276.0</v>
@@ -9096,17 +9096,17 @@
       <c r="Q43" s="36">
         <v>46277.0</v>
       </c>
-      <c r="R43" s="26" t="s">
+      <c r="R43" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
-      <c r="U43" s="26" t="s">
+      <c r="U43" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V43" s="36"/>
       <c r="W43" s="36"/>
-      <c r="X43" s="26">
+      <c r="X43" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -9122,43 +9122,43 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB43" s="26" t="str">
+      <c r="AB43" s="28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AC43" s="26" t="str">
+      <c r="AC43" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Sin fecha</v>
       </c>
-      <c r="AD43" s="28"/>
+      <c r="AD43" s="30"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G44" s="33" t="s">
+      <c r="E44" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H44" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>28</v>
+      <c r="G44" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>30</v>
       </c>
       <c r="J44" s="41">
         <v>46277.0</v>
@@ -9166,29 +9166,29 @@
       <c r="K44" s="36">
         <v>46275.0</v>
       </c>
-      <c r="L44" s="26" t="s">
-        <v>21</v>
+      <c r="L44" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="M44" s="36">
         <v>46276.0</v>
       </c>
       <c r="N44" s="36"/>
-      <c r="O44" s="26" t="s">
+      <c r="O44" s="28" t="s">
         <v>13</v>
       </c>
       <c r="P44" s="36"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="26" t="s">
+      <c r="R44" s="28" t="s">
         <v>13</v>
       </c>
       <c r="S44" s="36"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="26" t="s">
+      <c r="U44" s="28" t="s">
         <v>13</v>
       </c>
       <c r="V44" s="36"/>
       <c r="W44" s="36"/>
-      <c r="X44" s="26">
+      <c r="X44" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -9204,15 +9204,15 @@
         <f t="shared" si="2"/>
         <v>46276</v>
       </c>
-      <c r="AB44" s="26">
+      <c r="AB44" s="28">
         <f t="shared" si="3"/>
-        <v>-28</v>
-      </c>
-      <c r="AC44" s="26" t="str">
+        <v>-31</v>
+      </c>
+      <c r="AC44" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Vencido</v>
       </c>
-      <c r="AD44" s="28"/>
+      <c r="AD44" s="30"/>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
